--- a/Demonstrações 2026 final.xlsx
+++ b/Demonstrações 2026 final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/victorgaioso/Documents/Gaioso/ANDALUZ/ESTRATÉGICO/Relatórios Estratégicos/2026/Anual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E60F41-DFDE-7F4E-AD2B-40454FBEF4FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{706A8914-1CB8-9F42-8815-AF9487D5ECD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="600" windowWidth="36740" windowHeight="19420" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="600" windowWidth="38400" windowHeight="21000" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CNS" sheetId="17" r:id="rId1"/>
@@ -4779,20 +4779,24 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="32" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4803,13 +4807,19 @@
     <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -4830,15 +4840,6 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4851,11 +4852,11 @@
     <xf numFmtId="0" fontId="0" fillId="28" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="0" fontId="38" fillId="22" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="45"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="46" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4866,7 +4867,6 @@
     <xf numFmtId="0" fontId="64" fillId="46" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Moeda 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
@@ -26276,7 +26276,7 @@
       <sheetName val="Salários YTD"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="7">
           <cell r="E7">
@@ -28093,7 +28093,7 @@
       <c r="L12" s="200"/>
       <c r="M12" s="200"/>
       <c r="N12" s="200">
-        <f t="shared" si="2"/>
+        <f>SUM(B12:M12)</f>
         <v>64487.4</v>
       </c>
     </row>
@@ -36335,13 +36335,13 @@
       <c r="AF7" s="126"/>
     </row>
     <row r="10" spans="3:44">
-      <c r="AC10" s="396" t="s">
+      <c r="AC10" s="397" t="s">
         <v>299</v>
       </c>
       <c r="AD10" s="129"/>
     </row>
     <row r="11" spans="3:44">
-      <c r="AC11" s="396"/>
+      <c r="AC11" s="397"/>
       <c r="AD11" s="129"/>
     </row>
     <row r="12" spans="3:44" ht="15.75" customHeight="1"/>
@@ -44839,12 +44839,12 @@
   </cols>
   <sheetData>
     <row r="4" spans="5:8">
-      <c r="E4" s="397" t="s">
+      <c r="E4" s="398" t="s">
         <v>588</v>
       </c>
-      <c r="F4" s="397"/>
-      <c r="G4" s="397"/>
-      <c r="H4" s="397"/>
+      <c r="F4" s="398"/>
+      <c r="G4" s="398"/>
+      <c r="H4" s="398"/>
     </row>
     <row r="6" spans="5:8">
       <c r="E6" s="266" t="s">
@@ -45088,10 +45088,10 @@
     </row>
     <row r="32" spans="5:8" ht="16" thickTop="1"/>
     <row r="34" spans="5:8">
-      <c r="E34" s="398" t="s">
+      <c r="E34" s="399" t="s">
         <v>591</v>
       </c>
-      <c r="F34" s="398"/>
+      <c r="F34" s="399"/>
       <c r="G34" s="275">
         <f>H7+H8+H11+H12+H13+H14+H15+H16+H19+H23+H29+H26</f>
         <v>-1265.45</v>
@@ -45102,10 +45102,10 @@
       </c>
     </row>
     <row r="35" spans="5:8" ht="16" thickBot="1">
-      <c r="E35" s="399" t="s">
+      <c r="E35" s="400" t="s">
         <v>592</v>
       </c>
-      <c r="F35" s="399"/>
+      <c r="F35" s="400"/>
       <c r="G35" s="276">
         <f>G31+G34</f>
         <v>6579.79</v>
@@ -48237,17 +48237,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1">
-      <c r="A1" s="400" t="s">
+      <c r="A1" s="402" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="400"/>
-      <c r="C1" s="400"/>
-      <c r="D1" s="400"/>
-      <c r="E1" s="400"/>
-      <c r="F1" s="400"/>
-      <c r="G1" s="400"/>
-      <c r="H1" s="400"/>
-      <c r="I1" s="400"/>
+      <c r="B1" s="402"/>
+      <c r="C1" s="402"/>
+      <c r="D1" s="402"/>
+      <c r="E1" s="402"/>
+      <c r="F1" s="402"/>
+      <c r="G1" s="402"/>
+      <c r="H1" s="402"/>
+      <c r="I1" s="402"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1">
       <c r="A2" s="114"/>
@@ -49538,6 +49538,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="A18:A22"/>
     <mergeCell ref="A48:A52"/>
     <mergeCell ref="A53:A57"/>
     <mergeCell ref="A23:A27"/>
@@ -49545,11 +49550,6 @@
     <mergeCell ref="A33:A37"/>
     <mergeCell ref="A38:A42"/>
     <mergeCell ref="A43:A47"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="A8:A12"/>
-    <mergeCell ref="A13:A17"/>
-    <mergeCell ref="A18:A22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -49567,18 +49567,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.75" customHeight="1">
-      <c r="A1" s="402" t="s">
+      <c r="A1" s="403" t="s">
         <v>698</v>
       </c>
-      <c r="B1" s="402"/>
-      <c r="C1" s="402"/>
-      <c r="D1" s="402"/>
-      <c r="E1" s="402"/>
-      <c r="F1" s="402"/>
-      <c r="G1" s="402"/>
+      <c r="B1" s="403"/>
+      <c r="C1" s="403"/>
+      <c r="D1" s="403"/>
+      <c r="E1" s="403"/>
+      <c r="F1" s="403"/>
+      <c r="G1" s="403"/>
       <c r="I1" s="369">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46195</v>
       </c>
       <c r="J1" s="370">
         <f ca="1">YEAR(I1)</f>
@@ -49586,11 +49586,11 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="21.75" customHeight="1">
-      <c r="A3" s="403" t="s">
+      <c r="A3" s="404" t="s">
         <v>699</v>
       </c>
-      <c r="B3" s="403"/>
-      <c r="C3" s="403"/>
+      <c r="B3" s="404"/>
+      <c r="C3" s="404"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
       <c r="A4" s="353" t="s">
@@ -49635,15 +49635,15 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="21.75" customHeight="1">
-      <c r="A10" s="403" t="s">
+      <c r="A10" s="404" t="s">
         <v>703</v>
       </c>
-      <c r="B10" s="403"/>
-      <c r="C10" s="403"/>
-      <c r="D10" s="403"/>
-      <c r="E10" s="403"/>
-      <c r="F10" s="403"/>
-      <c r="G10" s="403"/>
+      <c r="B10" s="404"/>
+      <c r="C10" s="404"/>
+      <c r="D10" s="404"/>
+      <c r="E10" s="404"/>
+      <c r="F10" s="404"/>
+      <c r="G10" s="404"/>
     </row>
     <row r="11" spans="1:10" ht="19.5" customHeight="1">
       <c r="A11" s="356" t="s">
@@ -49789,15 +49789,15 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A18" s="404" t="s">
+      <c r="A18" s="405" t="s">
         <v>717</v>
       </c>
-      <c r="B18" s="404"/>
-      <c r="C18" s="404"/>
-      <c r="D18" s="404"/>
-      <c r="E18" s="404"/>
-      <c r="F18" s="404"/>
-      <c r="G18" s="404"/>
+      <c r="B18" s="405"/>
+      <c r="C18" s="405"/>
+      <c r="D18" s="405"/>
+      <c r="E18" s="405"/>
+      <c r="F18" s="405"/>
+      <c r="G18" s="405"/>
     </row>
     <row r="19" spans="1:7" ht="28" customHeight="1">
       <c r="A19" s="360" t="s">
@@ -51487,10 +51487,9 @@
   <cols>
     <col min="1" max="3" width="10.83203125" style="206"/>
     <col min="4" max="4" width="38" style="206" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="16.5" style="206" customWidth="1"/>
-    <col min="9" max="9" width="16.5" style="206" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="16" width="12.83203125" style="206" customWidth="1" outlineLevel="1"/>
-    <col min="17" max="17" width="14.33203125" style="209" customWidth="1"/>
+    <col min="5" max="9" width="16.5" style="206" customWidth="1"/>
+    <col min="10" max="16" width="12.83203125" style="206" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="17" max="17" width="14.33203125" style="209" customWidth="1" collapsed="1"/>
     <col min="18" max="18" width="10.83203125" style="209" customWidth="1"/>
     <col min="19" max="19" width="10.83203125" style="206" customWidth="1"/>
     <col min="20" max="20" width="38" style="206" hidden="1" customWidth="1" outlineLevel="1"/>
@@ -55391,8 +55390,8 @@
       <c r="H3" s="48"/>
       <c r="I3" s="49"/>
       <c r="J3" s="50"/>
-      <c r="K3" s="405">
-        <v>46185</v>
+      <c r="K3" s="376">
+        <v>46192</v>
       </c>
       <c r="N3" s="48"/>
       <c r="O3" s="48"/>
@@ -55482,7 +55481,7 @@
       </c>
       <c r="K6" s="65">
         <f t="shared" si="0"/>
-        <v>341946.62000000005</v>
+        <v>400289.01</v>
       </c>
       <c r="L6" s="7">
         <f t="shared" si="0"/>
@@ -55550,7 +55549,7 @@
       </c>
       <c r="K7" s="72">
         <f t="shared" si="1"/>
-        <v>228513.29</v>
+        <v>240608.09999999998</v>
       </c>
       <c r="L7" s="70">
         <f t="shared" si="1"/>
@@ -55610,7 +55609,7 @@
         <v>269766.64</v>
       </c>
       <c r="K8" s="77">
-        <v>175542.75</v>
+        <v>152267.24</v>
       </c>
       <c r="L8" s="75"/>
       <c r="M8" s="76"/>
@@ -55649,7 +55648,7 @@
         <v>37834.53</v>
       </c>
       <c r="K9" s="77">
-        <v>52970.54</v>
+        <v>88340.86</v>
       </c>
       <c r="L9" s="75"/>
       <c r="M9" s="76"/>
@@ -55697,7 +55696,7 @@
       </c>
       <c r="K10" s="83">
         <f t="shared" si="2"/>
-        <v>82702.5</v>
+        <v>130846.38999999998</v>
       </c>
       <c r="L10" s="81">
         <f t="shared" si="2"/>
@@ -55755,7 +55754,7 @@
         <v>70999.62</v>
       </c>
       <c r="K11" s="77">
-        <v>71286.77</v>
+        <v>71466.259999999995</v>
       </c>
       <c r="L11" s="75"/>
       <c r="M11" s="76"/>
@@ -55788,7 +55787,7 @@
         <v>4090.78</v>
       </c>
       <c r="K12" s="77">
-        <v>11415.73</v>
+        <v>59380.13</v>
       </c>
       <c r="L12" s="75"/>
       <c r="M12" s="76"/>
@@ -55835,7 +55834,7 @@
       </c>
       <c r="K13" s="83">
         <f t="shared" si="3"/>
-        <v>30730.83</v>
+        <v>28834.519999999997</v>
       </c>
       <c r="L13" s="81">
         <f t="shared" si="3"/>
@@ -55893,7 +55892,7 @@
         <v>29948.48</v>
       </c>
       <c r="K14" s="77">
-        <v>10640.78</v>
+        <v>10699.13</v>
       </c>
       <c r="L14" s="75"/>
       <c r="M14" s="76"/>
@@ -55933,7 +55932,7 @@
         <v>10595.43</v>
       </c>
       <c r="K15" s="77">
-        <v>20090.05</v>
+        <v>18135.39</v>
       </c>
       <c r="L15" s="75"/>
       <c r="M15" s="76"/>
@@ -56066,7 +56065,7 @@
       </c>
       <c r="K19" s="17">
         <f t="shared" si="5"/>
-        <v>-81288.860000000044</v>
+        <v>-22946.470000000088</v>
       </c>
       <c r="L19" s="17">
         <f t="shared" si="5"/>
@@ -56117,10 +56116,10 @@
         <v>131</v>
       </c>
       <c r="E42" s="91"/>
-      <c r="F42" s="376" t="s">
+      <c r="F42" s="377" t="s">
         <v>132</v>
       </c>
-      <c r="G42" s="376"/>
+      <c r="G42" s="377"/>
       <c r="H42" s="92">
         <f>SUM(H43:H57)</f>
         <v>30000</v>
@@ -56389,11 +56388,11 @@
       <c r="Q60" s="90"/>
     </row>
     <row r="61" spans="4:23" ht="15" customHeight="1" outlineLevel="1">
-      <c r="D61" s="376" t="s">
+      <c r="D61" s="377" t="s">
         <v>149</v>
       </c>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="E61" s="377"/>
+      <c r="F61" s="377"/>
       <c r="G61" s="94">
         <f>I6</f>
         <v>358806.95999999996</v>
@@ -56809,41 +56808,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:22" ht="27.75" customHeight="1">
-      <c r="B1" s="381" t="s">
+      <c r="B1" s="383" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="381"/>
-      <c r="D1" s="381"/>
-      <c r="E1" s="381"/>
-      <c r="F1" s="381"/>
-      <c r="G1" s="381"/>
-      <c r="H1" s="381"/>
-      <c r="I1" s="381"/>
-      <c r="J1" s="381"/>
-      <c r="K1" s="381"/>
-      <c r="L1" s="381"/>
-      <c r="M1" s="381"/>
-      <c r="N1" s="381"/>
-      <c r="O1" s="381"/>
+      <c r="C1" s="383"/>
+      <c r="D1" s="383"/>
+      <c r="E1" s="383"/>
+      <c r="F1" s="383"/>
+      <c r="G1" s="383"/>
+      <c r="H1" s="383"/>
+      <c r="I1" s="383"/>
+      <c r="J1" s="383"/>
+      <c r="K1" s="383"/>
+      <c r="L1" s="383"/>
+      <c r="M1" s="383"/>
+      <c r="N1" s="383"/>
+      <c r="O1" s="383"/>
       <c r="Q1" s="176"/>
     </row>
     <row r="2" spans="2:22">
-      <c r="B2" s="382" t="s">
+      <c r="B2" s="384" t="s">
         <v>561</v>
       </c>
-      <c r="C2" s="382"/>
-      <c r="D2" s="382"/>
-      <c r="E2" s="382"/>
-      <c r="F2" s="382"/>
-      <c r="G2" s="382"/>
-      <c r="H2" s="382"/>
-      <c r="I2" s="382"/>
-      <c r="J2" s="382"/>
-      <c r="K2" s="382"/>
-      <c r="L2" s="382"/>
-      <c r="M2" s="382"/>
-      <c r="N2" s="382"/>
-      <c r="O2" s="382"/>
+      <c r="C2" s="384"/>
+      <c r="D2" s="384"/>
+      <c r="E2" s="384"/>
+      <c r="F2" s="384"/>
+      <c r="G2" s="384"/>
+      <c r="H2" s="384"/>
+      <c r="I2" s="384"/>
+      <c r="J2" s="384"/>
+      <c r="K2" s="384"/>
+      <c r="L2" s="384"/>
+      <c r="M2" s="384"/>
+      <c r="N2" s="384"/>
+      <c r="O2" s="384"/>
       <c r="Q2" s="176"/>
     </row>
     <row r="3" spans="2:22">
@@ -56876,12 +56875,12 @@
         <f>J6</f>
         <v>280000000</v>
       </c>
-      <c r="D5" s="384" t="s">
+      <c r="D5" s="379" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="384"/>
-      <c r="F5" s="384"/>
-      <c r="G5" s="384"/>
+      <c r="E5" s="379"/>
+      <c r="F5" s="379"/>
+      <c r="G5" s="379"/>
       <c r="I5" s="158" t="s">
         <v>215</v>
       </c>
@@ -56918,12 +56917,12 @@
         <f>(1+L5)^(1/12)-1</f>
         <v>9.0536953684483557E-4</v>
       </c>
-      <c r="D6" s="385" t="s">
+      <c r="D6" s="378" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="385"/>
-      <c r="F6" s="385"/>
-      <c r="G6" s="385"/>
+      <c r="E6" s="378"/>
+      <c r="F6" s="378"/>
+      <c r="G6" s="378"/>
       <c r="I6" s="160" t="s">
         <v>132</v>
       </c>
@@ -56960,12 +56959,12 @@
       <c r="C7" s="23">
         <v>5.5E-2</v>
       </c>
-      <c r="D7" s="384" t="s">
+      <c r="D7" s="379" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="384"/>
-      <c r="F7" s="384"/>
-      <c r="G7" s="384"/>
+      <c r="E7" s="379"/>
+      <c r="F7" s="379"/>
+      <c r="G7" s="379"/>
       <c r="I7" s="160" t="s">
         <v>216</v>
       </c>
@@ -56992,12 +56991,12 @@
         <f>(1+C7)^(1/12)-1</f>
         <v>4.471698917043021E-3</v>
       </c>
-      <c r="D8" s="385" t="s">
+      <c r="D8" s="378" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="385"/>
-      <c r="F8" s="385"/>
-      <c r="G8" s="385"/>
+      <c r="E8" s="378"/>
+      <c r="F8" s="378"/>
+      <c r="G8" s="378"/>
       <c r="I8" s="162" t="s">
         <v>217</v>
       </c>
@@ -57049,14 +57048,14 @@
       <c r="C10" s="147">
         <v>-0.14000000000000001</v>
       </c>
-      <c r="D10" s="385"/>
-      <c r="E10" s="385"/>
-      <c r="F10" s="385"/>
-      <c r="G10" s="385"/>
-      <c r="I10" s="383" t="s">
+      <c r="D10" s="378"/>
+      <c r="E10" s="378"/>
+      <c r="F10" s="378"/>
+      <c r="G10" s="378"/>
+      <c r="I10" s="385" t="s">
         <v>381</v>
       </c>
-      <c r="J10" s="383"/>
+      <c r="J10" s="385"/>
       <c r="Q10" s="176"/>
       <c r="S10" s="172" t="s">
         <v>375</v>
@@ -57079,10 +57078,10 @@
       <c r="C11" s="147">
         <v>-0.43</v>
       </c>
-      <c r="D11" s="385"/>
-      <c r="E11" s="385"/>
-      <c r="F11" s="385"/>
-      <c r="G11" s="385"/>
+      <c r="D11" s="378"/>
+      <c r="E11" s="378"/>
+      <c r="F11" s="378"/>
+      <c r="G11" s="378"/>
       <c r="I11" s="20" t="s">
         <v>382</v>
       </c>
@@ -57114,12 +57113,12 @@
         <f>AVERAGE(Consolidated!E24:H24)</f>
         <v>-1257.6075000000001</v>
       </c>
-      <c r="D12" s="385" t="s">
+      <c r="D12" s="378" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="385"/>
-      <c r="F12" s="385"/>
-      <c r="G12" s="385"/>
+      <c r="E12" s="378"/>
+      <c r="F12" s="378"/>
+      <c r="G12" s="378"/>
       <c r="I12" s="20" t="s">
         <v>383</v>
       </c>
@@ -57147,12 +57146,12 @@
       <c r="C13" s="145">
         <v>0</v>
       </c>
-      <c r="D13" s="385" t="s">
+      <c r="D13" s="378" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="385"/>
-      <c r="F13" s="385"/>
-      <c r="G13" s="385"/>
+      <c r="E13" s="378"/>
+      <c r="F13" s="378"/>
+      <c r="G13" s="378"/>
       <c r="I13" s="20" t="s">
         <v>313</v>
       </c>
@@ -57171,12 +57170,12 @@
         <f>AVERAGE(Consolidated!E28:H28)</f>
         <v>-64908.31</v>
       </c>
-      <c r="D14" s="385" t="s">
+      <c r="D14" s="378" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="385"/>
-      <c r="F14" s="385"/>
-      <c r="G14" s="385"/>
+      <c r="E14" s="378"/>
+      <c r="F14" s="378"/>
+      <c r="G14" s="378"/>
       <c r="J14" s="167">
         <f>SUM(J11:J13)</f>
         <v>-8.6499999999999994E-2</v>
@@ -57202,16 +57201,16 @@
         <f>AVERAGE(Consolidated!E35:H35)</f>
         <v>-23355.479999999996</v>
       </c>
-      <c r="D15" s="385" t="s">
+      <c r="D15" s="378" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="385"/>
-      <c r="F15" s="385"/>
-      <c r="G15" s="385"/>
-      <c r="I15" s="383" t="s">
+      <c r="E15" s="378"/>
+      <c r="F15" s="378"/>
+      <c r="G15" s="378"/>
+      <c r="I15" s="385" t="s">
         <v>384</v>
       </c>
-      <c r="J15" s="383"/>
+      <c r="J15" s="385"/>
       <c r="K15" s="20" t="s">
         <v>386</v>
       </c>
@@ -57237,12 +57236,12 @@
         <f>-0.4%</f>
         <v>-4.0000000000000001E-3</v>
       </c>
-      <c r="D16" s="385" t="s">
+      <c r="D16" s="378" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="385"/>
-      <c r="F16" s="385"/>
-      <c r="G16" s="385"/>
+      <c r="E16" s="378"/>
+      <c r="F16" s="378"/>
+      <c r="G16" s="378"/>
       <c r="I16" s="20" t="s">
         <v>385</v>
       </c>
@@ -57269,12 +57268,12 @@
       <c r="C17" s="166">
         <v>-3.9277296541559398E-2</v>
       </c>
-      <c r="D17" s="385" t="s">
+      <c r="D17" s="378" t="s">
         <v>51</v>
       </c>
-      <c r="E17" s="385"/>
-      <c r="F17" s="385"/>
-      <c r="G17" s="385"/>
+      <c r="E17" s="378"/>
+      <c r="F17" s="378"/>
+      <c r="G17" s="378"/>
       <c r="I17" s="20" t="s">
         <v>377</v>
       </c>
@@ -57292,12 +57291,12 @@
       <c r="C18" s="166">
         <v>0</v>
       </c>
-      <c r="D18" s="385" t="s">
+      <c r="D18" s="378" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="385"/>
-      <c r="F18" s="385"/>
-      <c r="G18" s="385"/>
+      <c r="E18" s="378"/>
+      <c r="F18" s="378"/>
+      <c r="G18" s="378"/>
       <c r="J18" s="111">
         <f>J16+J17</f>
         <v>-0.23655912886349639</v>
@@ -59327,22 +59326,22 @@
       <c r="Q63" s="176"/>
     </row>
     <row r="64" spans="2:17">
-      <c r="B64" s="377" t="s">
+      <c r="B64" s="386" t="s">
         <v>85</v>
       </c>
-      <c r="C64" s="377"/>
-      <c r="D64" s="377"/>
-      <c r="E64" s="377"/>
-      <c r="F64" s="377"/>
-      <c r="G64" s="377"/>
-      <c r="H64" s="377"/>
-      <c r="I64" s="377"/>
-      <c r="J64" s="377"/>
-      <c r="K64" s="377"/>
-      <c r="L64" s="377"/>
-      <c r="M64" s="377"/>
-      <c r="N64" s="377"/>
-      <c r="O64" s="377"/>
+      <c r="C64" s="386"/>
+      <c r="D64" s="386"/>
+      <c r="E64" s="386"/>
+      <c r="F64" s="386"/>
+      <c r="G64" s="386"/>
+      <c r="H64" s="386"/>
+      <c r="I64" s="386"/>
+      <c r="J64" s="386"/>
+      <c r="K64" s="386"/>
+      <c r="L64" s="386"/>
+      <c r="M64" s="386"/>
+      <c r="N64" s="386"/>
+      <c r="O64" s="386"/>
       <c r="Q64" s="176"/>
     </row>
     <row r="65" spans="2:17">
@@ -59363,24 +59362,24 @@
       <c r="Q65" s="176"/>
     </row>
     <row r="66" spans="2:17">
-      <c r="B66" s="378" t="s">
+      <c r="B66" s="382" t="s">
         <v>371</v>
       </c>
-      <c r="C66" s="378"/>
-      <c r="D66" s="378"/>
-      <c r="E66" s="378"/>
-      <c r="F66" s="378"/>
-      <c r="G66" s="378"/>
-      <c r="H66" s="378"/>
-      <c r="I66" s="378"/>
-      <c r="J66" s="378"/>
-      <c r="K66" s="378"/>
-      <c r="L66" s="378"/>
-      <c r="M66" s="378"/>
-      <c r="N66" s="378"/>
-      <c r="O66" s="378"/>
-      <c r="P66" s="378"/>
-      <c r="Q66" s="378"/>
+      <c r="C66" s="382"/>
+      <c r="D66" s="382"/>
+      <c r="E66" s="382"/>
+      <c r="F66" s="382"/>
+      <c r="G66" s="382"/>
+      <c r="H66" s="382"/>
+      <c r="I66" s="382"/>
+      <c r="J66" s="382"/>
+      <c r="K66" s="382"/>
+      <c r="L66" s="382"/>
+      <c r="M66" s="382"/>
+      <c r="N66" s="382"/>
+      <c r="O66" s="382"/>
+      <c r="P66" s="382"/>
+      <c r="Q66" s="382"/>
     </row>
     <row r="67" spans="2:17">
       <c r="B67" s="149"/>
@@ -59629,24 +59628,24 @@
       <c r="Q71" s="176"/>
     </row>
     <row r="72" spans="2:17" ht="16.5" customHeight="1">
-      <c r="B72" s="378" t="s">
+      <c r="B72" s="382" t="s">
         <v>86</v>
       </c>
-      <c r="C72" s="378"/>
-      <c r="D72" s="378"/>
-      <c r="E72" s="378"/>
-      <c r="F72" s="378"/>
-      <c r="G72" s="378"/>
-      <c r="H72" s="378"/>
-      <c r="I72" s="378"/>
-      <c r="J72" s="378"/>
-      <c r="K72" s="378"/>
-      <c r="L72" s="378"/>
-      <c r="M72" s="378"/>
-      <c r="N72" s="378"/>
-      <c r="O72" s="378"/>
-      <c r="P72" s="378"/>
-      <c r="Q72" s="378"/>
+      <c r="C72" s="382"/>
+      <c r="D72" s="382"/>
+      <c r="E72" s="382"/>
+      <c r="F72" s="382"/>
+      <c r="G72" s="382"/>
+      <c r="H72" s="382"/>
+      <c r="I72" s="382"/>
+      <c r="J72" s="382"/>
+      <c r="K72" s="382"/>
+      <c r="L72" s="382"/>
+      <c r="M72" s="382"/>
+      <c r="N72" s="382"/>
+      <c r="O72" s="382"/>
+      <c r="P72" s="382"/>
+      <c r="Q72" s="382"/>
     </row>
     <row r="73" spans="2:17" ht="13.5" customHeight="1">
       <c r="B73" s="149"/>
@@ -59895,24 +59894,24 @@
       <c r="Q77" s="176"/>
     </row>
     <row r="78" spans="2:17" ht="16.5" customHeight="1">
-      <c r="B78" s="379" t="s">
+      <c r="B78" s="381" t="s">
         <v>91</v>
       </c>
-      <c r="C78" s="379"/>
-      <c r="D78" s="379"/>
-      <c r="E78" s="379"/>
-      <c r="F78" s="379"/>
-      <c r="G78" s="379"/>
-      <c r="H78" s="379"/>
-      <c r="I78" s="379"/>
-      <c r="J78" s="379"/>
-      <c r="K78" s="379"/>
-      <c r="L78" s="379"/>
-      <c r="M78" s="379"/>
-      <c r="N78" s="379"/>
-      <c r="O78" s="379"/>
-      <c r="P78" s="379"/>
-      <c r="Q78" s="379"/>
+      <c r="C78" s="381"/>
+      <c r="D78" s="381"/>
+      <c r="E78" s="381"/>
+      <c r="F78" s="381"/>
+      <c r="G78" s="381"/>
+      <c r="H78" s="381"/>
+      <c r="I78" s="381"/>
+      <c r="J78" s="381"/>
+      <c r="K78" s="381"/>
+      <c r="L78" s="381"/>
+      <c r="M78" s="381"/>
+      <c r="N78" s="381"/>
+      <c r="O78" s="381"/>
+      <c r="P78" s="381"/>
+      <c r="Q78" s="381"/>
     </row>
     <row r="79" spans="2:17" ht="13.5" customHeight="1">
       <c r="B79" s="149"/>
@@ -60161,24 +60160,24 @@
       <c r="Q83" s="176"/>
     </row>
     <row r="84" spans="2:17" ht="16.5" customHeight="1">
-      <c r="B84" s="379" t="s">
+      <c r="B84" s="381" t="s">
         <v>92</v>
       </c>
-      <c r="C84" s="379"/>
-      <c r="D84" s="379"/>
-      <c r="E84" s="379"/>
-      <c r="F84" s="379"/>
-      <c r="G84" s="379"/>
-      <c r="H84" s="379"/>
-      <c r="I84" s="379"/>
-      <c r="J84" s="379"/>
-      <c r="K84" s="379"/>
-      <c r="L84" s="379"/>
-      <c r="M84" s="379"/>
-      <c r="N84" s="379"/>
-      <c r="O84" s="379"/>
-      <c r="P84" s="379"/>
-      <c r="Q84" s="379"/>
+      <c r="C84" s="381"/>
+      <c r="D84" s="381"/>
+      <c r="E84" s="381"/>
+      <c r="F84" s="381"/>
+      <c r="G84" s="381"/>
+      <c r="H84" s="381"/>
+      <c r="I84" s="381"/>
+      <c r="J84" s="381"/>
+      <c r="K84" s="381"/>
+      <c r="L84" s="381"/>
+      <c r="M84" s="381"/>
+      <c r="N84" s="381"/>
+      <c r="O84" s="381"/>
+      <c r="P84" s="381"/>
+      <c r="Q84" s="381"/>
     </row>
     <row r="85" spans="2:17" ht="13.5" customHeight="1">
       <c r="B85" s="149"/>
@@ -60427,24 +60426,24 @@
       <c r="Q89" s="176"/>
     </row>
     <row r="90" spans="2:17" ht="16.5" customHeight="1">
-      <c r="B90" s="378" t="s">
+      <c r="B90" s="382" t="s">
         <v>93</v>
       </c>
-      <c r="C90" s="378"/>
-      <c r="D90" s="378"/>
-      <c r="E90" s="378"/>
-      <c r="F90" s="378"/>
-      <c r="G90" s="378"/>
-      <c r="H90" s="378"/>
-      <c r="I90" s="378"/>
-      <c r="J90" s="378"/>
-      <c r="K90" s="378"/>
-      <c r="L90" s="378"/>
-      <c r="M90" s="378"/>
-      <c r="N90" s="378"/>
-      <c r="O90" s="378"/>
-      <c r="P90" s="378"/>
-      <c r="Q90" s="378"/>
+      <c r="C90" s="382"/>
+      <c r="D90" s="382"/>
+      <c r="E90" s="382"/>
+      <c r="F90" s="382"/>
+      <c r="G90" s="382"/>
+      <c r="H90" s="382"/>
+      <c r="I90" s="382"/>
+      <c r="J90" s="382"/>
+      <c r="K90" s="382"/>
+      <c r="L90" s="382"/>
+      <c r="M90" s="382"/>
+      <c r="N90" s="382"/>
+      <c r="O90" s="382"/>
+      <c r="P90" s="382"/>
+      <c r="Q90" s="382"/>
     </row>
     <row r="91" spans="2:17" ht="13.5" customHeight="1">
       <c r="B91" s="149"/>
@@ -60693,24 +60692,24 @@
       <c r="Q95" s="176"/>
     </row>
     <row r="96" spans="2:17" ht="16.5" customHeight="1">
-      <c r="B96" s="379" t="s">
+      <c r="B96" s="381" t="s">
         <v>94</v>
       </c>
-      <c r="C96" s="379"/>
-      <c r="D96" s="379"/>
-      <c r="E96" s="379"/>
-      <c r="F96" s="379"/>
-      <c r="G96" s="379"/>
-      <c r="H96" s="379"/>
-      <c r="I96" s="379"/>
-      <c r="J96" s="379"/>
-      <c r="K96" s="379"/>
-      <c r="L96" s="379"/>
-      <c r="M96" s="379"/>
-      <c r="N96" s="379"/>
-      <c r="O96" s="379"/>
-      <c r="P96" s="379"/>
-      <c r="Q96" s="379"/>
+      <c r="C96" s="381"/>
+      <c r="D96" s="381"/>
+      <c r="E96" s="381"/>
+      <c r="F96" s="381"/>
+      <c r="G96" s="381"/>
+      <c r="H96" s="381"/>
+      <c r="I96" s="381"/>
+      <c r="J96" s="381"/>
+      <c r="K96" s="381"/>
+      <c r="L96" s="381"/>
+      <c r="M96" s="381"/>
+      <c r="N96" s="381"/>
+      <c r="O96" s="381"/>
+      <c r="P96" s="381"/>
+      <c r="Q96" s="381"/>
     </row>
     <row r="97" spans="2:17" ht="13.5" customHeight="1">
       <c r="B97" s="149"/>
@@ -60959,24 +60958,24 @@
       <c r="Q101" s="176"/>
     </row>
     <row r="102" spans="2:17" ht="16.5" customHeight="1">
-      <c r="B102" s="378" t="s">
+      <c r="B102" s="382" t="s">
         <v>95</v>
       </c>
-      <c r="C102" s="378"/>
-      <c r="D102" s="378"/>
-      <c r="E102" s="378"/>
-      <c r="F102" s="378"/>
-      <c r="G102" s="378"/>
-      <c r="H102" s="378"/>
-      <c r="I102" s="378"/>
-      <c r="J102" s="378"/>
-      <c r="K102" s="378"/>
-      <c r="L102" s="378"/>
-      <c r="M102" s="378"/>
-      <c r="N102" s="378"/>
-      <c r="O102" s="378"/>
-      <c r="P102" s="378"/>
-      <c r="Q102" s="378"/>
+      <c r="C102" s="382"/>
+      <c r="D102" s="382"/>
+      <c r="E102" s="382"/>
+      <c r="F102" s="382"/>
+      <c r="G102" s="382"/>
+      <c r="H102" s="382"/>
+      <c r="I102" s="382"/>
+      <c r="J102" s="382"/>
+      <c r="K102" s="382"/>
+      <c r="L102" s="382"/>
+      <c r="M102" s="382"/>
+      <c r="N102" s="382"/>
+      <c r="O102" s="382"/>
+      <c r="P102" s="382"/>
+      <c r="Q102" s="382"/>
     </row>
     <row r="103" spans="2:17" ht="13.5" customHeight="1">
       <c r="B103" s="149"/>
@@ -61225,24 +61224,24 @@
       <c r="Q107" s="176"/>
     </row>
     <row r="108" spans="2:17" ht="16.5" customHeight="1">
-      <c r="B108" s="378" t="s">
+      <c r="B108" s="382" t="s">
         <v>96</v>
       </c>
-      <c r="C108" s="378"/>
-      <c r="D108" s="378"/>
-      <c r="E108" s="378"/>
-      <c r="F108" s="378"/>
-      <c r="G108" s="378"/>
-      <c r="H108" s="378"/>
-      <c r="I108" s="378"/>
-      <c r="J108" s="378"/>
-      <c r="K108" s="378"/>
-      <c r="L108" s="378"/>
-      <c r="M108" s="378"/>
-      <c r="N108" s="378"/>
-      <c r="O108" s="378"/>
-      <c r="P108" s="378"/>
-      <c r="Q108" s="378"/>
+      <c r="C108" s="382"/>
+      <c r="D108" s="382"/>
+      <c r="E108" s="382"/>
+      <c r="F108" s="382"/>
+      <c r="G108" s="382"/>
+      <c r="H108" s="382"/>
+      <c r="I108" s="382"/>
+      <c r="J108" s="382"/>
+      <c r="K108" s="382"/>
+      <c r="L108" s="382"/>
+      <c r="M108" s="382"/>
+      <c r="N108" s="382"/>
+      <c r="O108" s="382"/>
+      <c r="P108" s="382"/>
+      <c r="Q108" s="382"/>
     </row>
     <row r="109" spans="2:17" ht="13.5" customHeight="1">
       <c r="B109" s="149"/>
@@ -61491,24 +61490,24 @@
       <c r="Q113" s="176"/>
     </row>
     <row r="114" spans="2:17" ht="16.5" customHeight="1">
-      <c r="B114" s="379" t="s">
+      <c r="B114" s="381" t="s">
         <v>97</v>
       </c>
-      <c r="C114" s="379"/>
-      <c r="D114" s="379"/>
-      <c r="E114" s="379"/>
-      <c r="F114" s="379"/>
-      <c r="G114" s="379"/>
-      <c r="H114" s="379"/>
-      <c r="I114" s="379"/>
-      <c r="J114" s="379"/>
-      <c r="K114" s="379"/>
-      <c r="L114" s="379"/>
-      <c r="M114" s="379"/>
-      <c r="N114" s="379"/>
-      <c r="O114" s="379"/>
-      <c r="P114" s="379"/>
-      <c r="Q114" s="379"/>
+      <c r="C114" s="381"/>
+      <c r="D114" s="381"/>
+      <c r="E114" s="381"/>
+      <c r="F114" s="381"/>
+      <c r="G114" s="381"/>
+      <c r="H114" s="381"/>
+      <c r="I114" s="381"/>
+      <c r="J114" s="381"/>
+      <c r="K114" s="381"/>
+      <c r="L114" s="381"/>
+      <c r="M114" s="381"/>
+      <c r="N114" s="381"/>
+      <c r="O114" s="381"/>
+      <c r="P114" s="381"/>
+      <c r="Q114" s="381"/>
     </row>
     <row r="115" spans="2:17" ht="13.5" customHeight="1">
       <c r="B115" s="149"/>
@@ -61757,24 +61756,24 @@
       <c r="Q119" s="176"/>
     </row>
     <row r="120" spans="2:17" ht="16.5" customHeight="1">
-      <c r="B120" s="378" t="s">
+      <c r="B120" s="382" t="s">
         <v>98</v>
       </c>
-      <c r="C120" s="378"/>
-      <c r="D120" s="378"/>
-      <c r="E120" s="378"/>
-      <c r="F120" s="378"/>
-      <c r="G120" s="378"/>
-      <c r="H120" s="378"/>
-      <c r="I120" s="378"/>
-      <c r="J120" s="378"/>
-      <c r="K120" s="378"/>
-      <c r="L120" s="378"/>
-      <c r="M120" s="378"/>
-      <c r="N120" s="378"/>
-      <c r="O120" s="378"/>
-      <c r="P120" s="378"/>
-      <c r="Q120" s="378"/>
+      <c r="C120" s="382"/>
+      <c r="D120" s="382"/>
+      <c r="E120" s="382"/>
+      <c r="F120" s="382"/>
+      <c r="G120" s="382"/>
+      <c r="H120" s="382"/>
+      <c r="I120" s="382"/>
+      <c r="J120" s="382"/>
+      <c r="K120" s="382"/>
+      <c r="L120" s="382"/>
+      <c r="M120" s="382"/>
+      <c r="N120" s="382"/>
+      <c r="O120" s="382"/>
+      <c r="P120" s="382"/>
+      <c r="Q120" s="382"/>
     </row>
     <row r="121" spans="2:17" ht="13.5" customHeight="1">
       <c r="B121" s="149"/>
@@ -62009,24 +62008,24 @@
       <c r="Q125" s="176"/>
     </row>
     <row r="127" spans="2:17">
-      <c r="B127" s="378" t="s">
+      <c r="B127" s="382" t="s">
         <v>28</v>
       </c>
-      <c r="C127" s="378"/>
-      <c r="D127" s="378"/>
-      <c r="E127" s="378"/>
-      <c r="F127" s="378"/>
-      <c r="G127" s="378"/>
-      <c r="H127" s="378"/>
-      <c r="I127" s="378"/>
-      <c r="J127" s="378"/>
-      <c r="K127" s="378"/>
-      <c r="L127" s="378"/>
-      <c r="M127" s="378"/>
-      <c r="N127" s="378"/>
-      <c r="O127" s="378"/>
-      <c r="P127" s="378"/>
-      <c r="Q127" s="378"/>
+      <c r="C127" s="382"/>
+      <c r="D127" s="382"/>
+      <c r="E127" s="382"/>
+      <c r="F127" s="382"/>
+      <c r="G127" s="382"/>
+      <c r="H127" s="382"/>
+      <c r="I127" s="382"/>
+      <c r="J127" s="382"/>
+      <c r="K127" s="382"/>
+      <c r="L127" s="382"/>
+      <c r="M127" s="382"/>
+      <c r="N127" s="382"/>
+      <c r="O127" s="382"/>
+      <c r="P127" s="382"/>
+      <c r="Q127" s="382"/>
     </row>
     <row r="128" spans="2:17">
       <c r="B128" s="149"/>
@@ -62161,7 +62160,7 @@
       </c>
       <c r="H130" s="154">
         <f>IF(OR(Caixa!K6=0,Caixa!K6=""),"",Caixa!K6)</f>
-        <v>341946.62000000005</v>
+        <v>400289.01</v>
       </c>
       <c r="I130" s="154" t="str">
         <f>IF(OR(Caixa!L6=0,Caixa!L6=""),"",Caixa!L6)</f>
@@ -62222,7 +62221,7 @@
       </c>
       <c r="H131" s="44">
         <f t="shared" si="61"/>
-        <v>-0.20805411523282841</v>
+        <v>-7.293356434689964E-2</v>
       </c>
       <c r="I131" s="44" t="str">
         <f t="shared" si="61"/>
@@ -63229,15 +63228,15 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="D16:G16"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="B55:O55"/>
-    <mergeCell ref="D12:G12"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="D14:G14"/>
-    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="B64:O64"/>
+    <mergeCell ref="B66:Q66"/>
+    <mergeCell ref="B84:Q84"/>
+    <mergeCell ref="B72:Q72"/>
+    <mergeCell ref="B127:Q127"/>
+    <mergeCell ref="B90:Q90"/>
+    <mergeCell ref="B96:Q96"/>
+    <mergeCell ref="B102:Q102"/>
+    <mergeCell ref="B108:Q108"/>
     <mergeCell ref="B63:O63"/>
     <mergeCell ref="B78:Q78"/>
     <mergeCell ref="B114:Q114"/>
@@ -63254,15 +63253,15 @@
     <mergeCell ref="D8:G8"/>
     <mergeCell ref="D10:G10"/>
     <mergeCell ref="D11:G11"/>
-    <mergeCell ref="B64:O64"/>
-    <mergeCell ref="B66:Q66"/>
-    <mergeCell ref="B84:Q84"/>
-    <mergeCell ref="B72:Q72"/>
-    <mergeCell ref="B127:Q127"/>
-    <mergeCell ref="B90:Q90"/>
-    <mergeCell ref="B96:Q96"/>
-    <mergeCell ref="B102:Q102"/>
-    <mergeCell ref="B108:Q108"/>
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="B55:O55"/>
+    <mergeCell ref="D12:G12"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="D14:G14"/>
+    <mergeCell ref="D15:G15"/>
   </mergeCells>
   <conditionalFormatting sqref="C70:N70">
     <cfRule type="expression" dxfId="22" priority="3">
@@ -63366,27 +63365,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:20" ht="27.75" customHeight="1">
-      <c r="B1" s="386" t="s">
+      <c r="B1" s="387" t="s">
         <v>100</v>
       </c>
-      <c r="C1" s="386"/>
-      <c r="D1" s="386"/>
-      <c r="E1" s="386"/>
-      <c r="F1" s="386"/>
-      <c r="G1" s="386"/>
-      <c r="H1" s="386"/>
-      <c r="I1" s="386"/>
-      <c r="J1" s="386"/>
-      <c r="K1" s="386"/>
-      <c r="L1" s="386"/>
-      <c r="M1" s="386"/>
-      <c r="N1" s="386"/>
-      <c r="O1" s="386"/>
-      <c r="P1" s="386"/>
-      <c r="Q1" s="386"/>
-      <c r="R1" s="386"/>
-      <c r="S1" s="386"/>
-      <c r="T1" s="386"/>
+      <c r="C1" s="387"/>
+      <c r="D1" s="387"/>
+      <c r="E1" s="387"/>
+      <c r="F1" s="387"/>
+      <c r="G1" s="387"/>
+      <c r="H1" s="387"/>
+      <c r="I1" s="387"/>
+      <c r="J1" s="387"/>
+      <c r="K1" s="387"/>
+      <c r="L1" s="387"/>
+      <c r="M1" s="387"/>
+      <c r="N1" s="387"/>
+      <c r="O1" s="387"/>
+      <c r="P1" s="387"/>
+      <c r="Q1" s="387"/>
+      <c r="R1" s="387"/>
+      <c r="S1" s="387"/>
+      <c r="T1" s="387"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -67532,18 +67531,18 @@
         <f t="shared" ref="N5:N8" si="2">IF(H5&lt;0,H5,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="P5" s="393" t="s">
+      <c r="P5" s="388" t="s">
         <v>609</v>
       </c>
-      <c r="Q5" s="387">
+      <c r="Q5" s="391">
         <f>SUM(H4:H6)</f>
         <v>51025.550000000025</v>
       </c>
-      <c r="R5" s="390">
+      <c r="R5" s="394">
         <f>IF(Q5&gt;=0,Q5,NA())</f>
         <v>51025.550000000025</v>
       </c>
-      <c r="S5" s="390" t="e">
+      <c r="S5" s="394" t="e">
         <f>IF(Q5&lt;0,Q5,NA())</f>
         <v>#N/A</v>
       </c>
@@ -67593,10 +67592,10 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="P6" s="394"/>
-      <c r="Q6" s="388"/>
-      <c r="R6" s="391"/>
-      <c r="S6" s="391"/>
+      <c r="P6" s="389"/>
+      <c r="Q6" s="392"/>
+      <c r="R6" s="395"/>
+      <c r="S6" s="395"/>
       <c r="V6" s="323"/>
       <c r="W6" s="323"/>
       <c r="X6" s="323"/>
@@ -67643,10 +67642,10 @@
         <f t="shared" si="2"/>
         <v>-120711.43</v>
       </c>
-      <c r="P7" s="395"/>
-      <c r="Q7" s="389"/>
-      <c r="R7" s="392"/>
-      <c r="S7" s="392"/>
+      <c r="P7" s="390"/>
+      <c r="Q7" s="393"/>
+      <c r="R7" s="396"/>
+      <c r="S7" s="396"/>
     </row>
     <row r="8" spans="4:33" ht="15" customHeight="1">
       <c r="D8" s="107">
@@ -67681,18 +67680,18 @@
         <f t="shared" si="2"/>
         <v>-10290.099999999984</v>
       </c>
-      <c r="P8" s="393" t="s">
+      <c r="P8" s="388" t="s">
         <v>610</v>
       </c>
-      <c r="Q8" s="387">
+      <c r="Q8" s="391">
         <f>SUM(H7:H9)</f>
         <v>-128684.78999999996</v>
       </c>
-      <c r="R8" s="390" t="e">
+      <c r="R8" s="394" t="e">
         <f>IF(Q8&gt;=0,Q8,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="S8" s="390">
+      <c r="S8" s="394">
         <f>IF(Q8&lt;0,Q8,NA())</f>
         <v>-128684.78999999996</v>
       </c>
@@ -67730,10 +67729,10 @@
         <f t="shared" ref="N9:N63" si="5">IF(H9&lt;0,H9,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="P9" s="394"/>
-      <c r="Q9" s="388"/>
-      <c r="R9" s="391"/>
-      <c r="S9" s="391"/>
+      <c r="P9" s="389"/>
+      <c r="Q9" s="392"/>
+      <c r="R9" s="395"/>
+      <c r="S9" s="395"/>
     </row>
     <row r="10" spans="4:33" ht="15" customHeight="1">
       <c r="D10" s="107">
@@ -67768,10 +67767,10 @@
         <f t="shared" si="5"/>
         <v>-6944.5299999999934</v>
       </c>
-      <c r="P10" s="395"/>
-      <c r="Q10" s="389"/>
-      <c r="R10" s="392"/>
-      <c r="S10" s="392"/>
+      <c r="P10" s="390"/>
+      <c r="Q10" s="393"/>
+      <c r="R10" s="396"/>
+      <c r="S10" s="396"/>
     </row>
     <row r="11" spans="4:33" ht="15" customHeight="1">
       <c r="D11" s="107">
@@ -67806,18 +67805,18 @@
         <f t="shared" si="5"/>
         <v>-1944.2300000000014</v>
       </c>
-      <c r="P11" s="393" t="s">
+      <c r="P11" s="388" t="s">
         <v>611</v>
       </c>
-      <c r="Q11" s="387">
+      <c r="Q11" s="391">
         <f t="shared" ref="Q11" si="6">SUM(H10:H12)</f>
         <v>63263.910000000018</v>
       </c>
-      <c r="R11" s="390">
+      <c r="R11" s="394">
         <f t="shared" ref="R11" si="7">IF(Q11&gt;=0,Q11,NA())</f>
         <v>63263.910000000018</v>
       </c>
-      <c r="S11" s="390" t="e">
+      <c r="S11" s="394" t="e">
         <f t="shared" ref="S11" si="8">IF(Q11&lt;0,Q11,NA())</f>
         <v>#N/A</v>
       </c>
@@ -67855,10 +67854,10 @@
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="P12" s="394"/>
-      <c r="Q12" s="388"/>
-      <c r="R12" s="391"/>
-      <c r="S12" s="391"/>
+      <c r="P12" s="389"/>
+      <c r="Q12" s="392"/>
+      <c r="R12" s="395"/>
+      <c r="S12" s="395"/>
     </row>
     <row r="13" spans="4:33" ht="15" customHeight="1">
       <c r="D13" s="107">
@@ -67893,10 +67892,10 @@
         <f t="shared" si="5"/>
         <v>-29851.530000000013</v>
       </c>
-      <c r="P13" s="395"/>
-      <c r="Q13" s="389"/>
-      <c r="R13" s="392"/>
-      <c r="S13" s="392"/>
+      <c r="P13" s="390"/>
+      <c r="Q13" s="393"/>
+      <c r="R13" s="396"/>
+      <c r="S13" s="396"/>
     </row>
     <row r="14" spans="4:33" ht="15" customHeight="1">
       <c r="D14" s="107">
@@ -67931,18 +67930,18 @@
         <f t="shared" si="5"/>
         <v>-7189.3699999999917</v>
       </c>
-      <c r="P14" s="393" t="s">
+      <c r="P14" s="388" t="s">
         <v>612</v>
       </c>
-      <c r="Q14" s="387">
+      <c r="Q14" s="391">
         <f t="shared" ref="Q14" si="9">SUM(H13:H15)</f>
         <v>2032.5599999999977</v>
       </c>
-      <c r="R14" s="390">
+      <c r="R14" s="394">
         <f t="shared" ref="R14" si="10">IF(Q14&gt;=0,Q14,NA())</f>
         <v>2032.5599999999977</v>
       </c>
-      <c r="S14" s="390" t="e">
+      <c r="S14" s="394" t="e">
         <f t="shared" ref="S14" si="11">IF(Q14&lt;0,Q14,NA())</f>
         <v>#N/A</v>
       </c>
@@ -67980,10 +67979,10 @@
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="P15" s="394"/>
-      <c r="Q15" s="388"/>
-      <c r="R15" s="391"/>
-      <c r="S15" s="391"/>
+      <c r="P15" s="389"/>
+      <c r="Q15" s="392"/>
+      <c r="R15" s="395"/>
+      <c r="S15" s="395"/>
     </row>
     <row r="16" spans="4:33" ht="15" customHeight="1">
       <c r="D16" s="107">
@@ -68018,10 +68017,10 @@
         <f t="shared" si="5"/>
         <v>-50335.23</v>
       </c>
-      <c r="P16" s="395"/>
-      <c r="Q16" s="389"/>
-      <c r="R16" s="392"/>
-      <c r="S16" s="392"/>
+      <c r="P16" s="390"/>
+      <c r="Q16" s="393"/>
+      <c r="R16" s="396"/>
+      <c r="S16" s="396"/>
     </row>
     <row r="17" spans="4:19" ht="15" customHeight="1">
       <c r="D17" s="107">
@@ -68059,15 +68058,15 @@
       <c r="P17" s="325" t="s">
         <v>613</v>
       </c>
-      <c r="Q17" s="387">
+      <c r="Q17" s="391">
         <f t="shared" ref="Q17" si="12">SUM(H16:H18)</f>
         <v>-13021.260000000017</v>
       </c>
-      <c r="R17" s="390" t="e">
+      <c r="R17" s="394" t="e">
         <f t="shared" ref="R17" si="13">IF(Q17&gt;=0,Q17,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="S17" s="390">
+      <c r="S17" s="394">
         <f t="shared" ref="S17" si="14">IF(Q17&lt;0,Q17,NA())</f>
         <v>-13021.260000000017</v>
       </c>
@@ -68106,9 +68105,9 @@
         <v>#N/A</v>
       </c>
       <c r="P18" s="325"/>
-      <c r="Q18" s="388"/>
-      <c r="R18" s="391"/>
-      <c r="S18" s="391"/>
+      <c r="Q18" s="392"/>
+      <c r="R18" s="395"/>
+      <c r="S18" s="395"/>
     </row>
     <row r="19" spans="4:19" ht="15" customHeight="1">
       <c r="D19" s="107">
@@ -68144,9 +68143,9 @@
         <v>#N/A</v>
       </c>
       <c r="P19" s="326"/>
-      <c r="Q19" s="389"/>
-      <c r="R19" s="392"/>
-      <c r="S19" s="392"/>
+      <c r="Q19" s="393"/>
+      <c r="R19" s="396"/>
+      <c r="S19" s="396"/>
     </row>
     <row r="20" spans="4:19" ht="15" customHeight="1">
       <c r="D20" s="107">
@@ -68184,15 +68183,15 @@
       <c r="P20" s="325" t="s">
         <v>614</v>
       </c>
-      <c r="Q20" s="387">
+      <c r="Q20" s="391">
         <f t="shared" ref="Q20" si="15">SUM(H19:H21)</f>
         <v>1864.0900000000547</v>
       </c>
-      <c r="R20" s="390">
+      <c r="R20" s="394">
         <f t="shared" ref="R20" si="16">IF(Q20&gt;=0,Q20,NA())</f>
         <v>1864.0900000000547</v>
       </c>
-      <c r="S20" s="390" t="e">
+      <c r="S20" s="394" t="e">
         <f t="shared" ref="S20" si="17">IF(Q20&lt;0,Q20,NA())</f>
         <v>#N/A</v>
       </c>
@@ -68231,9 +68230,9 @@
         <v>-36345.219999999972</v>
       </c>
       <c r="P21" s="325"/>
-      <c r="Q21" s="388"/>
-      <c r="R21" s="391"/>
-      <c r="S21" s="391"/>
+      <c r="Q21" s="392"/>
+      <c r="R21" s="395"/>
+      <c r="S21" s="395"/>
     </row>
     <row r="22" spans="4:19" ht="15" customHeight="1">
       <c r="D22" s="107">
@@ -68269,9 +68268,9 @@
         <v>-6132.7899999999781</v>
       </c>
       <c r="P22" s="326"/>
-      <c r="Q22" s="389"/>
-      <c r="R22" s="392"/>
-      <c r="S22" s="392"/>
+      <c r="Q22" s="393"/>
+      <c r="R22" s="396"/>
+      <c r="S22" s="396"/>
     </row>
     <row r="23" spans="4:19" ht="15" customHeight="1">
       <c r="D23" s="107">
@@ -68309,15 +68308,15 @@
       <c r="P23" s="325" t="s">
         <v>615</v>
       </c>
-      <c r="Q23" s="387">
+      <c r="Q23" s="391">
         <f t="shared" ref="Q23" si="18">SUM(H22:H24)</f>
         <v>10423.430000000033</v>
       </c>
-      <c r="R23" s="390">
+      <c r="R23" s="394">
         <f t="shared" ref="R23" si="19">IF(Q23&gt;=0,Q23,NA())</f>
         <v>10423.430000000033</v>
       </c>
-      <c r="S23" s="390" t="e">
+      <c r="S23" s="394" t="e">
         <f t="shared" ref="S23" si="20">IF(Q23&lt;0,Q23,NA())</f>
         <v>#N/A</v>
       </c>
@@ -68356,9 +68355,9 @@
         <v>-3318.8700000000126</v>
       </c>
       <c r="P24" s="325"/>
-      <c r="Q24" s="388"/>
-      <c r="R24" s="391"/>
-      <c r="S24" s="391"/>
+      <c r="Q24" s="392"/>
+      <c r="R24" s="395"/>
+      <c r="S24" s="395"/>
     </row>
     <row r="25" spans="4:19" ht="15" customHeight="1">
       <c r="D25" s="107">
@@ -68394,9 +68393,9 @@
         <v>-44373.710000000021</v>
       </c>
       <c r="P25" s="326"/>
-      <c r="Q25" s="389"/>
-      <c r="R25" s="392"/>
-      <c r="S25" s="392"/>
+      <c r="Q25" s="393"/>
+      <c r="R25" s="396"/>
+      <c r="S25" s="396"/>
     </row>
     <row r="26" spans="4:19" ht="15" customHeight="1">
       <c r="D26" s="107">
@@ -68434,15 +68433,15 @@
       <c r="P26" s="325" t="s">
         <v>616</v>
       </c>
-      <c r="Q26" s="387">
+      <c r="Q26" s="391">
         <f t="shared" ref="Q26" si="21">SUM(H25:H27)</f>
         <v>-31621.239999999965</v>
       </c>
-      <c r="R26" s="390" t="e">
+      <c r="R26" s="394" t="e">
         <f t="shared" ref="R26" si="22">IF(Q26&gt;=0,Q26,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="S26" s="390">
+      <c r="S26" s="394">
         <f t="shared" ref="S26" si="23">IF(Q26&lt;0,Q26,NA())</f>
         <v>-31621.239999999965</v>
       </c>
@@ -68481,9 +68480,9 @@
         <v>#N/A</v>
       </c>
       <c r="P27" s="325"/>
-      <c r="Q27" s="388"/>
-      <c r="R27" s="391"/>
-      <c r="S27" s="391"/>
+      <c r="Q27" s="392"/>
+      <c r="R27" s="395"/>
+      <c r="S27" s="395"/>
     </row>
     <row r="28" spans="4:19" ht="15" customHeight="1">
       <c r="D28" s="107">
@@ -68519,9 +68518,9 @@
         <v>-44170.299999999988</v>
       </c>
       <c r="P28" s="326"/>
-      <c r="Q28" s="389"/>
-      <c r="R28" s="392"/>
-      <c r="S28" s="392"/>
+      <c r="Q28" s="393"/>
+      <c r="R28" s="396"/>
+      <c r="S28" s="396"/>
     </row>
     <row r="29" spans="4:19" ht="15" customHeight="1">
       <c r="D29" s="107">
@@ -68559,15 +68558,15 @@
       <c r="P29" s="325" t="s">
         <v>617</v>
       </c>
-      <c r="Q29" s="387">
+      <c r="Q29" s="391">
         <f t="shared" ref="Q29" si="24">SUM(H28:H30)</f>
         <v>-2864.9200000000164</v>
       </c>
-      <c r="R29" s="390" t="e">
+      <c r="R29" s="394" t="e">
         <f t="shared" ref="R29" si="25">IF(Q29&gt;=0,Q29,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="S29" s="390">
+      <c r="S29" s="394">
         <f t="shared" ref="S29" si="26">IF(Q29&lt;0,Q29,NA())</f>
         <v>-2864.9200000000164</v>
       </c>
@@ -68606,9 +68605,9 @@
         <v>#N/A</v>
       </c>
       <c r="P30" s="325"/>
-      <c r="Q30" s="388"/>
-      <c r="R30" s="391"/>
-      <c r="S30" s="391"/>
+      <c r="Q30" s="392"/>
+      <c r="R30" s="395"/>
+      <c r="S30" s="395"/>
     </row>
     <row r="31" spans="4:19" ht="15" customHeight="1">
       <c r="D31" s="107">
@@ -68644,9 +68643,9 @@
         <v>-43839.760000000009</v>
       </c>
       <c r="P31" s="326"/>
-      <c r="Q31" s="389"/>
-      <c r="R31" s="392"/>
-      <c r="S31" s="392"/>
+      <c r="Q31" s="393"/>
+      <c r="R31" s="396"/>
+      <c r="S31" s="396"/>
     </row>
     <row r="32" spans="4:19" ht="15" customHeight="1">
       <c r="D32" s="107">
@@ -68684,15 +68683,15 @@
       <c r="P32" s="325" t="s">
         <v>618</v>
       </c>
-      <c r="Q32" s="387">
+      <c r="Q32" s="391">
         <f t="shared" ref="Q32" si="27">SUM(H31:H33)</f>
         <v>16410.719999999972</v>
       </c>
-      <c r="R32" s="390">
+      <c r="R32" s="394">
         <f t="shared" ref="R32" si="28">IF(Q32&gt;=0,Q32,NA())</f>
         <v>16410.719999999972</v>
       </c>
-      <c r="S32" s="390" t="e">
+      <c r="S32" s="394" t="e">
         <f t="shared" ref="S32" si="29">IF(Q32&lt;0,Q32,NA())</f>
         <v>#N/A</v>
       </c>
@@ -68731,9 +68730,9 @@
         <v>#N/A</v>
       </c>
       <c r="P33" s="325"/>
-      <c r="Q33" s="388"/>
-      <c r="R33" s="391"/>
-      <c r="S33" s="391"/>
+      <c r="Q33" s="392"/>
+      <c r="R33" s="395"/>
+      <c r="S33" s="395"/>
     </row>
     <row r="34" spans="3:19" ht="15" customHeight="1">
       <c r="D34" s="107">
@@ -68769,9 +68768,9 @@
         <v>#N/A</v>
       </c>
       <c r="P34" s="326"/>
-      <c r="Q34" s="389"/>
-      <c r="R34" s="392"/>
-      <c r="S34" s="392"/>
+      <c r="Q34" s="393"/>
+      <c r="R34" s="396"/>
+      <c r="S34" s="396"/>
     </row>
     <row r="35" spans="3:19" ht="15" customHeight="1">
       <c r="D35" s="107">
@@ -68809,15 +68808,15 @@
       <c r="P35" s="325" t="s">
         <v>619</v>
       </c>
-      <c r="Q35" s="387">
+      <c r="Q35" s="391">
         <f t="shared" ref="Q35" si="30">SUM(H34:H36)</f>
         <v>48719.930000000044</v>
       </c>
-      <c r="R35" s="390">
+      <c r="R35" s="394">
         <f t="shared" ref="R35" si="31">IF(Q35&gt;=0,Q35,NA())</f>
         <v>48719.930000000044</v>
       </c>
-      <c r="S35" s="390" t="e">
+      <c r="S35" s="394" t="e">
         <f t="shared" ref="S35" si="32">IF(Q35&lt;0,Q35,NA())</f>
         <v>#N/A</v>
       </c>
@@ -68856,9 +68855,9 @@
         <v>#N/A</v>
       </c>
       <c r="P36" s="325"/>
-      <c r="Q36" s="388"/>
-      <c r="R36" s="391"/>
-      <c r="S36" s="391"/>
+      <c r="Q36" s="392"/>
+      <c r="R36" s="395"/>
+      <c r="S36" s="395"/>
     </row>
     <row r="37" spans="3:19" ht="15" customHeight="1">
       <c r="D37" s="107">
@@ -68894,9 +68893,9 @@
         <v>-34959.109999999971</v>
       </c>
       <c r="P37" s="326"/>
-      <c r="Q37" s="389"/>
-      <c r="R37" s="392"/>
-      <c r="S37" s="392"/>
+      <c r="Q37" s="393"/>
+      <c r="R37" s="396"/>
+      <c r="S37" s="396"/>
     </row>
     <row r="38" spans="3:19" ht="15" customHeight="1">
       <c r="D38" s="107">
@@ -68934,15 +68933,15 @@
       <c r="P38" s="325" t="s">
         <v>620</v>
       </c>
-      <c r="Q38" s="387">
+      <c r="Q38" s="391">
         <f t="shared" ref="Q38" si="33">SUM(H37:H39)</f>
         <v>57951.049999999974</v>
       </c>
-      <c r="R38" s="390">
+      <c r="R38" s="394">
         <f t="shared" ref="R38" si="34">IF(Q38&gt;=0,Q38,NA())</f>
         <v>57951.049999999974</v>
       </c>
-      <c r="S38" s="390" t="e">
+      <c r="S38" s="394" t="e">
         <f t="shared" ref="S38" si="35">IF(Q38&lt;0,Q38,NA())</f>
         <v>#N/A</v>
       </c>
@@ -68981,9 +68980,9 @@
         <v>#N/A</v>
       </c>
       <c r="P39" s="325"/>
-      <c r="Q39" s="388"/>
-      <c r="R39" s="391"/>
-      <c r="S39" s="391"/>
+      <c r="Q39" s="392"/>
+      <c r="R39" s="395"/>
+      <c r="S39" s="395"/>
     </row>
     <row r="40" spans="3:19" ht="15" customHeight="1">
       <c r="D40" s="107">
@@ -69021,9 +69020,9 @@
         <v>-45310.300000000017</v>
       </c>
       <c r="P40" s="326"/>
-      <c r="Q40" s="389"/>
-      <c r="R40" s="392"/>
-      <c r="S40" s="392"/>
+      <c r="Q40" s="393"/>
+      <c r="R40" s="396"/>
+      <c r="S40" s="396"/>
     </row>
     <row r="41" spans="3:19" ht="15" customHeight="1">
       <c r="D41" s="107">
@@ -69063,15 +69062,15 @@
       <c r="P41" s="325" t="s">
         <v>621</v>
       </c>
-      <c r="Q41" s="387">
+      <c r="Q41" s="391">
         <f t="shared" ref="Q41" si="37">SUM(H40:H42)</f>
         <v>-4982.5900000000365</v>
       </c>
-      <c r="R41" s="390" t="e">
+      <c r="R41" s="394" t="e">
         <f t="shared" ref="R41" si="38">IF(Q41&gt;=0,Q41,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="S41" s="390">
+      <c r="S41" s="394">
         <f t="shared" ref="S41" si="39">IF(Q41&lt;0,Q41,NA())</f>
         <v>-4982.5900000000365</v>
       </c>
@@ -69112,9 +69111,9 @@
         <v>#N/A</v>
       </c>
       <c r="P42" s="325"/>
-      <c r="Q42" s="388"/>
-      <c r="R42" s="391"/>
-      <c r="S42" s="391"/>
+      <c r="Q42" s="392"/>
+      <c r="R42" s="395"/>
+      <c r="S42" s="395"/>
     </row>
     <row r="43" spans="3:19" ht="15" customHeight="1">
       <c r="D43" s="107">
@@ -69152,9 +69151,9 @@
         <v>-27414.700000000044</v>
       </c>
       <c r="P43" s="326"/>
-      <c r="Q43" s="389"/>
-      <c r="R43" s="392"/>
-      <c r="S43" s="392"/>
+      <c r="Q43" s="393"/>
+      <c r="R43" s="396"/>
+      <c r="S43" s="396"/>
     </row>
     <row r="44" spans="3:19" ht="15" customHeight="1">
       <c r="D44" s="107">
@@ -69194,15 +69193,15 @@
       <c r="P44" s="325" t="s">
         <v>622</v>
       </c>
-      <c r="Q44" s="387">
+      <c r="Q44" s="391">
         <f t="shared" ref="Q44" si="40">SUM(H43:H45)</f>
         <v>42552.479999999967</v>
       </c>
-      <c r="R44" s="390">
+      <c r="R44" s="394">
         <f t="shared" ref="R44" si="41">IF(Q44&gt;=0,Q44,NA())</f>
         <v>42552.479999999967</v>
       </c>
-      <c r="S44" s="390" t="e">
+      <c r="S44" s="394" t="e">
         <f t="shared" ref="S44" si="42">IF(Q44&lt;0,Q44,NA())</f>
         <v>#N/A</v>
       </c>
@@ -69247,9 +69246,9 @@
         <v>#N/A</v>
       </c>
       <c r="P45" s="325"/>
-      <c r="Q45" s="388"/>
-      <c r="R45" s="391"/>
-      <c r="S45" s="391"/>
+      <c r="Q45" s="392"/>
+      <c r="R45" s="395"/>
+      <c r="S45" s="395"/>
     </row>
     <row r="46" spans="3:19" ht="15" customHeight="1">
       <c r="C46" s="111"/>
@@ -69288,9 +69287,9 @@
         <v>-32580.719999999943</v>
       </c>
       <c r="P46" s="326"/>
-      <c r="Q46" s="389"/>
-      <c r="R46" s="392"/>
-      <c r="S46" s="392"/>
+      <c r="Q46" s="393"/>
+      <c r="R46" s="396"/>
+      <c r="S46" s="396"/>
     </row>
     <row r="47" spans="3:19" ht="15" customHeight="1">
       <c r="D47" s="107">
@@ -69330,15 +69329,15 @@
       <c r="P47" s="325" t="s">
         <v>623</v>
       </c>
-      <c r="Q47" s="387">
+      <c r="Q47" s="391">
         <f t="shared" ref="Q47" si="43">SUM(H46:H48)</f>
         <v>84772.810000000172</v>
       </c>
-      <c r="R47" s="390">
+      <c r="R47" s="394">
         <f t="shared" ref="R47" si="44">IF(Q47&gt;=0,Q47,NA())</f>
         <v>84772.810000000172</v>
       </c>
-      <c r="S47" s="390" t="e">
+      <c r="S47" s="394" t="e">
         <f t="shared" ref="S47" si="45">IF(Q47&lt;0,Q47,NA())</f>
         <v>#N/A</v>
       </c>
@@ -69383,9 +69382,9 @@
         <v>#N/A</v>
       </c>
       <c r="P48" s="325"/>
-      <c r="Q48" s="388"/>
-      <c r="R48" s="391"/>
-      <c r="S48" s="391"/>
+      <c r="Q48" s="392"/>
+      <c r="R48" s="395"/>
+      <c r="S48" s="395"/>
     </row>
     <row r="49" spans="3:19" ht="15" customHeight="1">
       <c r="C49" s="111"/>
@@ -69424,9 +69423,9 @@
         <v>#N/A</v>
       </c>
       <c r="P49" s="326"/>
-      <c r="Q49" s="389"/>
-      <c r="R49" s="392"/>
-      <c r="S49" s="392"/>
+      <c r="Q49" s="393"/>
+      <c r="R49" s="396"/>
+      <c r="S49" s="396"/>
     </row>
     <row r="50" spans="3:19" ht="15" customHeight="1">
       <c r="D50" s="107">
@@ -69466,15 +69465,15 @@
       <c r="P50" s="325" t="s">
         <v>624</v>
       </c>
-      <c r="Q50" s="387">
+      <c r="Q50" s="391">
         <f t="shared" ref="Q50" si="46">SUM(H49:H51)</f>
         <v>154229.81000000003</v>
       </c>
-      <c r="R50" s="390">
+      <c r="R50" s="394">
         <f t="shared" ref="R50" si="47">IF(Q50&gt;=0,Q50,NA())</f>
         <v>154229.81000000003</v>
       </c>
-      <c r="S50" s="390" t="e">
+      <c r="S50" s="394" t="e">
         <f t="shared" ref="S50" si="48">IF(Q50&lt;0,Q50,NA())</f>
         <v>#N/A</v>
       </c>
@@ -69519,9 +69518,9 @@
         <v>#N/A</v>
       </c>
       <c r="P51" s="325"/>
-      <c r="Q51" s="388"/>
-      <c r="R51" s="391"/>
-      <c r="S51" s="391"/>
+      <c r="Q51" s="392"/>
+      <c r="R51" s="395"/>
+      <c r="S51" s="395"/>
     </row>
     <row r="52" spans="3:19" ht="15" customHeight="1">
       <c r="C52" s="111"/>
@@ -69565,9 +69564,9 @@
         <v>-4213.9399999999459</v>
       </c>
       <c r="P52" s="326"/>
-      <c r="Q52" s="389"/>
-      <c r="R52" s="392"/>
-      <c r="S52" s="392"/>
+      <c r="Q52" s="393"/>
+      <c r="R52" s="396"/>
+      <c r="S52" s="396"/>
     </row>
     <row r="53" spans="3:19" ht="15" customHeight="1">
       <c r="D53" s="107">
@@ -69612,15 +69611,15 @@
       <c r="P53" s="325" t="s">
         <v>625</v>
       </c>
-      <c r="Q53" s="387">
+      <c r="Q53" s="391">
         <f t="shared" ref="Q53" si="49">SUM(H52:H54)</f>
         <v>45917.990000000224</v>
       </c>
-      <c r="R53" s="390">
+      <c r="R53" s="394">
         <f t="shared" ref="R53" si="50">IF(Q53&gt;=0,Q53,NA())</f>
         <v>45917.990000000224</v>
       </c>
-      <c r="S53" s="390" t="e">
+      <c r="S53" s="394" t="e">
         <f t="shared" ref="S53" si="51">IF(Q53&lt;0,Q53,NA())</f>
         <v>#N/A</v>
       </c>
@@ -69670,9 +69669,9 @@
         <v>#N/A</v>
       </c>
       <c r="P54" s="325"/>
-      <c r="Q54" s="388"/>
-      <c r="R54" s="391"/>
-      <c r="S54" s="391"/>
+      <c r="Q54" s="392"/>
+      <c r="R54" s="395"/>
+      <c r="S54" s="395"/>
     </row>
     <row r="55" spans="3:19" ht="15" customHeight="1">
       <c r="D55" s="107">
@@ -69715,9 +69714,9 @@
         <v>#N/A</v>
       </c>
       <c r="P55" s="326"/>
-      <c r="Q55" s="389"/>
-      <c r="R55" s="392"/>
-      <c r="S55" s="392"/>
+      <c r="Q55" s="393"/>
+      <c r="R55" s="396"/>
+      <c r="S55" s="396"/>
     </row>
     <row r="56" spans="3:19" ht="15" customHeight="1">
       <c r="D56" s="107">
@@ -69762,15 +69761,15 @@
       <c r="P56" s="325" t="s">
         <v>626</v>
       </c>
-      <c r="Q56" s="387">
+      <c r="Q56" s="391">
         <f t="shared" ref="Q56" si="52">SUM(H55:H57)</f>
         <v>42861.07000000016</v>
       </c>
-      <c r="R56" s="390">
+      <c r="R56" s="394">
         <f t="shared" ref="R56" si="53">IF(Q56&gt;=0,Q56,NA())</f>
         <v>42861.07000000016</v>
       </c>
-      <c r="S56" s="390" t="e">
+      <c r="S56" s="394" t="e">
         <f t="shared" ref="S56" si="54">IF(Q56&lt;0,Q56,NA())</f>
         <v>#N/A</v>
       </c>
@@ -69817,9 +69816,9 @@
         <v>#N/A</v>
       </c>
       <c r="P57" s="325"/>
-      <c r="Q57" s="388"/>
-      <c r="R57" s="391"/>
-      <c r="S57" s="391"/>
+      <c r="Q57" s="392"/>
+      <c r="R57" s="395"/>
+      <c r="S57" s="395"/>
     </row>
     <row r="58" spans="3:19" ht="15" customHeight="1">
       <c r="D58" s="107">
@@ -69859,9 +69858,9 @@
         <v>#N/A</v>
       </c>
       <c r="P58" s="326"/>
-      <c r="Q58" s="389"/>
-      <c r="R58" s="392"/>
-      <c r="S58" s="392"/>
+      <c r="Q58" s="393"/>
+      <c r="R58" s="396"/>
+      <c r="S58" s="396"/>
     </row>
     <row r="59" spans="3:19" ht="15" customHeight="1">
       <c r="D59" s="107">
@@ -69903,15 +69902,15 @@
       <c r="P59" s="325" t="s">
         <v>627</v>
       </c>
-      <c r="Q59" s="387">
+      <c r="Q59" s="391">
         <f t="shared" ref="Q59" si="55">SUM(H58:H60)</f>
         <v>0</v>
       </c>
-      <c r="R59" s="390">
+      <c r="R59" s="394">
         <f t="shared" ref="R59" si="56">IF(Q59&gt;=0,Q59,NA())</f>
         <v>0</v>
       </c>
-      <c r="S59" s="390" t="e">
+      <c r="S59" s="394" t="e">
         <f t="shared" ref="S59" si="57">IF(Q59&lt;0,Q59,NA())</f>
         <v>#N/A</v>
       </c>
@@ -69958,9 +69957,9 @@
         <v>#N/A</v>
       </c>
       <c r="P60" s="325"/>
-      <c r="Q60" s="388"/>
-      <c r="R60" s="391"/>
-      <c r="S60" s="391"/>
+      <c r="Q60" s="392"/>
+      <c r="R60" s="395"/>
+      <c r="S60" s="395"/>
     </row>
     <row r="61" spans="3:19" ht="15" customHeight="1">
       <c r="D61" s="107">
@@ -70000,9 +69999,9 @@
         <v>#N/A</v>
       </c>
       <c r="P61" s="326"/>
-      <c r="Q61" s="389"/>
-      <c r="R61" s="392"/>
-      <c r="S61" s="392"/>
+      <c r="Q61" s="393"/>
+      <c r="R61" s="396"/>
+      <c r="S61" s="396"/>
     </row>
     <row r="62" spans="3:19" ht="15" customHeight="1">
       <c r="D62" s="107">
@@ -70044,15 +70043,15 @@
       <c r="P62" s="325" t="s">
         <v>628</v>
       </c>
-      <c r="Q62" s="387">
+      <c r="Q62" s="391">
         <f t="shared" ref="Q62" si="58">SUM(H61:H63)</f>
         <v>0</v>
       </c>
-      <c r="R62" s="390">
+      <c r="R62" s="394">
         <f t="shared" ref="R62" si="59">IF(Q62&gt;=0,Q62,NA())</f>
         <v>0</v>
       </c>
-      <c r="S62" s="390" t="e">
+      <c r="S62" s="394" t="e">
         <f t="shared" ref="S62" si="60">IF(Q62&lt;0,Q62,NA())</f>
         <v>#N/A</v>
       </c>
@@ -70099,23 +70098,66 @@
         <v>#N/A</v>
       </c>
       <c r="P63" s="325"/>
-      <c r="Q63" s="388"/>
-      <c r="R63" s="391"/>
-      <c r="S63" s="391"/>
+      <c r="Q63" s="392"/>
+      <c r="R63" s="395"/>
+      <c r="S63" s="395"/>
     </row>
     <row r="64" spans="3:19">
       <c r="P64" s="326"/>
-      <c r="Q64" s="389"/>
-      <c r="R64" s="392"/>
-      <c r="S64" s="392"/>
+      <c r="Q64" s="393"/>
+      <c r="R64" s="396"/>
+      <c r="S64" s="396"/>
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="P5:P7"/>
-    <mergeCell ref="Q5:Q7"/>
-    <mergeCell ref="R5:R7"/>
-    <mergeCell ref="S5:S7"/>
-    <mergeCell ref="P8:P10"/>
+    <mergeCell ref="Q59:Q61"/>
+    <mergeCell ref="R59:R61"/>
+    <mergeCell ref="S59:S61"/>
+    <mergeCell ref="Q62:Q64"/>
+    <mergeCell ref="R62:R64"/>
+    <mergeCell ref="S62:S64"/>
+    <mergeCell ref="Q53:Q55"/>
+    <mergeCell ref="R53:R55"/>
+    <mergeCell ref="S53:S55"/>
+    <mergeCell ref="Q56:Q58"/>
+    <mergeCell ref="R56:R58"/>
+    <mergeCell ref="S56:S58"/>
+    <mergeCell ref="Q47:Q49"/>
+    <mergeCell ref="R47:R49"/>
+    <mergeCell ref="S47:S49"/>
+    <mergeCell ref="Q50:Q52"/>
+    <mergeCell ref="R50:R52"/>
+    <mergeCell ref="S50:S52"/>
+    <mergeCell ref="Q41:Q43"/>
+    <mergeCell ref="R41:R43"/>
+    <mergeCell ref="S41:S43"/>
+    <mergeCell ref="Q44:Q46"/>
+    <mergeCell ref="R44:R46"/>
+    <mergeCell ref="S44:S46"/>
+    <mergeCell ref="Q35:Q37"/>
+    <mergeCell ref="R35:R37"/>
+    <mergeCell ref="S35:S37"/>
+    <mergeCell ref="Q38:Q40"/>
+    <mergeCell ref="R38:R40"/>
+    <mergeCell ref="S38:S40"/>
+    <mergeCell ref="Q29:Q31"/>
+    <mergeCell ref="R29:R31"/>
+    <mergeCell ref="S29:S31"/>
+    <mergeCell ref="Q32:Q34"/>
+    <mergeCell ref="R32:R34"/>
+    <mergeCell ref="S32:S34"/>
+    <mergeCell ref="Q23:Q25"/>
+    <mergeCell ref="R23:R25"/>
+    <mergeCell ref="S23:S25"/>
+    <mergeCell ref="Q26:Q28"/>
+    <mergeCell ref="R26:R28"/>
+    <mergeCell ref="S26:S28"/>
+    <mergeCell ref="Q17:Q19"/>
+    <mergeCell ref="R17:R19"/>
+    <mergeCell ref="S17:S19"/>
+    <mergeCell ref="Q20:Q22"/>
+    <mergeCell ref="R20:R22"/>
+    <mergeCell ref="S20:S22"/>
     <mergeCell ref="P14:P16"/>
     <mergeCell ref="Q8:Q10"/>
     <mergeCell ref="R8:R10"/>
@@ -70127,54 +70169,11 @@
     <mergeCell ref="R14:R16"/>
     <mergeCell ref="S14:S16"/>
     <mergeCell ref="P11:P13"/>
-    <mergeCell ref="Q17:Q19"/>
-    <mergeCell ref="R17:R19"/>
-    <mergeCell ref="S17:S19"/>
-    <mergeCell ref="Q20:Q22"/>
-    <mergeCell ref="R20:R22"/>
-    <mergeCell ref="S20:S22"/>
-    <mergeCell ref="Q23:Q25"/>
-    <mergeCell ref="R23:R25"/>
-    <mergeCell ref="S23:S25"/>
-    <mergeCell ref="Q26:Q28"/>
-    <mergeCell ref="R26:R28"/>
-    <mergeCell ref="S26:S28"/>
-    <mergeCell ref="Q29:Q31"/>
-    <mergeCell ref="R29:R31"/>
-    <mergeCell ref="S29:S31"/>
-    <mergeCell ref="Q32:Q34"/>
-    <mergeCell ref="R32:R34"/>
-    <mergeCell ref="S32:S34"/>
-    <mergeCell ref="Q35:Q37"/>
-    <mergeCell ref="R35:R37"/>
-    <mergeCell ref="S35:S37"/>
-    <mergeCell ref="Q38:Q40"/>
-    <mergeCell ref="R38:R40"/>
-    <mergeCell ref="S38:S40"/>
-    <mergeCell ref="Q41:Q43"/>
-    <mergeCell ref="R41:R43"/>
-    <mergeCell ref="S41:S43"/>
-    <mergeCell ref="Q44:Q46"/>
-    <mergeCell ref="R44:R46"/>
-    <mergeCell ref="S44:S46"/>
-    <mergeCell ref="Q47:Q49"/>
-    <mergeCell ref="R47:R49"/>
-    <mergeCell ref="S47:S49"/>
-    <mergeCell ref="Q50:Q52"/>
-    <mergeCell ref="R50:R52"/>
-    <mergeCell ref="S50:S52"/>
-    <mergeCell ref="Q53:Q55"/>
-    <mergeCell ref="R53:R55"/>
-    <mergeCell ref="S53:S55"/>
-    <mergeCell ref="Q56:Q58"/>
-    <mergeCell ref="R56:R58"/>
-    <mergeCell ref="S56:S58"/>
-    <mergeCell ref="Q59:Q61"/>
-    <mergeCell ref="R59:R61"/>
-    <mergeCell ref="S59:S61"/>
-    <mergeCell ref="Q62:Q64"/>
-    <mergeCell ref="R62:R64"/>
-    <mergeCell ref="S62:S64"/>
+    <mergeCell ref="P5:P7"/>
+    <mergeCell ref="Q5:Q7"/>
+    <mergeCell ref="R5:R7"/>
+    <mergeCell ref="S5:S7"/>
+    <mergeCell ref="P8:P10"/>
   </mergeCells>
   <pageMargins left="0.51180555555555596" right="0.51180555555555596" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Demonstrações 2026 final.xlsx
+++ b/Demonstrações 2026 final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/victorgaioso/Documents/Gaioso/ANDALUZ/ESTRATÉGICO/Relatórios Estratégicos/2026/Anual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C24D1D-8ABC-F64C-B962-1D0E0C1361E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A79B3F-95F6-0944-88A9-4D947CD22EAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19340" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19340" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CNS" sheetId="17" r:id="rId1"/>
@@ -130,7 +130,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -3834,7 +3834,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="415">
+  <cellXfs count="410">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4814,23 +4814,26 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="177" fontId="54" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="55" fillId="28" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4841,19 +4844,13 @@
     <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -4874,6 +4871,15 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4886,11 +4892,11 @@
     <xf numFmtId="0" fontId="0" fillId="28" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="38" fillId="22" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="22" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="46" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4901,21 +4907,6 @@
     <xf numFmtId="0" fontId="64" fillId="46" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="54" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="55" fillId="28" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Moeda 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
@@ -5248,43 +5239,12 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
       <numFmt numFmtId="165" formatCode="&quot;R$ &quot;#,##0.00"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="170" formatCode="0.0%"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -5309,26 +5269,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF0F3652"/>
-          <bgColor rgb="FF003354"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill>
           <bgColor rgb="FF043557"/>
         </patternFill>
       </fill>
@@ -5353,577 +5293,10 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
+          <fgColor rgb="FF0F3652"/>
+          <bgColor rgb="FF043557"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="&quot;R$ &quot;#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;R$ &quot;#,##0.00"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.0%"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5943,6 +5316,10 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="170" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="0.0%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
@@ -5967,65 +5344,6 @@
       </font>
       <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -6099,345 +5417,13 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
+        <sz val="12"/>
+        <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -6451,235 +5437,12 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="&quot;R$ &quot;#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF033254"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;R$ &quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.0%"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -6702,9 +5465,10 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF0F3652"/>
-          <bgColor rgb="FF043557"/>
+          <bgColor rgb="FF003354"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -6718,21 +5482,78 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
         <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0F3652"/>
-          <bgColor rgb="FF043557"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <numFmt numFmtId="170" formatCode="0.0%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -6806,76 +5627,6 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0F3652"/>
-          <bgColor rgb="FF003354"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.0%"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
         <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
@@ -6914,6 +5665,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="170" formatCode="0.0%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -6932,6 +5687,85 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -7068,37 +5902,445 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
       <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
       <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
       <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
       <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
       <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
       <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="&quot;R$ &quot;#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -7133,12 +6375,18 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color theme="1"/>
+        <color theme="0"/>
         <name val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
         <scheme val="none"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -7171,6 +6419,31 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
         <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
@@ -7190,12 +6463,156 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
         <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
         <scheme val="none"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -7281,6 +6698,580 @@
         <patternFill patternType="solid">
           <fgColor rgb="FF0F3652"/>
           <bgColor rgb="FF003354"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="&quot;R$ &quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="170" formatCode="0.0%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0F3652"/>
+          <bgColor rgb="FF003354"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF043557"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="&quot;R$ &quot;#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;R$ &quot;#,##0.00"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF033254"/>
         </patternFill>
       </fill>
     </dxf>
@@ -27244,9 +27235,9 @@
     <sortCondition descending="1" ref="K7:K29"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{24003485-C01D-E147-9B14-D5D3EED61C82}" name="Centro de custo" totalsRowLabel="Total" dataDxfId="99" totalsRowDxfId="98"/>
-    <tableColumn id="2" xr3:uid="{9DA54C49-C7F4-A848-8182-9F2126DDCAC3}" name="%" dataDxfId="97" totalsRowDxfId="96"/>
-    <tableColumn id="3" xr3:uid="{BDAF6979-3949-9244-989A-33A73FF11A98}" name="R$" totalsRowFunction="sum" dataDxfId="95"/>
+    <tableColumn id="1" xr3:uid="{24003485-C01D-E147-9B14-D5D3EED61C82}" name="Centro de custo" totalsRowLabel="Total" dataDxfId="27" totalsRowDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{9DA54C49-C7F4-A848-8182-9F2126DDCAC3}" name="%" dataDxfId="25" totalsRowDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{BDAF6979-3949-9244-989A-33A73FF11A98}" name="R$" totalsRowFunction="sum" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -27259,29 +27250,29 @@
     <sortCondition descending="1" ref="Q14:Q149"/>
   </sortState>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Centro de custos" totalsRowDxfId="43"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Categoria" totalsRowDxfId="42"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="consultor" totalsRowDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Coluna1" totalsRowFunction="sum" dataDxfId="56" totalsRowDxfId="40">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Centro de custos" totalsRowDxfId="139"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Categoria" totalsRowDxfId="138"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="consultor" totalsRowDxfId="137"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Coluna1" totalsRowFunction="sum" dataDxfId="136" totalsRowDxfId="135">
       <calculatedColumnFormula>SUM(Tabela1[[#This Row],[jan./26]:[dez./26]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="100%" totalsRowFunction="sum" totalsRowDxfId="39"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="jan./26" dataDxfId="55" totalsRowDxfId="38"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="fev./26" dataDxfId="54" totalsRowDxfId="37"/>
-    <tableColumn id="9" xr3:uid="{AABBF02E-246F-2943-880B-34452D6B51BA}" name="mar./26" dataDxfId="53" totalsRowDxfId="36"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="abr./26" dataDxfId="52" totalsRowDxfId="35"/>
-    <tableColumn id="10" xr3:uid="{EAB1B330-99DA-3248-A314-3831BFE2A743}" name="mai./26" totalsRowFunction="sum" dataDxfId="51" totalsRowDxfId="34">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="100%" totalsRowFunction="sum" totalsRowDxfId="134"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="jan./26" dataDxfId="133" totalsRowDxfId="132"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="fev./26" dataDxfId="131" totalsRowDxfId="130"/>
+    <tableColumn id="9" xr3:uid="{AABBF02E-246F-2943-880B-34452D6B51BA}" name="mar./26" dataDxfId="129" totalsRowDxfId="128"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="abr./26" dataDxfId="127" totalsRowDxfId="126"/>
+    <tableColumn id="10" xr3:uid="{EAB1B330-99DA-3248-A314-3831BFE2A743}" name="mai./26" totalsRowFunction="sum" dataDxfId="125" totalsRowDxfId="124">
       <calculatedColumnFormula>VLOOKUP(Tabela1[[#This Row],[Categoria]],[4]Planilha1!$B$3:$E$16,4,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{B6400945-D01B-DC4E-B35C-18AA298CDD6C}" name="jun./26" totalsRowFunction="sum" dataDxfId="50" totalsRowDxfId="33">
+    <tableColumn id="11" xr3:uid="{B6400945-D01B-DC4E-B35C-18AA298CDD6C}" name="jun./26" totalsRowFunction="sum" dataDxfId="123" totalsRowDxfId="122">
       <calculatedColumnFormula>VLOOKUP(Tabela1[[#This Row],[Categoria]],[5]Planilha1!E$7:F$55,2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{3E94630B-C6C3-AE4C-9D9C-9FC6D3AAFE0F}" name="jul./26" dataDxfId="49" totalsRowDxfId="32"/>
-    <tableColumn id="13" xr3:uid="{8A08E242-3F78-434D-AA4E-71D707845A06}" name="ago./26" dataDxfId="48" totalsRowDxfId="31"/>
-    <tableColumn id="14" xr3:uid="{1488188E-82BB-A040-BE55-098B625FA87D}" name="set./26" dataDxfId="47" totalsRowDxfId="30"/>
-    <tableColumn id="15" xr3:uid="{6BD1CE9C-3587-EA43-A66E-8DB33FAE6FD0}" name="out./26" dataDxfId="46" totalsRowDxfId="29"/>
-    <tableColumn id="16" xr3:uid="{A45A99EE-5478-5A46-ACFF-60E7732A2E36}" name="nov./26" dataDxfId="45" totalsRowDxfId="28"/>
-    <tableColumn id="17" xr3:uid="{51770A9B-D122-D549-99A0-206A077F6532}" name="dez./26" dataDxfId="44" totalsRowDxfId="27"/>
+    <tableColumn id="12" xr3:uid="{3E94630B-C6C3-AE4C-9D9C-9FC6D3AAFE0F}" name="jul./26" dataDxfId="121" totalsRowDxfId="120"/>
+    <tableColumn id="13" xr3:uid="{8A08E242-3F78-434D-AA4E-71D707845A06}" name="ago./26" dataDxfId="119" totalsRowDxfId="118"/>
+    <tableColumn id="14" xr3:uid="{1488188E-82BB-A040-BE55-098B625FA87D}" name="set./26" dataDxfId="117" totalsRowDxfId="116"/>
+    <tableColumn id="15" xr3:uid="{6BD1CE9C-3587-EA43-A66E-8DB33FAE6FD0}" name="out./26" dataDxfId="115" totalsRowDxfId="114"/>
+    <tableColumn id="16" xr3:uid="{A45A99EE-5478-5A46-ACFF-60E7732A2E36}" name="nov./26" dataDxfId="113" totalsRowDxfId="112"/>
+    <tableColumn id="17" xr3:uid="{51770A9B-D122-D549-99A0-206A077F6532}" name="dez./26" dataDxfId="111" totalsRowDxfId="110"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -27294,11 +27285,11 @@
     <sortCondition descending="1" ref="AA29:AA53"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Centro de custo" totalsRowLabel="Total" dataDxfId="26" totalsRowDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="%" totalsRowFunction="sum" totalsRowDxfId="24">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Centro de custo" totalsRowLabel="Total" dataDxfId="109" totalsRowDxfId="108"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="%" totalsRowFunction="sum" totalsRowDxfId="107">
       <calculatedColumnFormula>AA30/$J$150</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="R$" totalsRowFunction="sum" totalsRowDxfId="23">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="R$" totalsRowFunction="sum" totalsRowDxfId="106">
       <calculatedColumnFormula>SUMIF($G$15:$G$149,Y30,$J$15:$J$149)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -27313,16 +27304,16 @@
     <sortCondition ref="AE14:AE34"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Centro de Custos" totalsRowLabel="Total" totalsRowDxfId="139"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="%" totalsRowFunction="sum" totalsRowDxfId="138"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Valor" totalsRowFunction="sum" totalsRowDxfId="137"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Centro de Custos" totalsRowLabel="Total" totalsRowDxfId="105"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="%" totalsRowFunction="sum" totalsRowDxfId="104"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Valor" totalsRowFunction="sum" totalsRowDxfId="103"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Tabela8" displayName="Tabela8" ref="F14:AA132" totalsRowCount="1" totalsRowDxfId="136">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Tabela8" displayName="Tabela8" ref="F14:AA132" totalsRowCount="1" totalsRowDxfId="102">
   <autoFilter ref="F14:AA131" xr:uid="{00000000-0009-0000-0100-000006000000}">
     <filterColumn colId="1">
       <filters>
@@ -27334,43 +27325,43 @@
     <sortCondition descending="1" ref="U14:U131"/>
   </sortState>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Empresa" totalsRowLabel="Total" totalsRowDxfId="93"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Centro de custos" totalsRowDxfId="92"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Categoria" totalsRowDxfId="91"/>
-    <tableColumn id="10" xr3:uid="{BAA97004-D35C-B34D-A848-E2E809C9E0A1}" name="Destino" dataDxfId="135" totalsRowDxfId="90"/>
-    <tableColumn id="11" xr3:uid="{5748DA56-ED3D-2142-9256-492A8D49FC84}" name="Natureza" dataDxfId="134" totalsRowDxfId="89"/>
-    <tableColumn id="12" xr3:uid="{1F8C8E0B-7B4F-2F41-BD3E-B6207E1597C0}" name="Utilidade" dataDxfId="133" totalsRowDxfId="88"/>
-    <tableColumn id="13" xr3:uid="{358B4DBE-BA25-2741-99DA-246AD9CDB40D}" name="Obs" dataDxfId="132" totalsRowDxfId="87"/>
-    <tableColumn id="14" xr3:uid="{79081247-EB07-1E4D-9E8A-72F1A825AC8A}" name="Média" totalsRowFunction="sum" dataDxfId="131" totalsRowDxfId="86">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Empresa" totalsRowLabel="Total" totalsRowDxfId="101"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Centro de custos" totalsRowDxfId="100"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Categoria" totalsRowDxfId="99"/>
+    <tableColumn id="10" xr3:uid="{BAA97004-D35C-B34D-A848-E2E809C9E0A1}" name="Destino" dataDxfId="98" totalsRowDxfId="97"/>
+    <tableColumn id="11" xr3:uid="{5748DA56-ED3D-2142-9256-492A8D49FC84}" name="Natureza" dataDxfId="96" totalsRowDxfId="95"/>
+    <tableColumn id="12" xr3:uid="{1F8C8E0B-7B4F-2F41-BD3E-B6207E1597C0}" name="Utilidade" dataDxfId="94" totalsRowDxfId="93"/>
+    <tableColumn id="13" xr3:uid="{358B4DBE-BA25-2741-99DA-246AD9CDB40D}" name="Obs" dataDxfId="92" totalsRowDxfId="91"/>
+    <tableColumn id="14" xr3:uid="{79081247-EB07-1E4D-9E8A-72F1A825AC8A}" name="Média" totalsRowFunction="sum" dataDxfId="90" totalsRowDxfId="89">
       <calculatedColumnFormula>AVERAGE(Tabela8[[#This Row],[jan./26]:[dez/26]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="YTD" totalsRowFunction="sum" totalsRowDxfId="85">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="YTD" totalsRowFunction="sum" totalsRowDxfId="88">
       <calculatedColumnFormula>SUM(Tabela8[[#This Row],[jan./26]:[dez/26]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="100%" totalsRowFunction="sum" totalsRowDxfId="84"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="jan./26" totalsRowFunction="sum" dataDxfId="130" totalsRowDxfId="83"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="fev./26" totalsRowFunction="sum" dataDxfId="129" totalsRowDxfId="82"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" name="mar./26" totalsRowFunction="sum" dataDxfId="128" totalsRowDxfId="81"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" name="abr./26" totalsRowFunction="sum" dataDxfId="127" totalsRowDxfId="80"/>
-    <tableColumn id="15" xr3:uid="{FDDCA405-118D-9449-BDBF-9C7C40F72DBF}" name="mai/26" totalsRowFunction="sum" dataDxfId="126" totalsRowDxfId="79"/>
-    <tableColumn id="16" xr3:uid="{C69C506A-D73A-2E44-ADE6-2EE1608757E1}" name="jun/26" totalsRowFunction="sum" dataDxfId="94" totalsRowDxfId="78"/>
-    <tableColumn id="17" xr3:uid="{05171C8F-D6BD-0C42-A401-40D79BAD4862}" name="jul/26" totalsRowFunction="sum" dataDxfId="125" totalsRowDxfId="77"/>
-    <tableColumn id="18" xr3:uid="{9E9ED4AB-2B85-EA48-9DF5-E55BB0C5C446}" name="ago/26" totalsRowFunction="sum" dataDxfId="124" totalsRowDxfId="76"/>
-    <tableColumn id="19" xr3:uid="{3C6323D0-3831-2448-AD29-AAE75A232848}" name="set/26" totalsRowFunction="sum" dataDxfId="123" totalsRowDxfId="75"/>
-    <tableColumn id="20" xr3:uid="{D47B3FDF-016A-6844-A033-C6CF5E813821}" name="out/26" totalsRowFunction="sum" dataDxfId="122" totalsRowDxfId="74"/>
-    <tableColumn id="21" xr3:uid="{376ACAF0-01C1-1944-9D9E-8A1C18A42F02}" name="nov/26" totalsRowFunction="sum" dataDxfId="121" totalsRowDxfId="73"/>
-    <tableColumn id="22" xr3:uid="{1EE0E33D-8669-9940-985C-20ED056693D8}" name="dez/26" totalsRowFunction="sum" dataDxfId="120" totalsRowDxfId="72"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="100%" totalsRowFunction="sum" totalsRowDxfId="87"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="jan./26" totalsRowFunction="sum" dataDxfId="86" totalsRowDxfId="85"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="fev./26" totalsRowFunction="sum" dataDxfId="84" totalsRowDxfId="83"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" name="mar./26" totalsRowFunction="sum" dataDxfId="82" totalsRowDxfId="81"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" name="abr./26" totalsRowFunction="sum" dataDxfId="80" totalsRowDxfId="79"/>
+    <tableColumn id="15" xr3:uid="{FDDCA405-118D-9449-BDBF-9C7C40F72DBF}" name="mai/26" totalsRowFunction="sum" dataDxfId="78" totalsRowDxfId="77"/>
+    <tableColumn id="16" xr3:uid="{C69C506A-D73A-2E44-ADE6-2EE1608757E1}" name="jun/26" totalsRowFunction="sum" dataDxfId="76" totalsRowDxfId="75"/>
+    <tableColumn id="17" xr3:uid="{05171C8F-D6BD-0C42-A401-40D79BAD4862}" name="jul/26" totalsRowFunction="sum" dataDxfId="74" totalsRowDxfId="73"/>
+    <tableColumn id="18" xr3:uid="{9E9ED4AB-2B85-EA48-9DF5-E55BB0C5C446}" name="ago/26" totalsRowFunction="sum" dataDxfId="72" totalsRowDxfId="71"/>
+    <tableColumn id="19" xr3:uid="{3C6323D0-3831-2448-AD29-AAE75A232848}" name="set/26" totalsRowFunction="sum" dataDxfId="70" totalsRowDxfId="69"/>
+    <tableColumn id="20" xr3:uid="{D47B3FDF-016A-6844-A033-C6CF5E813821}" name="out/26" totalsRowFunction="sum" dataDxfId="68" totalsRowDxfId="67"/>
+    <tableColumn id="21" xr3:uid="{376ACAF0-01C1-1944-9D9E-8A1C18A42F02}" name="nov/26" totalsRowFunction="sum" dataDxfId="66" totalsRowDxfId="65"/>
+    <tableColumn id="22" xr3:uid="{1EE0E33D-8669-9940-985C-20ED056693D8}" name="dez/26" totalsRowFunction="sum" dataDxfId="64" totalsRowDxfId="63"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{56A3A1B2-3AD2-324A-8343-8748FCA245E5}" name="Tabela9" displayName="Tabela9" ref="AC38:AD49" totalsRowCount="1" headerRowDxfId="119">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{56A3A1B2-3AD2-324A-8343-8748FCA245E5}" name="Tabela9" displayName="Tabela9" ref="AC38:AD49" totalsRowCount="1" headerRowDxfId="62">
   <autoFilter ref="AC38:AD48" xr:uid="{56A3A1B2-3AD2-324A-8343-8748FCA245E5}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{A61FCBEA-BBD2-8146-BD90-DA89F078B5FF}" name="Consultor" totalsRowLabel="Total" dataDxfId="118" totalsRowDxfId="117"/>
-    <tableColumn id="2" xr3:uid="{700CB55E-A07A-1646-B9AA-D97A9EE764D9}" name="Total" totalsRowFunction="sum" dataDxfId="116" totalsRowDxfId="115">
+    <tableColumn id="1" xr3:uid="{A61FCBEA-BBD2-8146-BD90-DA89F078B5FF}" name="Consultor" totalsRowLabel="Total" dataDxfId="61" totalsRowDxfId="60"/>
+    <tableColumn id="2" xr3:uid="{700CB55E-A07A-1646-B9AA-D97A9EE764D9}" name="Total" totalsRowFunction="sum" dataDxfId="59" totalsRowDxfId="58">
       <calculatedColumnFormula>SUMIF(Tabela8[Destino],Tabela9[[#This Row],[Consultor]],Tabela8[YTD])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -27379,20 +27370,20 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{6CB670A0-F49C-DA4B-81BB-5DD1E6B518A9}" name="Tabela10" displayName="Tabela10" ref="AG14:AJ34" totalsRowCount="1" headerRowDxfId="114" dataDxfId="113">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{6CB670A0-F49C-DA4B-81BB-5DD1E6B518A9}" name="Tabela10" displayName="Tabela10" ref="AG14:AJ34" totalsRowCount="1" headerRowDxfId="57" dataDxfId="56">
   <autoFilter ref="AG14:AJ33" xr:uid="{6CB670A0-F49C-DA4B-81BB-5DD1E6B518A9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="AG15:AJ33">
     <sortCondition descending="1" ref="AI14:AI33"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{EE1880B1-4338-BD40-9AF2-A218F3AB3EE5}" name="Destino" totalsRowLabel="Total" dataDxfId="112" totalsRowDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{3379F72A-B2CA-4F4A-89F5-21BA29A71D19}" name="R$" totalsRowFunction="sum" dataDxfId="111" totalsRowDxfId="60">
+    <tableColumn id="1" xr3:uid="{EE1880B1-4338-BD40-9AF2-A218F3AB3EE5}" name="Destino" totalsRowLabel="Total" dataDxfId="55" totalsRowDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{3379F72A-B2CA-4F4A-89F5-21BA29A71D19}" name="R$" totalsRowFunction="sum" dataDxfId="53" totalsRowDxfId="52">
       <calculatedColumnFormula>SUMIF(Tabela8[Destino],Tabela10[[#This Row],[Destino]],Tabela8[YTD])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{8CE33079-5ADD-0947-86CD-7B1800C9E6EA}" name="Coluna1" totalsRowFunction="sum" dataDxfId="57" totalsRowDxfId="59">
+    <tableColumn id="4" xr3:uid="{8CE33079-5ADD-0947-86CD-7B1800C9E6EA}" name="Coluna1" totalsRowFunction="sum" dataDxfId="51" totalsRowDxfId="50">
       <calculatedColumnFormula>Tabela10[[#This Row],[R$]]/6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{978E1586-9A15-0542-A0A8-B3B95763380A}" name="%" dataDxfId="110" totalsRowDxfId="58" dataCellStyle="Porcentagem" totalsRowCellStyle="Porcentagem">
+    <tableColumn id="3" xr3:uid="{978E1586-9A15-0542-A0A8-B3B95763380A}" name="%" dataDxfId="49" totalsRowDxfId="48" dataCellStyle="Porcentagem" totalsRowCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela10[[#This Row],[R$]]/Tabela10[[#Totals],[R$]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -27401,17 +27392,17 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{1C1D956F-F518-C445-920F-073B042398A2}" name="Tabela11" displayName="Tabela11" ref="AL14:AO20" totalsRowCount="1" headerRowDxfId="109" dataDxfId="108">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{1C1D956F-F518-C445-920F-073B042398A2}" name="Tabela11" displayName="Tabela11" ref="AL14:AO20" totalsRowCount="1" headerRowDxfId="47" dataDxfId="46">
   <autoFilter ref="AL14:AO19" xr:uid="{1C1D956F-F518-C445-920F-073B042398A2}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{26F479D7-9348-D944-8762-F8EED16FBF95}" name="Natureza" totalsRowLabel="Total" dataDxfId="107" totalsRowDxfId="71"/>
-    <tableColumn id="2" xr3:uid="{BA1F7373-0DFB-8E44-A34D-4C8DB653C8A5}" name="R$" totalsRowFunction="sum" dataDxfId="106" totalsRowDxfId="70">
+    <tableColumn id="1" xr3:uid="{26F479D7-9348-D944-8762-F8EED16FBF95}" name="Natureza" totalsRowLabel="Total" dataDxfId="45" totalsRowDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{BA1F7373-0DFB-8E44-A34D-4C8DB653C8A5}" name="R$" totalsRowFunction="sum" dataDxfId="43" totalsRowDxfId="42">
       <calculatedColumnFormula>SUMIF(Tabela8[Natureza],Tabela11[[#This Row],[Natureza]],Tabela8[YTD])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D40E5632-C648-BC41-B8EB-5F4ECF6E8EE4}" name="/6" totalsRowFunction="sum" dataDxfId="67" totalsRowDxfId="69">
+    <tableColumn id="4" xr3:uid="{D40E5632-C648-BC41-B8EB-5F4ECF6E8EE4}" name="/6" totalsRowFunction="sum" dataDxfId="41" totalsRowDxfId="40">
       <calculatedColumnFormula>Tabela11[[#This Row],[R$]]/6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{4354E7FD-81CA-7242-A391-C99FCBAABFB5}" name="%" dataDxfId="105" totalsRowDxfId="68" dataCellStyle="Porcentagem">
+    <tableColumn id="3" xr3:uid="{4354E7FD-81CA-7242-A391-C99FCBAABFB5}" name="%" dataDxfId="39" totalsRowDxfId="38" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela11[[#This Row],[R$]]/Tabela11[[#Totals],[R$]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -27420,17 +27411,17 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{B1E63430-37FC-4C43-9393-246F4A2208D6}" name="Tabela12" displayName="Tabela12" ref="AL26:AO34" totalsRowCount="1" headerRowDxfId="104" dataDxfId="103">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{B1E63430-37FC-4C43-9393-246F4A2208D6}" name="Tabela12" displayName="Tabela12" ref="AL26:AO34" totalsRowCount="1" headerRowDxfId="37" dataDxfId="36">
   <autoFilter ref="AL26:AO33" xr:uid="{B1E63430-37FC-4C43-9393-246F4A2208D6}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{34DA6249-C349-024A-9110-04604D3EDACE}" name="Utilidade" totalsRowLabel="Total" dataDxfId="102" totalsRowDxfId="66"/>
-    <tableColumn id="2" xr3:uid="{7AC05CA7-881C-7044-BA95-EC7091EC887E}" name="R$" totalsRowFunction="sum" dataDxfId="101" totalsRowDxfId="65">
+    <tableColumn id="1" xr3:uid="{34DA6249-C349-024A-9110-04604D3EDACE}" name="Utilidade" totalsRowLabel="Total" dataDxfId="35" totalsRowDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{7AC05CA7-881C-7044-BA95-EC7091EC887E}" name="R$" totalsRowFunction="sum" dataDxfId="33" totalsRowDxfId="32">
       <calculatedColumnFormula>SUMIF(Tabela8[Utilidade],Tabela12[[#This Row],[Utilidade]],Tabela8[YTD])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{36BEA06B-0562-1549-80D3-A17AA3418FA8}" name="/6" totalsRowFunction="sum" dataDxfId="62" totalsRowDxfId="64">
+    <tableColumn id="5" xr3:uid="{36BEA06B-0562-1549-80D3-A17AA3418FA8}" name="/6" totalsRowFunction="sum" dataDxfId="31" totalsRowDxfId="30">
       <calculatedColumnFormula>Tabela12[[#This Row],[R$]]/6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{42033DA4-4025-F847-B785-B892773950A8}" name="%" dataDxfId="100" totalsRowDxfId="63" dataCellStyle="Porcentagem">
+    <tableColumn id="3" xr3:uid="{42033DA4-4025-F847-B785-B892773950A8}" name="%" dataDxfId="29" totalsRowDxfId="28" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela12[[#This Row],[R$]]/Tabela12[[#Totals],[R$]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -29752,7 +29743,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="T6" s="406"/>
+      <c r="T6" s="4"/>
     </row>
     <row r="7" spans="6:20">
       <c r="F7" t="s">
@@ -31243,7 +31234,7 @@
         <v>0.65741692904096238</v>
       </c>
       <c r="AA30" s="3">
-        <f>SUMIF($G$15:$G$149,Y30,$J$15:$J$149)</f>
+        <f t="shared" ref="AA30:AA53" si="1">SUMIF($G$15:$G$149,Y30,$J$15:$J$149)</f>
         <v>1100212.1599999999</v>
       </c>
       <c r="AC30" s="130" t="s">
@@ -31302,11 +31293,11 @@
         <v>394</v>
       </c>
       <c r="Z31" s="19">
-        <f t="shared" ref="Z31:Z53" si="1">AA31/$J$150</f>
+        <f t="shared" ref="Z31:Z53" si="2">AA31/$J$150</f>
         <v>0.12497738921864404</v>
       </c>
       <c r="AA31" s="3">
-        <f>SUMIF($G$15:$G$149,Y31,$J$15:$J$149)</f>
+        <f t="shared" si="1"/>
         <v>209154.4</v>
       </c>
       <c r="AC31" s="130" t="s">
@@ -31365,11 +31356,11 @@
         <v>245</v>
       </c>
       <c r="Z32" s="19">
+        <f t="shared" si="2"/>
+        <v>5.4152415022660487E-2</v>
+      </c>
+      <c r="AA32" s="3">
         <f t="shared" si="1"/>
-        <v>5.4152415022660487E-2</v>
-      </c>
-      <c r="AA32" s="3">
-        <f>SUMIF($G$15:$G$149,Y32,$J$15:$J$149)</f>
         <v>90626.12</v>
       </c>
       <c r="AC32" s="130" t="s">
@@ -31428,11 +31419,11 @@
         <v>234</v>
       </c>
       <c r="Z33" s="19">
+        <f t="shared" si="2"/>
+        <v>4.0232843962089607E-2</v>
+      </c>
+      <c r="AA33" s="3">
         <f t="shared" si="1"/>
-        <v>4.0232843962089607E-2</v>
-      </c>
-      <c r="AA33" s="3">
-        <f>SUMIF($G$15:$G$149,Y33,$J$15:$J$149)</f>
         <v>67331.19</v>
       </c>
       <c r="AC33" s="130" t="str">
@@ -31498,15 +31489,15 @@
         <v>24</v>
       </c>
       <c r="Z34" s="19">
+        <f t="shared" si="2"/>
+        <v>3.1503797655209387E-2</v>
+      </c>
+      <c r="AA34" s="3">
         <f t="shared" si="1"/>
-        <v>3.1503797655209387E-2</v>
-      </c>
-      <c r="AA34" s="3">
-        <f>SUMIF($G$15:$G$149,Y34,$J$15:$J$149)</f>
         <v>52722.799999999996</v>
       </c>
       <c r="AC34" s="130" t="str">
-        <f t="shared" ref="AC34:AC35" si="2">Y35</f>
+        <f t="shared" ref="AC34:AC35" si="3">Y35</f>
         <v>Planejamento</v>
       </c>
       <c r="AD34" s="19">
@@ -31562,15 +31553,15 @@
         <v>236</v>
       </c>
       <c r="Z35" s="19">
+        <f t="shared" si="2"/>
+        <v>3.1424444807321719E-2</v>
+      </c>
+      <c r="AA35" s="3">
         <f t="shared" si="1"/>
-        <v>3.1424444807321719E-2</v>
-      </c>
-      <c r="AA35" s="3">
-        <f>SUMIF($G$15:$G$149,Y35,$J$15:$J$149)</f>
         <v>52590</v>
       </c>
       <c r="AC35" s="130" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Previdência</v>
       </c>
       <c r="AD35" s="19">
@@ -31626,11 +31617,11 @@
         <v>562</v>
       </c>
       <c r="Z36" s="19">
+        <f t="shared" si="2"/>
+        <v>1.583413180144732E-2</v>
+      </c>
+      <c r="AA36" s="3">
         <f t="shared" si="1"/>
-        <v>1.583413180144732E-2</v>
-      </c>
-      <c r="AA36" s="3">
-        <f>SUMIF($G$15:$G$149,Y36,$J$15:$J$149)</f>
         <v>26499.02</v>
       </c>
       <c r="AC36" s="130" t="s">
@@ -31689,11 +31680,11 @@
         <v>243</v>
       </c>
       <c r="Z37" s="19">
+        <f t="shared" si="2"/>
+        <v>1.282226697319174E-2</v>
+      </c>
+      <c r="AA37" s="3">
         <f t="shared" si="1"/>
-        <v>1.282226697319174E-2</v>
-      </c>
-      <c r="AA37" s="3">
-        <f>SUMIF($G$15:$G$149,Y37,$J$15:$J$149)</f>
         <v>21458.550000000003</v>
       </c>
       <c r="AD37" s="140"/>
@@ -31750,11 +31741,11 @@
         <v>324</v>
       </c>
       <c r="Z38" s="19">
+        <f t="shared" si="2"/>
+        <v>7.6925594849981049E-3</v>
+      </c>
+      <c r="AA38" s="3">
         <f t="shared" si="1"/>
-        <v>7.6925594849981049E-3</v>
-      </c>
-      <c r="AA38" s="3">
-        <f>SUMIF($G$15:$G$149,Y38,$J$15:$J$149)</f>
         <v>12873.79</v>
       </c>
       <c r="AD38" s="140"/>
@@ -31811,11 +31802,11 @@
         <v>252</v>
       </c>
       <c r="Z39" s="19">
+        <f t="shared" si="2"/>
+        <v>7.3204496017634313E-3</v>
+      </c>
+      <c r="AA39" s="3">
         <f t="shared" si="1"/>
-        <v>7.3204496017634313E-3</v>
-      </c>
-      <c r="AA39" s="3">
-        <f>SUMIF($G$15:$G$149,Y39,$J$15:$J$149)</f>
         <v>12251.050000000003</v>
       </c>
       <c r="AD39" s="140"/>
@@ -31872,11 +31863,11 @@
         <v>397</v>
       </c>
       <c r="Z40" s="19">
+        <f t="shared" si="2"/>
+        <v>5.8379973846066193E-3</v>
+      </c>
+      <c r="AA40" s="3">
         <f t="shared" si="1"/>
-        <v>5.8379973846066193E-3</v>
-      </c>
-      <c r="AA40" s="3">
-        <f>SUMIF($G$15:$G$149,Y40,$J$15:$J$149)</f>
         <v>9770.1100000000024</v>
       </c>
     </row>
@@ -31929,11 +31920,11 @@
         <v>259</v>
       </c>
       <c r="Z41" s="19">
+        <f t="shared" si="2"/>
+        <v>3.337725385989461E-3</v>
+      </c>
+      <c r="AA41" s="3">
         <f t="shared" si="1"/>
-        <v>3.337725385989461E-3</v>
-      </c>
-      <c r="AA41" s="3">
-        <f>SUMIF($G$15:$G$149,Y41,$J$15:$J$149)</f>
         <v>5585.81</v>
       </c>
       <c r="AH41" s="126"/>
@@ -31973,11 +31964,11 @@
         <v>271</v>
       </c>
       <c r="Z42" s="19">
+        <f t="shared" si="2"/>
+        <v>3.1256895571269753E-3</v>
+      </c>
+      <c r="AA42" s="3">
         <f t="shared" si="1"/>
-        <v>3.1256895571269753E-3</v>
-      </c>
-      <c r="AA42" s="3">
-        <f>SUMIF($G$15:$G$149,Y42,$J$15:$J$149)</f>
         <v>5230.96</v>
       </c>
       <c r="AH42" s="126"/>
@@ -32031,11 +32022,11 @@
         <v>239</v>
       </c>
       <c r="Z43" s="19">
+        <f t="shared" si="2"/>
+        <v>1.7477942776462452E-3</v>
+      </c>
+      <c r="AA43" s="3">
         <f t="shared" si="1"/>
-        <v>1.7477942776462452E-3</v>
-      </c>
-      <c r="AA43" s="3">
-        <f>SUMIF($G$15:$G$149,Y43,$J$15:$J$149)</f>
         <v>2925</v>
       </c>
       <c r="AH43" s="126"/>
@@ -32089,11 +32080,11 @@
         <v>719</v>
       </c>
       <c r="Z44" s="19">
+        <f t="shared" si="2"/>
+        <v>6.8722673460545176E-4</v>
+      </c>
+      <c r="AA44" s="3">
         <f t="shared" si="1"/>
-        <v>6.8722673460545176E-4</v>
-      </c>
-      <c r="AA44" s="3">
-        <f>SUMIF($G$15:$G$149,Y44,$J$15:$J$149)</f>
         <v>1150.0999999999999</v>
       </c>
       <c r="AD44" s="90"/>
@@ -32147,11 +32138,11 @@
         <v>257</v>
       </c>
       <c r="Z45" s="19">
+        <f t="shared" si="2"/>
+        <v>5.5566712226036679E-4</v>
+      </c>
+      <c r="AA45" s="3">
         <f t="shared" si="1"/>
-        <v>5.5566712226036679E-4</v>
-      </c>
-      <c r="AA45" s="3">
-        <f>SUMIF($G$15:$G$149,Y45,$J$15:$J$149)</f>
         <v>929.93000000000006</v>
       </c>
       <c r="AD45" s="141"/>
@@ -32205,11 +32196,11 @@
         <v>264</v>
       </c>
       <c r="Z46" s="19">
+        <f t="shared" si="2"/>
+        <v>4.4984938255835874E-4</v>
+      </c>
+      <c r="AA46" s="3">
         <f t="shared" si="1"/>
-        <v>4.4984938255835874E-4</v>
-      </c>
-      <c r="AA46" s="3">
-        <f>SUMIF($G$15:$G$149,Y46,$J$15:$J$149)</f>
         <v>752.84</v>
       </c>
       <c r="AD46" s="141"/>
@@ -32263,11 +32254,11 @@
         <v>262</v>
       </c>
       <c r="Z47" s="19">
+        <f t="shared" si="2"/>
+        <v>3.2102051204193802E-4</v>
+      </c>
+      <c r="AA47" s="3">
         <f t="shared" si="1"/>
-        <v>3.2102051204193802E-4</v>
-      </c>
-      <c r="AA47" s="3">
-        <f>SUMIF($G$15:$G$149,Y47,$J$15:$J$149)</f>
         <v>537.24</v>
       </c>
     </row>
@@ -32320,11 +32311,11 @@
         <v>326</v>
       </c>
       <c r="Z48" s="19">
+        <f t="shared" si="2"/>
+        <v>1.5632152511966982E-4</v>
+      </c>
+      <c r="AA48" s="3">
         <f t="shared" si="1"/>
-        <v>1.5632152511966982E-4</v>
-      </c>
-      <c r="AA48" s="3">
-        <f>SUMIF($G$15:$G$149,Y48,$J$15:$J$149)</f>
         <v>261.61</v>
       </c>
     </row>
@@ -32375,11 +32366,11 @@
         <v>722</v>
       </c>
       <c r="Z49" s="19">
+        <f t="shared" si="2"/>
+        <v>1.2995821451120749E-4</v>
+      </c>
+      <c r="AA49" s="3">
         <f t="shared" si="1"/>
-        <v>1.2995821451120749E-4</v>
-      </c>
-      <c r="AA49" s="3">
-        <f>SUMIF($G$15:$G$149,Y49,$J$15:$J$149)</f>
         <v>217.49</v>
       </c>
     </row>
@@ -32418,11 +32409,11 @@
         <v>269</v>
       </c>
       <c r="Z50" s="19">
+        <f t="shared" si="2"/>
+        <v>1.2989846086068965E-4</v>
+      </c>
+      <c r="AA50" s="3">
         <f t="shared" si="1"/>
-        <v>1.2989846086068965E-4</v>
-      </c>
-      <c r="AA50" s="3">
-        <f>SUMIF($G$15:$G$149,Y50,$J$15:$J$149)</f>
         <v>217.39000000000001</v>
       </c>
     </row>
@@ -32475,11 +32466,11 @@
         <v>267</v>
       </c>
       <c r="Z51" s="19">
+        <f t="shared" si="2"/>
+        <v>1.249628093279177E-4</v>
+      </c>
+      <c r="AA51" s="3">
         <f t="shared" si="1"/>
-        <v>1.249628093279177E-4</v>
-      </c>
-      <c r="AA51" s="3">
-        <f>SUMIF($G$15:$G$149,Y51,$J$15:$J$149)</f>
         <v>209.13</v>
       </c>
     </row>
@@ -32532,11 +32523,11 @@
         <v>273</v>
       </c>
       <c r="Z52" s="19">
+        <f t="shared" si="2"/>
+        <v>9.9549581762688697E-6</v>
+      </c>
+      <c r="AA52" s="3">
         <f t="shared" si="1"/>
-        <v>9.9549581762688697E-6</v>
-      </c>
-      <c r="AA52" s="3">
-        <f>SUMIF($G$15:$G$149,Y52,$J$15:$J$149)</f>
         <v>16.66</v>
       </c>
     </row>
@@ -32589,11 +32580,11 @@
         <v>444</v>
       </c>
       <c r="Z53" s="19">
+        <f t="shared" si="2"/>
+        <v>8.7061068804464244E-6</v>
+      </c>
+      <c r="AA53" s="3">
         <f t="shared" si="1"/>
-        <v>8.7061068804464244E-6</v>
-      </c>
-      <c r="AA53" s="3">
-        <f>SUMIF($G$15:$G$149,Y53,$J$15:$J$149)</f>
         <v>14.57</v>
       </c>
     </row>
@@ -36790,13 +36781,13 @@
       <c r="AF7" s="126"/>
     </row>
     <row r="10" spans="3:44">
-      <c r="AC10" s="397" t="s">
+      <c r="AC10" s="401" t="s">
         <v>299</v>
       </c>
       <c r="AD10" s="129"/>
     </row>
     <row r="11" spans="3:44">
-      <c r="AC11" s="397"/>
+      <c r="AC11" s="401"/>
       <c r="AD11" s="129"/>
     </row>
     <row r="12" spans="3:44" ht="15.75" customHeight="1"/>
@@ -37027,7 +37018,7 @@
         <v>0</v>
       </c>
       <c r="AE15" s="5">
-        <f>SUMIF($G$15:$G$131,AC15,$N$15:$N$131)</f>
+        <f t="shared" ref="AE15:AE34" si="0">SUMIF($G$15:$G$131,AC15,$N$15:$N$131)</f>
         <v>0</v>
       </c>
       <c r="AF15" s="132"/>
@@ -37123,7 +37114,7 @@
         <v>0</v>
       </c>
       <c r="AE16" s="5">
-        <f>SUMIF($G$15:$G$131,AC16,$N$15:$N$131)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AF16" s="126"/>
@@ -37223,7 +37214,7 @@
         <v>0</v>
       </c>
       <c r="AE17" s="5">
-        <f>SUMIF($G$15:$G$131,AC17,$N$15:$N$131)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AF17" s="126"/>
@@ -37319,7 +37310,7 @@
         <v>0</v>
       </c>
       <c r="AE18" s="5">
-        <f>SUMIF($G$15:$G$131,AC18,$N$15:$N$131)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AF18" s="126"/>
@@ -37419,7 +37410,7 @@
         <v>0</v>
       </c>
       <c r="AE19" s="5">
-        <f>SUMIF($G$15:$G$131,AC19,$N$15:$N$131)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AF19" s="126"/>
@@ -37519,7 +37510,7 @@
         <v>0</v>
       </c>
       <c r="AE20" s="5">
-        <f>SUMIF($G$15:$G$131,AC20,$N$15:$N$131)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AF20" s="126"/>
@@ -37615,7 +37606,7 @@
         <v>0</v>
       </c>
       <c r="AE21" s="5">
-        <f>SUMIF($G$15:$G$131,AC21,$N$15:$N$131)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AF21" s="126"/>
@@ -37702,7 +37693,7 @@
         <v>0</v>
       </c>
       <c r="AE22" s="5">
-        <f>SUMIF($G$15:$G$131,AC22,$N$15:$N$131)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AF22" s="126"/>
@@ -37785,7 +37776,7 @@
         <v>2.8909895300645929E-6</v>
       </c>
       <c r="AE23" s="5">
-        <f>SUMIF($G$15:$G$131,AC23,$N$15:$N$131)</f>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="AF23" s="126"/>
@@ -37872,7 +37863,7 @@
         <v>3.0246255210918285E-3</v>
       </c>
       <c r="AE24" s="5">
-        <f>SUMIF($G$15:$G$131,AC24,$N$15:$N$131)</f>
+        <f t="shared" si="0"/>
         <v>836.98</v>
       </c>
       <c r="AF24" s="126"/>
@@ -37959,7 +37950,7 @@
         <v>4.6380506404517519E-3</v>
       </c>
       <c r="AE25" s="5">
-        <f>SUMIF($G$15:$G$131,AC25,$N$15:$N$131)</f>
+        <f t="shared" si="0"/>
         <v>1283.45</v>
       </c>
       <c r="AF25" s="126"/>
@@ -38046,7 +38037,7 @@
         <v>1.1990053839620766E-2</v>
       </c>
       <c r="AE26" s="5">
-        <f>SUMIF($G$15:$G$131,AC26,$N$15:$N$131)</f>
+        <f t="shared" si="0"/>
         <v>3317.91</v>
       </c>
       <c r="AF26" s="126"/>
@@ -38141,7 +38132,7 @@
         <v>2.4113382296577508E-2</v>
       </c>
       <c r="AE27" s="5">
-        <f>SUMIF($G$15:$G$131,AC27,$N$15:$N$131)</f>
+        <f t="shared" si="0"/>
         <v>6672.6999999999989</v>
       </c>
       <c r="AG27" s="125" t="s">
@@ -38240,7 +38231,7 @@
         <v>4.1196094880252679E-2</v>
       </c>
       <c r="AE28" s="5">
-        <f>SUMIF($G$15:$G$131,AC28,$N$15:$N$131)</f>
+        <f t="shared" si="0"/>
         <v>11399.859999999999</v>
       </c>
       <c r="AG28" s="125" t="s">
@@ -38339,7 +38330,7 @@
         <v>8.0052981719622732E-2</v>
       </c>
       <c r="AE29" s="5">
-        <f>SUMIF($G$15:$G$131,AC29,$N$15:$N$131)</f>
+        <f t="shared" si="0"/>
         <v>22152.41</v>
       </c>
       <c r="AF29" s="111"/>
@@ -38439,7 +38430,7 @@
         <v>0.19201797068001783</v>
       </c>
       <c r="AE30" s="5">
-        <f>SUMIF($G$15:$G$131,AC30,$N$15:$N$131)</f>
+        <f t="shared" si="0"/>
         <v>53135.57</v>
       </c>
       <c r="AG30" s="125" t="s">
@@ -38538,7 +38529,7 @@
         <v>0.55070528219201764</v>
       </c>
       <c r="AE31" s="5">
-        <f>SUMIF($G$15:$G$131,AC31,$N$15:$N$131)</f>
+        <f t="shared" si="0"/>
         <v>152392.19</v>
       </c>
       <c r="AG31" s="125" t="s">
@@ -38637,7 +38628,7 @@
         <v>0.64186168739975946</v>
       </c>
       <c r="AE32" s="5">
-        <f>SUMIF($G$15:$G$131,AC32,$N$15:$N$131)</f>
+        <f t="shared" si="0"/>
         <v>177617.16</v>
       </c>
       <c r="AG32" s="125" t="s">
@@ -38736,7 +38727,7 @@
         <v>1</v>
       </c>
       <c r="AE33" s="5">
-        <f>SUMIF($G$15:$G$131,AC33,$N$15:$N$131)</f>
+        <f t="shared" si="0"/>
         <v>276721.86</v>
       </c>
       <c r="AG33" s="125" t="s">
@@ -38835,7 +38826,7 @@
         <v>2.1964133588867902</v>
       </c>
       <c r="AE34" s="5">
-        <f>SUMIF($G$15:$G$131,AC34,$N$15:$N$131)</f>
+        <f t="shared" si="0"/>
         <v>607795.59000000008</v>
       </c>
       <c r="AG34" s="125" t="s">
@@ -45520,12 +45511,12 @@
   </cols>
   <sheetData>
     <row r="4" spans="5:8">
-      <c r="E4" s="398" t="s">
+      <c r="E4" s="402" t="s">
         <v>584</v>
       </c>
-      <c r="F4" s="398"/>
-      <c r="G4" s="398"/>
-      <c r="H4" s="398"/>
+      <c r="F4" s="402"/>
+      <c r="G4" s="402"/>
+      <c r="H4" s="402"/>
     </row>
     <row r="6" spans="5:8">
       <c r="E6" s="266" t="s">
@@ -45725,48 +45716,45 @@
       <c r="E27" s="4"/>
     </row>
     <row r="28" spans="5:8">
-      <c r="E28" s="407" t="s">
+      <c r="E28" s="377" t="s">
         <v>572</v>
       </c>
-      <c r="F28" s="408"/>
-      <c r="G28" s="409">
+      <c r="F28" s="378"/>
+      <c r="G28" s="379">
         <f>SUM(G29:G32)</f>
         <v>484.9</v>
       </c>
-      <c r="H28" s="410">
+      <c r="H28" s="380">
         <f>G28/$G$34</f>
         <v>5.810031500459506E-2</v>
       </c>
     </row>
     <row r="29" spans="5:8">
-      <c r="E29" s="411"/>
-      <c r="F29" s="412" t="s">
+      <c r="E29" s="4"/>
+      <c r="F29" t="s">
         <v>728</v>
       </c>
-      <c r="G29" s="413">
+      <c r="G29" s="192">
         <v>289.89999999999998</v>
       </c>
-      <c r="H29" s="412"/>
     </row>
     <row r="30" spans="5:8">
-      <c r="E30" s="411"/>
-      <c r="F30" s="412" t="s">
+      <c r="E30" s="4"/>
+      <c r="F30" t="s">
         <v>729</v>
       </c>
-      <c r="G30" s="413">
+      <c r="G30" s="192">
         <v>100</v>
       </c>
-      <c r="H30" s="412"/>
     </row>
     <row r="31" spans="5:8">
-      <c r="E31" s="411"/>
-      <c r="F31" s="414" t="s">
+      <c r="E31" s="4"/>
+      <c r="F31" t="s">
         <v>583</v>
       </c>
-      <c r="G31" s="413">
+      <c r="G31" s="192">
         <v>95</v>
       </c>
-      <c r="H31" s="412"/>
     </row>
     <row r="32" spans="5:8">
       <c r="E32" s="265"/>
@@ -45793,10 +45781,10 @@
     </row>
     <row r="35" spans="5:8" ht="16" thickTop="1"/>
     <row r="37" spans="5:8">
-      <c r="E37" s="399" t="s">
+      <c r="E37" s="403" t="s">
         <v>587</v>
       </c>
-      <c r="F37" s="399"/>
+      <c r="F37" s="403"/>
       <c r="G37" s="275">
         <f>H7+H8+H11+H12+H13+H14+H15+H16+H19+H23+H32+H26</f>
         <v>-800</v>
@@ -45807,10 +45795,10 @@
       </c>
     </row>
     <row r="38" spans="5:8" ht="16" thickBot="1">
-      <c r="E38" s="400" t="s">
+      <c r="E38" s="404" t="s">
         <v>588</v>
       </c>
-      <c r="F38" s="400"/>
+      <c r="F38" s="404"/>
       <c r="G38" s="276">
         <f>G34+G37</f>
         <v>7545.91</v>
@@ -48942,17 +48930,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1">
-      <c r="A1" s="402" t="s">
+      <c r="A1" s="405" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="402"/>
-      <c r="C1" s="402"/>
-      <c r="D1" s="402"/>
-      <c r="E1" s="402"/>
-      <c r="F1" s="402"/>
-      <c r="G1" s="402"/>
-      <c r="H1" s="402"/>
-      <c r="I1" s="402"/>
+      <c r="B1" s="405"/>
+      <c r="C1" s="405"/>
+      <c r="D1" s="405"/>
+      <c r="E1" s="405"/>
+      <c r="F1" s="405"/>
+      <c r="G1" s="405"/>
+      <c r="H1" s="405"/>
+      <c r="I1" s="405"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1">
       <c r="A2" s="114"/>
@@ -48980,7 +48968,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="15" customHeight="1">
-      <c r="A3" s="401" t="s">
+      <c r="A3" s="406" t="s">
         <v>197</v>
       </c>
       <c r="B3" s="116" t="s">
@@ -49002,7 +48990,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1">
-      <c r="A4" s="401"/>
+      <c r="A4" s="406"/>
       <c r="B4" s="116" t="s">
         <v>199</v>
       </c>
@@ -49021,7 +49009,7 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1">
-      <c r="A5" s="401"/>
+      <c r="A5" s="406"/>
       <c r="B5" s="116" t="s">
         <v>200</v>
       </c>
@@ -49039,7 +49027,7 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="15" customHeight="1">
-      <c r="A6" s="401"/>
+      <c r="A6" s="406"/>
       <c r="B6" s="116" t="s">
         <v>201</v>
       </c>
@@ -49057,7 +49045,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1">
-      <c r="A7" s="401"/>
+      <c r="A7" s="406"/>
       <c r="B7" s="116" t="s">
         <v>25</v>
       </c>
@@ -49075,7 +49063,7 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1">
-      <c r="A8" s="401" t="s">
+      <c r="A8" s="406" t="s">
         <v>202</v>
       </c>
       <c r="B8" s="116" t="s">
@@ -49099,7 +49087,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1">
-      <c r="A9" s="401"/>
+      <c r="A9" s="406"/>
       <c r="B9" s="116" t="s">
         <v>199</v>
       </c>
@@ -49117,7 +49105,7 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1">
-      <c r="A10" s="401"/>
+      <c r="A10" s="406"/>
       <c r="B10" s="116" t="s">
         <v>200</v>
       </c>
@@ -49135,7 +49123,7 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1">
-      <c r="A11" s="401"/>
+      <c r="A11" s="406"/>
       <c r="B11" s="116" t="s">
         <v>201</v>
       </c>
@@ -49153,7 +49141,7 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1">
-      <c r="A12" s="401"/>
+      <c r="A12" s="406"/>
       <c r="B12" s="116" t="s">
         <v>25</v>
       </c>
@@ -49171,7 +49159,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1">
-      <c r="A13" s="401" t="s">
+      <c r="A13" s="406" t="s">
         <v>203</v>
       </c>
       <c r="B13" s="116" t="s">
@@ -49195,7 +49183,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1">
-      <c r="A14" s="401"/>
+      <c r="A14" s="406"/>
       <c r="B14" s="116" t="s">
         <v>199</v>
       </c>
@@ -49215,7 +49203,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1">
-      <c r="A15" s="401"/>
+      <c r="A15" s="406"/>
       <c r="B15" s="116" t="s">
         <v>200</v>
       </c>
@@ -49233,7 +49221,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1">
-      <c r="A16" s="401"/>
+      <c r="A16" s="406"/>
       <c r="B16" s="116" t="s">
         <v>201</v>
       </c>
@@ -49251,7 +49239,7 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
-      <c r="A17" s="401"/>
+      <c r="A17" s="406"/>
       <c r="B17" s="116" t="s">
         <v>25</v>
       </c>
@@ -49269,7 +49257,7 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1">
-      <c r="A18" s="401" t="s">
+      <c r="A18" s="406" t="s">
         <v>190</v>
       </c>
       <c r="B18" s="116" t="s">
@@ -49295,7 +49283,7 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1">
-      <c r="A19" s="401"/>
+      <c r="A19" s="406"/>
       <c r="B19" s="116" t="s">
         <v>199</v>
       </c>
@@ -49315,7 +49303,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1">
-      <c r="A20" s="401"/>
+      <c r="A20" s="406"/>
       <c r="B20" s="116" t="s">
         <v>200</v>
       </c>
@@ -49333,7 +49321,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1">
-      <c r="A21" s="401"/>
+      <c r="A21" s="406"/>
       <c r="B21" s="116" t="s">
         <v>201</v>
       </c>
@@ -49351,7 +49339,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="15" customHeight="1">
-      <c r="A22" s="401"/>
+      <c r="A22" s="406"/>
       <c r="B22" s="116" t="s">
         <v>25</v>
       </c>
@@ -49369,7 +49357,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1">
-      <c r="A23" s="401" t="s">
+      <c r="A23" s="406" t="s">
         <v>204</v>
       </c>
       <c r="B23" s="116" t="s">
@@ -49395,7 +49383,7 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1">
-      <c r="A24" s="401"/>
+      <c r="A24" s="406"/>
       <c r="B24" s="116" t="s">
         <v>199</v>
       </c>
@@ -49417,7 +49405,7 @@
       </c>
     </row>
     <row r="25" spans="1:9" ht="15" customHeight="1">
-      <c r="A25" s="401"/>
+      <c r="A25" s="406"/>
       <c r="B25" s="116" t="s">
         <v>200</v>
       </c>
@@ -49437,7 +49425,7 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="15" customHeight="1">
-      <c r="A26" s="401"/>
+      <c r="A26" s="406"/>
       <c r="B26" s="116" t="s">
         <v>201</v>
       </c>
@@ -49455,7 +49443,7 @@
       </c>
     </row>
     <row r="27" spans="1:9" ht="15" customHeight="1">
-      <c r="A27" s="401"/>
+      <c r="A27" s="406"/>
       <c r="B27" s="116" t="s">
         <v>25</v>
       </c>
@@ -49473,7 +49461,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" ht="15" customHeight="1">
-      <c r="A28" s="401" t="s">
+      <c r="A28" s="406" t="s">
         <v>205</v>
       </c>
       <c r="B28" s="116" t="s">
@@ -49499,7 +49487,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="15" customHeight="1">
-      <c r="A29" s="401"/>
+      <c r="A29" s="406"/>
       <c r="B29" s="116" t="s">
         <v>199</v>
       </c>
@@ -49521,7 +49509,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" ht="15" customHeight="1">
-      <c r="A30" s="401"/>
+      <c r="A30" s="406"/>
       <c r="B30" s="116" t="s">
         <v>200</v>
       </c>
@@ -49541,7 +49529,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="15" customHeight="1">
-      <c r="A31" s="401"/>
+      <c r="A31" s="406"/>
       <c r="B31" s="116" t="s">
         <v>201</v>
       </c>
@@ -49559,7 +49547,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" ht="15" customHeight="1">
-      <c r="A32" s="401"/>
+      <c r="A32" s="406"/>
       <c r="B32" s="116" t="s">
         <v>25</v>
       </c>
@@ -49577,7 +49565,7 @@
       </c>
     </row>
     <row r="33" spans="1:9" ht="15" customHeight="1">
-      <c r="A33" s="401" t="s">
+      <c r="A33" s="406" t="s">
         <v>206</v>
       </c>
       <c r="B33" s="116" t="s">
@@ -49603,7 +49591,7 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="15" customHeight="1">
-      <c r="A34" s="401"/>
+      <c r="A34" s="406"/>
       <c r="B34" s="116" t="s">
         <v>199</v>
       </c>
@@ -49625,7 +49613,7 @@
       </c>
     </row>
     <row r="35" spans="1:9" ht="15" customHeight="1">
-      <c r="A35" s="401"/>
+      <c r="A35" s="406"/>
       <c r="B35" s="116" t="s">
         <v>200</v>
       </c>
@@ -49645,7 +49633,7 @@
       </c>
     </row>
     <row r="36" spans="1:9" ht="15" customHeight="1">
-      <c r="A36" s="401"/>
+      <c r="A36" s="406"/>
       <c r="B36" s="116" t="s">
         <v>201</v>
       </c>
@@ -49663,7 +49651,7 @@
       </c>
     </row>
     <row r="37" spans="1:9" ht="15" customHeight="1">
-      <c r="A37" s="401"/>
+      <c r="A37" s="406"/>
       <c r="B37" s="116" t="s">
         <v>25</v>
       </c>
@@ -49681,7 +49669,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" ht="15" customHeight="1">
-      <c r="A38" s="401" t="s">
+      <c r="A38" s="406" t="s">
         <v>207</v>
       </c>
       <c r="B38" s="116" t="s">
@@ -49709,7 +49697,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" ht="15" customHeight="1">
-      <c r="A39" s="401"/>
+      <c r="A39" s="406"/>
       <c r="B39" s="116" t="s">
         <v>199</v>
       </c>
@@ -49733,7 +49721,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="15" customHeight="1">
-      <c r="A40" s="401"/>
+      <c r="A40" s="406"/>
       <c r="B40" s="116" t="s">
         <v>200</v>
       </c>
@@ -49755,7 +49743,7 @@
       </c>
     </row>
     <row r="41" spans="1:9" ht="15" customHeight="1">
-      <c r="A41" s="401"/>
+      <c r="A41" s="406"/>
       <c r="B41" s="116" t="s">
         <v>201</v>
       </c>
@@ -49773,7 +49761,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1">
-      <c r="A42" s="401"/>
+      <c r="A42" s="406"/>
       <c r="B42" s="116" t="s">
         <v>25</v>
       </c>
@@ -49791,7 +49779,7 @@
       </c>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1">
-      <c r="A43" s="401" t="s">
+      <c r="A43" s="406" t="s">
         <v>208</v>
       </c>
       <c r="B43" s="116" t="s">
@@ -49819,7 +49807,7 @@
       </c>
     </row>
     <row r="44" spans="1:9" ht="15" customHeight="1">
-      <c r="A44" s="401"/>
+      <c r="A44" s="406"/>
       <c r="B44" s="116" t="s">
         <v>199</v>
       </c>
@@ -49844,7 +49832,7 @@
       </c>
     </row>
     <row r="45" spans="1:9" ht="15" customHeight="1">
-      <c r="A45" s="401"/>
+      <c r="A45" s="406"/>
       <c r="B45" s="116" t="s">
         <v>200</v>
       </c>
@@ -49866,7 +49854,7 @@
       </c>
     </row>
     <row r="46" spans="1:9" ht="15" customHeight="1">
-      <c r="A46" s="401"/>
+      <c r="A46" s="406"/>
       <c r="B46" s="116" t="s">
         <v>201</v>
       </c>
@@ -49888,7 +49876,7 @@
       </c>
     </row>
     <row r="47" spans="1:9" ht="15" customHeight="1">
-      <c r="A47" s="401"/>
+      <c r="A47" s="406"/>
       <c r="B47" s="116" t="s">
         <v>25</v>
       </c>
@@ -49906,7 +49894,7 @@
       </c>
     </row>
     <row r="48" spans="1:9" ht="15" customHeight="1">
-      <c r="A48" s="401" t="s">
+      <c r="A48" s="406" t="s">
         <v>209</v>
       </c>
       <c r="B48" s="116" t="s">
@@ -49934,7 +49922,7 @@
       </c>
     </row>
     <row r="49" spans="1:9" ht="15" customHeight="1">
-      <c r="A49" s="401"/>
+      <c r="A49" s="406"/>
       <c r="B49" s="116" t="s">
         <v>199</v>
       </c>
@@ -49958,7 +49946,7 @@
       </c>
     </row>
     <row r="50" spans="1:9" ht="15" customHeight="1">
-      <c r="A50" s="401"/>
+      <c r="A50" s="406"/>
       <c r="B50" s="116" t="s">
         <v>200</v>
       </c>
@@ -49980,7 +49968,7 @@
       </c>
     </row>
     <row r="51" spans="1:9" ht="15" customHeight="1">
-      <c r="A51" s="401"/>
+      <c r="A51" s="406"/>
       <c r="B51" s="116" t="s">
         <v>201</v>
       </c>
@@ -50002,7 +49990,7 @@
       </c>
     </row>
     <row r="52" spans="1:9" ht="15" customHeight="1">
-      <c r="A52" s="401"/>
+      <c r="A52" s="406"/>
       <c r="B52" s="116" t="s">
         <v>25</v>
       </c>
@@ -50020,7 +50008,7 @@
       </c>
     </row>
     <row r="53" spans="1:9" ht="15" customHeight="1">
-      <c r="A53" s="401" t="s">
+      <c r="A53" s="406" t="s">
         <v>210</v>
       </c>
       <c r="B53" s="116" t="s">
@@ -50051,7 +50039,7 @@
       </c>
     </row>
     <row r="54" spans="1:9" ht="15" customHeight="1">
-      <c r="A54" s="401"/>
+      <c r="A54" s="406"/>
       <c r="B54" s="116" t="s">
         <v>199</v>
       </c>
@@ -50077,7 +50065,7 @@
       </c>
     </row>
     <row r="55" spans="1:9" ht="15" customHeight="1">
-      <c r="A55" s="401"/>
+      <c r="A55" s="406"/>
       <c r="B55" s="116" t="s">
         <v>200</v>
       </c>
@@ -50101,7 +50089,7 @@
       </c>
     </row>
     <row r="56" spans="1:9" ht="15" customHeight="1">
-      <c r="A56" s="401"/>
+      <c r="A56" s="406"/>
       <c r="B56" s="116" t="s">
         <v>201</v>
       </c>
@@ -50125,7 +50113,7 @@
       </c>
     </row>
     <row r="57" spans="1:9" ht="15" customHeight="1">
-      <c r="A57" s="401"/>
+      <c r="A57" s="406"/>
       <c r="B57" s="116" t="s">
         <v>25</v>
       </c>
@@ -50243,11 +50231,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="A8:A12"/>
-    <mergeCell ref="A13:A17"/>
-    <mergeCell ref="A18:A22"/>
     <mergeCell ref="A48:A52"/>
     <mergeCell ref="A53:A57"/>
     <mergeCell ref="A23:A27"/>
@@ -50255,6 +50238,11 @@
     <mergeCell ref="A33:A37"/>
     <mergeCell ref="A38:A42"/>
     <mergeCell ref="A43:A47"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="A18:A22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -50272,15 +50260,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.75" customHeight="1">
-      <c r="A1" s="403" t="s">
+      <c r="A1" s="407" t="s">
         <v>694</v>
       </c>
-      <c r="B1" s="403"/>
-      <c r="C1" s="403"/>
-      <c r="D1" s="403"/>
-      <c r="E1" s="403"/>
-      <c r="F1" s="403"/>
-      <c r="G1" s="403"/>
+      <c r="B1" s="407"/>
+      <c r="C1" s="407"/>
+      <c r="D1" s="407"/>
+      <c r="E1" s="407"/>
+      <c r="F1" s="407"/>
+      <c r="G1" s="407"/>
       <c r="I1" s="369">
         <f ca="1">TODAY()</f>
         <v>46216</v>
@@ -50291,11 +50279,11 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="21.75" customHeight="1">
-      <c r="A3" s="404" t="s">
+      <c r="A3" s="408" t="s">
         <v>695</v>
       </c>
-      <c r="B3" s="404"/>
-      <c r="C3" s="404"/>
+      <c r="B3" s="408"/>
+      <c r="C3" s="408"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
       <c r="A4" s="353" t="s">
@@ -50340,15 +50328,15 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="21.75" customHeight="1">
-      <c r="A10" s="404" t="s">
+      <c r="A10" s="408" t="s">
         <v>699</v>
       </c>
-      <c r="B10" s="404"/>
-      <c r="C10" s="404"/>
-      <c r="D10" s="404"/>
-      <c r="E10" s="404"/>
-      <c r="F10" s="404"/>
-      <c r="G10" s="404"/>
+      <c r="B10" s="408"/>
+      <c r="C10" s="408"/>
+      <c r="D10" s="408"/>
+      <c r="E10" s="408"/>
+      <c r="F10" s="408"/>
+      <c r="G10" s="408"/>
     </row>
     <row r="11" spans="1:10" ht="19.5" customHeight="1">
       <c r="A11" s="356" t="s">
@@ -50494,15 +50482,15 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A18" s="405" t="s">
+      <c r="A18" s="409" t="s">
         <v>713</v>
       </c>
-      <c r="B18" s="405"/>
-      <c r="C18" s="405"/>
-      <c r="D18" s="405"/>
-      <c r="E18" s="405"/>
-      <c r="F18" s="405"/>
-      <c r="G18" s="405"/>
+      <c r="B18" s="409"/>
+      <c r="C18" s="409"/>
+      <c r="D18" s="409"/>
+      <c r="E18" s="409"/>
+      <c r="F18" s="409"/>
+      <c r="G18" s="409"/>
     </row>
     <row r="19" spans="1:7" ht="28" customHeight="1">
       <c r="A19" s="360" t="s">
@@ -56905,10 +56893,10 @@
         <v>131</v>
       </c>
       <c r="E42" s="91"/>
-      <c r="F42" s="377" t="s">
+      <c r="F42" s="381" t="s">
         <v>132</v>
       </c>
-      <c r="G42" s="377"/>
+      <c r="G42" s="381"/>
       <c r="H42" s="92">
         <f>SUM(H43:H57)</f>
         <v>30000</v>
@@ -57177,11 +57165,11 @@
       <c r="Q60" s="90"/>
     </row>
     <row r="61" spans="4:23" ht="15" customHeight="1" outlineLevel="1">
-      <c r="D61" s="377" t="s">
+      <c r="D61" s="381" t="s">
         <v>149</v>
       </c>
-      <c r="E61" s="377"/>
-      <c r="F61" s="377"/>
+      <c r="E61" s="381"/>
+      <c r="F61" s="381"/>
       <c r="G61" s="94">
         <f>I6</f>
         <v>358806.95999999996</v>
@@ -57597,63 +57585,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:22" ht="27.75" customHeight="1">
-      <c r="B1" s="383" t="s">
+      <c r="B1" s="386" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="383"/>
-      <c r="D1" s="383"/>
-      <c r="E1" s="383"/>
-      <c r="F1" s="383"/>
-      <c r="G1" s="383"/>
-      <c r="H1" s="383"/>
-      <c r="I1" s="383"/>
-      <c r="J1" s="383"/>
-      <c r="K1" s="383"/>
-      <c r="L1" s="383"/>
-      <c r="M1" s="383"/>
-      <c r="N1" s="383"/>
-      <c r="O1" s="383"/>
+      <c r="C1" s="386"/>
+      <c r="D1" s="386"/>
+      <c r="E1" s="386"/>
+      <c r="F1" s="386"/>
+      <c r="G1" s="386"/>
+      <c r="H1" s="386"/>
+      <c r="I1" s="386"/>
+      <c r="J1" s="386"/>
+      <c r="K1" s="386"/>
+      <c r="L1" s="386"/>
+      <c r="M1" s="386"/>
+      <c r="N1" s="386"/>
+      <c r="O1" s="386"/>
       <c r="Q1" s="176"/>
     </row>
     <row r="2" spans="2:22">
-      <c r="B2" s="384" t="s">
+      <c r="B2" s="387" t="s">
         <v>557</v>
       </c>
-      <c r="C2" s="384"/>
-      <c r="D2" s="384"/>
-      <c r="E2" s="384"/>
-      <c r="F2" s="384"/>
-      <c r="G2" s="384"/>
-      <c r="H2" s="384"/>
-      <c r="I2" s="384"/>
-      <c r="J2" s="384"/>
-      <c r="K2" s="384"/>
-      <c r="L2" s="384"/>
-      <c r="M2" s="384"/>
-      <c r="N2" s="384"/>
-      <c r="O2" s="384"/>
+      <c r="C2" s="387"/>
+      <c r="D2" s="387"/>
+      <c r="E2" s="387"/>
+      <c r="F2" s="387"/>
+      <c r="G2" s="387"/>
+      <c r="H2" s="387"/>
+      <c r="I2" s="387"/>
+      <c r="J2" s="387"/>
+      <c r="K2" s="387"/>
+      <c r="L2" s="387"/>
+      <c r="M2" s="387"/>
+      <c r="N2" s="387"/>
+      <c r="O2" s="387"/>
       <c r="Q2" s="176"/>
     </row>
     <row r="3" spans="2:22">
       <c r="Q3" s="176"/>
     </row>
     <row r="4" spans="2:22" ht="18" customHeight="1">
-      <c r="B4" s="380" t="s">
+      <c r="B4" s="385" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="380"/>
-      <c r="D4" s="380"/>
-      <c r="E4" s="380"/>
-      <c r="F4" s="380"/>
-      <c r="G4" s="380"/>
-      <c r="H4" s="380"/>
-      <c r="I4" s="380"/>
-      <c r="J4" s="380"/>
-      <c r="K4" s="380"/>
-      <c r="L4" s="380"/>
-      <c r="M4" s="380"/>
-      <c r="N4" s="380"/>
-      <c r="O4" s="380"/>
+      <c r="C4" s="385"/>
+      <c r="D4" s="385"/>
+      <c r="E4" s="385"/>
+      <c r="F4" s="385"/>
+      <c r="G4" s="385"/>
+      <c r="H4" s="385"/>
+      <c r="I4" s="385"/>
+      <c r="J4" s="385"/>
+      <c r="K4" s="385"/>
+      <c r="L4" s="385"/>
+      <c r="M4" s="385"/>
+      <c r="N4" s="385"/>
+      <c r="O4" s="385"/>
       <c r="Q4" s="176"/>
     </row>
     <row r="5" spans="2:22" ht="15.75" customHeight="1">
@@ -57664,12 +57652,12 @@
         <f>J6</f>
         <v>280000000</v>
       </c>
-      <c r="D5" s="379" t="s">
+      <c r="D5" s="389" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="379"/>
-      <c r="F5" s="379"/>
-      <c r="G5" s="379"/>
+      <c r="E5" s="389"/>
+      <c r="F5" s="389"/>
+      <c r="G5" s="389"/>
       <c r="I5" s="158" t="s">
         <v>215</v>
       </c>
@@ -57706,12 +57694,12 @@
         <f>(1+L5)^(1/12)-1</f>
         <v>9.0536953684483557E-4</v>
       </c>
-      <c r="D6" s="378" t="s">
+      <c r="D6" s="390" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="378"/>
-      <c r="F6" s="378"/>
-      <c r="G6" s="378"/>
+      <c r="E6" s="390"/>
+      <c r="F6" s="390"/>
+      <c r="G6" s="390"/>
       <c r="I6" s="160" t="s">
         <v>132</v>
       </c>
@@ -57748,12 +57736,12 @@
       <c r="C7" s="23">
         <v>5.5E-2</v>
       </c>
-      <c r="D7" s="379" t="s">
+      <c r="D7" s="389" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="379"/>
-      <c r="F7" s="379"/>
-      <c r="G7" s="379"/>
+      <c r="E7" s="389"/>
+      <c r="F7" s="389"/>
+      <c r="G7" s="389"/>
       <c r="I7" s="160" t="s">
         <v>216</v>
       </c>
@@ -57780,12 +57768,12 @@
         <f>(1+C7)^(1/12)-1</f>
         <v>4.471698917043021E-3</v>
       </c>
-      <c r="D8" s="378" t="s">
+      <c r="D8" s="390" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="378"/>
-      <c r="F8" s="378"/>
-      <c r="G8" s="378"/>
+      <c r="E8" s="390"/>
+      <c r="F8" s="390"/>
+      <c r="G8" s="390"/>
       <c r="I8" s="162" t="s">
         <v>217</v>
       </c>
@@ -57837,14 +57825,14 @@
       <c r="C10" s="147">
         <v>-0.14000000000000001</v>
       </c>
-      <c r="D10" s="378"/>
-      <c r="E10" s="378"/>
-      <c r="F10" s="378"/>
-      <c r="G10" s="378"/>
-      <c r="I10" s="385" t="s">
+      <c r="D10" s="390"/>
+      <c r="E10" s="390"/>
+      <c r="F10" s="390"/>
+      <c r="G10" s="390"/>
+      <c r="I10" s="388" t="s">
         <v>381</v>
       </c>
-      <c r="J10" s="385"/>
+      <c r="J10" s="388"/>
       <c r="Q10" s="176"/>
       <c r="S10" s="172" t="s">
         <v>375</v>
@@ -57867,10 +57855,10 @@
       <c r="C11" s="147">
         <v>-0.43</v>
       </c>
-      <c r="D11" s="378"/>
-      <c r="E11" s="378"/>
-      <c r="F11" s="378"/>
-      <c r="G11" s="378"/>
+      <c r="D11" s="390"/>
+      <c r="E11" s="390"/>
+      <c r="F11" s="390"/>
+      <c r="G11" s="390"/>
       <c r="I11" s="20" t="s">
         <v>382</v>
       </c>
@@ -57902,12 +57890,12 @@
         <f>AVERAGE(Consolidated!E24:H24)</f>
         <v>-1257.6075000000001</v>
       </c>
-      <c r="D12" s="378" t="s">
+      <c r="D12" s="390" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="378"/>
-      <c r="F12" s="378"/>
-      <c r="G12" s="378"/>
+      <c r="E12" s="390"/>
+      <c r="F12" s="390"/>
+      <c r="G12" s="390"/>
       <c r="I12" s="20" t="s">
         <v>383</v>
       </c>
@@ -57935,12 +57923,12 @@
       <c r="C13" s="145">
         <v>0</v>
       </c>
-      <c r="D13" s="378" t="s">
+      <c r="D13" s="390" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="378"/>
-      <c r="F13" s="378"/>
-      <c r="G13" s="378"/>
+      <c r="E13" s="390"/>
+      <c r="F13" s="390"/>
+      <c r="G13" s="390"/>
       <c r="I13" s="20" t="s">
         <v>313</v>
       </c>
@@ -57959,12 +57947,12 @@
         <f>AVERAGE(Consolidated!E28:H28)</f>
         <v>-64688.31</v>
       </c>
-      <c r="D14" s="378" t="s">
+      <c r="D14" s="390" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="378"/>
-      <c r="F14" s="378"/>
-      <c r="G14" s="378"/>
+      <c r="E14" s="390"/>
+      <c r="F14" s="390"/>
+      <c r="G14" s="390"/>
       <c r="J14" s="167">
         <f>SUM(J11:J13)</f>
         <v>-8.6499999999999994E-2</v>
@@ -57990,16 +57978,16 @@
         <f>AVERAGE(Consolidated!E35:H35)</f>
         <v>-23355.479999999996</v>
       </c>
-      <c r="D15" s="378" t="s">
+      <c r="D15" s="390" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="378"/>
-      <c r="F15" s="378"/>
-      <c r="G15" s="378"/>
-      <c r="I15" s="385" t="s">
+      <c r="E15" s="390"/>
+      <c r="F15" s="390"/>
+      <c r="G15" s="390"/>
+      <c r="I15" s="388" t="s">
         <v>384</v>
       </c>
-      <c r="J15" s="385"/>
+      <c r="J15" s="388"/>
       <c r="K15" s="20" t="s">
         <v>386</v>
       </c>
@@ -58025,12 +58013,12 @@
         <f>-0.4%</f>
         <v>-4.0000000000000001E-3</v>
       </c>
-      <c r="D16" s="378" t="s">
+      <c r="D16" s="390" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="378"/>
-      <c r="F16" s="378"/>
-      <c r="G16" s="378"/>
+      <c r="E16" s="390"/>
+      <c r="F16" s="390"/>
+      <c r="G16" s="390"/>
       <c r="I16" s="20" t="s">
         <v>385</v>
       </c>
@@ -58057,12 +58045,12 @@
       <c r="C17" s="166">
         <v>-3.9277296541559398E-2</v>
       </c>
-      <c r="D17" s="378" t="s">
+      <c r="D17" s="390" t="s">
         <v>51</v>
       </c>
-      <c r="E17" s="378"/>
-      <c r="F17" s="378"/>
-      <c r="G17" s="378"/>
+      <c r="E17" s="390"/>
+      <c r="F17" s="390"/>
+      <c r="G17" s="390"/>
       <c r="I17" s="20" t="s">
         <v>377</v>
       </c>
@@ -58080,12 +58068,12 @@
       <c r="C18" s="166">
         <v>0</v>
       </c>
-      <c r="D18" s="378" t="s">
+      <c r="D18" s="390" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="378"/>
-      <c r="F18" s="378"/>
-      <c r="G18" s="378"/>
+      <c r="E18" s="390"/>
+      <c r="F18" s="390"/>
+      <c r="G18" s="390"/>
       <c r="J18" s="111">
         <f>J16+J17</f>
         <v>-0.23655912886349639</v>
@@ -58181,22 +58169,22 @@
       <c r="Q24" s="176"/>
     </row>
     <row r="25" spans="1:24" ht="18" customHeight="1">
-      <c r="B25" s="380" t="s">
+      <c r="B25" s="385" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="380"/>
-      <c r="D25" s="380"/>
-      <c r="E25" s="380"/>
-      <c r="F25" s="380"/>
-      <c r="G25" s="380"/>
-      <c r="H25" s="380"/>
-      <c r="I25" s="380"/>
-      <c r="J25" s="380"/>
-      <c r="K25" s="380"/>
-      <c r="L25" s="380"/>
-      <c r="M25" s="380"/>
-      <c r="N25" s="380"/>
-      <c r="O25" s="380"/>
+      <c r="C25" s="385"/>
+      <c r="D25" s="385"/>
+      <c r="E25" s="385"/>
+      <c r="F25" s="385"/>
+      <c r="G25" s="385"/>
+      <c r="H25" s="385"/>
+      <c r="I25" s="385"/>
+      <c r="J25" s="385"/>
+      <c r="K25" s="385"/>
+      <c r="L25" s="385"/>
+      <c r="M25" s="385"/>
+      <c r="N25" s="385"/>
+      <c r="O25" s="385"/>
       <c r="Q25" s="176"/>
     </row>
     <row r="26" spans="1:24" ht="18" customHeight="1">
@@ -58306,22 +58294,22 @@
       <c r="Q28" s="176"/>
     </row>
     <row r="29" spans="1:24" ht="18" customHeight="1">
-      <c r="B29" s="380" t="s">
+      <c r="B29" s="385" t="s">
         <v>370</v>
       </c>
-      <c r="C29" s="380"/>
-      <c r="D29" s="380"/>
-      <c r="E29" s="380"/>
-      <c r="F29" s="380"/>
-      <c r="G29" s="380"/>
-      <c r="H29" s="380"/>
-      <c r="I29" s="380"/>
-      <c r="J29" s="380"/>
-      <c r="K29" s="380"/>
-      <c r="L29" s="380"/>
-      <c r="M29" s="380"/>
-      <c r="N29" s="380"/>
-      <c r="O29" s="380"/>
+      <c r="C29" s="385"/>
+      <c r="D29" s="385"/>
+      <c r="E29" s="385"/>
+      <c r="F29" s="385"/>
+      <c r="G29" s="385"/>
+      <c r="H29" s="385"/>
+      <c r="I29" s="385"/>
+      <c r="J29" s="385"/>
+      <c r="K29" s="385"/>
+      <c r="L29" s="385"/>
+      <c r="M29" s="385"/>
+      <c r="N29" s="385"/>
+      <c r="O29" s="385"/>
       <c r="Q29" s="176"/>
     </row>
     <row r="30" spans="1:24" ht="18" customHeight="1">
@@ -59739,22 +59727,22 @@
       <c r="Q54" s="176"/>
     </row>
     <row r="55" spans="2:17" ht="18" customHeight="1">
-      <c r="B55" s="380" t="s">
+      <c r="B55" s="385" t="s">
         <v>80</v>
       </c>
-      <c r="C55" s="380"/>
-      <c r="D55" s="380"/>
-      <c r="E55" s="380"/>
-      <c r="F55" s="380"/>
-      <c r="G55" s="380"/>
-      <c r="H55" s="380"/>
-      <c r="I55" s="380"/>
-      <c r="J55" s="380"/>
-      <c r="K55" s="380"/>
-      <c r="L55" s="380"/>
-      <c r="M55" s="380"/>
-      <c r="N55" s="380"/>
-      <c r="O55" s="380"/>
+      <c r="C55" s="385"/>
+      <c r="D55" s="385"/>
+      <c r="E55" s="385"/>
+      <c r="F55" s="385"/>
+      <c r="G55" s="385"/>
+      <c r="H55" s="385"/>
+      <c r="I55" s="385"/>
+      <c r="J55" s="385"/>
+      <c r="K55" s="385"/>
+      <c r="L55" s="385"/>
+      <c r="M55" s="385"/>
+      <c r="N55" s="385"/>
+      <c r="O55" s="385"/>
       <c r="Q55" s="176"/>
     </row>
     <row r="56" spans="2:17" ht="18" customHeight="1">
@@ -60096,41 +60084,41 @@
       <c r="Q62" s="176"/>
     </row>
     <row r="63" spans="2:17" ht="18" customHeight="1">
-      <c r="B63" s="380" t="s">
+      <c r="B63" s="385" t="s">
         <v>84</v>
       </c>
-      <c r="C63" s="380"/>
-      <c r="D63" s="380"/>
-      <c r="E63" s="380"/>
-      <c r="F63" s="380"/>
-      <c r="G63" s="380"/>
-      <c r="H63" s="380"/>
-      <c r="I63" s="380"/>
-      <c r="J63" s="380"/>
-      <c r="K63" s="380"/>
-      <c r="L63" s="380"/>
-      <c r="M63" s="380"/>
-      <c r="N63" s="380"/>
-      <c r="O63" s="380"/>
+      <c r="C63" s="385"/>
+      <c r="D63" s="385"/>
+      <c r="E63" s="385"/>
+      <c r="F63" s="385"/>
+      <c r="G63" s="385"/>
+      <c r="H63" s="385"/>
+      <c r="I63" s="385"/>
+      <c r="J63" s="385"/>
+      <c r="K63" s="385"/>
+      <c r="L63" s="385"/>
+      <c r="M63" s="385"/>
+      <c r="N63" s="385"/>
+      <c r="O63" s="385"/>
       <c r="Q63" s="176"/>
     </row>
     <row r="64" spans="2:17">
-      <c r="B64" s="386" t="s">
+      <c r="B64" s="382" t="s">
         <v>85</v>
       </c>
-      <c r="C64" s="386"/>
-      <c r="D64" s="386"/>
-      <c r="E64" s="386"/>
-      <c r="F64" s="386"/>
-      <c r="G64" s="386"/>
-      <c r="H64" s="386"/>
-      <c r="I64" s="386"/>
-      <c r="J64" s="386"/>
-      <c r="K64" s="386"/>
-      <c r="L64" s="386"/>
-      <c r="M64" s="386"/>
-      <c r="N64" s="386"/>
-      <c r="O64" s="386"/>
+      <c r="C64" s="382"/>
+      <c r="D64" s="382"/>
+      <c r="E64" s="382"/>
+      <c r="F64" s="382"/>
+      <c r="G64" s="382"/>
+      <c r="H64" s="382"/>
+      <c r="I64" s="382"/>
+      <c r="J64" s="382"/>
+      <c r="K64" s="382"/>
+      <c r="L64" s="382"/>
+      <c r="M64" s="382"/>
+      <c r="N64" s="382"/>
+      <c r="O64" s="382"/>
       <c r="Q64" s="176"/>
     </row>
     <row r="65" spans="2:17">
@@ -60151,24 +60139,24 @@
       <c r="Q65" s="176"/>
     </row>
     <row r="66" spans="2:17">
-      <c r="B66" s="382" t="s">
+      <c r="B66" s="383" t="s">
         <v>371</v>
       </c>
-      <c r="C66" s="382"/>
-      <c r="D66" s="382"/>
-      <c r="E66" s="382"/>
-      <c r="F66" s="382"/>
-      <c r="G66" s="382"/>
-      <c r="H66" s="382"/>
-      <c r="I66" s="382"/>
-      <c r="J66" s="382"/>
-      <c r="K66" s="382"/>
-      <c r="L66" s="382"/>
-      <c r="M66" s="382"/>
-      <c r="N66" s="382"/>
-      <c r="O66" s="382"/>
-      <c r="P66" s="382"/>
-      <c r="Q66" s="382"/>
+      <c r="C66" s="383"/>
+      <c r="D66" s="383"/>
+      <c r="E66" s="383"/>
+      <c r="F66" s="383"/>
+      <c r="G66" s="383"/>
+      <c r="H66" s="383"/>
+      <c r="I66" s="383"/>
+      <c r="J66" s="383"/>
+      <c r="K66" s="383"/>
+      <c r="L66" s="383"/>
+      <c r="M66" s="383"/>
+      <c r="N66" s="383"/>
+      <c r="O66" s="383"/>
+      <c r="P66" s="383"/>
+      <c r="Q66" s="383"/>
     </row>
     <row r="67" spans="2:17">
       <c r="B67" s="149"/>
@@ -60417,24 +60405,24 @@
       <c r="Q71" s="176"/>
     </row>
     <row r="72" spans="2:17" ht="16.5" customHeight="1">
-      <c r="B72" s="382" t="s">
+      <c r="B72" s="383" t="s">
         <v>86</v>
       </c>
-      <c r="C72" s="382"/>
-      <c r="D72" s="382"/>
-      <c r="E72" s="382"/>
-      <c r="F72" s="382"/>
-      <c r="G72" s="382"/>
-      <c r="H72" s="382"/>
-      <c r="I72" s="382"/>
-      <c r="J72" s="382"/>
-      <c r="K72" s="382"/>
-      <c r="L72" s="382"/>
-      <c r="M72" s="382"/>
-      <c r="N72" s="382"/>
-      <c r="O72" s="382"/>
-      <c r="P72" s="382"/>
-      <c r="Q72" s="382"/>
+      <c r="C72" s="383"/>
+      <c r="D72" s="383"/>
+      <c r="E72" s="383"/>
+      <c r="F72" s="383"/>
+      <c r="G72" s="383"/>
+      <c r="H72" s="383"/>
+      <c r="I72" s="383"/>
+      <c r="J72" s="383"/>
+      <c r="K72" s="383"/>
+      <c r="L72" s="383"/>
+      <c r="M72" s="383"/>
+      <c r="N72" s="383"/>
+      <c r="O72" s="383"/>
+      <c r="P72" s="383"/>
+      <c r="Q72" s="383"/>
     </row>
     <row r="73" spans="2:17" ht="13.5" customHeight="1">
       <c r="B73" s="149"/>
@@ -60683,24 +60671,24 @@
       <c r="Q77" s="176"/>
     </row>
     <row r="78" spans="2:17" ht="16.5" customHeight="1">
-      <c r="B78" s="381" t="s">
+      <c r="B78" s="384" t="s">
         <v>91</v>
       </c>
-      <c r="C78" s="381"/>
-      <c r="D78" s="381"/>
-      <c r="E78" s="381"/>
-      <c r="F78" s="381"/>
-      <c r="G78" s="381"/>
-      <c r="H78" s="381"/>
-      <c r="I78" s="381"/>
-      <c r="J78" s="381"/>
-      <c r="K78" s="381"/>
-      <c r="L78" s="381"/>
-      <c r="M78" s="381"/>
-      <c r="N78" s="381"/>
-      <c r="O78" s="381"/>
-      <c r="P78" s="381"/>
-      <c r="Q78" s="381"/>
+      <c r="C78" s="384"/>
+      <c r="D78" s="384"/>
+      <c r="E78" s="384"/>
+      <c r="F78" s="384"/>
+      <c r="G78" s="384"/>
+      <c r="H78" s="384"/>
+      <c r="I78" s="384"/>
+      <c r="J78" s="384"/>
+      <c r="K78" s="384"/>
+      <c r="L78" s="384"/>
+      <c r="M78" s="384"/>
+      <c r="N78" s="384"/>
+      <c r="O78" s="384"/>
+      <c r="P78" s="384"/>
+      <c r="Q78" s="384"/>
     </row>
     <row r="79" spans="2:17" ht="13.5" customHeight="1">
       <c r="B79" s="149"/>
@@ -60949,24 +60937,24 @@
       <c r="Q83" s="176"/>
     </row>
     <row r="84" spans="2:17" ht="16.5" customHeight="1">
-      <c r="B84" s="381" t="s">
+      <c r="B84" s="384" t="s">
         <v>92</v>
       </c>
-      <c r="C84" s="381"/>
-      <c r="D84" s="381"/>
-      <c r="E84" s="381"/>
-      <c r="F84" s="381"/>
-      <c r="G84" s="381"/>
-      <c r="H84" s="381"/>
-      <c r="I84" s="381"/>
-      <c r="J84" s="381"/>
-      <c r="K84" s="381"/>
-      <c r="L84" s="381"/>
-      <c r="M84" s="381"/>
-      <c r="N84" s="381"/>
-      <c r="O84" s="381"/>
-      <c r="P84" s="381"/>
-      <c r="Q84" s="381"/>
+      <c r="C84" s="384"/>
+      <c r="D84" s="384"/>
+      <c r="E84" s="384"/>
+      <c r="F84" s="384"/>
+      <c r="G84" s="384"/>
+      <c r="H84" s="384"/>
+      <c r="I84" s="384"/>
+      <c r="J84" s="384"/>
+      <c r="K84" s="384"/>
+      <c r="L84" s="384"/>
+      <c r="M84" s="384"/>
+      <c r="N84" s="384"/>
+      <c r="O84" s="384"/>
+      <c r="P84" s="384"/>
+      <c r="Q84" s="384"/>
     </row>
     <row r="85" spans="2:17" ht="13.5" customHeight="1">
       <c r="B85" s="149"/>
@@ -61215,24 +61203,24 @@
       <c r="Q89" s="176"/>
     </row>
     <row r="90" spans="2:17" ht="16.5" customHeight="1">
-      <c r="B90" s="382" t="s">
+      <c r="B90" s="383" t="s">
         <v>93</v>
       </c>
-      <c r="C90" s="382"/>
-      <c r="D90" s="382"/>
-      <c r="E90" s="382"/>
-      <c r="F90" s="382"/>
-      <c r="G90" s="382"/>
-      <c r="H90" s="382"/>
-      <c r="I90" s="382"/>
-      <c r="J90" s="382"/>
-      <c r="K90" s="382"/>
-      <c r="L90" s="382"/>
-      <c r="M90" s="382"/>
-      <c r="N90" s="382"/>
-      <c r="O90" s="382"/>
-      <c r="P90" s="382"/>
-      <c r="Q90" s="382"/>
+      <c r="C90" s="383"/>
+      <c r="D90" s="383"/>
+      <c r="E90" s="383"/>
+      <c r="F90" s="383"/>
+      <c r="G90" s="383"/>
+      <c r="H90" s="383"/>
+      <c r="I90" s="383"/>
+      <c r="J90" s="383"/>
+      <c r="K90" s="383"/>
+      <c r="L90" s="383"/>
+      <c r="M90" s="383"/>
+      <c r="N90" s="383"/>
+      <c r="O90" s="383"/>
+      <c r="P90" s="383"/>
+      <c r="Q90" s="383"/>
     </row>
     <row r="91" spans="2:17" ht="13.5" customHeight="1">
       <c r="B91" s="149"/>
@@ -61481,24 +61469,24 @@
       <c r="Q95" s="176"/>
     </row>
     <row r="96" spans="2:17" ht="16.5" customHeight="1">
-      <c r="B96" s="381" t="s">
+      <c r="B96" s="384" t="s">
         <v>94</v>
       </c>
-      <c r="C96" s="381"/>
-      <c r="D96" s="381"/>
-      <c r="E96" s="381"/>
-      <c r="F96" s="381"/>
-      <c r="G96" s="381"/>
-      <c r="H96" s="381"/>
-      <c r="I96" s="381"/>
-      <c r="J96" s="381"/>
-      <c r="K96" s="381"/>
-      <c r="L96" s="381"/>
-      <c r="M96" s="381"/>
-      <c r="N96" s="381"/>
-      <c r="O96" s="381"/>
-      <c r="P96" s="381"/>
-      <c r="Q96" s="381"/>
+      <c r="C96" s="384"/>
+      <c r="D96" s="384"/>
+      <c r="E96" s="384"/>
+      <c r="F96" s="384"/>
+      <c r="G96" s="384"/>
+      <c r="H96" s="384"/>
+      <c r="I96" s="384"/>
+      <c r="J96" s="384"/>
+      <c r="K96" s="384"/>
+      <c r="L96" s="384"/>
+      <c r="M96" s="384"/>
+      <c r="N96" s="384"/>
+      <c r="O96" s="384"/>
+      <c r="P96" s="384"/>
+      <c r="Q96" s="384"/>
     </row>
     <row r="97" spans="2:17" ht="13.5" customHeight="1">
       <c r="B97" s="149"/>
@@ -61747,24 +61735,24 @@
       <c r="Q101" s="176"/>
     </row>
     <row r="102" spans="2:17" ht="16.5" customHeight="1">
-      <c r="B102" s="382" t="s">
+      <c r="B102" s="383" t="s">
         <v>95</v>
       </c>
-      <c r="C102" s="382"/>
-      <c r="D102" s="382"/>
-      <c r="E102" s="382"/>
-      <c r="F102" s="382"/>
-      <c r="G102" s="382"/>
-      <c r="H102" s="382"/>
-      <c r="I102" s="382"/>
-      <c r="J102" s="382"/>
-      <c r="K102" s="382"/>
-      <c r="L102" s="382"/>
-      <c r="M102" s="382"/>
-      <c r="N102" s="382"/>
-      <c r="O102" s="382"/>
-      <c r="P102" s="382"/>
-      <c r="Q102" s="382"/>
+      <c r="C102" s="383"/>
+      <c r="D102" s="383"/>
+      <c r="E102" s="383"/>
+      <c r="F102" s="383"/>
+      <c r="G102" s="383"/>
+      <c r="H102" s="383"/>
+      <c r="I102" s="383"/>
+      <c r="J102" s="383"/>
+      <c r="K102" s="383"/>
+      <c r="L102" s="383"/>
+      <c r="M102" s="383"/>
+      <c r="N102" s="383"/>
+      <c r="O102" s="383"/>
+      <c r="P102" s="383"/>
+      <c r="Q102" s="383"/>
     </row>
     <row r="103" spans="2:17" ht="13.5" customHeight="1">
       <c r="B103" s="149"/>
@@ -62013,24 +62001,24 @@
       <c r="Q107" s="176"/>
     </row>
     <row r="108" spans="2:17" ht="16.5" customHeight="1">
-      <c r="B108" s="382" t="s">
+      <c r="B108" s="383" t="s">
         <v>96</v>
       </c>
-      <c r="C108" s="382"/>
-      <c r="D108" s="382"/>
-      <c r="E108" s="382"/>
-      <c r="F108" s="382"/>
-      <c r="G108" s="382"/>
-      <c r="H108" s="382"/>
-      <c r="I108" s="382"/>
-      <c r="J108" s="382"/>
-      <c r="K108" s="382"/>
-      <c r="L108" s="382"/>
-      <c r="M108" s="382"/>
-      <c r="N108" s="382"/>
-      <c r="O108" s="382"/>
-      <c r="P108" s="382"/>
-      <c r="Q108" s="382"/>
+      <c r="C108" s="383"/>
+      <c r="D108" s="383"/>
+      <c r="E108" s="383"/>
+      <c r="F108" s="383"/>
+      <c r="G108" s="383"/>
+      <c r="H108" s="383"/>
+      <c r="I108" s="383"/>
+      <c r="J108" s="383"/>
+      <c r="K108" s="383"/>
+      <c r="L108" s="383"/>
+      <c r="M108" s="383"/>
+      <c r="N108" s="383"/>
+      <c r="O108" s="383"/>
+      <c r="P108" s="383"/>
+      <c r="Q108" s="383"/>
     </row>
     <row r="109" spans="2:17" ht="13.5" customHeight="1">
       <c r="B109" s="149"/>
@@ -62279,24 +62267,24 @@
       <c r="Q113" s="176"/>
     </row>
     <row r="114" spans="2:17" ht="16.5" customHeight="1">
-      <c r="B114" s="381" t="s">
+      <c r="B114" s="384" t="s">
         <v>97</v>
       </c>
-      <c r="C114" s="381"/>
-      <c r="D114" s="381"/>
-      <c r="E114" s="381"/>
-      <c r="F114" s="381"/>
-      <c r="G114" s="381"/>
-      <c r="H114" s="381"/>
-      <c r="I114" s="381"/>
-      <c r="J114" s="381"/>
-      <c r="K114" s="381"/>
-      <c r="L114" s="381"/>
-      <c r="M114" s="381"/>
-      <c r="N114" s="381"/>
-      <c r="O114" s="381"/>
-      <c r="P114" s="381"/>
-      <c r="Q114" s="381"/>
+      <c r="C114" s="384"/>
+      <c r="D114" s="384"/>
+      <c r="E114" s="384"/>
+      <c r="F114" s="384"/>
+      <c r="G114" s="384"/>
+      <c r="H114" s="384"/>
+      <c r="I114" s="384"/>
+      <c r="J114" s="384"/>
+      <c r="K114" s="384"/>
+      <c r="L114" s="384"/>
+      <c r="M114" s="384"/>
+      <c r="N114" s="384"/>
+      <c r="O114" s="384"/>
+      <c r="P114" s="384"/>
+      <c r="Q114" s="384"/>
     </row>
     <row r="115" spans="2:17" ht="13.5" customHeight="1">
       <c r="B115" s="149"/>
@@ -62545,24 +62533,24 @@
       <c r="Q119" s="176"/>
     </row>
     <row r="120" spans="2:17" ht="16.5" customHeight="1">
-      <c r="B120" s="382" t="s">
+      <c r="B120" s="383" t="s">
         <v>98</v>
       </c>
-      <c r="C120" s="382"/>
-      <c r="D120" s="382"/>
-      <c r="E120" s="382"/>
-      <c r="F120" s="382"/>
-      <c r="G120" s="382"/>
-      <c r="H120" s="382"/>
-      <c r="I120" s="382"/>
-      <c r="J120" s="382"/>
-      <c r="K120" s="382"/>
-      <c r="L120" s="382"/>
-      <c r="M120" s="382"/>
-      <c r="N120" s="382"/>
-      <c r="O120" s="382"/>
-      <c r="P120" s="382"/>
-      <c r="Q120" s="382"/>
+      <c r="C120" s="383"/>
+      <c r="D120" s="383"/>
+      <c r="E120" s="383"/>
+      <c r="F120" s="383"/>
+      <c r="G120" s="383"/>
+      <c r="H120" s="383"/>
+      <c r="I120" s="383"/>
+      <c r="J120" s="383"/>
+      <c r="K120" s="383"/>
+      <c r="L120" s="383"/>
+      <c r="M120" s="383"/>
+      <c r="N120" s="383"/>
+      <c r="O120" s="383"/>
+      <c r="P120" s="383"/>
+      <c r="Q120" s="383"/>
     </row>
     <row r="121" spans="2:17" ht="13.5" customHeight="1">
       <c r="B121" s="149"/>
@@ -62797,24 +62785,24 @@
       <c r="Q125" s="176"/>
     </row>
     <row r="127" spans="2:17">
-      <c r="B127" s="382" t="s">
+      <c r="B127" s="383" t="s">
         <v>28</v>
       </c>
-      <c r="C127" s="382"/>
-      <c r="D127" s="382"/>
-      <c r="E127" s="382"/>
-      <c r="F127" s="382"/>
-      <c r="G127" s="382"/>
-      <c r="H127" s="382"/>
-      <c r="I127" s="382"/>
-      <c r="J127" s="382"/>
-      <c r="K127" s="382"/>
-      <c r="L127" s="382"/>
-      <c r="M127" s="382"/>
-      <c r="N127" s="382"/>
-      <c r="O127" s="382"/>
-      <c r="P127" s="382"/>
-      <c r="Q127" s="382"/>
+      <c r="C127" s="383"/>
+      <c r="D127" s="383"/>
+      <c r="E127" s="383"/>
+      <c r="F127" s="383"/>
+      <c r="G127" s="383"/>
+      <c r="H127" s="383"/>
+      <c r="I127" s="383"/>
+      <c r="J127" s="383"/>
+      <c r="K127" s="383"/>
+      <c r="L127" s="383"/>
+      <c r="M127" s="383"/>
+      <c r="N127" s="383"/>
+      <c r="O127" s="383"/>
+      <c r="P127" s="383"/>
+      <c r="Q127" s="383"/>
     </row>
     <row r="128" spans="2:17">
       <c r="B128" s="149"/>
@@ -64017,15 +64005,15 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="B64:O64"/>
-    <mergeCell ref="B66:Q66"/>
-    <mergeCell ref="B84:Q84"/>
-    <mergeCell ref="B72:Q72"/>
-    <mergeCell ref="B127:Q127"/>
-    <mergeCell ref="B90:Q90"/>
-    <mergeCell ref="B96:Q96"/>
-    <mergeCell ref="B102:Q102"/>
-    <mergeCell ref="B108:Q108"/>
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="B55:O55"/>
+    <mergeCell ref="D12:G12"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="D14:G14"/>
+    <mergeCell ref="D15:G15"/>
     <mergeCell ref="B63:O63"/>
     <mergeCell ref="B78:Q78"/>
     <mergeCell ref="B114:Q114"/>
@@ -64042,15 +64030,15 @@
     <mergeCell ref="D8:G8"/>
     <mergeCell ref="D10:G10"/>
     <mergeCell ref="D11:G11"/>
-    <mergeCell ref="D16:G16"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="B55:O55"/>
-    <mergeCell ref="D12:G12"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="D14:G14"/>
-    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="B64:O64"/>
+    <mergeCell ref="B66:Q66"/>
+    <mergeCell ref="B84:Q84"/>
+    <mergeCell ref="B72:Q72"/>
+    <mergeCell ref="B127:Q127"/>
+    <mergeCell ref="B90:Q90"/>
+    <mergeCell ref="B96:Q96"/>
+    <mergeCell ref="B102:Q102"/>
+    <mergeCell ref="B108:Q108"/>
   </mergeCells>
   <conditionalFormatting sqref="C70:N70">
     <cfRule type="expression" dxfId="22" priority="3">
@@ -64154,27 +64142,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:20" ht="27.75" customHeight="1">
-      <c r="B1" s="387" t="s">
+      <c r="B1" s="391" t="s">
         <v>100</v>
       </c>
-      <c r="C1" s="387"/>
-      <c r="D1" s="387"/>
-      <c r="E1" s="387"/>
-      <c r="F1" s="387"/>
-      <c r="G1" s="387"/>
-      <c r="H1" s="387"/>
-      <c r="I1" s="387"/>
-      <c r="J1" s="387"/>
-      <c r="K1" s="387"/>
-      <c r="L1" s="387"/>
-      <c r="M1" s="387"/>
-      <c r="N1" s="387"/>
-      <c r="O1" s="387"/>
-      <c r="P1" s="387"/>
-      <c r="Q1" s="387"/>
-      <c r="R1" s="387"/>
-      <c r="S1" s="387"/>
-      <c r="T1" s="387"/>
+      <c r="C1" s="391"/>
+      <c r="D1" s="391"/>
+      <c r="E1" s="391"/>
+      <c r="F1" s="391"/>
+      <c r="G1" s="391"/>
+      <c r="H1" s="391"/>
+      <c r="I1" s="391"/>
+      <c r="J1" s="391"/>
+      <c r="K1" s="391"/>
+      <c r="L1" s="391"/>
+      <c r="M1" s="391"/>
+      <c r="N1" s="391"/>
+      <c r="O1" s="391"/>
+      <c r="P1" s="391"/>
+      <c r="Q1" s="391"/>
+      <c r="R1" s="391"/>
+      <c r="S1" s="391"/>
+      <c r="T1" s="391"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -68319,18 +68307,18 @@
         <f t="shared" ref="N5:N8" si="2">IF(H5&lt;0,H5,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="P5" s="388" t="s">
+      <c r="P5" s="398" t="s">
         <v>605</v>
       </c>
-      <c r="Q5" s="391">
+      <c r="Q5" s="392">
         <f>SUM(H4:H6)</f>
         <v>51025.550000000025</v>
       </c>
-      <c r="R5" s="394">
+      <c r="R5" s="395">
         <f>IF(Q5&gt;=0,Q5,NA())</f>
         <v>51025.550000000025</v>
       </c>
-      <c r="S5" s="394" t="e">
+      <c r="S5" s="395" t="e">
         <f>IF(Q5&lt;0,Q5,NA())</f>
         <v>#N/A</v>
       </c>
@@ -68380,10 +68368,10 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="P6" s="389"/>
-      <c r="Q6" s="392"/>
-      <c r="R6" s="395"/>
-      <c r="S6" s="395"/>
+      <c r="P6" s="399"/>
+      <c r="Q6" s="393"/>
+      <c r="R6" s="396"/>
+      <c r="S6" s="396"/>
       <c r="V6" s="323"/>
       <c r="W6" s="323"/>
       <c r="X6" s="323"/>
@@ -68430,10 +68418,10 @@
         <f t="shared" si="2"/>
         <v>-120711.43</v>
       </c>
-      <c r="P7" s="390"/>
-      <c r="Q7" s="393"/>
-      <c r="R7" s="396"/>
-      <c r="S7" s="396"/>
+      <c r="P7" s="400"/>
+      <c r="Q7" s="394"/>
+      <c r="R7" s="397"/>
+      <c r="S7" s="397"/>
     </row>
     <row r="8" spans="4:33" ht="15" customHeight="1">
       <c r="D8" s="107">
@@ -68468,18 +68456,18 @@
         <f t="shared" si="2"/>
         <v>-10290.099999999984</v>
       </c>
-      <c r="P8" s="388" t="s">
+      <c r="P8" s="398" t="s">
         <v>606</v>
       </c>
-      <c r="Q8" s="391">
+      <c r="Q8" s="392">
         <f>SUM(H7:H9)</f>
         <v>-128684.78999999996</v>
       </c>
-      <c r="R8" s="394" t="e">
+      <c r="R8" s="395" t="e">
         <f>IF(Q8&gt;=0,Q8,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="S8" s="394">
+      <c r="S8" s="395">
         <f>IF(Q8&lt;0,Q8,NA())</f>
         <v>-128684.78999999996</v>
       </c>
@@ -68517,10 +68505,10 @@
         <f t="shared" ref="N9:N63" si="5">IF(H9&lt;0,H9,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="P9" s="389"/>
-      <c r="Q9" s="392"/>
-      <c r="R9" s="395"/>
-      <c r="S9" s="395"/>
+      <c r="P9" s="399"/>
+      <c r="Q9" s="393"/>
+      <c r="R9" s="396"/>
+      <c r="S9" s="396"/>
     </row>
     <row r="10" spans="4:33" ht="15" customHeight="1">
       <c r="D10" s="107">
@@ -68555,10 +68543,10 @@
         <f t="shared" si="5"/>
         <v>-6944.5299999999934</v>
       </c>
-      <c r="P10" s="390"/>
-      <c r="Q10" s="393"/>
-      <c r="R10" s="396"/>
-      <c r="S10" s="396"/>
+      <c r="P10" s="400"/>
+      <c r="Q10" s="394"/>
+      <c r="R10" s="397"/>
+      <c r="S10" s="397"/>
     </row>
     <row r="11" spans="4:33" ht="15" customHeight="1">
       <c r="D11" s="107">
@@ -68593,18 +68581,18 @@
         <f t="shared" si="5"/>
         <v>-1944.2300000000014</v>
       </c>
-      <c r="P11" s="388" t="s">
+      <c r="P11" s="398" t="s">
         <v>607</v>
       </c>
-      <c r="Q11" s="391">
+      <c r="Q11" s="392">
         <f t="shared" ref="Q11" si="6">SUM(H10:H12)</f>
         <v>63263.910000000018</v>
       </c>
-      <c r="R11" s="394">
+      <c r="R11" s="395">
         <f t="shared" ref="R11" si="7">IF(Q11&gt;=0,Q11,NA())</f>
         <v>63263.910000000018</v>
       </c>
-      <c r="S11" s="394" t="e">
+      <c r="S11" s="395" t="e">
         <f t="shared" ref="S11" si="8">IF(Q11&lt;0,Q11,NA())</f>
         <v>#N/A</v>
       </c>
@@ -68642,10 +68630,10 @@
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="P12" s="389"/>
-      <c r="Q12" s="392"/>
-      <c r="R12" s="395"/>
-      <c r="S12" s="395"/>
+      <c r="P12" s="399"/>
+      <c r="Q12" s="393"/>
+      <c r="R12" s="396"/>
+      <c r="S12" s="396"/>
     </row>
     <row r="13" spans="4:33" ht="15" customHeight="1">
       <c r="D13" s="107">
@@ -68680,10 +68668,10 @@
         <f t="shared" si="5"/>
         <v>-29851.530000000013</v>
       </c>
-      <c r="P13" s="390"/>
-      <c r="Q13" s="393"/>
-      <c r="R13" s="396"/>
-      <c r="S13" s="396"/>
+      <c r="P13" s="400"/>
+      <c r="Q13" s="394"/>
+      <c r="R13" s="397"/>
+      <c r="S13" s="397"/>
     </row>
     <row r="14" spans="4:33" ht="15" customHeight="1">
       <c r="D14" s="107">
@@ -68718,18 +68706,18 @@
         <f t="shared" si="5"/>
         <v>-7189.3699999999917</v>
       </c>
-      <c r="P14" s="388" t="s">
+      <c r="P14" s="398" t="s">
         <v>608</v>
       </c>
-      <c r="Q14" s="391">
+      <c r="Q14" s="392">
         <f t="shared" ref="Q14" si="9">SUM(H13:H15)</f>
         <v>2032.5599999999977</v>
       </c>
-      <c r="R14" s="394">
+      <c r="R14" s="395">
         <f t="shared" ref="R14" si="10">IF(Q14&gt;=0,Q14,NA())</f>
         <v>2032.5599999999977</v>
       </c>
-      <c r="S14" s="394" t="e">
+      <c r="S14" s="395" t="e">
         <f t="shared" ref="S14" si="11">IF(Q14&lt;0,Q14,NA())</f>
         <v>#N/A</v>
       </c>
@@ -68767,10 +68755,10 @@
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="P15" s="389"/>
-      <c r="Q15" s="392"/>
-      <c r="R15" s="395"/>
-      <c r="S15" s="395"/>
+      <c r="P15" s="399"/>
+      <c r="Q15" s="393"/>
+      <c r="R15" s="396"/>
+      <c r="S15" s="396"/>
     </row>
     <row r="16" spans="4:33" ht="15" customHeight="1">
       <c r="D16" s="107">
@@ -68805,10 +68793,10 @@
         <f t="shared" si="5"/>
         <v>-50335.23</v>
       </c>
-      <c r="P16" s="390"/>
-      <c r="Q16" s="393"/>
-      <c r="R16" s="396"/>
-      <c r="S16" s="396"/>
+      <c r="P16" s="400"/>
+      <c r="Q16" s="394"/>
+      <c r="R16" s="397"/>
+      <c r="S16" s="397"/>
     </row>
     <row r="17" spans="4:19" ht="15" customHeight="1">
       <c r="D17" s="107">
@@ -68846,15 +68834,15 @@
       <c r="P17" s="325" t="s">
         <v>609</v>
       </c>
-      <c r="Q17" s="391">
+      <c r="Q17" s="392">
         <f t="shared" ref="Q17" si="12">SUM(H16:H18)</f>
         <v>-13021.260000000017</v>
       </c>
-      <c r="R17" s="394" t="e">
+      <c r="R17" s="395" t="e">
         <f t="shared" ref="R17" si="13">IF(Q17&gt;=0,Q17,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="S17" s="394">
+      <c r="S17" s="395">
         <f t="shared" ref="S17" si="14">IF(Q17&lt;0,Q17,NA())</f>
         <v>-13021.260000000017</v>
       </c>
@@ -68893,9 +68881,9 @@
         <v>#N/A</v>
       </c>
       <c r="P18" s="325"/>
-      <c r="Q18" s="392"/>
-      <c r="R18" s="395"/>
-      <c r="S18" s="395"/>
+      <c r="Q18" s="393"/>
+      <c r="R18" s="396"/>
+      <c r="S18" s="396"/>
     </row>
     <row r="19" spans="4:19" ht="15" customHeight="1">
       <c r="D19" s="107">
@@ -68931,9 +68919,9 @@
         <v>#N/A</v>
       </c>
       <c r="P19" s="326"/>
-      <c r="Q19" s="393"/>
-      <c r="R19" s="396"/>
-      <c r="S19" s="396"/>
+      <c r="Q19" s="394"/>
+      <c r="R19" s="397"/>
+      <c r="S19" s="397"/>
     </row>
     <row r="20" spans="4:19" ht="15" customHeight="1">
       <c r="D20" s="107">
@@ -68971,15 +68959,15 @@
       <c r="P20" s="325" t="s">
         <v>610</v>
       </c>
-      <c r="Q20" s="391">
+      <c r="Q20" s="392">
         <f t="shared" ref="Q20" si="15">SUM(H19:H21)</f>
         <v>1864.0900000000547</v>
       </c>
-      <c r="R20" s="394">
+      <c r="R20" s="395">
         <f t="shared" ref="R20" si="16">IF(Q20&gt;=0,Q20,NA())</f>
         <v>1864.0900000000547</v>
       </c>
-      <c r="S20" s="394" t="e">
+      <c r="S20" s="395" t="e">
         <f t="shared" ref="S20" si="17">IF(Q20&lt;0,Q20,NA())</f>
         <v>#N/A</v>
       </c>
@@ -69018,9 +69006,9 @@
         <v>-36345.219999999972</v>
       </c>
       <c r="P21" s="325"/>
-      <c r="Q21" s="392"/>
-      <c r="R21" s="395"/>
-      <c r="S21" s="395"/>
+      <c r="Q21" s="393"/>
+      <c r="R21" s="396"/>
+      <c r="S21" s="396"/>
     </row>
     <row r="22" spans="4:19" ht="15" customHeight="1">
       <c r="D22" s="107">
@@ -69056,9 +69044,9 @@
         <v>-6132.7899999999781</v>
       </c>
       <c r="P22" s="326"/>
-      <c r="Q22" s="393"/>
-      <c r="R22" s="396"/>
-      <c r="S22" s="396"/>
+      <c r="Q22" s="394"/>
+      <c r="R22" s="397"/>
+      <c r="S22" s="397"/>
     </row>
     <row r="23" spans="4:19" ht="15" customHeight="1">
       <c r="D23" s="107">
@@ -69096,15 +69084,15 @@
       <c r="P23" s="325" t="s">
         <v>611</v>
       </c>
-      <c r="Q23" s="391">
+      <c r="Q23" s="392">
         <f t="shared" ref="Q23" si="18">SUM(H22:H24)</f>
         <v>10423.430000000033</v>
       </c>
-      <c r="R23" s="394">
+      <c r="R23" s="395">
         <f t="shared" ref="R23" si="19">IF(Q23&gt;=0,Q23,NA())</f>
         <v>10423.430000000033</v>
       </c>
-      <c r="S23" s="394" t="e">
+      <c r="S23" s="395" t="e">
         <f t="shared" ref="S23" si="20">IF(Q23&lt;0,Q23,NA())</f>
         <v>#N/A</v>
       </c>
@@ -69143,9 +69131,9 @@
         <v>-3318.8700000000126</v>
       </c>
       <c r="P24" s="325"/>
-      <c r="Q24" s="392"/>
-      <c r="R24" s="395"/>
-      <c r="S24" s="395"/>
+      <c r="Q24" s="393"/>
+      <c r="R24" s="396"/>
+      <c r="S24" s="396"/>
     </row>
     <row r="25" spans="4:19" ht="15" customHeight="1">
       <c r="D25" s="107">
@@ -69181,9 +69169,9 @@
         <v>-44373.710000000021</v>
       </c>
       <c r="P25" s="326"/>
-      <c r="Q25" s="393"/>
-      <c r="R25" s="396"/>
-      <c r="S25" s="396"/>
+      <c r="Q25" s="394"/>
+      <c r="R25" s="397"/>
+      <c r="S25" s="397"/>
     </row>
     <row r="26" spans="4:19" ht="15" customHeight="1">
       <c r="D26" s="107">
@@ -69221,15 +69209,15 @@
       <c r="P26" s="325" t="s">
         <v>612</v>
       </c>
-      <c r="Q26" s="391">
+      <c r="Q26" s="392">
         <f t="shared" ref="Q26" si="21">SUM(H25:H27)</f>
         <v>-31621.239999999965</v>
       </c>
-      <c r="R26" s="394" t="e">
+      <c r="R26" s="395" t="e">
         <f t="shared" ref="R26" si="22">IF(Q26&gt;=0,Q26,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="S26" s="394">
+      <c r="S26" s="395">
         <f t="shared" ref="S26" si="23">IF(Q26&lt;0,Q26,NA())</f>
         <v>-31621.239999999965</v>
       </c>
@@ -69268,9 +69256,9 @@
         <v>#N/A</v>
       </c>
       <c r="P27" s="325"/>
-      <c r="Q27" s="392"/>
-      <c r="R27" s="395"/>
-      <c r="S27" s="395"/>
+      <c r="Q27" s="393"/>
+      <c r="R27" s="396"/>
+      <c r="S27" s="396"/>
     </row>
     <row r="28" spans="4:19" ht="15" customHeight="1">
       <c r="D28" s="107">
@@ -69306,9 +69294,9 @@
         <v>-44170.299999999988</v>
       </c>
       <c r="P28" s="326"/>
-      <c r="Q28" s="393"/>
-      <c r="R28" s="396"/>
-      <c r="S28" s="396"/>
+      <c r="Q28" s="394"/>
+      <c r="R28" s="397"/>
+      <c r="S28" s="397"/>
     </row>
     <row r="29" spans="4:19" ht="15" customHeight="1">
       <c r="D29" s="107">
@@ -69346,15 +69334,15 @@
       <c r="P29" s="325" t="s">
         <v>613</v>
       </c>
-      <c r="Q29" s="391">
+      <c r="Q29" s="392">
         <f t="shared" ref="Q29" si="24">SUM(H28:H30)</f>
         <v>-2864.9200000000164</v>
       </c>
-      <c r="R29" s="394" t="e">
+      <c r="R29" s="395" t="e">
         <f t="shared" ref="R29" si="25">IF(Q29&gt;=0,Q29,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="S29" s="394">
+      <c r="S29" s="395">
         <f t="shared" ref="S29" si="26">IF(Q29&lt;0,Q29,NA())</f>
         <v>-2864.9200000000164</v>
       </c>
@@ -69393,9 +69381,9 @@
         <v>#N/A</v>
       </c>
       <c r="P30" s="325"/>
-      <c r="Q30" s="392"/>
-      <c r="R30" s="395"/>
-      <c r="S30" s="395"/>
+      <c r="Q30" s="393"/>
+      <c r="R30" s="396"/>
+      <c r="S30" s="396"/>
     </row>
     <row r="31" spans="4:19" ht="15" customHeight="1">
       <c r="D31" s="107">
@@ -69431,9 +69419,9 @@
         <v>-43839.760000000009</v>
       </c>
       <c r="P31" s="326"/>
-      <c r="Q31" s="393"/>
-      <c r="R31" s="396"/>
-      <c r="S31" s="396"/>
+      <c r="Q31" s="394"/>
+      <c r="R31" s="397"/>
+      <c r="S31" s="397"/>
     </row>
     <row r="32" spans="4:19" ht="15" customHeight="1">
       <c r="D32" s="107">
@@ -69471,15 +69459,15 @@
       <c r="P32" s="325" t="s">
         <v>614</v>
       </c>
-      <c r="Q32" s="391">
+      <c r="Q32" s="392">
         <f t="shared" ref="Q32" si="27">SUM(H31:H33)</f>
         <v>16410.719999999972</v>
       </c>
-      <c r="R32" s="394">
+      <c r="R32" s="395">
         <f t="shared" ref="R32" si="28">IF(Q32&gt;=0,Q32,NA())</f>
         <v>16410.719999999972</v>
       </c>
-      <c r="S32" s="394" t="e">
+      <c r="S32" s="395" t="e">
         <f t="shared" ref="S32" si="29">IF(Q32&lt;0,Q32,NA())</f>
         <v>#N/A</v>
       </c>
@@ -69518,9 +69506,9 @@
         <v>#N/A</v>
       </c>
       <c r="P33" s="325"/>
-      <c r="Q33" s="392"/>
-      <c r="R33" s="395"/>
-      <c r="S33" s="395"/>
+      <c r="Q33" s="393"/>
+      <c r="R33" s="396"/>
+      <c r="S33" s="396"/>
     </row>
     <row r="34" spans="3:19" ht="15" customHeight="1">
       <c r="D34" s="107">
@@ -69556,9 +69544,9 @@
         <v>#N/A</v>
       </c>
       <c r="P34" s="326"/>
-      <c r="Q34" s="393"/>
-      <c r="R34" s="396"/>
-      <c r="S34" s="396"/>
+      <c r="Q34" s="394"/>
+      <c r="R34" s="397"/>
+      <c r="S34" s="397"/>
     </row>
     <row r="35" spans="3:19" ht="15" customHeight="1">
       <c r="D35" s="107">
@@ -69596,15 +69584,15 @@
       <c r="P35" s="325" t="s">
         <v>615</v>
       </c>
-      <c r="Q35" s="391">
+      <c r="Q35" s="392">
         <f t="shared" ref="Q35" si="30">SUM(H34:H36)</f>
         <v>48719.930000000044</v>
       </c>
-      <c r="R35" s="394">
+      <c r="R35" s="395">
         <f t="shared" ref="R35" si="31">IF(Q35&gt;=0,Q35,NA())</f>
         <v>48719.930000000044</v>
       </c>
-      <c r="S35" s="394" t="e">
+      <c r="S35" s="395" t="e">
         <f t="shared" ref="S35" si="32">IF(Q35&lt;0,Q35,NA())</f>
         <v>#N/A</v>
       </c>
@@ -69643,9 +69631,9 @@
         <v>#N/A</v>
       </c>
       <c r="P36" s="325"/>
-      <c r="Q36" s="392"/>
-      <c r="R36" s="395"/>
-      <c r="S36" s="395"/>
+      <c r="Q36" s="393"/>
+      <c r="R36" s="396"/>
+      <c r="S36" s="396"/>
     </row>
     <row r="37" spans="3:19" ht="15" customHeight="1">
       <c r="D37" s="107">
@@ -69681,9 +69669,9 @@
         <v>-34959.109999999971</v>
       </c>
       <c r="P37" s="326"/>
-      <c r="Q37" s="393"/>
-      <c r="R37" s="396"/>
-      <c r="S37" s="396"/>
+      <c r="Q37" s="394"/>
+      <c r="R37" s="397"/>
+      <c r="S37" s="397"/>
     </row>
     <row r="38" spans="3:19" ht="15" customHeight="1">
       <c r="D38" s="107">
@@ -69721,15 +69709,15 @@
       <c r="P38" s="325" t="s">
         <v>616</v>
       </c>
-      <c r="Q38" s="391">
+      <c r="Q38" s="392">
         <f t="shared" ref="Q38" si="33">SUM(H37:H39)</f>
         <v>57951.049999999974</v>
       </c>
-      <c r="R38" s="394">
+      <c r="R38" s="395">
         <f t="shared" ref="R38" si="34">IF(Q38&gt;=0,Q38,NA())</f>
         <v>57951.049999999974</v>
       </c>
-      <c r="S38" s="394" t="e">
+      <c r="S38" s="395" t="e">
         <f t="shared" ref="S38" si="35">IF(Q38&lt;0,Q38,NA())</f>
         <v>#N/A</v>
       </c>
@@ -69768,9 +69756,9 @@
         <v>#N/A</v>
       </c>
       <c r="P39" s="325"/>
-      <c r="Q39" s="392"/>
-      <c r="R39" s="395"/>
-      <c r="S39" s="395"/>
+      <c r="Q39" s="393"/>
+      <c r="R39" s="396"/>
+      <c r="S39" s="396"/>
     </row>
     <row r="40" spans="3:19" ht="15" customHeight="1">
       <c r="D40" s="107">
@@ -69808,9 +69796,9 @@
         <v>-45310.300000000017</v>
       </c>
       <c r="P40" s="326"/>
-      <c r="Q40" s="393"/>
-      <c r="R40" s="396"/>
-      <c r="S40" s="396"/>
+      <c r="Q40" s="394"/>
+      <c r="R40" s="397"/>
+      <c r="S40" s="397"/>
     </row>
     <row r="41" spans="3:19" ht="15" customHeight="1">
       <c r="D41" s="107">
@@ -69850,15 +69838,15 @@
       <c r="P41" s="325" t="s">
         <v>617</v>
       </c>
-      <c r="Q41" s="391">
+      <c r="Q41" s="392">
         <f t="shared" ref="Q41" si="37">SUM(H40:H42)</f>
         <v>-4982.5900000000365</v>
       </c>
-      <c r="R41" s="394" t="e">
+      <c r="R41" s="395" t="e">
         <f t="shared" ref="R41" si="38">IF(Q41&gt;=0,Q41,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="S41" s="394">
+      <c r="S41" s="395">
         <f t="shared" ref="S41" si="39">IF(Q41&lt;0,Q41,NA())</f>
         <v>-4982.5900000000365</v>
       </c>
@@ -69899,9 +69887,9 @@
         <v>#N/A</v>
       </c>
       <c r="P42" s="325"/>
-      <c r="Q42" s="392"/>
-      <c r="R42" s="395"/>
-      <c r="S42" s="395"/>
+      <c r="Q42" s="393"/>
+      <c r="R42" s="396"/>
+      <c r="S42" s="396"/>
     </row>
     <row r="43" spans="3:19" ht="15" customHeight="1">
       <c r="D43" s="107">
@@ -69939,9 +69927,9 @@
         <v>-27414.700000000044</v>
       </c>
       <c r="P43" s="326"/>
-      <c r="Q43" s="393"/>
-      <c r="R43" s="396"/>
-      <c r="S43" s="396"/>
+      <c r="Q43" s="394"/>
+      <c r="R43" s="397"/>
+      <c r="S43" s="397"/>
     </row>
     <row r="44" spans="3:19" ht="15" customHeight="1">
       <c r="D44" s="107">
@@ -69981,15 +69969,15 @@
       <c r="P44" s="325" t="s">
         <v>618</v>
       </c>
-      <c r="Q44" s="391">
+      <c r="Q44" s="392">
         <f t="shared" ref="Q44" si="40">SUM(H43:H45)</f>
         <v>42552.479999999967</v>
       </c>
-      <c r="R44" s="394">
+      <c r="R44" s="395">
         <f t="shared" ref="R44" si="41">IF(Q44&gt;=0,Q44,NA())</f>
         <v>42552.479999999967</v>
       </c>
-      <c r="S44" s="394" t="e">
+      <c r="S44" s="395" t="e">
         <f t="shared" ref="S44" si="42">IF(Q44&lt;0,Q44,NA())</f>
         <v>#N/A</v>
       </c>
@@ -70034,9 +70022,9 @@
         <v>#N/A</v>
       </c>
       <c r="P45" s="325"/>
-      <c r="Q45" s="392"/>
-      <c r="R45" s="395"/>
-      <c r="S45" s="395"/>
+      <c r="Q45" s="393"/>
+      <c r="R45" s="396"/>
+      <c r="S45" s="396"/>
     </row>
     <row r="46" spans="3:19" ht="15" customHeight="1">
       <c r="C46" s="111"/>
@@ -70075,9 +70063,9 @@
         <v>-32580.719999999943</v>
       </c>
       <c r="P46" s="326"/>
-      <c r="Q46" s="393"/>
-      <c r="R46" s="396"/>
-      <c r="S46" s="396"/>
+      <c r="Q46" s="394"/>
+      <c r="R46" s="397"/>
+      <c r="S46" s="397"/>
     </row>
     <row r="47" spans="3:19" ht="15" customHeight="1">
       <c r="D47" s="107">
@@ -70117,15 +70105,15 @@
       <c r="P47" s="325" t="s">
         <v>619</v>
       </c>
-      <c r="Q47" s="391">
+      <c r="Q47" s="392">
         <f t="shared" ref="Q47" si="43">SUM(H46:H48)</f>
         <v>84772.810000000172</v>
       </c>
-      <c r="R47" s="394">
+      <c r="R47" s="395">
         <f t="shared" ref="R47" si="44">IF(Q47&gt;=0,Q47,NA())</f>
         <v>84772.810000000172</v>
       </c>
-      <c r="S47" s="394" t="e">
+      <c r="S47" s="395" t="e">
         <f t="shared" ref="S47" si="45">IF(Q47&lt;0,Q47,NA())</f>
         <v>#N/A</v>
       </c>
@@ -70170,9 +70158,9 @@
         <v>#N/A</v>
       </c>
       <c r="P48" s="325"/>
-      <c r="Q48" s="392"/>
-      <c r="R48" s="395"/>
-      <c r="S48" s="395"/>
+      <c r="Q48" s="393"/>
+      <c r="R48" s="396"/>
+      <c r="S48" s="396"/>
     </row>
     <row r="49" spans="3:19" ht="15" customHeight="1">
       <c r="C49" s="111"/>
@@ -70211,9 +70199,9 @@
         <v>#N/A</v>
       </c>
       <c r="P49" s="326"/>
-      <c r="Q49" s="393"/>
-      <c r="R49" s="396"/>
-      <c r="S49" s="396"/>
+      <c r="Q49" s="394"/>
+      <c r="R49" s="397"/>
+      <c r="S49" s="397"/>
     </row>
     <row r="50" spans="3:19" ht="15" customHeight="1">
       <c r="D50" s="107">
@@ -70253,15 +70241,15 @@
       <c r="P50" s="325" t="s">
         <v>620</v>
       </c>
-      <c r="Q50" s="391">
+      <c r="Q50" s="392">
         <f t="shared" ref="Q50" si="46">SUM(H49:H51)</f>
         <v>154229.81000000003</v>
       </c>
-      <c r="R50" s="394">
+      <c r="R50" s="395">
         <f t="shared" ref="R50" si="47">IF(Q50&gt;=0,Q50,NA())</f>
         <v>154229.81000000003</v>
       </c>
-      <c r="S50" s="394" t="e">
+      <c r="S50" s="395" t="e">
         <f t="shared" ref="S50" si="48">IF(Q50&lt;0,Q50,NA())</f>
         <v>#N/A</v>
       </c>
@@ -70306,9 +70294,9 @@
         <v>#N/A</v>
       </c>
       <c r="P51" s="325"/>
-      <c r="Q51" s="392"/>
-      <c r="R51" s="395"/>
-      <c r="S51" s="395"/>
+      <c r="Q51" s="393"/>
+      <c r="R51" s="396"/>
+      <c r="S51" s="396"/>
     </row>
     <row r="52" spans="3:19" ht="15" customHeight="1">
       <c r="C52" s="111"/>
@@ -70352,9 +70340,9 @@
         <v>-15843.279999999942</v>
       </c>
       <c r="P52" s="326"/>
-      <c r="Q52" s="393"/>
-      <c r="R52" s="396"/>
-      <c r="S52" s="396"/>
+      <c r="Q52" s="394"/>
+      <c r="R52" s="397"/>
+      <c r="S52" s="397"/>
     </row>
     <row r="53" spans="3:19" ht="15" customHeight="1">
       <c r="D53" s="107">
@@ -70399,15 +70387,15 @@
       <c r="P53" s="325" t="s">
         <v>621</v>
       </c>
-      <c r="Q53" s="391">
+      <c r="Q53" s="392">
         <f t="shared" ref="Q53" si="49">SUM(H52:H54)</f>
         <v>78790.990000000107</v>
       </c>
-      <c r="R53" s="394">
+      <c r="R53" s="395">
         <f t="shared" ref="R53" si="50">IF(Q53&gt;=0,Q53,NA())</f>
         <v>78790.990000000107</v>
       </c>
-      <c r="S53" s="394" t="e">
+      <c r="S53" s="395" t="e">
         <f t="shared" ref="S53" si="51">IF(Q53&lt;0,Q53,NA())</f>
         <v>#N/A</v>
       </c>
@@ -70457,9 +70445,9 @@
         <v>#N/A</v>
       </c>
       <c r="P54" s="325"/>
-      <c r="Q54" s="392"/>
-      <c r="R54" s="395"/>
-      <c r="S54" s="395"/>
+      <c r="Q54" s="393"/>
+      <c r="R54" s="396"/>
+      <c r="S54" s="396"/>
     </row>
     <row r="55" spans="3:19" ht="15" customHeight="1">
       <c r="D55" s="107">
@@ -70502,9 +70490,9 @@
         <v>-26786.079999999929</v>
       </c>
       <c r="P55" s="326"/>
-      <c r="Q55" s="393"/>
-      <c r="R55" s="396"/>
-      <c r="S55" s="396"/>
+      <c r="Q55" s="394"/>
+      <c r="R55" s="397"/>
+      <c r="S55" s="397"/>
     </row>
     <row r="56" spans="3:19" ht="15" customHeight="1">
       <c r="D56" s="107">
@@ -70549,15 +70537,15 @@
       <c r="P56" s="325" t="s">
         <v>622</v>
       </c>
-      <c r="Q56" s="391">
+      <c r="Q56" s="392">
         <f t="shared" ref="Q56" si="52">SUM(H55:H57)</f>
         <v>81808.630000000121</v>
       </c>
-      <c r="R56" s="394">
+      <c r="R56" s="395">
         <f t="shared" ref="R56" si="53">IF(Q56&gt;=0,Q56,NA())</f>
         <v>81808.630000000121</v>
       </c>
-      <c r="S56" s="394" t="e">
+      <c r="S56" s="395" t="e">
         <f t="shared" ref="S56" si="54">IF(Q56&lt;0,Q56,NA())</f>
         <v>#N/A</v>
       </c>
@@ -70607,9 +70595,9 @@
         <v>-15997.259999999986</v>
       </c>
       <c r="P57" s="325"/>
-      <c r="Q57" s="392"/>
-      <c r="R57" s="395"/>
-      <c r="S57" s="395"/>
+      <c r="Q57" s="393"/>
+      <c r="R57" s="396"/>
+      <c r="S57" s="396"/>
     </row>
     <row r="58" spans="3:19" ht="15" customHeight="1">
       <c r="D58" s="107">
@@ -70649,9 +70637,9 @@
         <v>#N/A</v>
       </c>
       <c r="P58" s="326"/>
-      <c r="Q58" s="393"/>
-      <c r="R58" s="396"/>
-      <c r="S58" s="396"/>
+      <c r="Q58" s="394"/>
+      <c r="R58" s="397"/>
+      <c r="S58" s="397"/>
     </row>
     <row r="59" spans="3:19" ht="15" customHeight="1">
       <c r="D59" s="107">
@@ -70693,15 +70681,15 @@
       <c r="P59" s="325" t="s">
         <v>623</v>
       </c>
-      <c r="Q59" s="391">
+      <c r="Q59" s="392">
         <f t="shared" ref="Q59" si="55">SUM(H58:H60)</f>
         <v>0</v>
       </c>
-      <c r="R59" s="394">
+      <c r="R59" s="395">
         <f t="shared" ref="R59" si="56">IF(Q59&gt;=0,Q59,NA())</f>
         <v>0</v>
       </c>
-      <c r="S59" s="394" t="e">
+      <c r="S59" s="395" t="e">
         <f t="shared" ref="S59" si="57">IF(Q59&lt;0,Q59,NA())</f>
         <v>#N/A</v>
       </c>
@@ -70748,9 +70736,9 @@
         <v>#N/A</v>
       </c>
       <c r="P60" s="325"/>
-      <c r="Q60" s="392"/>
-      <c r="R60" s="395"/>
-      <c r="S60" s="395"/>
+      <c r="Q60" s="393"/>
+      <c r="R60" s="396"/>
+      <c r="S60" s="396"/>
     </row>
     <row r="61" spans="3:19" ht="15" customHeight="1">
       <c r="D61" s="107">
@@ -70790,9 +70778,9 @@
         <v>#N/A</v>
       </c>
       <c r="P61" s="326"/>
-      <c r="Q61" s="393"/>
-      <c r="R61" s="396"/>
-      <c r="S61" s="396"/>
+      <c r="Q61" s="394"/>
+      <c r="R61" s="397"/>
+      <c r="S61" s="397"/>
     </row>
     <row r="62" spans="3:19" ht="15" customHeight="1">
       <c r="D62" s="107">
@@ -70834,15 +70822,15 @@
       <c r="P62" s="325" t="s">
         <v>624</v>
       </c>
-      <c r="Q62" s="391">
+      <c r="Q62" s="392">
         <f t="shared" ref="Q62" si="58">SUM(H61:H63)</f>
         <v>0</v>
       </c>
-      <c r="R62" s="394">
+      <c r="R62" s="395">
         <f t="shared" ref="R62" si="59">IF(Q62&gt;=0,Q62,NA())</f>
         <v>0</v>
       </c>
-      <c r="S62" s="394" t="e">
+      <c r="S62" s="395" t="e">
         <f t="shared" ref="S62" si="60">IF(Q62&lt;0,Q62,NA())</f>
         <v>#N/A</v>
       </c>
@@ -70889,66 +70877,23 @@
         <v>#N/A</v>
       </c>
       <c r="P63" s="325"/>
-      <c r="Q63" s="392"/>
-      <c r="R63" s="395"/>
-      <c r="S63" s="395"/>
+      <c r="Q63" s="393"/>
+      <c r="R63" s="396"/>
+      <c r="S63" s="396"/>
     </row>
     <row r="64" spans="3:19">
       <c r="P64" s="326"/>
-      <c r="Q64" s="393"/>
-      <c r="R64" s="396"/>
-      <c r="S64" s="396"/>
+      <c r="Q64" s="394"/>
+      <c r="R64" s="397"/>
+      <c r="S64" s="397"/>
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="Q59:Q61"/>
-    <mergeCell ref="R59:R61"/>
-    <mergeCell ref="S59:S61"/>
-    <mergeCell ref="Q62:Q64"/>
-    <mergeCell ref="R62:R64"/>
-    <mergeCell ref="S62:S64"/>
-    <mergeCell ref="Q53:Q55"/>
-    <mergeCell ref="R53:R55"/>
-    <mergeCell ref="S53:S55"/>
-    <mergeCell ref="Q56:Q58"/>
-    <mergeCell ref="R56:R58"/>
-    <mergeCell ref="S56:S58"/>
-    <mergeCell ref="Q47:Q49"/>
-    <mergeCell ref="R47:R49"/>
-    <mergeCell ref="S47:S49"/>
-    <mergeCell ref="Q50:Q52"/>
-    <mergeCell ref="R50:R52"/>
-    <mergeCell ref="S50:S52"/>
-    <mergeCell ref="Q41:Q43"/>
-    <mergeCell ref="R41:R43"/>
-    <mergeCell ref="S41:S43"/>
-    <mergeCell ref="Q44:Q46"/>
-    <mergeCell ref="R44:R46"/>
-    <mergeCell ref="S44:S46"/>
-    <mergeCell ref="Q35:Q37"/>
-    <mergeCell ref="R35:R37"/>
-    <mergeCell ref="S35:S37"/>
-    <mergeCell ref="Q38:Q40"/>
-    <mergeCell ref="R38:R40"/>
-    <mergeCell ref="S38:S40"/>
-    <mergeCell ref="Q29:Q31"/>
-    <mergeCell ref="R29:R31"/>
-    <mergeCell ref="S29:S31"/>
-    <mergeCell ref="Q32:Q34"/>
-    <mergeCell ref="R32:R34"/>
-    <mergeCell ref="S32:S34"/>
-    <mergeCell ref="Q23:Q25"/>
-    <mergeCell ref="R23:R25"/>
-    <mergeCell ref="S23:S25"/>
-    <mergeCell ref="Q26:Q28"/>
-    <mergeCell ref="R26:R28"/>
-    <mergeCell ref="S26:S28"/>
-    <mergeCell ref="Q17:Q19"/>
-    <mergeCell ref="R17:R19"/>
-    <mergeCell ref="S17:S19"/>
-    <mergeCell ref="Q20:Q22"/>
-    <mergeCell ref="R20:R22"/>
-    <mergeCell ref="S20:S22"/>
+    <mergeCell ref="P5:P7"/>
+    <mergeCell ref="Q5:Q7"/>
+    <mergeCell ref="R5:R7"/>
+    <mergeCell ref="S5:S7"/>
+    <mergeCell ref="P8:P10"/>
     <mergeCell ref="P14:P16"/>
     <mergeCell ref="Q8:Q10"/>
     <mergeCell ref="R8:R10"/>
@@ -70960,11 +70905,54 @@
     <mergeCell ref="R14:R16"/>
     <mergeCell ref="S14:S16"/>
     <mergeCell ref="P11:P13"/>
-    <mergeCell ref="P5:P7"/>
-    <mergeCell ref="Q5:Q7"/>
-    <mergeCell ref="R5:R7"/>
-    <mergeCell ref="S5:S7"/>
-    <mergeCell ref="P8:P10"/>
+    <mergeCell ref="Q17:Q19"/>
+    <mergeCell ref="R17:R19"/>
+    <mergeCell ref="S17:S19"/>
+    <mergeCell ref="Q20:Q22"/>
+    <mergeCell ref="R20:R22"/>
+    <mergeCell ref="S20:S22"/>
+    <mergeCell ref="Q23:Q25"/>
+    <mergeCell ref="R23:R25"/>
+    <mergeCell ref="S23:S25"/>
+    <mergeCell ref="Q26:Q28"/>
+    <mergeCell ref="R26:R28"/>
+    <mergeCell ref="S26:S28"/>
+    <mergeCell ref="Q29:Q31"/>
+    <mergeCell ref="R29:R31"/>
+    <mergeCell ref="S29:S31"/>
+    <mergeCell ref="Q32:Q34"/>
+    <mergeCell ref="R32:R34"/>
+    <mergeCell ref="S32:S34"/>
+    <mergeCell ref="Q35:Q37"/>
+    <mergeCell ref="R35:R37"/>
+    <mergeCell ref="S35:S37"/>
+    <mergeCell ref="Q38:Q40"/>
+    <mergeCell ref="R38:R40"/>
+    <mergeCell ref="S38:S40"/>
+    <mergeCell ref="Q41:Q43"/>
+    <mergeCell ref="R41:R43"/>
+    <mergeCell ref="S41:S43"/>
+    <mergeCell ref="Q44:Q46"/>
+    <mergeCell ref="R44:R46"/>
+    <mergeCell ref="S44:S46"/>
+    <mergeCell ref="Q47:Q49"/>
+    <mergeCell ref="R47:R49"/>
+    <mergeCell ref="S47:S49"/>
+    <mergeCell ref="Q50:Q52"/>
+    <mergeCell ref="R50:R52"/>
+    <mergeCell ref="S50:S52"/>
+    <mergeCell ref="Q53:Q55"/>
+    <mergeCell ref="R53:R55"/>
+    <mergeCell ref="S53:S55"/>
+    <mergeCell ref="Q56:Q58"/>
+    <mergeCell ref="R56:R58"/>
+    <mergeCell ref="S56:S58"/>
+    <mergeCell ref="Q59:Q61"/>
+    <mergeCell ref="R59:R61"/>
+    <mergeCell ref="S59:S61"/>
+    <mergeCell ref="Q62:Q64"/>
+    <mergeCell ref="R62:R64"/>
+    <mergeCell ref="S62:S64"/>
   </mergeCells>
   <pageMargins left="0.51180555555555596" right="0.51180555555555596" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Demonstrações 2026 final.xlsx
+++ b/Demonstrações 2026 final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/victorgaioso/Documents/Gaioso/ANDALUZ/ESTRATÉGICO/Relatórios Estratégicos/2026/Anual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A79B3F-95F6-0944-88A9-4D947CD22EAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1941BE1-0189-2249-9549-F7F65B0453AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19340" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="600" windowWidth="38400" windowHeight="19340" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CNS" sheetId="17" r:id="rId1"/>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2749" uniqueCount="730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2750" uniqueCount="730">
   <si>
     <t>Investimento estratégico</t>
   </si>
@@ -4823,17 +4823,20 @@
     <xf numFmtId="0" fontId="32" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4844,13 +4847,19 @@
     <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -4871,15 +4880,6 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4892,11 +4892,11 @@
     <xf numFmtId="0" fontId="0" fillId="28" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="0" fontId="38" fillId="22" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="45"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="46" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -9206,7 +9206,7 @@
                 <c:formatCode>"R$ "#,##0.00</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>-15843.279999999942</c:v>
+                  <c:v>-15843.279999999993</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>62114.709999999955</c:v>
@@ -9215,13 +9215,13 @@
                   <c:v>32519.560000000092</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-26786.079999999929</c:v>
+                  <c:v>-26786.079999999936</c:v>
                 </c:pt>
                 <c:pt idx="4" formatCode="General">
-                  <c:v>124591.97000000003</c:v>
+                  <c:v>37989.300000000003</c:v>
                 </c:pt>
                 <c:pt idx="5" formatCode="General">
-                  <c:v>-15997.259999999986</c:v>
+                  <c:v>70982.610000000044</c:v>
                 </c:pt>
                 <c:pt idx="6" formatCode="General">
                   <c:v>#N/A</c:v>
@@ -9731,7 +9731,7 @@
                 <c:formatCode>"R$ "#,##0.00</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>-15843.279999999942</c:v>
+                  <c:v>-15843.279999999993</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>62114.709999999955</c:v>
@@ -9740,13 +9740,13 @@
                   <c:v>32519.560000000092</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-26786.079999999929</c:v>
+                  <c:v>-26786.079999999936</c:v>
                 </c:pt>
                 <c:pt idx="4" formatCode="General">
-                  <c:v>124591.97000000003</c:v>
+                  <c:v>37989.300000000003</c:v>
                 </c:pt>
                 <c:pt idx="5" formatCode="General">
-                  <c:v>-15997.259999999986</c:v>
+                  <c:v>70982.610000000044</c:v>
                 </c:pt>
                 <c:pt idx="6" formatCode="General">
                   <c:v>#N/A</c:v>
@@ -10373,7 +10373,7 @@
                   <c:v>293606.69</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>282443.93000000005</c:v>
+                  <c:v>282443.93</c:v>
                 </c:pt>
                 <c:pt idx="49">
                   <c:v>284996.23999999993</c:v>
@@ -10385,10 +10385,10 @@
                   <c:v>266720.63000000006</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>367273.20000000007</c:v>
+                  <c:v>277334.58</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>211611.88000000003</c:v>
+                  <c:v>301550.50000000006</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10992,10 +10992,10 @@
                   <c:v>404076.45000000042</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>528668.42000000039</c:v>
+                  <c:v>442065.75000000041</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>512671.16000000038</c:v>
+                  <c:v>513048.36000000045</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11385,10 +11385,10 @@
                   <c:v>154229.81000000003</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>78790.990000000107</c:v>
+                  <c:v>78790.990000000049</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>81808.630000000121</c:v>
+                  <c:v>82185.830000000104</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12158,10 +12158,10 @@
                   <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>124591.97000000003</c:v>
+                  <c:v>37989.300000000003</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>#N/A</c:v>
+                  <c:v>70982.610000000044</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12515,7 +12515,7 @@
                   <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>-15843.279999999942</c:v>
+                  <c:v>-15843.279999999993</c:v>
                 </c:pt>
                 <c:pt idx="49">
                   <c:v>#N/A</c:v>
@@ -12524,7 +12524,7 @@
                   <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>-26786.079999999929</c:v>
+                  <c:v>-26786.079999999936</c:v>
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>#N/A</c:v>
@@ -12920,10 +12920,10 @@
                   <c:v>404076.45000000042</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>528668.42000000039</c:v>
+                  <c:v>442065.75000000041</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>512671.16000000038</c:v>
+                  <c:v>513048.36000000045</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15715,7 +15715,7 @@
                 <c:formatCode>"R$ "#,##0.00</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>282443.93000000005</c:v>
+                  <c:v>282443.93</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>284996.23999999993</c:v>
@@ -15727,10 +15727,10 @@
                   <c:v>266720.63000000006</c:v>
                 </c:pt>
                 <c:pt idx="4" formatCode="General">
-                  <c:v>367273.20000000007</c:v>
+                  <c:v>277334.58</c:v>
                 </c:pt>
                 <c:pt idx="5" formatCode="General">
-                  <c:v>211611.88000000003</c:v>
+                  <c:v>301550.50000000006</c:v>
                 </c:pt>
                 <c:pt idx="6" formatCode="General">
                   <c:v>#N/A</c:v>
@@ -18067,19 +18067,19 @@
                 <c:formatCode>"R$ "#,##0;"(R$ "#,##0\);\-</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>412102.19410619029</c:v>
+                  <c:v>411081.85010619019</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>428586.28187043796</c:v>
+                  <c:v>427525.12411043787</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>445729.73314525548</c:v>
+                  <c:v>444626.12907485542</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>463558.92247106571</c:v>
+                  <c:v>462411.17423784966</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>482101.27936990838</c:v>
+                  <c:v>480907.62120736373</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18576,16 +18576,16 @@
                   <c:v>-126321.09</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-138181.44</c:v>
+                  <c:v>-138181.44000000003</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>-196414.43999999997</c:v>
                 </c:pt>
                 <c:pt idx="4" formatCode="General">
-                  <c:v>-129779.16000000002</c:v>
+                  <c:v>-128726.11</c:v>
                 </c:pt>
                 <c:pt idx="5" formatCode="General">
-                  <c:v>-127763.55000000002</c:v>
+                  <c:v>-128816.60000000002</c:v>
                 </c:pt>
                 <c:pt idx="6" formatCode="General">
                   <c:v>#N/A</c:v>
@@ -19104,7 +19104,7 @@
                   <c:v>-68382.22</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-64575.130000000005</c:v>
+                  <c:v>-64575.130000000012</c:v>
                 </c:pt>
                 <c:pt idx="4" formatCode="General">
                   <c:v>-80932.890000000014</c:v>
@@ -19620,7 +19620,7 @@
                 <c:formatCode>"R$ "#,##0.00</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>19129.020000000051</c:v>
+                  <c:v>19129.02</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>97377.519999999946</c:v>
@@ -19629,13 +19629,13 @@
                   <c:v>66232.690000000075</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5731.0600000000632</c:v>
+                  <c:v>5731.0600000000559</c:v>
                 </c:pt>
                 <c:pt idx="4" formatCode="General">
-                  <c:v>156561.15000000002</c:v>
+                  <c:v>67675.579999999987</c:v>
                 </c:pt>
                 <c:pt idx="5" formatCode="General">
-                  <c:v>14464.840000000011</c:v>
+                  <c:v>103350.41000000003</c:v>
                 </c:pt>
                 <c:pt idx="6" formatCode="General">
                   <c:v>#N/A</c:v>
@@ -20157,7 +20157,7 @@
                   <c:v>-21131.769999999997</c:v>
                 </c:pt>
                 <c:pt idx="4" formatCode="General">
-                  <c:v>-19711.419999999995</c:v>
+                  <c:v>-20692.519999999997</c:v>
                 </c:pt>
                 <c:pt idx="5" formatCode="General">
                   <c:v>-19731.16</c:v>
@@ -20670,7 +20670,7 @@
                 <c:formatCode>"R$ "#,##0.00</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>-4352.479999999945</c:v>
+                  <c:v>-4352.4799999999959</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>73205.26999999996</c:v>
@@ -20679,13 +20679,13 @@
                   <c:v>41596.290000000088</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-15400.709999999932</c:v>
+                  <c:v>-15400.709999999939</c:v>
                 </c:pt>
                 <c:pt idx="4" formatCode="General">
-                  <c:v>136849.73000000004</c:v>
+                  <c:v>46983.06</c:v>
                 </c:pt>
                 <c:pt idx="5" formatCode="General">
-                  <c:v>-5266.3199999999888</c:v>
+                  <c:v>83619.250000000044</c:v>
                 </c:pt>
                 <c:pt idx="6" formatCode="General">
                   <c:v>#N/A</c:v>
@@ -21195,7 +21195,7 @@
                 <c:formatCode>"R$ "#,##0.00</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>-5606.7099999999427</c:v>
+                  <c:v>-5606.7099999999937</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>72233.959999999963</c:v>
@@ -21204,13 +21204,13 @@
                   <c:v>41259.140000000087</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-16149.21999999993</c:v>
+                  <c:v>-16149.219999999937</c:v>
                 </c:pt>
                 <c:pt idx="4" formatCode="General">
-                  <c:v>133862.00000000003</c:v>
+                  <c:v>47259.33</c:v>
                 </c:pt>
                 <c:pt idx="5" formatCode="General">
-                  <c:v>-6871.1399999999867</c:v>
+                  <c:v>80108.73000000004</c:v>
                 </c:pt>
                 <c:pt idx="6" formatCode="General">
                   <c:v>#N/A</c:v>
@@ -27710,23 +27710,23 @@
       </c>
       <c r="B3" s="247">
         <f>IF(B9&gt;0,B9/B2,0)</f>
-        <v>6.0518524985168345E-4</v>
+        <v>6.0518524985168313E-4</v>
       </c>
       <c r="C3" s="247">
         <f t="shared" ref="C3:M3" si="0">IF(C9&gt;0,C9/C2,0)</f>
-        <v>5.854146323609927E-4</v>
+        <v>5.8541463236099281E-4</v>
       </c>
       <c r="D3" s="247">
         <f t="shared" si="0"/>
-        <v>5.9200573774115532E-4</v>
+        <v>5.9200573774115522E-4</v>
       </c>
       <c r="E3" s="247">
         <f t="shared" si="0"/>
-        <v>6.1552271929499278E-4</v>
+        <v>6.1552271929499289E-4</v>
       </c>
       <c r="F3" s="247">
         <f t="shared" si="0"/>
-        <v>6.1657497413773982E-4</v>
+        <v>6.165749741377396E-4</v>
       </c>
       <c r="G3" s="247">
         <f t="shared" si="0"/>
@@ -27867,22 +27867,22 @@
         <v>9</v>
       </c>
       <c r="B8" s="292">
-        <v>239855.20000000004</v>
+        <v>239855.19999999998</v>
       </c>
       <c r="C8" s="292">
         <v>250631.13999999996</v>
       </c>
       <c r="D8" s="292">
-        <v>228175.54000000004</v>
+        <v>228175.54000000007</v>
       </c>
       <c r="E8" s="292">
         <v>230080.36000000002</v>
       </c>
       <c r="F8" s="292">
-        <v>322852.92000000004</v>
+        <v>232914.3</v>
       </c>
       <c r="G8" s="292">
-        <v>187551.84000000005</v>
+        <v>277490.46000000008</v>
       </c>
       <c r="H8" s="292"/>
       <c r="I8" s="292"/>
@@ -27892,7 +27892,7 @@
       <c r="M8" s="292"/>
       <c r="N8" s="292">
         <f>SUM(B8:M8)</f>
-        <v>1459147.0000000002</v>
+        <v>1459147</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -27900,19 +27900,19 @@
         <v>523</v>
       </c>
       <c r="B9" s="290">
-        <v>175809.20000000007</v>
+        <v>175809.19999999998</v>
       </c>
       <c r="C9" s="290">
-        <v>178265.27999999994</v>
+        <v>178265.27999999997</v>
       </c>
       <c r="D9" s="290">
-        <v>183175.54000000007</v>
+        <v>183175.54000000004</v>
       </c>
       <c r="E9" s="290">
-        <v>191954.81999999998</v>
+        <v>191954.82</v>
       </c>
       <c r="F9" s="290">
-        <v>192414.30000000005</v>
+        <v>192414.3</v>
       </c>
       <c r="G9" s="290">
         <v>187551.84000000005</v>
@@ -27925,7 +27925,7 @@
       <c r="M9" s="290"/>
       <c r="N9" s="290">
         <f t="shared" ref="N9:N49" si="2">SUM(B9:M9)</f>
-        <v>1109170.98</v>
+        <v>1109170.9800000002</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -27978,10 +27978,10 @@
         <v>13</v>
       </c>
       <c r="F11" s="200">
-        <v>117700</v>
+        <v>34000</v>
       </c>
       <c r="G11" s="200">
-        <v>0</v>
+        <v>83700</v>
       </c>
       <c r="H11" s="200"/>
       <c r="I11" s="200"/>
@@ -28010,11 +28010,11 @@
       <c r="E12" s="200">
         <v>30425.54</v>
       </c>
-      <c r="F12" s="200">
+      <c r="F12" s="200" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="200">
         <v>6238.62</v>
-      </c>
-      <c r="G12" s="200">
-        <v>0</v>
       </c>
       <c r="H12" s="200"/>
       <c r="I12" s="200"/>
@@ -28098,22 +28098,22 @@
         <v>10</v>
       </c>
       <c r="B15" s="292">
-        <v>239855.20000000004</v>
+        <v>239855.19999999998</v>
       </c>
       <c r="C15" s="292">
         <v>250631.13999999996</v>
       </c>
       <c r="D15" s="292">
-        <v>228175.54000000004</v>
+        <v>228175.54000000007</v>
       </c>
       <c r="E15" s="292">
         <v>230080.36000000002</v>
       </c>
       <c r="F15" s="292">
-        <v>322852.92000000004</v>
+        <v>232914.3</v>
       </c>
       <c r="G15" s="292">
-        <v>187551.84000000005</v>
+        <v>277490.46000000008</v>
       </c>
       <c r="H15" s="292"/>
       <c r="I15" s="292"/>
@@ -28123,7 +28123,7 @@
       <c r="M15" s="292"/>
       <c r="N15" s="292">
         <f t="shared" si="2"/>
-        <v>1459147.0000000002</v>
+        <v>1459147</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -28137,16 +28137,16 @@
         <v>-108921.69</v>
       </c>
       <c r="D16" s="290">
-        <v>-121072.98</v>
+        <v>-121072.98000000003</v>
       </c>
       <c r="E16" s="290">
         <v>-170232.02</v>
       </c>
       <c r="F16" s="290">
-        <v>-111814.32000000002</v>
+        <v>-110761.27</v>
       </c>
       <c r="G16" s="290">
-        <v>-110497.56</v>
+        <v>-111550.61</v>
       </c>
       <c r="H16" s="290"/>
       <c r="I16" s="290"/>
@@ -28156,7 +28156,7 @@
       <c r="M16" s="290"/>
       <c r="N16" s="290">
         <f t="shared" si="2"/>
-        <v>-800282.45</v>
+        <v>-800282.45000000007</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -28176,10 +28176,10 @@
         <v>-81040.13</v>
       </c>
       <c r="F17" s="200">
-        <v>-22001.09</v>
+        <v>-20948.04</v>
       </c>
       <c r="G17" s="200">
-        <v>-22491.67</v>
+        <v>-23544.719999999998</v>
       </c>
       <c r="H17" s="200"/>
       <c r="I17" s="200"/>
@@ -28193,7 +28193,7 @@
       </c>
       <c r="O17" s="241">
         <f>N17/N8</f>
-        <v>-0.1821290658172206</v>
+        <v>-0.18212906581722063</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -28216,7 +28216,7 @@
         <v>-80187.14</v>
       </c>
       <c r="G18" s="200">
-        <v>-81460.06</v>
+        <v>-81460.060000000012</v>
       </c>
       <c r="H18" s="200"/>
       <c r="I18" s="200"/>
@@ -28366,7 +28366,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="292">
-        <v>62111.320000000036</v>
+        <v>62111.319999999978</v>
       </c>
       <c r="C23" s="292">
         <v>141709.44999999995</v>
@@ -28378,10 +28378,10 @@
         <v>59848.340000000026</v>
       </c>
       <c r="F23" s="292">
-        <v>211038.60000000003</v>
+        <v>122153.02999999998</v>
       </c>
       <c r="G23" s="292">
-        <v>77054.280000000057</v>
+        <v>165939.85000000009</v>
       </c>
       <c r="H23" s="292"/>
       <c r="I23" s="292"/>
@@ -28399,7 +28399,7 @@
         <v>15</v>
       </c>
       <c r="B24" s="290">
-        <v>-45973.640000000014</v>
+        <v>-45973.640000000007</v>
       </c>
       <c r="C24" s="290">
         <v>-39048.449999999997</v>
@@ -28408,7 +28408,7 @@
         <v>-52448.170000000006</v>
       </c>
       <c r="E24" s="290">
-        <v>-47406.540000000008</v>
+        <v>-47406.540000000015</v>
       </c>
       <c r="F24" s="290">
         <v>-60020.040000000023</v>
@@ -28435,7 +28435,7 @@
         <v>-6659.05</v>
       </c>
       <c r="C25" s="200">
-        <v>-10429.4</v>
+        <v>-10429.400000000001</v>
       </c>
       <c r="D25" s="200">
         <v>-13062.59</v>
@@ -28471,16 +28471,16 @@
         <v>-9519.0499999999993</v>
       </c>
       <c r="D26" s="200">
-        <v>-13097.35</v>
+        <v>-13097.349999999999</v>
       </c>
       <c r="E26" s="200">
-        <v>-10678.38</v>
+        <v>-10678.379999999997</v>
       </c>
       <c r="F26" s="200">
         <v>-9918.6999999999989</v>
       </c>
       <c r="G26" s="200">
-        <v>-9939.9599999999991</v>
+        <v>-9939.9600000000009</v>
       </c>
       <c r="H26" s="200"/>
       <c r="I26" s="200"/>
@@ -28531,7 +28531,7 @@
         <v>509</v>
       </c>
       <c r="B28" s="200">
-        <v>-1119.1799999999998</v>
+        <v>-1119.18</v>
       </c>
       <c r="C28" s="200" t="s">
         <v>13</v>
@@ -28556,7 +28556,7 @@
       <c r="M28" s="200"/>
       <c r="N28" s="200">
         <f t="shared" si="2"/>
-        <v>-1119.1799999999998</v>
+        <v>-1119.18</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -28597,7 +28597,7 @@
         <v>16</v>
       </c>
       <c r="B30" s="292">
-        <v>16137.680000000022</v>
+        <v>16137.679999999971</v>
       </c>
       <c r="C30" s="292">
         <v>102660.99999999996</v>
@@ -28606,13 +28606,13 @@
         <v>54654.390000000036</v>
       </c>
       <c r="E30" s="292">
-        <v>12441.800000000017</v>
+        <v>12441.80000000001</v>
       </c>
       <c r="F30" s="292">
-        <v>151018.56</v>
+        <v>62132.989999999962</v>
       </c>
       <c r="G30" s="292">
-        <v>30506.250000000036</v>
+        <v>119391.82000000007</v>
       </c>
       <c r="H30" s="292"/>
       <c r="I30" s="292"/>
@@ -28622,7 +28622,7 @@
       <c r="M30" s="292"/>
       <c r="N30" s="292">
         <f t="shared" si="2"/>
-        <v>367419.68000000011</v>
+        <v>367419.68000000005</v>
       </c>
       <c r="P30" s="207"/>
     </row>
@@ -28643,7 +28643,7 @@
         <v>-20323.959999999995</v>
       </c>
       <c r="F31" s="290">
-        <v>-18923.659999999996</v>
+        <v>-19904.759999999998</v>
       </c>
       <c r="G31" s="290">
         <v>-18471.95</v>
@@ -28656,7 +28656,7 @@
       <c r="M31" s="290"/>
       <c r="N31" s="290">
         <f t="shared" si="2"/>
-        <v>-126441.01999999997</v>
+        <v>-127422.11999999997</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -28676,7 +28676,7 @@
         <v>-8252.4599999999991</v>
       </c>
       <c r="F32" s="200">
-        <v>-8184.48</v>
+        <v>-9165.58</v>
       </c>
       <c r="G32" s="200">
         <v>-7997.1799999999994</v>
@@ -28689,7 +28689,7 @@
       <c r="M32" s="200"/>
       <c r="N32" s="200">
         <f t="shared" si="2"/>
-        <v>-51305.659999999996</v>
+        <v>-52286.76</v>
       </c>
     </row>
     <row r="33" spans="1:14">
@@ -28865,10 +28865,10 @@
         <v>-906.8599999999999</v>
       </c>
       <c r="C38" s="200">
-        <v>-906.86</v>
+        <v>-906.8599999999999</v>
       </c>
       <c r="D38" s="200">
-        <v>-906.86</v>
+        <v>-906.8599999999999</v>
       </c>
       <c r="E38" s="200">
         <v>-906.8599999999999</v>
@@ -28994,7 +28994,7 @@
         <v>18</v>
       </c>
       <c r="B42" s="292">
-        <v>-6585.0499999999738</v>
+        <v>-6585.0500000000247</v>
       </c>
       <c r="C42" s="292">
         <v>80447.51999999996</v>
@@ -29003,13 +29003,13 @@
         <v>30869.150000000045</v>
       </c>
       <c r="E42" s="292">
-        <v>-7882.159999999978</v>
+        <v>-7882.1599999999853</v>
       </c>
       <c r="F42" s="292">
-        <v>132094.9</v>
+        <v>42228.229999999967</v>
       </c>
       <c r="G42" s="292">
-        <v>12034.300000000036</v>
+        <v>100919.87000000007</v>
       </c>
       <c r="H42" s="292"/>
       <c r="I42" s="292"/>
@@ -29019,7 +29019,7 @@
       <c r="M42" s="292"/>
       <c r="N42" s="292">
         <f t="shared" si="2"/>
-        <v>240978.66000000009</v>
+        <v>239997.56000000006</v>
       </c>
     </row>
     <row r="43" spans="1:14">
@@ -29027,22 +29027,22 @@
         <v>19</v>
       </c>
       <c r="B43" s="290">
-        <v>-1256.5699999999977</v>
+        <v>-1256.5699999999981</v>
       </c>
       <c r="C43" s="290">
-        <v>-973.19999999999925</v>
+        <v>-973.19999999999879</v>
       </c>
       <c r="D43" s="290">
         <v>-337.74999999999767</v>
       </c>
       <c r="E43" s="290">
-        <v>-751.95999999999833</v>
+        <v>-751.95999999999879</v>
       </c>
       <c r="F43" s="290">
-        <v>-2992.9199999999992</v>
+        <v>271.08000000000072</v>
       </c>
       <c r="G43" s="290">
-        <v>-1597.2699999999993</v>
+        <v>-3502.9699999999984</v>
       </c>
       <c r="H43" s="290"/>
       <c r="I43" s="290"/>
@@ -29052,7 +29052,7 @@
       <c r="M43" s="290"/>
       <c r="N43" s="290">
         <f t="shared" si="2"/>
-        <v>-7909.6699999999919</v>
+        <v>-6551.3699999999908</v>
       </c>
     </row>
     <row r="44" spans="1:14">
@@ -29093,7 +29093,7 @@
         <v>21</v>
       </c>
       <c r="B45" s="292">
-        <v>-7832.9899999999716</v>
+        <v>-7832.9900000000225</v>
       </c>
       <c r="C45" s="292">
         <v>79476.209999999963</v>
@@ -29102,13 +29102,13 @@
         <v>30532.000000000047</v>
       </c>
       <c r="E45" s="292">
-        <v>-8630.6699999999764</v>
+        <v>-8630.6699999999837</v>
       </c>
       <c r="F45" s="292">
-        <v>129107.17</v>
+        <v>42504.499999999971</v>
       </c>
       <c r="G45" s="292">
-        <v>10437.030000000037</v>
+        <v>97416.900000000067</v>
       </c>
       <c r="H45" s="292"/>
       <c r="I45" s="292"/>
@@ -29118,7 +29118,7 @@
       <c r="M45" s="292"/>
       <c r="N45" s="292">
         <f t="shared" si="2"/>
-        <v>233088.75000000006</v>
+        <v>233465.95000000007</v>
       </c>
     </row>
     <row r="46" spans="1:14">
@@ -29225,7 +29225,7 @@
         <v>23</v>
       </c>
       <c r="B49" s="292">
-        <v>-18069.559999999972</v>
+        <v>-18069.560000000023</v>
       </c>
       <c r="C49" s="292">
         <v>69356.959999999963</v>
@@ -29234,13 +29234,13 @@
         <v>21792.420000000049</v>
       </c>
       <c r="E49" s="292">
-        <v>-19267.529999999977</v>
+        <v>-19267.529999999984</v>
       </c>
       <c r="F49" s="292">
-        <v>119837.14</v>
+        <v>33234.469999999972</v>
       </c>
       <c r="G49" s="292">
-        <v>1310.9100000000381</v>
+        <v>88290.780000000072</v>
       </c>
       <c r="H49" s="292"/>
       <c r="I49" s="292"/>
@@ -29250,7 +29250,7 @@
       <c r="M49" s="292"/>
       <c r="N49" s="292">
         <f t="shared" si="2"/>
-        <v>174960.34000000008</v>
+        <v>175337.54000000004</v>
       </c>
     </row>
     <row r="53" spans="1:14">
@@ -29259,15 +29259,15 @@
       </c>
       <c r="B53" s="14">
         <f t="shared" ref="B53:N53" si="3">(B11*(1+$O$17))+B27</f>
-        <v>6439.7317622145019</v>
+        <v>6439.7317622144983</v>
       </c>
       <c r="C53" s="14">
         <f t="shared" si="3"/>
-        <v>8707.611762214503</v>
+        <v>8707.6117622144993</v>
       </c>
       <c r="D53" s="14">
         <f t="shared" si="3"/>
-        <v>1572.3817622145034</v>
+        <v>1572.3817622144998</v>
       </c>
       <c r="E53" s="14">
         <f t="shared" si="3"/>
@@ -29275,11 +29275,11 @@
       </c>
       <c r="F53" s="14">
         <f t="shared" si="3"/>
-        <v>63527.948953313142</v>
+        <v>-4927.8482377855034</v>
       </c>
       <c r="G53" s="14">
         <f t="shared" si="3"/>
-        <v>-22372</v>
+        <v>46083.797191098638</v>
       </c>
       <c r="H53" s="14">
         <f t="shared" si="3"/>
@@ -29320,7 +29320,7 @@
       </c>
       <c r="C54" s="14">
         <f t="shared" ref="C54:N54" si="4">(C12*(1+$O$17))+C28</f>
-        <v>15307.157902234116</v>
+        <v>15307.157902234114</v>
       </c>
       <c r="D54" s="14">
         <f t="shared" si="4"/>
@@ -29328,15 +29328,15 @@
       </c>
       <c r="E54" s="14">
         <f t="shared" si="4"/>
-        <v>24884.164822815525</v>
+        <v>24884.164822815521</v>
       </c>
       <c r="F54" s="14">
         <f t="shared" si="4"/>
-        <v>5102.3859674113719</v>
+        <v>0</v>
       </c>
       <c r="G54" s="14">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5102.385967411371</v>
       </c>
       <c r="H54" s="14">
         <f t="shared" si="4"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="N54" s="14">
         <f t="shared" si="4"/>
-        <v>56725.576048429946</v>
+        <v>56725.576048429939</v>
       </c>
     </row>
     <row r="58" spans="1:14">
@@ -29427,23 +29427,23 @@
       </c>
       <c r="B59" s="250">
         <f>IF(B58&gt;0,B9/B2,"")</f>
-        <v>6.0518524985168345E-4</v>
+        <v>6.0518524985168313E-4</v>
       </c>
       <c r="C59" s="250">
         <f t="shared" ref="C59:M59" si="6">IF(C58&gt;0,C9/C2,"")</f>
-        <v>5.854146323609927E-4</v>
+        <v>5.8541463236099281E-4</v>
       </c>
       <c r="D59" s="250">
         <f t="shared" si="6"/>
-        <v>5.9200573774115532E-4</v>
+        <v>5.9200573774115522E-4</v>
       </c>
       <c r="E59" s="250">
         <f t="shared" si="6"/>
-        <v>6.1552271929499278E-4</v>
+        <v>6.1552271929499289E-4</v>
       </c>
       <c r="F59" s="250">
         <f t="shared" si="6"/>
-        <v>6.1657497413773982E-4</v>
+        <v>6.165749741377396E-4</v>
       </c>
       <c r="G59" s="250">
         <f t="shared" si="6"/>
@@ -29475,7 +29475,7 @@
       </c>
       <c r="N59" s="252">
         <f>AVERAGE(B59:E59)</f>
-        <v>5.9953208481220615E-4</v>
+        <v>5.9953208481220593E-4</v>
       </c>
     </row>
     <row r="60" spans="1:14">
@@ -48930,17 +48930,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1">
-      <c r="A1" s="405" t="s">
+      <c r="A1" s="406" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="405"/>
-      <c r="C1" s="405"/>
-      <c r="D1" s="405"/>
-      <c r="E1" s="405"/>
-      <c r="F1" s="405"/>
-      <c r="G1" s="405"/>
-      <c r="H1" s="405"/>
-      <c r="I1" s="405"/>
+      <c r="B1" s="406"/>
+      <c r="C1" s="406"/>
+      <c r="D1" s="406"/>
+      <c r="E1" s="406"/>
+      <c r="F1" s="406"/>
+      <c r="G1" s="406"/>
+      <c r="H1" s="406"/>
+      <c r="I1" s="406"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1">
       <c r="A2" s="114"/>
@@ -48968,7 +48968,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="15" customHeight="1">
-      <c r="A3" s="406" t="s">
+      <c r="A3" s="405" t="s">
         <v>197</v>
       </c>
       <c r="B3" s="116" t="s">
@@ -48990,7 +48990,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1">
-      <c r="A4" s="406"/>
+      <c r="A4" s="405"/>
       <c r="B4" s="116" t="s">
         <v>199</v>
       </c>
@@ -49009,7 +49009,7 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1">
-      <c r="A5" s="406"/>
+      <c r="A5" s="405"/>
       <c r="B5" s="116" t="s">
         <v>200</v>
       </c>
@@ -49027,7 +49027,7 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="15" customHeight="1">
-      <c r="A6" s="406"/>
+      <c r="A6" s="405"/>
       <c r="B6" s="116" t="s">
         <v>201</v>
       </c>
@@ -49045,7 +49045,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1">
-      <c r="A7" s="406"/>
+      <c r="A7" s="405"/>
       <c r="B7" s="116" t="s">
         <v>25</v>
       </c>
@@ -49063,7 +49063,7 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1">
-      <c r="A8" s="406" t="s">
+      <c r="A8" s="405" t="s">
         <v>202</v>
       </c>
       <c r="B8" s="116" t="s">
@@ -49087,7 +49087,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1">
-      <c r="A9" s="406"/>
+      <c r="A9" s="405"/>
       <c r="B9" s="116" t="s">
         <v>199</v>
       </c>
@@ -49105,7 +49105,7 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1">
-      <c r="A10" s="406"/>
+      <c r="A10" s="405"/>
       <c r="B10" s="116" t="s">
         <v>200</v>
       </c>
@@ -49123,7 +49123,7 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1">
-      <c r="A11" s="406"/>
+      <c r="A11" s="405"/>
       <c r="B11" s="116" t="s">
         <v>201</v>
       </c>
@@ -49141,7 +49141,7 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1">
-      <c r="A12" s="406"/>
+      <c r="A12" s="405"/>
       <c r="B12" s="116" t="s">
         <v>25</v>
       </c>
@@ -49159,7 +49159,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1">
-      <c r="A13" s="406" t="s">
+      <c r="A13" s="405" t="s">
         <v>203</v>
       </c>
       <c r="B13" s="116" t="s">
@@ -49183,7 +49183,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1">
-      <c r="A14" s="406"/>
+      <c r="A14" s="405"/>
       <c r="B14" s="116" t="s">
         <v>199</v>
       </c>
@@ -49203,7 +49203,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1">
-      <c r="A15" s="406"/>
+      <c r="A15" s="405"/>
       <c r="B15" s="116" t="s">
         <v>200</v>
       </c>
@@ -49221,7 +49221,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1">
-      <c r="A16" s="406"/>
+      <c r="A16" s="405"/>
       <c r="B16" s="116" t="s">
         <v>201</v>
       </c>
@@ -49239,7 +49239,7 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
-      <c r="A17" s="406"/>
+      <c r="A17" s="405"/>
       <c r="B17" s="116" t="s">
         <v>25</v>
       </c>
@@ -49257,7 +49257,7 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1">
-      <c r="A18" s="406" t="s">
+      <c r="A18" s="405" t="s">
         <v>190</v>
       </c>
       <c r="B18" s="116" t="s">
@@ -49283,7 +49283,7 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1">
-      <c r="A19" s="406"/>
+      <c r="A19" s="405"/>
       <c r="B19" s="116" t="s">
         <v>199</v>
       </c>
@@ -49303,7 +49303,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1">
-      <c r="A20" s="406"/>
+      <c r="A20" s="405"/>
       <c r="B20" s="116" t="s">
         <v>200</v>
       </c>
@@ -49321,7 +49321,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1">
-      <c r="A21" s="406"/>
+      <c r="A21" s="405"/>
       <c r="B21" s="116" t="s">
         <v>201</v>
       </c>
@@ -49339,7 +49339,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="15" customHeight="1">
-      <c r="A22" s="406"/>
+      <c r="A22" s="405"/>
       <c r="B22" s="116" t="s">
         <v>25</v>
       </c>
@@ -49357,7 +49357,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1">
-      <c r="A23" s="406" t="s">
+      <c r="A23" s="405" t="s">
         <v>204</v>
       </c>
       <c r="B23" s="116" t="s">
@@ -49383,7 +49383,7 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1">
-      <c r="A24" s="406"/>
+      <c r="A24" s="405"/>
       <c r="B24" s="116" t="s">
         <v>199</v>
       </c>
@@ -49405,7 +49405,7 @@
       </c>
     </row>
     <row r="25" spans="1:9" ht="15" customHeight="1">
-      <c r="A25" s="406"/>
+      <c r="A25" s="405"/>
       <c r="B25" s="116" t="s">
         <v>200</v>
       </c>
@@ -49425,7 +49425,7 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="15" customHeight="1">
-      <c r="A26" s="406"/>
+      <c r="A26" s="405"/>
       <c r="B26" s="116" t="s">
         <v>201</v>
       </c>
@@ -49443,7 +49443,7 @@
       </c>
     </row>
     <row r="27" spans="1:9" ht="15" customHeight="1">
-      <c r="A27" s="406"/>
+      <c r="A27" s="405"/>
       <c r="B27" s="116" t="s">
         <v>25</v>
       </c>
@@ -49461,7 +49461,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" ht="15" customHeight="1">
-      <c r="A28" s="406" t="s">
+      <c r="A28" s="405" t="s">
         <v>205</v>
       </c>
       <c r="B28" s="116" t="s">
@@ -49487,7 +49487,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="15" customHeight="1">
-      <c r="A29" s="406"/>
+      <c r="A29" s="405"/>
       <c r="B29" s="116" t="s">
         <v>199</v>
       </c>
@@ -49509,7 +49509,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" ht="15" customHeight="1">
-      <c r="A30" s="406"/>
+      <c r="A30" s="405"/>
       <c r="B30" s="116" t="s">
         <v>200</v>
       </c>
@@ -49529,7 +49529,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="15" customHeight="1">
-      <c r="A31" s="406"/>
+      <c r="A31" s="405"/>
       <c r="B31" s="116" t="s">
         <v>201</v>
       </c>
@@ -49547,7 +49547,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" ht="15" customHeight="1">
-      <c r="A32" s="406"/>
+      <c r="A32" s="405"/>
       <c r="B32" s="116" t="s">
         <v>25</v>
       </c>
@@ -49565,7 +49565,7 @@
       </c>
     </row>
     <row r="33" spans="1:9" ht="15" customHeight="1">
-      <c r="A33" s="406" t="s">
+      <c r="A33" s="405" t="s">
         <v>206</v>
       </c>
       <c r="B33" s="116" t="s">
@@ -49591,7 +49591,7 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="15" customHeight="1">
-      <c r="A34" s="406"/>
+      <c r="A34" s="405"/>
       <c r="B34" s="116" t="s">
         <v>199</v>
       </c>
@@ -49613,7 +49613,7 @@
       </c>
     </row>
     <row r="35" spans="1:9" ht="15" customHeight="1">
-      <c r="A35" s="406"/>
+      <c r="A35" s="405"/>
       <c r="B35" s="116" t="s">
         <v>200</v>
       </c>
@@ -49633,7 +49633,7 @@
       </c>
     </row>
     <row r="36" spans="1:9" ht="15" customHeight="1">
-      <c r="A36" s="406"/>
+      <c r="A36" s="405"/>
       <c r="B36" s="116" t="s">
         <v>201</v>
       </c>
@@ -49651,7 +49651,7 @@
       </c>
     </row>
     <row r="37" spans="1:9" ht="15" customHeight="1">
-      <c r="A37" s="406"/>
+      <c r="A37" s="405"/>
       <c r="B37" s="116" t="s">
         <v>25</v>
       </c>
@@ -49669,7 +49669,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" ht="15" customHeight="1">
-      <c r="A38" s="406" t="s">
+      <c r="A38" s="405" t="s">
         <v>207</v>
       </c>
       <c r="B38" s="116" t="s">
@@ -49697,7 +49697,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" ht="15" customHeight="1">
-      <c r="A39" s="406"/>
+      <c r="A39" s="405"/>
       <c r="B39" s="116" t="s">
         <v>199</v>
       </c>
@@ -49721,7 +49721,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="15" customHeight="1">
-      <c r="A40" s="406"/>
+      <c r="A40" s="405"/>
       <c r="B40" s="116" t="s">
         <v>200</v>
       </c>
@@ -49743,7 +49743,7 @@
       </c>
     </row>
     <row r="41" spans="1:9" ht="15" customHeight="1">
-      <c r="A41" s="406"/>
+      <c r="A41" s="405"/>
       <c r="B41" s="116" t="s">
         <v>201</v>
       </c>
@@ -49761,7 +49761,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1">
-      <c r="A42" s="406"/>
+      <c r="A42" s="405"/>
       <c r="B42" s="116" t="s">
         <v>25</v>
       </c>
@@ -49779,7 +49779,7 @@
       </c>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1">
-      <c r="A43" s="406" t="s">
+      <c r="A43" s="405" t="s">
         <v>208</v>
       </c>
       <c r="B43" s="116" t="s">
@@ -49807,7 +49807,7 @@
       </c>
     </row>
     <row r="44" spans="1:9" ht="15" customHeight="1">
-      <c r="A44" s="406"/>
+      <c r="A44" s="405"/>
       <c r="B44" s="116" t="s">
         <v>199</v>
       </c>
@@ -49832,7 +49832,7 @@
       </c>
     </row>
     <row r="45" spans="1:9" ht="15" customHeight="1">
-      <c r="A45" s="406"/>
+      <c r="A45" s="405"/>
       <c r="B45" s="116" t="s">
         <v>200</v>
       </c>
@@ -49854,7 +49854,7 @@
       </c>
     </row>
     <row r="46" spans="1:9" ht="15" customHeight="1">
-      <c r="A46" s="406"/>
+      <c r="A46" s="405"/>
       <c r="B46" s="116" t="s">
         <v>201</v>
       </c>
@@ -49876,7 +49876,7 @@
       </c>
     </row>
     <row r="47" spans="1:9" ht="15" customHeight="1">
-      <c r="A47" s="406"/>
+      <c r="A47" s="405"/>
       <c r="B47" s="116" t="s">
         <v>25</v>
       </c>
@@ -49894,7 +49894,7 @@
       </c>
     </row>
     <row r="48" spans="1:9" ht="15" customHeight="1">
-      <c r="A48" s="406" t="s">
+      <c r="A48" s="405" t="s">
         <v>209</v>
       </c>
       <c r="B48" s="116" t="s">
@@ -49922,7 +49922,7 @@
       </c>
     </row>
     <row r="49" spans="1:9" ht="15" customHeight="1">
-      <c r="A49" s="406"/>
+      <c r="A49" s="405"/>
       <c r="B49" s="116" t="s">
         <v>199</v>
       </c>
@@ -49946,7 +49946,7 @@
       </c>
     </row>
     <row r="50" spans="1:9" ht="15" customHeight="1">
-      <c r="A50" s="406"/>
+      <c r="A50" s="405"/>
       <c r="B50" s="116" t="s">
         <v>200</v>
       </c>
@@ -49968,7 +49968,7 @@
       </c>
     </row>
     <row r="51" spans="1:9" ht="15" customHeight="1">
-      <c r="A51" s="406"/>
+      <c r="A51" s="405"/>
       <c r="B51" s="116" t="s">
         <v>201</v>
       </c>
@@ -49990,7 +49990,7 @@
       </c>
     </row>
     <row r="52" spans="1:9" ht="15" customHeight="1">
-      <c r="A52" s="406"/>
+      <c r="A52" s="405"/>
       <c r="B52" s="116" t="s">
         <v>25</v>
       </c>
@@ -50008,7 +50008,7 @@
       </c>
     </row>
     <row r="53" spans="1:9" ht="15" customHeight="1">
-      <c r="A53" s="406" t="s">
+      <c r="A53" s="405" t="s">
         <v>210</v>
       </c>
       <c r="B53" s="116" t="s">
@@ -50039,7 +50039,7 @@
       </c>
     </row>
     <row r="54" spans="1:9" ht="15" customHeight="1">
-      <c r="A54" s="406"/>
+      <c r="A54" s="405"/>
       <c r="B54" s="116" t="s">
         <v>199</v>
       </c>
@@ -50065,7 +50065,7 @@
       </c>
     </row>
     <row r="55" spans="1:9" ht="15" customHeight="1">
-      <c r="A55" s="406"/>
+      <c r="A55" s="405"/>
       <c r="B55" s="116" t="s">
         <v>200</v>
       </c>
@@ -50089,7 +50089,7 @@
       </c>
     </row>
     <row r="56" spans="1:9" ht="15" customHeight="1">
-      <c r="A56" s="406"/>
+      <c r="A56" s="405"/>
       <c r="B56" s="116" t="s">
         <v>201</v>
       </c>
@@ -50113,7 +50113,7 @@
       </c>
     </row>
     <row r="57" spans="1:9" ht="15" customHeight="1">
-      <c r="A57" s="406"/>
+      <c r="A57" s="405"/>
       <c r="B57" s="116" t="s">
         <v>25</v>
       </c>
@@ -50231,6 +50231,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="A18:A22"/>
     <mergeCell ref="A48:A52"/>
     <mergeCell ref="A53:A57"/>
     <mergeCell ref="A23:A27"/>
@@ -50238,11 +50243,6 @@
     <mergeCell ref="A33:A37"/>
     <mergeCell ref="A38:A42"/>
     <mergeCell ref="A43:A47"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="A8:A12"/>
-    <mergeCell ref="A13:A17"/>
-    <mergeCell ref="A18:A22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -50271,7 +50271,7 @@
       <c r="G1" s="407"/>
       <c r="I1" s="369">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="J1" s="370">
         <f ca="1">YEAR(I1)</f>
@@ -50291,7 +50291,7 @@
       </c>
       <c r="B4" s="354">
         <f>Projeção!Q61</f>
-        <v>1007499.862058525</v>
+        <v>1006518.7620585249</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="18" customHeight="1">
@@ -50324,7 +50324,7 @@
       </c>
       <c r="B8" s="355">
         <f>Projeção!R61</f>
-        <v>0.39330239600020178</v>
+        <v>0.39271102002021818</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="21.75" customHeight="1">
@@ -50372,23 +50372,23 @@
       </c>
       <c r="B12" s="358">
         <f>B4*(1+B6)</f>
-        <v>1309749.8206760825</v>
+        <v>1308474.3906760823</v>
       </c>
       <c r="C12" s="358">
         <f>B12*(1+B6)</f>
-        <v>1702674.7668789073</v>
+        <v>1701016.7078789072</v>
       </c>
       <c r="D12" s="358">
         <f>C12*(1+B6)</f>
-        <v>2213477.1969425795</v>
+        <v>2211321.7202425795</v>
       </c>
       <c r="E12" s="358">
         <f>D12*(1+B6)</f>
-        <v>2877520.3560253535</v>
+        <v>2874718.2363153533</v>
       </c>
       <c r="F12" s="358">
         <f>E12*(1+B6)</f>
-        <v>3740776.4628329598</v>
+        <v>3737133.7072099596</v>
       </c>
       <c r="G12" s="359" t="s">
         <v>703</v>
@@ -50400,27 +50400,27 @@
       </c>
       <c r="B13" s="361">
         <f>B12*B8</f>
-        <v>515127.74263273785</v>
+        <v>513852.31263273774</v>
       </c>
       <c r="C13" s="361">
         <f>C12*B8</f>
-        <v>669666.06542255927</v>
+        <v>668008.00642255915</v>
       </c>
       <c r="D13" s="361">
         <f>D12*B8</f>
-        <v>870565.88504932704</v>
+        <v>868410.40834932693</v>
       </c>
       <c r="E13" s="361">
         <f>E12*B8</f>
-        <v>1131735.6505641253</v>
+        <v>1128933.530854125</v>
       </c>
       <c r="F13" s="361">
         <f>F12*B8</f>
-        <v>1471256.3457333629</v>
+        <v>1467613.5901103627</v>
       </c>
       <c r="G13" s="361">
         <f>F13*(1+B7)/(B5-B7)</f>
-        <v>7724095.8151001548</v>
+        <v>7704971.3480794039</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15" customHeight="1">
@@ -50458,27 +50458,27 @@
       </c>
       <c r="B15" s="364">
         <f t="shared" ref="B15:G15" si="1">B13*B14</f>
-        <v>412102.19410619029</v>
+        <v>411081.85010619019</v>
       </c>
       <c r="C15" s="364">
         <f t="shared" si="1"/>
-        <v>428586.28187043796</v>
+        <v>427525.12411043787</v>
       </c>
       <c r="D15" s="364">
         <f t="shared" si="1"/>
-        <v>445729.73314525548</v>
+        <v>444626.12907485542</v>
       </c>
       <c r="E15" s="364">
         <f t="shared" si="1"/>
-        <v>463558.92247106571</v>
+        <v>462411.17423784966</v>
       </c>
       <c r="F15" s="364">
         <f t="shared" si="1"/>
-        <v>482101.27936990838</v>
+        <v>480907.62120736373</v>
       </c>
       <c r="G15" s="364">
         <f t="shared" si="1"/>
-        <v>2531031.7166920188</v>
+        <v>2524765.0113386591</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="21.75" customHeight="1">
@@ -50498,7 +50498,7 @@
       </c>
       <c r="B19" s="361">
         <f>SUM(B15:F15)</f>
-        <v>2232078.4109628582</v>
+        <v>2226551.8987366972</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1">
@@ -50507,7 +50507,7 @@
       </c>
       <c r="B20" s="361">
         <f>G15</f>
-        <v>2531031.7166920188</v>
+        <v>2524765.0113386591</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="18" customHeight="1">
@@ -50516,7 +50516,7 @@
       </c>
       <c r="B21" s="364">
         <f>B19+B20</f>
-        <v>4763110.1276548766</v>
+        <v>4751316.9100753563</v>
       </c>
       <c r="D21" s="365"/>
     </row>
@@ -50543,7 +50543,7 @@
       </c>
       <c r="B24" s="364">
         <f>B21+B22+B23</f>
-        <v>4645068.0667601842</v>
+        <v>4633274.8491806639</v>
       </c>
       <c r="C24" s="366"/>
       <c r="D24" s="366"/>
@@ -52376,7 +52376,7 @@
       </c>
       <c r="E5" s="232">
         <f>IF(E4&gt;0,(E7/E4)*12,"")</f>
-        <v>1.1667027687707446E-2</v>
+        <v>1.1667027687707445E-2</v>
       </c>
       <c r="F5" s="233">
         <f t="shared" ref="F5:P5" si="1">IF(F4&gt;0,(F7/F4)*12,"")</f>
@@ -52392,11 +52392,11 @@
       </c>
       <c r="I5" s="233">
         <f t="shared" si="1"/>
-        <v>1.4122742257190964E-2</v>
+        <v>1.0664335955758022E-2</v>
       </c>
       <c r="J5" s="234">
         <f t="shared" si="1"/>
-        <v>8.5848934979539868E-3</v>
+        <v>1.2233618106671392E-2</v>
       </c>
       <c r="K5" s="232" t="str">
         <f t="shared" si="1"/>
@@ -52424,7 +52424,7 @@
       </c>
       <c r="Q5" s="240">
         <f>AVERAGE(E5:P5)</f>
-        <v>1.1074775548833189E-2</v>
+        <v>1.1106495266713935E-2</v>
       </c>
       <c r="U5" s="261">
         <v>4</v>
@@ -52483,7 +52483,7 @@
       </c>
       <c r="E7" s="212">
         <f>CNS!B8+CRR!B8</f>
-        <v>282443.93000000005</v>
+        <v>282443.93</v>
       </c>
       <c r="F7" s="208">
         <f>CNS!C8+CRR!C8</f>
@@ -52499,11 +52499,11 @@
       </c>
       <c r="I7" s="208">
         <f>CNS!F8+CRR!F8</f>
-        <v>367273.20000000007</v>
+        <v>277334.58</v>
       </c>
       <c r="J7" s="208">
         <f>CNS!G8+CRR!G8</f>
-        <v>211611.88000000003</v>
+        <v>301550.50000000006</v>
       </c>
       <c r="K7" s="212">
         <f>CNS!H8+CRR!H8</f>
@@ -52547,23 +52547,23 @@
       </c>
       <c r="E8" s="123">
         <f>CNS!B9</f>
-        <v>175809.20000000007</v>
+        <v>175809.19999999998</v>
       </c>
       <c r="F8" s="6">
         <f>CNS!C9</f>
-        <v>178265.27999999994</v>
+        <v>178265.27999999997</v>
       </c>
       <c r="G8" s="6">
         <f>CNS!D9</f>
-        <v>183175.54000000007</v>
+        <v>183175.54000000004</v>
       </c>
       <c r="H8" s="123">
         <f>CNS!E9</f>
-        <v>191954.81999999998</v>
+        <v>191954.82</v>
       </c>
       <c r="I8" s="6">
         <f>CNS!F9</f>
-        <v>192414.30000000005</v>
+        <v>192414.3</v>
       </c>
       <c r="J8" s="6">
         <f>CNS!G9</f>
@@ -52595,18 +52595,18 @@
       </c>
       <c r="Q8" s="9">
         <f t="shared" ref="Q8:Q52" si="2">SUM(E8:P8)</f>
-        <v>1109170.98</v>
+        <v>1109170.9800000002</v>
       </c>
       <c r="R8" s="229">
         <f>Q8/$Q$7</f>
-        <v>0.65793284820015441</v>
+        <v>0.65793284820015452</v>
       </c>
       <c r="T8" s="219" t="s">
         <v>225</v>
       </c>
       <c r="U8" s="9">
         <f t="shared" ref="U8:U53" si="3">Q8/$U$5</f>
-        <v>277292.745</v>
+        <v>277292.74500000005</v>
       </c>
     </row>
     <row r="9" spans="4:28">
@@ -52703,11 +52703,11 @@
       </c>
       <c r="I10" s="6">
         <f>CNS!F11</f>
-        <v>117700</v>
+        <v>34000</v>
       </c>
       <c r="J10" s="6">
         <f>CNS!G11</f>
-        <v>0</v>
+        <v>83700</v>
       </c>
       <c r="K10" s="123">
         <f>CNS!H11</f>
@@ -52769,13 +52769,13 @@
         <f>CNS!E12</f>
         <v>30425.54</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="6" t="str">
         <f>CNS!F12</f>
-        <v>6238.62</v>
+        <v>0,00</v>
       </c>
       <c r="J11" s="6">
         <f>CNS!G12</f>
-        <v>0</v>
+        <v>6238.62</v>
       </c>
       <c r="K11" s="123">
         <f>CNS!H12</f>
@@ -53339,7 +53339,7 @@
       </c>
       <c r="G20" s="10">
         <f>CNS!D16+CRR!D15</f>
-        <v>-138181.44</v>
+        <v>-138181.44000000003</v>
       </c>
       <c r="H20" s="122">
         <f>CNS!E16+CRR!E15</f>
@@ -53347,11 +53347,11 @@
       </c>
       <c r="I20" s="10">
         <f>CNS!F16+CRR!F15</f>
-        <v>-129779.16000000002</v>
+        <v>-128726.11</v>
       </c>
       <c r="J20" s="10">
         <f>CNS!G16+CRR!G15</f>
-        <v>-127763.55000000002</v>
+        <v>-128816.60000000002</v>
       </c>
       <c r="K20" s="122">
         <f>CNS!H16+CRR!H15</f>
@@ -53379,7 +53379,7 @@
       </c>
       <c r="Q20" s="11">
         <f t="shared" si="2"/>
-        <v>-917276.33000000007</v>
+        <v>-917276.33</v>
       </c>
       <c r="R20" s="230">
         <f>Q20/$Q$7</f>
@@ -53390,7 +53390,7 @@
       </c>
       <c r="U20" s="11">
         <f t="shared" si="3"/>
-        <v>-229319.08250000002</v>
+        <v>-229319.08249999999</v>
       </c>
     </row>
     <row r="21" spans="4:27">
@@ -53415,11 +53415,11 @@
       </c>
       <c r="I21" s="6">
         <f>CNS!F17+CRR!F16</f>
-        <v>-24317.29</v>
+        <v>-23264.240000000002</v>
       </c>
       <c r="J21" s="6">
         <f>CNS!G17+CRR!G16</f>
-        <v>-24405.439999999999</v>
+        <v>-25458.489999999998</v>
       </c>
       <c r="K21" s="123">
         <f>CNS!H17+CRR!H16</f>
@@ -53811,7 +53811,7 @@
       </c>
       <c r="E27" s="212">
         <f>CNS!B23+CRR!B22</f>
-        <v>83627.280000000057</v>
+        <v>83627.28</v>
       </c>
       <c r="F27" s="208">
         <f>CNS!C23+CRR!C22</f>
@@ -53827,11 +53827,11 @@
       </c>
       <c r="I27" s="208">
         <f>CNS!F23+CRR!F22</f>
-        <v>237494.04000000007</v>
+        <v>148608.47</v>
       </c>
       <c r="J27" s="208">
         <f>CNS!G23+CRR!G22</f>
-        <v>83848.330000000031</v>
+        <v>172733.90000000008</v>
       </c>
       <c r="K27" s="212">
         <f>CNS!H23+CRR!H22</f>
@@ -53859,18 +53859,18 @@
       </c>
       <c r="Q27" s="215">
         <f t="shared" si="2"/>
-        <v>768565.90000000026</v>
+        <v>768565.90000000014</v>
       </c>
       <c r="R27" s="12">
         <f>Q27/$Q$7</f>
-        <v>0.45589432173614503</v>
+        <v>0.45589432173614491</v>
       </c>
       <c r="T27" s="330" t="s">
         <v>14</v>
       </c>
       <c r="U27" s="215">
         <f t="shared" si="3"/>
-        <v>192141.47500000006</v>
+        <v>192141.47500000003</v>
       </c>
     </row>
     <row r="28" spans="4:27">
@@ -53891,7 +53891,7 @@
       </c>
       <c r="H28" s="122">
         <f>CNS!E24+CRR!E23</f>
-        <v>-64575.130000000005</v>
+        <v>-64575.130000000012</v>
       </c>
       <c r="I28" s="10">
         <f>CNS!F24+CRR!F23</f>
@@ -53951,7 +53951,7 @@
       </c>
       <c r="F29" s="6">
         <f>CNS!C25+CRR!C24</f>
-        <v>-32678.579999999994</v>
+        <v>-32678.579999999998</v>
       </c>
       <c r="G29" s="6">
         <f>CNS!D25+CRR!D24</f>
@@ -54023,11 +54023,11 @@
       </c>
       <c r="G30" s="6">
         <f>CNS!D26+CRR!D25</f>
-        <v>-13097.35</v>
+        <v>-13097.349999999999</v>
       </c>
       <c r="H30" s="123">
         <f>CNS!E26+CRR!E25</f>
-        <v>-10678.38</v>
+        <v>-10678.379999999997</v>
       </c>
       <c r="I30" s="6">
         <f>CNS!F26+CRR!F25</f>
@@ -54035,7 +54035,7 @@
       </c>
       <c r="J30" s="6">
         <f>CNS!G26+CRR!G25</f>
-        <v>-9939.9599999999991</v>
+        <v>-9939.9600000000009</v>
       </c>
       <c r="K30" s="123">
         <f>CNS!H26+CRR!H25</f>
@@ -54151,7 +54151,7 @@
       </c>
       <c r="E32" s="123">
         <f>CNS!B28+CRR!B27</f>
-        <v>-1119.1799999999998</v>
+        <v>-1119.18</v>
       </c>
       <c r="F32" s="6">
         <f>CNS!C28+CRR!C27</f>
@@ -54199,18 +54199,18 @@
       </c>
       <c r="Q32" s="9">
         <f t="shared" si="2"/>
-        <v>-1119.1799999999998</v>
+        <v>-1119.18</v>
       </c>
       <c r="R32" s="230">
         <f t="shared" si="6"/>
-        <v>-6.6386995181630945E-4</v>
+        <v>-6.6386995181630956E-4</v>
       </c>
       <c r="T32" s="219" t="s">
         <v>509</v>
       </c>
       <c r="U32" s="9">
         <f t="shared" si="3"/>
-        <v>-279.79499999999996</v>
+        <v>-279.79500000000002</v>
       </c>
     </row>
     <row r="33" spans="4:21">
@@ -54287,7 +54287,7 @@
       </c>
       <c r="E34" s="212">
         <f>CNS!B30+CRR!B29</f>
-        <v>19129.020000000051</v>
+        <v>19129.02</v>
       </c>
       <c r="F34" s="208">
         <f>CNS!C30+CRR!C29</f>
@@ -54299,15 +54299,15 @@
       </c>
       <c r="H34" s="212">
         <f>CNS!E30+CRR!E29</f>
-        <v>5731.0600000000632</v>
+        <v>5731.0600000000559</v>
       </c>
       <c r="I34" s="208">
         <f>CNS!F30+CRR!F29</f>
-        <v>156561.15000000002</v>
+        <v>67675.579999999987</v>
       </c>
       <c r="J34" s="208">
         <f>CNS!G30+CRR!G29</f>
-        <v>14464.840000000011</v>
+        <v>103350.41000000003</v>
       </c>
       <c r="K34" s="212">
         <f>CNS!H30+CRR!H29</f>
@@ -54335,18 +54335,18 @@
       </c>
       <c r="Q34" s="215">
         <f t="shared" si="2"/>
-        <v>359496.2800000002</v>
+        <v>359496.28000000014</v>
       </c>
       <c r="R34" s="12">
         <f>Q34/$Q$7</f>
-        <v>0.21324432002157173</v>
+        <v>0.2132443200215717</v>
       </c>
       <c r="T34" s="330" t="s">
         <v>16</v>
       </c>
       <c r="U34" s="215">
         <f t="shared" si="3"/>
-        <v>89874.070000000051</v>
+        <v>89874.070000000036</v>
       </c>
     </row>
     <row r="35" spans="4:21">
@@ -54371,7 +54371,7 @@
       </c>
       <c r="I35" s="10">
         <f>CNS!F31+CRR!F30</f>
-        <v>-19711.419999999995</v>
+        <v>-20692.519999999997</v>
       </c>
       <c r="J35" s="10">
         <f>CNS!G31+CRR!G30</f>
@@ -54403,18 +54403,18 @@
       </c>
       <c r="Q35" s="11">
         <f t="shared" si="2"/>
-        <v>-132864.49999999997</v>
+        <v>-133845.59999999998</v>
       </c>
       <c r="R35" s="230">
         <f t="shared" ref="R35:R52" si="7">Q35/$Q$7</f>
-        <v>-7.8811941969207849E-2</v>
+        <v>-7.939390627318664E-2</v>
       </c>
       <c r="T35" s="221" t="s">
         <v>17</v>
       </c>
       <c r="U35" s="11">
         <f t="shared" si="3"/>
-        <v>-33216.124999999993</v>
+        <v>-33461.399999999994</v>
       </c>
     </row>
     <row r="36" spans="4:21">
@@ -54439,7 +54439,7 @@
       </c>
       <c r="I36" s="6">
         <f>CNS!F32+CRR!F31</f>
-        <v>-8184.48</v>
+        <v>-9165.58</v>
       </c>
       <c r="J36" s="6">
         <f>CNS!G32+CRR!G31</f>
@@ -54471,18 +54471,18 @@
       </c>
       <c r="Q36" s="9">
         <f t="shared" si="2"/>
-        <v>-51305.659999999996</v>
+        <v>-52286.76</v>
       </c>
       <c r="R36" s="230">
         <f t="shared" si="7"/>
-        <v>-3.0433251158977073E-2</v>
+        <v>-3.1015215462955863E-2</v>
       </c>
       <c r="T36" s="219" t="s">
         <v>507</v>
       </c>
       <c r="U36" s="9">
         <f t="shared" si="3"/>
-        <v>-12826.414999999999</v>
+        <v>-13071.69</v>
       </c>
     </row>
     <row r="37" spans="4:21">
@@ -54835,11 +54835,11 @@
       </c>
       <c r="F42" s="6">
         <f>CNS!C38+CRR!C37</f>
-        <v>-906.86</v>
+        <v>-906.8599999999999</v>
       </c>
       <c r="G42" s="6">
         <f>CNS!D38+CRR!D37</f>
-        <v>-906.86</v>
+        <v>-906.8599999999999</v>
       </c>
       <c r="H42" s="123">
         <f>CNS!E38+CRR!E37</f>
@@ -55103,7 +55103,7 @@
       </c>
       <c r="E46" s="212">
         <f>CNS!B42+CRR!B41</f>
-        <v>-4352.479999999945</v>
+        <v>-4352.4799999999959</v>
       </c>
       <c r="F46" s="208">
         <f>CNS!C42+CRR!C41</f>
@@ -55115,15 +55115,15 @@
       </c>
       <c r="H46" s="212">
         <f>CNS!E42+CRR!E41</f>
-        <v>-15400.709999999932</v>
+        <v>-15400.709999999939</v>
       </c>
       <c r="I46" s="208">
         <f>CNS!F42+CRR!F41</f>
-        <v>136849.73000000004</v>
+        <v>46983.06</v>
       </c>
       <c r="J46" s="208">
         <f>CNS!G42+CRR!G41</f>
-        <v>-5266.3199999999888</v>
+        <v>83619.250000000044</v>
       </c>
       <c r="K46" s="212">
         <f>CNS!H42+CRR!H41</f>
@@ -55151,22 +55151,22 @@
       </c>
       <c r="Q46" s="215">
         <f t="shared" si="2"/>
-        <v>226631.78000000023</v>
+        <v>225650.68000000017</v>
       </c>
       <c r="R46" s="12">
         <f>Q46/$Q$7</f>
-        <v>0.13443237805236388</v>
+        <v>0.13385041374838508</v>
       </c>
       <c r="S46" s="12">
         <f>Q46/$Q$27</f>
-        <v>0.29487618433240426</v>
+        <v>0.29359965098633717</v>
       </c>
       <c r="T46" s="330" t="s">
         <v>18</v>
       </c>
       <c r="U46" s="215">
         <f t="shared" si="3"/>
-        <v>56657.945000000058</v>
+        <v>56412.670000000042</v>
       </c>
     </row>
     <row r="47" spans="4:21">
@@ -55175,11 +55175,11 @@
       </c>
       <c r="E47" s="122">
         <f>CNS!B43+CRR!B42</f>
-        <v>-1262.8599999999976</v>
+        <v>-1262.8599999999981</v>
       </c>
       <c r="F47" s="10">
         <f>CNS!C43+CRR!C42</f>
-        <v>-973.19999999999925</v>
+        <v>-973.19999999999879</v>
       </c>
       <c r="G47" s="10">
         <f>CNS!D43+CRR!D42</f>
@@ -55187,15 +55187,15 @@
       </c>
       <c r="H47" s="122">
         <f>CNS!E43+CRR!E42</f>
-        <v>-751.95999999999833</v>
+        <v>-751.95999999999879</v>
       </c>
       <c r="I47" s="10">
         <f>CNS!F43+CRR!F42</f>
-        <v>-2992.9199999999992</v>
+        <v>271.08000000000072</v>
       </c>
       <c r="J47" s="10">
         <f>CNS!G43+CRR!G42</f>
-        <v>-1604.8199999999993</v>
+        <v>-3510.5199999999986</v>
       </c>
       <c r="K47" s="122">
         <f>CNS!H43+CRR!H42</f>
@@ -55223,18 +55223,18 @@
       </c>
       <c r="Q47" s="11">
         <f t="shared" si="2"/>
-        <v>-7923.5099999999911</v>
+        <v>-6565.2099999999909</v>
       </c>
       <c r="R47" s="230">
         <f t="shared" si="7"/>
-        <v>-4.7000305597991758E-3</v>
+        <v>-3.8943205260672524E-3</v>
       </c>
       <c r="T47" s="221" t="s">
         <v>19</v>
       </c>
       <c r="U47" s="11">
         <f t="shared" si="3"/>
-        <v>-1980.8774999999978</v>
+        <v>-1641.3024999999977</v>
       </c>
     </row>
     <row r="48" spans="4:21">
@@ -55311,7 +55311,7 @@
       </c>
       <c r="E49" s="212">
         <f>CNS!B45+CRR!B44</f>
-        <v>-5606.7099999999427</v>
+        <v>-5606.7099999999937</v>
       </c>
       <c r="F49" s="208">
         <f>CNS!C45+CRR!C44</f>
@@ -55323,15 +55323,15 @@
       </c>
       <c r="H49" s="212">
         <f>CNS!E45+CRR!E44</f>
-        <v>-16149.21999999993</v>
+        <v>-16149.219999999937</v>
       </c>
       <c r="I49" s="208">
         <f>CNS!F45+CRR!F44</f>
-        <v>133862.00000000003</v>
+        <v>47259.33</v>
       </c>
       <c r="J49" s="208">
         <f>CNS!G45+CRR!G44</f>
-        <v>-6871.1399999999867</v>
+        <v>80108.73000000004</v>
       </c>
       <c r="K49" s="212">
         <f>CNS!H45+CRR!H44</f>
@@ -55359,22 +55359,22 @@
       </c>
       <c r="Q49" s="215">
         <f t="shared" si="2"/>
-        <v>218728.03000000023</v>
+        <v>219105.23000000016</v>
       </c>
       <c r="R49" s="12">
         <f>Q49/$Q$7</f>
-        <v>0.1297440686368381</v>
+        <v>0.12996781436659119</v>
       </c>
       <c r="S49" s="12">
         <f>Q49/$Q$27</f>
-        <v>0.28459242076704178</v>
+        <v>0.28508320496654888</v>
       </c>
       <c r="T49" s="330" t="s">
         <v>21</v>
       </c>
       <c r="U49" s="215">
         <f t="shared" si="3"/>
-        <v>54682.007500000058</v>
+        <v>54776.307500000039</v>
       </c>
     </row>
     <row r="50" spans="4:21">
@@ -55587,7 +55587,7 @@
       </c>
       <c r="E53" s="213">
         <f>CNS!B49+CRR!B48</f>
-        <v>-15843.279999999942</v>
+        <v>-15843.279999999993</v>
       </c>
       <c r="F53" s="211">
         <f>CNS!C49+CRR!C48</f>
@@ -55599,15 +55599,15 @@
       </c>
       <c r="H53" s="213">
         <f>CNS!E49+CRR!E48</f>
-        <v>-26786.079999999929</v>
+        <v>-26786.079999999936</v>
       </c>
       <c r="I53" s="211">
         <f>CNS!F49+CRR!F48</f>
-        <v>124591.97000000003</v>
+        <v>37989.300000000003</v>
       </c>
       <c r="J53" s="211">
         <f>CNS!G49+CRR!G48</f>
-        <v>-15997.259999999986</v>
+        <v>70982.610000000044</v>
       </c>
       <c r="K53" s="213">
         <f>CNS!H49+CRR!H48</f>
@@ -55635,22 +55635,22 @@
       </c>
       <c r="Q53" s="216">
         <f>SUM(E53:P53)</f>
-        <v>160599.62000000023</v>
+        <v>160976.82000000015</v>
       </c>
       <c r="R53" s="12">
         <f>Q53/$Q$7</f>
-        <v>9.5263730580530184E-2</v>
+        <v>9.5487476310283273E-2</v>
       </c>
       <c r="S53" s="12">
         <f>Q53/$Q$27</f>
-        <v>0.20896011649749249</v>
+        <v>0.20945090069699959</v>
       </c>
       <c r="T53" s="332" t="s">
         <v>23</v>
       </c>
       <c r="U53" s="216">
         <f t="shared" si="3"/>
-        <v>40149.905000000057</v>
+        <v>40244.205000000038</v>
       </c>
     </row>
     <row r="58" spans="4:21">
@@ -55659,7 +55659,7 @@
       </c>
       <c r="E58" s="14">
         <f>E46+(-E21)</f>
-        <v>97162.120000000054</v>
+        <v>97162.12000000001</v>
       </c>
       <c r="F58" s="14">
         <f t="shared" ref="F58:P58" si="8">F46+(-F21)</f>
@@ -55675,11 +55675,11 @@
       </c>
       <c r="I58" s="14">
         <f t="shared" si="8"/>
-        <v>161167.02000000005</v>
+        <v>70247.3</v>
       </c>
       <c r="J58" s="14">
         <f t="shared" si="8"/>
-        <v>19139.12000000001</v>
+        <v>109077.74000000005</v>
       </c>
       <c r="K58" s="14">
         <f t="shared" si="8"/>
@@ -55707,7 +55707,7 @@
       </c>
       <c r="Q58" s="14">
         <f>Q46+(-Q21)</f>
-        <v>518128.05000000028</v>
+        <v>517146.95000000019</v>
       </c>
     </row>
     <row r="59" spans="4:21" outlineLevel="1">
@@ -55878,7 +55878,7 @@
       </c>
       <c r="E63" s="18">
         <f>IF(E58&lt;&gt;0,E58/E7,"")</f>
-        <v>0.3440049853434628</v>
+        <v>0.34400498534346274</v>
       </c>
       <c r="F63" s="18">
         <f t="shared" ref="F63:P63" si="10">IF(F58&lt;&gt;0,F58/F7,"")</f>
@@ -55894,11 +55894,11 @@
       </c>
       <c r="I63" s="18">
         <f t="shared" si="10"/>
-        <v>0.43882052924090298</v>
+        <v>0.25329441427751276</v>
       </c>
       <c r="J63" s="18">
         <f t="shared" si="10"/>
-        <v>9.0444449527124882E-2</v>
+        <v>0.3617229618256313</v>
       </c>
       <c r="K63" s="18" t="str">
         <f t="shared" si="10"/>
@@ -55926,7 +55926,7 @@
       </c>
       <c r="Q63" s="18">
         <f>IF(Q58&lt;&gt;0,Q58/Q7,"")</f>
-        <v>0.30734077055360048</v>
+        <v>0.30675880624962165</v>
       </c>
     </row>
     <row r="64" spans="4:21">
@@ -55935,7 +55935,7 @@
       </c>
       <c r="E64" s="18">
         <f>IF(E34&lt;&gt;0,E34/E7,"")</f>
-        <v>6.7726787401662505E-2</v>
+        <v>6.7726787401662339E-2</v>
       </c>
       <c r="F64" s="18">
         <f t="shared" ref="F64:Q64" si="11">IF(F34&lt;&gt;0,F34/F7,"")</f>
@@ -55947,15 +55947,15 @@
       </c>
       <c r="H64" s="18">
         <f t="shared" si="11"/>
-        <v>2.1487126811300879E-2</v>
+        <v>2.1487126811300852E-2</v>
       </c>
       <c r="I64" s="18">
         <f t="shared" si="11"/>
-        <v>0.4262798102339076</v>
+        <v>0.2440214271152194</v>
       </c>
       <c r="J64" s="18">
         <f t="shared" si="11"/>
-        <v>6.8355519548335422E-2</v>
+        <v>0.34273002366104521</v>
       </c>
       <c r="K64" s="18" t="str">
         <f t="shared" si="11"/>
@@ -55983,7 +55983,7 @@
       </c>
       <c r="Q64" s="18">
         <f t="shared" si="11"/>
-        <v>0.21324432002157173</v>
+        <v>0.2132443200215717</v>
       </c>
     </row>
     <row r="65" spans="4:17">
@@ -55992,7 +55992,7 @@
       </c>
       <c r="E65" s="18">
         <f>IF(E49&lt;&gt;0,E49/E7,"")</f>
-        <v>-1.98507009869178E-2</v>
+        <v>-1.9850700986917984E-2</v>
       </c>
       <c r="F65" s="18">
         <f t="shared" ref="F65:Q65" si="12">IF(F49&lt;&gt;0,F49/F7,"")</f>
@@ -56004,15 +56004,15 @@
       </c>
       <c r="H65" s="18">
         <f t="shared" si="12"/>
-        <v>-6.0547322492451844E-2</v>
+        <v>-6.0547322492451872E-2</v>
       </c>
       <c r="I65" s="18">
         <f t="shared" si="12"/>
-        <v>0.36447527344766784</v>
+        <v>0.17040547197540243</v>
       </c>
       <c r="J65" s="18">
         <f t="shared" si="12"/>
-        <v>-3.2470483226177974E-2</v>
+        <v>0.2656561007194484</v>
       </c>
       <c r="K65" s="18" t="str">
         <f t="shared" si="12"/>
@@ -56040,7 +56040,7 @@
       </c>
       <c r="Q65" s="18">
         <f t="shared" si="12"/>
-        <v>0.1297440686368381</v>
+        <v>0.12996781436659119</v>
       </c>
     </row>
     <row r="66" spans="4:17">
@@ -56049,7 +56049,7 @@
       </c>
       <c r="E66" s="18">
         <f>IF(E53&lt;&gt;0,E53/E7,"")</f>
-        <v>-5.6093540406408945E-2</v>
+        <v>-5.609354040640914E-2</v>
       </c>
       <c r="F66" s="18">
         <f t="shared" ref="F66:Q66" si="13">IF(F53&lt;&gt;0,F53/F7,"")</f>
@@ -56061,15 +56061,15 @@
       </c>
       <c r="H66" s="18">
         <f t="shared" si="13"/>
-        <v>-0.1004274772446358</v>
+        <v>-0.10042747724463583</v>
       </c>
       <c r="I66" s="18">
         <f t="shared" si="13"/>
-        <v>0.33923512524191801</v>
+        <v>0.13698003328686961</v>
       </c>
       <c r="J66" s="18">
         <f t="shared" si="13"/>
-        <v>-7.5597173466820405E-2</v>
+        <v>0.23539211508520141</v>
       </c>
       <c r="K66" s="18" t="str">
         <f t="shared" si="13"/>
@@ -56097,7 +56097,7 @@
       </c>
       <c r="Q66" s="18">
         <f t="shared" si="13"/>
-        <v>9.5263730580530184E-2</v>
+        <v>9.5487476310283273E-2</v>
       </c>
     </row>
     <row r="70" spans="4:17">
@@ -56439,7 +56439,7 @@
       </c>
       <c r="U9" s="79">
         <f>U13</f>
-        <v>64239.848000000093</v>
+        <v>64390.728000000061</v>
       </c>
       <c r="W9" s="3"/>
     </row>
@@ -56505,7 +56505,7 @@
       </c>
       <c r="U10" s="68">
         <f>U6-U8-U9</f>
-        <v>-64239.848000000093</v>
+        <v>-64390.728000000061</v>
       </c>
     </row>
     <row r="11" spans="4:23" ht="15" customHeight="1" outlineLevel="1">
@@ -56578,7 +56578,7 @@
       </c>
       <c r="U12" s="79">
         <f>Consolidated!Q53</f>
-        <v>160599.62000000023</v>
+        <v>160976.82000000015</v>
       </c>
     </row>
     <row r="13" spans="4:23" ht="15" customHeight="1">
@@ -56643,7 +56643,7 @@
       </c>
       <c r="U13" s="79">
         <f>U12*T13</f>
-        <v>64239.848000000093</v>
+        <v>64390.728000000061</v>
       </c>
     </row>
     <row r="14" spans="4:23" ht="15" customHeight="1" outlineLevel="1">
@@ -57585,63 +57585,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:22" ht="27.75" customHeight="1">
-      <c r="B1" s="386" t="s">
+      <c r="B1" s="387" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="386"/>
-      <c r="D1" s="386"/>
-      <c r="E1" s="386"/>
-      <c r="F1" s="386"/>
-      <c r="G1" s="386"/>
-      <c r="H1" s="386"/>
-      <c r="I1" s="386"/>
-      <c r="J1" s="386"/>
-      <c r="K1" s="386"/>
-      <c r="L1" s="386"/>
-      <c r="M1" s="386"/>
-      <c r="N1" s="386"/>
-      <c r="O1" s="386"/>
+      <c r="C1" s="387"/>
+      <c r="D1" s="387"/>
+      <c r="E1" s="387"/>
+      <c r="F1" s="387"/>
+      <c r="G1" s="387"/>
+      <c r="H1" s="387"/>
+      <c r="I1" s="387"/>
+      <c r="J1" s="387"/>
+      <c r="K1" s="387"/>
+      <c r="L1" s="387"/>
+      <c r="M1" s="387"/>
+      <c r="N1" s="387"/>
+      <c r="O1" s="387"/>
       <c r="Q1" s="176"/>
     </row>
     <row r="2" spans="2:22">
-      <c r="B2" s="387" t="s">
+      <c r="B2" s="388" t="s">
         <v>557</v>
       </c>
-      <c r="C2" s="387"/>
-      <c r="D2" s="387"/>
-      <c r="E2" s="387"/>
-      <c r="F2" s="387"/>
-      <c r="G2" s="387"/>
-      <c r="H2" s="387"/>
-      <c r="I2" s="387"/>
-      <c r="J2" s="387"/>
-      <c r="K2" s="387"/>
-      <c r="L2" s="387"/>
-      <c r="M2" s="387"/>
-      <c r="N2" s="387"/>
-      <c r="O2" s="387"/>
+      <c r="C2" s="388"/>
+      <c r="D2" s="388"/>
+      <c r="E2" s="388"/>
+      <c r="F2" s="388"/>
+      <c r="G2" s="388"/>
+      <c r="H2" s="388"/>
+      <c r="I2" s="388"/>
+      <c r="J2" s="388"/>
+      <c r="K2" s="388"/>
+      <c r="L2" s="388"/>
+      <c r="M2" s="388"/>
+      <c r="N2" s="388"/>
+      <c r="O2" s="388"/>
       <c r="Q2" s="176"/>
     </row>
     <row r="3" spans="2:22">
       <c r="Q3" s="176"/>
     </row>
     <row r="4" spans="2:22" ht="18" customHeight="1">
-      <c r="B4" s="385" t="s">
+      <c r="B4" s="384" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="385"/>
-      <c r="D4" s="385"/>
-      <c r="E4" s="385"/>
-      <c r="F4" s="385"/>
-      <c r="G4" s="385"/>
-      <c r="H4" s="385"/>
-      <c r="I4" s="385"/>
-      <c r="J4" s="385"/>
-      <c r="K4" s="385"/>
-      <c r="L4" s="385"/>
-      <c r="M4" s="385"/>
-      <c r="N4" s="385"/>
-      <c r="O4" s="385"/>
+      <c r="C4" s="384"/>
+      <c r="D4" s="384"/>
+      <c r="E4" s="384"/>
+      <c r="F4" s="384"/>
+      <c r="G4" s="384"/>
+      <c r="H4" s="384"/>
+      <c r="I4" s="384"/>
+      <c r="J4" s="384"/>
+      <c r="K4" s="384"/>
+      <c r="L4" s="384"/>
+      <c r="M4" s="384"/>
+      <c r="N4" s="384"/>
+      <c r="O4" s="384"/>
       <c r="Q4" s="176"/>
     </row>
     <row r="5" spans="2:22" ht="15.75" customHeight="1">
@@ -57652,12 +57652,12 @@
         <f>J6</f>
         <v>280000000</v>
       </c>
-      <c r="D5" s="389" t="s">
+      <c r="D5" s="383" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="389"/>
-      <c r="F5" s="389"/>
-      <c r="G5" s="389"/>
+      <c r="E5" s="383"/>
+      <c r="F5" s="383"/>
+      <c r="G5" s="383"/>
       <c r="I5" s="158" t="s">
         <v>215</v>
       </c>
@@ -57694,12 +57694,12 @@
         <f>(1+L5)^(1/12)-1</f>
         <v>9.0536953684483557E-4</v>
       </c>
-      <c r="D6" s="390" t="s">
+      <c r="D6" s="382" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="390"/>
-      <c r="F6" s="390"/>
-      <c r="G6" s="390"/>
+      <c r="E6" s="382"/>
+      <c r="F6" s="382"/>
+      <c r="G6" s="382"/>
       <c r="I6" s="160" t="s">
         <v>132</v>
       </c>
@@ -57736,12 +57736,12 @@
       <c r="C7" s="23">
         <v>5.5E-2</v>
       </c>
-      <c r="D7" s="389" t="s">
+      <c r="D7" s="383" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="389"/>
-      <c r="F7" s="389"/>
-      <c r="G7" s="389"/>
+      <c r="E7" s="383"/>
+      <c r="F7" s="383"/>
+      <c r="G7" s="383"/>
       <c r="I7" s="160" t="s">
         <v>216</v>
       </c>
@@ -57768,12 +57768,12 @@
         <f>(1+C7)^(1/12)-1</f>
         <v>4.471698917043021E-3</v>
       </c>
-      <c r="D8" s="390" t="s">
+      <c r="D8" s="382" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="390"/>
-      <c r="F8" s="390"/>
-      <c r="G8" s="390"/>
+      <c r="E8" s="382"/>
+      <c r="F8" s="382"/>
+      <c r="G8" s="382"/>
       <c r="I8" s="162" t="s">
         <v>217</v>
       </c>
@@ -57825,14 +57825,14 @@
       <c r="C10" s="147">
         <v>-0.14000000000000001</v>
       </c>
-      <c r="D10" s="390"/>
-      <c r="E10" s="390"/>
-      <c r="F10" s="390"/>
-      <c r="G10" s="390"/>
-      <c r="I10" s="388" t="s">
+      <c r="D10" s="382"/>
+      <c r="E10" s="382"/>
+      <c r="F10" s="382"/>
+      <c r="G10" s="382"/>
+      <c r="I10" s="389" t="s">
         <v>381</v>
       </c>
-      <c r="J10" s="388"/>
+      <c r="J10" s="389"/>
       <c r="Q10" s="176"/>
       <c r="S10" s="172" t="s">
         <v>375</v>
@@ -57855,10 +57855,10 @@
       <c r="C11" s="147">
         <v>-0.43</v>
       </c>
-      <c r="D11" s="390"/>
-      <c r="E11" s="390"/>
-      <c r="F11" s="390"/>
-      <c r="G11" s="390"/>
+      <c r="D11" s="382"/>
+      <c r="E11" s="382"/>
+      <c r="F11" s="382"/>
+      <c r="G11" s="382"/>
       <c r="I11" s="20" t="s">
         <v>382</v>
       </c>
@@ -57890,12 +57890,12 @@
         <f>AVERAGE(Consolidated!E24:H24)</f>
         <v>-1257.6075000000001</v>
       </c>
-      <c r="D12" s="390" t="s">
+      <c r="D12" s="382" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="390"/>
-      <c r="F12" s="390"/>
-      <c r="G12" s="390"/>
+      <c r="E12" s="382"/>
+      <c r="F12" s="382"/>
+      <c r="G12" s="382"/>
       <c r="I12" s="20" t="s">
         <v>383</v>
       </c>
@@ -57923,12 +57923,12 @@
       <c r="C13" s="145">
         <v>0</v>
       </c>
-      <c r="D13" s="390" t="s">
+      <c r="D13" s="382" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="390"/>
-      <c r="F13" s="390"/>
-      <c r="G13" s="390"/>
+      <c r="E13" s="382"/>
+      <c r="F13" s="382"/>
+      <c r="G13" s="382"/>
       <c r="I13" s="20" t="s">
         <v>313</v>
       </c>
@@ -57947,12 +57947,12 @@
         <f>AVERAGE(Consolidated!E28:H28)</f>
         <v>-64688.31</v>
       </c>
-      <c r="D14" s="390" t="s">
+      <c r="D14" s="382" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="390"/>
-      <c r="F14" s="390"/>
-      <c r="G14" s="390"/>
+      <c r="E14" s="382"/>
+      <c r="F14" s="382"/>
+      <c r="G14" s="382"/>
       <c r="J14" s="167">
         <f>SUM(J11:J13)</f>
         <v>-8.6499999999999994E-2</v>
@@ -57978,16 +57978,16 @@
         <f>AVERAGE(Consolidated!E35:H35)</f>
         <v>-23355.479999999996</v>
       </c>
-      <c r="D15" s="390" t="s">
+      <c r="D15" s="382" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="390"/>
-      <c r="F15" s="390"/>
-      <c r="G15" s="390"/>
-      <c r="I15" s="388" t="s">
+      <c r="E15" s="382"/>
+      <c r="F15" s="382"/>
+      <c r="G15" s="382"/>
+      <c r="I15" s="389" t="s">
         <v>384</v>
       </c>
-      <c r="J15" s="388"/>
+      <c r="J15" s="389"/>
       <c r="K15" s="20" t="s">
         <v>386</v>
       </c>
@@ -58013,12 +58013,12 @@
         <f>-0.4%</f>
         <v>-4.0000000000000001E-3</v>
       </c>
-      <c r="D16" s="390" t="s">
+      <c r="D16" s="382" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="390"/>
-      <c r="F16" s="390"/>
-      <c r="G16" s="390"/>
+      <c r="E16" s="382"/>
+      <c r="F16" s="382"/>
+      <c r="G16" s="382"/>
       <c r="I16" s="20" t="s">
         <v>385</v>
       </c>
@@ -58045,12 +58045,12 @@
       <c r="C17" s="166">
         <v>-3.9277296541559398E-2</v>
       </c>
-      <c r="D17" s="390" t="s">
+      <c r="D17" s="382" t="s">
         <v>51</v>
       </c>
-      <c r="E17" s="390"/>
-      <c r="F17" s="390"/>
-      <c r="G17" s="390"/>
+      <c r="E17" s="382"/>
+      <c r="F17" s="382"/>
+      <c r="G17" s="382"/>
       <c r="I17" s="20" t="s">
         <v>377</v>
       </c>
@@ -58068,12 +58068,12 @@
       <c r="C18" s="166">
         <v>0</v>
       </c>
-      <c r="D18" s="390" t="s">
+      <c r="D18" s="382" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="390"/>
-      <c r="F18" s="390"/>
-      <c r="G18" s="390"/>
+      <c r="E18" s="382"/>
+      <c r="F18" s="382"/>
+      <c r="G18" s="382"/>
       <c r="J18" s="111">
         <f>J16+J17</f>
         <v>-0.23655912886349639</v>
@@ -58169,22 +58169,22 @@
       <c r="Q24" s="176"/>
     </row>
     <row r="25" spans="1:24" ht="18" customHeight="1">
-      <c r="B25" s="385" t="s">
+      <c r="B25" s="384" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="385"/>
-      <c r="D25" s="385"/>
-      <c r="E25" s="385"/>
-      <c r="F25" s="385"/>
-      <c r="G25" s="385"/>
-      <c r="H25" s="385"/>
-      <c r="I25" s="385"/>
-      <c r="J25" s="385"/>
-      <c r="K25" s="385"/>
-      <c r="L25" s="385"/>
-      <c r="M25" s="385"/>
-      <c r="N25" s="385"/>
-      <c r="O25" s="385"/>
+      <c r="C25" s="384"/>
+      <c r="D25" s="384"/>
+      <c r="E25" s="384"/>
+      <c r="F25" s="384"/>
+      <c r="G25" s="384"/>
+      <c r="H25" s="384"/>
+      <c r="I25" s="384"/>
+      <c r="J25" s="384"/>
+      <c r="K25" s="384"/>
+      <c r="L25" s="384"/>
+      <c r="M25" s="384"/>
+      <c r="N25" s="384"/>
+      <c r="O25" s="384"/>
       <c r="Q25" s="176"/>
     </row>
     <row r="26" spans="1:24" ht="18" customHeight="1">
@@ -58294,22 +58294,22 @@
       <c r="Q28" s="176"/>
     </row>
     <row r="29" spans="1:24" ht="18" customHeight="1">
-      <c r="B29" s="385" t="s">
+      <c r="B29" s="384" t="s">
         <v>370</v>
       </c>
-      <c r="C29" s="385"/>
-      <c r="D29" s="385"/>
-      <c r="E29" s="385"/>
-      <c r="F29" s="385"/>
-      <c r="G29" s="385"/>
-      <c r="H29" s="385"/>
-      <c r="I29" s="385"/>
-      <c r="J29" s="385"/>
-      <c r="K29" s="385"/>
-      <c r="L29" s="385"/>
-      <c r="M29" s="385"/>
-      <c r="N29" s="385"/>
-      <c r="O29" s="385"/>
+      <c r="C29" s="384"/>
+      <c r="D29" s="384"/>
+      <c r="E29" s="384"/>
+      <c r="F29" s="384"/>
+      <c r="G29" s="384"/>
+      <c r="H29" s="384"/>
+      <c r="I29" s="384"/>
+      <c r="J29" s="384"/>
+      <c r="K29" s="384"/>
+      <c r="L29" s="384"/>
+      <c r="M29" s="384"/>
+      <c r="N29" s="384"/>
+      <c r="O29" s="384"/>
       <c r="Q29" s="176"/>
     </row>
     <row r="30" spans="1:24" ht="18" customHeight="1">
@@ -59727,22 +59727,22 @@
       <c r="Q54" s="176"/>
     </row>
     <row r="55" spans="2:17" ht="18" customHeight="1">
-      <c r="B55" s="385" t="s">
+      <c r="B55" s="384" t="s">
         <v>80</v>
       </c>
-      <c r="C55" s="385"/>
-      <c r="D55" s="385"/>
-      <c r="E55" s="385"/>
-      <c r="F55" s="385"/>
-      <c r="G55" s="385"/>
-      <c r="H55" s="385"/>
-      <c r="I55" s="385"/>
-      <c r="J55" s="385"/>
-      <c r="K55" s="385"/>
-      <c r="L55" s="385"/>
-      <c r="M55" s="385"/>
-      <c r="N55" s="385"/>
-      <c r="O55" s="385"/>
+      <c r="C55" s="384"/>
+      <c r="D55" s="384"/>
+      <c r="E55" s="384"/>
+      <c r="F55" s="384"/>
+      <c r="G55" s="384"/>
+      <c r="H55" s="384"/>
+      <c r="I55" s="384"/>
+      <c r="J55" s="384"/>
+      <c r="K55" s="384"/>
+      <c r="L55" s="384"/>
+      <c r="M55" s="384"/>
+      <c r="N55" s="384"/>
+      <c r="O55" s="384"/>
       <c r="Q55" s="176"/>
     </row>
     <row r="56" spans="2:17" ht="18" customHeight="1">
@@ -60084,41 +60084,41 @@
       <c r="Q62" s="176"/>
     </row>
     <row r="63" spans="2:17" ht="18" customHeight="1">
-      <c r="B63" s="385" t="s">
+      <c r="B63" s="384" t="s">
         <v>84</v>
       </c>
-      <c r="C63" s="385"/>
-      <c r="D63" s="385"/>
-      <c r="E63" s="385"/>
-      <c r="F63" s="385"/>
-      <c r="G63" s="385"/>
-      <c r="H63" s="385"/>
-      <c r="I63" s="385"/>
-      <c r="J63" s="385"/>
-      <c r="K63" s="385"/>
-      <c r="L63" s="385"/>
-      <c r="M63" s="385"/>
-      <c r="N63" s="385"/>
-      <c r="O63" s="385"/>
+      <c r="C63" s="384"/>
+      <c r="D63" s="384"/>
+      <c r="E63" s="384"/>
+      <c r="F63" s="384"/>
+      <c r="G63" s="384"/>
+      <c r="H63" s="384"/>
+      <c r="I63" s="384"/>
+      <c r="J63" s="384"/>
+      <c r="K63" s="384"/>
+      <c r="L63" s="384"/>
+      <c r="M63" s="384"/>
+      <c r="N63" s="384"/>
+      <c r="O63" s="384"/>
       <c r="Q63" s="176"/>
     </row>
     <row r="64" spans="2:17">
-      <c r="B64" s="382" t="s">
+      <c r="B64" s="390" t="s">
         <v>85</v>
       </c>
-      <c r="C64" s="382"/>
-      <c r="D64" s="382"/>
-      <c r="E64" s="382"/>
-      <c r="F64" s="382"/>
-      <c r="G64" s="382"/>
-      <c r="H64" s="382"/>
-      <c r="I64" s="382"/>
-      <c r="J64" s="382"/>
-      <c r="K64" s="382"/>
-      <c r="L64" s="382"/>
-      <c r="M64" s="382"/>
-      <c r="N64" s="382"/>
-      <c r="O64" s="382"/>
+      <c r="C64" s="390"/>
+      <c r="D64" s="390"/>
+      <c r="E64" s="390"/>
+      <c r="F64" s="390"/>
+      <c r="G64" s="390"/>
+      <c r="H64" s="390"/>
+      <c r="I64" s="390"/>
+      <c r="J64" s="390"/>
+      <c r="K64" s="390"/>
+      <c r="L64" s="390"/>
+      <c r="M64" s="390"/>
+      <c r="N64" s="390"/>
+      <c r="O64" s="390"/>
       <c r="Q64" s="176"/>
     </row>
     <row r="65" spans="2:17">
@@ -60139,24 +60139,24 @@
       <c r="Q65" s="176"/>
     </row>
     <row r="66" spans="2:17">
-      <c r="B66" s="383" t="s">
+      <c r="B66" s="386" t="s">
         <v>371</v>
       </c>
-      <c r="C66" s="383"/>
-      <c r="D66" s="383"/>
-      <c r="E66" s="383"/>
-      <c r="F66" s="383"/>
-      <c r="G66" s="383"/>
-      <c r="H66" s="383"/>
-      <c r="I66" s="383"/>
-      <c r="J66" s="383"/>
-      <c r="K66" s="383"/>
-      <c r="L66" s="383"/>
-      <c r="M66" s="383"/>
-      <c r="N66" s="383"/>
-      <c r="O66" s="383"/>
-      <c r="P66" s="383"/>
-      <c r="Q66" s="383"/>
+      <c r="C66" s="386"/>
+      <c r="D66" s="386"/>
+      <c r="E66" s="386"/>
+      <c r="F66" s="386"/>
+      <c r="G66" s="386"/>
+      <c r="H66" s="386"/>
+      <c r="I66" s="386"/>
+      <c r="J66" s="386"/>
+      <c r="K66" s="386"/>
+      <c r="L66" s="386"/>
+      <c r="M66" s="386"/>
+      <c r="N66" s="386"/>
+      <c r="O66" s="386"/>
+      <c r="P66" s="386"/>
+      <c r="Q66" s="386"/>
     </row>
     <row r="67" spans="2:17">
       <c r="B67" s="149"/>
@@ -60405,24 +60405,24 @@
       <c r="Q71" s="176"/>
     </row>
     <row r="72" spans="2:17" ht="16.5" customHeight="1">
-      <c r="B72" s="383" t="s">
+      <c r="B72" s="386" t="s">
         <v>86</v>
       </c>
-      <c r="C72" s="383"/>
-      <c r="D72" s="383"/>
-      <c r="E72" s="383"/>
-      <c r="F72" s="383"/>
-      <c r="G72" s="383"/>
-      <c r="H72" s="383"/>
-      <c r="I72" s="383"/>
-      <c r="J72" s="383"/>
-      <c r="K72" s="383"/>
-      <c r="L72" s="383"/>
-      <c r="M72" s="383"/>
-      <c r="N72" s="383"/>
-      <c r="O72" s="383"/>
-      <c r="P72" s="383"/>
-      <c r="Q72" s="383"/>
+      <c r="C72" s="386"/>
+      <c r="D72" s="386"/>
+      <c r="E72" s="386"/>
+      <c r="F72" s="386"/>
+      <c r="G72" s="386"/>
+      <c r="H72" s="386"/>
+      <c r="I72" s="386"/>
+      <c r="J72" s="386"/>
+      <c r="K72" s="386"/>
+      <c r="L72" s="386"/>
+      <c r="M72" s="386"/>
+      <c r="N72" s="386"/>
+      <c r="O72" s="386"/>
+      <c r="P72" s="386"/>
+      <c r="Q72" s="386"/>
     </row>
     <row r="73" spans="2:17" ht="13.5" customHeight="1">
       <c r="B73" s="149"/>
@@ -60537,7 +60537,7 @@
       </c>
       <c r="C75" s="154">
         <f>IF(OR(Consolidated!E7=0,Consolidated!E7=""),"",Consolidated!E7)</f>
-        <v>282443.93000000005</v>
+        <v>282443.93</v>
       </c>
       <c r="D75" s="154">
         <f>IF(OR(Consolidated!F7=0,Consolidated!F7=""),"",Consolidated!F7)</f>
@@ -60553,11 +60553,11 @@
       </c>
       <c r="G75" s="154">
         <f>IF(OR(Consolidated!I7=0,Consolidated!I7=""),"",Consolidated!I7)</f>
-        <v>367273.20000000007</v>
+        <v>277334.58</v>
       </c>
       <c r="H75" s="154">
         <f>IF(OR(Consolidated!J7=0,Consolidated!J7=""),"",Consolidated!J7)</f>
-        <v>211611.88000000003</v>
+        <v>301550.50000000006</v>
       </c>
       <c r="I75" s="154" t="str">
         <f>IF(OR(Consolidated!K7=0,Consolidated!K7=""),"",Consolidated!K7)</f>
@@ -60589,7 +60589,7 @@
       </c>
       <c r="Q75" s="182">
         <f>SUM(C75:G75)</f>
-        <v>1474230.35</v>
+        <v>1384291.7300000002</v>
       </c>
     </row>
     <row r="76" spans="2:17" ht="15" customHeight="1">
@@ -60598,7 +60598,7 @@
       </c>
       <c r="C76" s="44">
         <f t="shared" ref="C76:N76" si="43">IFERROR(IF(C75="","",(C75-C74)/ABS(C74)),"—")</f>
-        <v>1.140482965096298E-2</v>
+        <v>1.140482965096277E-2</v>
       </c>
       <c r="D76" s="44">
         <f t="shared" si="43"/>
@@ -60614,11 +60614,11 @@
       </c>
       <c r="G76" s="44">
         <f t="shared" si="43"/>
-        <v>0.22216790768838959</v>
+        <v>-7.7119094537150393E-2</v>
       </c>
       <c r="H76" s="44">
         <f t="shared" si="43"/>
-        <v>-0.24574184812550054</v>
+        <v>7.4830594703998929E-2</v>
       </c>
       <c r="I76" s="44" t="str">
         <f t="shared" si="43"/>
@@ -60650,7 +60650,7 @@
       </c>
       <c r="Q76" s="183">
         <f>IFERROR(IF(Q75=0,"",(Q75-Q74)/ABS(Q74)),"—")</f>
-        <v>3.4296146344402846E-2</v>
+        <v>-2.8803333376343308E-2</v>
       </c>
     </row>
     <row r="77" spans="2:17" ht="4.5" customHeight="1">
@@ -60671,24 +60671,24 @@
       <c r="Q77" s="176"/>
     </row>
     <row r="78" spans="2:17" ht="16.5" customHeight="1">
-      <c r="B78" s="384" t="s">
+      <c r="B78" s="385" t="s">
         <v>91</v>
       </c>
-      <c r="C78" s="384"/>
-      <c r="D78" s="384"/>
-      <c r="E78" s="384"/>
-      <c r="F78" s="384"/>
-      <c r="G78" s="384"/>
-      <c r="H78" s="384"/>
-      <c r="I78" s="384"/>
-      <c r="J78" s="384"/>
-      <c r="K78" s="384"/>
-      <c r="L78" s="384"/>
-      <c r="M78" s="384"/>
-      <c r="N78" s="384"/>
-      <c r="O78" s="384"/>
-      <c r="P78" s="384"/>
-      <c r="Q78" s="384"/>
+      <c r="C78" s="385"/>
+      <c r="D78" s="385"/>
+      <c r="E78" s="385"/>
+      <c r="F78" s="385"/>
+      <c r="G78" s="385"/>
+      <c r="H78" s="385"/>
+      <c r="I78" s="385"/>
+      <c r="J78" s="385"/>
+      <c r="K78" s="385"/>
+      <c r="L78" s="385"/>
+      <c r="M78" s="385"/>
+      <c r="N78" s="385"/>
+      <c r="O78" s="385"/>
+      <c r="P78" s="385"/>
+      <c r="Q78" s="385"/>
     </row>
     <row r="79" spans="2:17" ht="13.5" customHeight="1">
       <c r="B79" s="149"/>
@@ -60811,7 +60811,7 @@
       </c>
       <c r="E81" s="154">
         <f>IF(OR(Consolidated!G20=0,Consolidated!G20=""),"",Consolidated!G20)</f>
-        <v>-138181.44</v>
+        <v>-138181.44000000003</v>
       </c>
       <c r="F81" s="154">
         <f>IF(OR(Consolidated!H20=0,Consolidated!H20=""),"",Consolidated!H20)</f>
@@ -60819,11 +60819,11 @@
       </c>
       <c r="G81" s="154">
         <f>IF(OR(Consolidated!I20=0,Consolidated!I20=""),"",Consolidated!I20)</f>
-        <v>-129779.16000000002</v>
+        <v>-128726.11</v>
       </c>
       <c r="H81" s="154">
         <f>IF(OR(Consolidated!J20=0,Consolidated!J20=""),"",Consolidated!J20)</f>
-        <v>-127763.55000000002</v>
+        <v>-128816.60000000002</v>
       </c>
       <c r="I81" s="154" t="str">
         <f>IF(OR(Consolidated!K20=0,Consolidated!K20=""),"",Consolidated!K20)</f>
@@ -60851,11 +60851,11 @@
       </c>
       <c r="O81" s="155">
         <f>SUMIF(C81:N81,"&lt;&gt;")</f>
-        <v>-917276.33000000007</v>
+        <v>-917276.33</v>
       </c>
       <c r="Q81" s="182">
         <f>SUM(C81:G81)</f>
-        <v>-789512.78</v>
+        <v>-788459.73</v>
       </c>
     </row>
     <row r="82" spans="2:17" ht="15" customHeight="1">
@@ -60872,7 +60872,7 @@
       </c>
       <c r="E82" s="44">
         <f t="shared" si="45"/>
-        <v>4.6199613621097618E-2</v>
+        <v>4.6199613621097417E-2</v>
       </c>
       <c r="F82" s="44">
         <f t="shared" si="45"/>
@@ -60880,11 +60880,11 @@
       </c>
       <c r="G82" s="44">
         <f t="shared" si="45"/>
-        <v>0.12715300472476276</v>
+        <v>0.13423543250727119</v>
       </c>
       <c r="H82" s="44">
         <f t="shared" si="45"/>
-        <v>6.9535011738678917E-2</v>
+        <v>6.1865953107413683E-2</v>
       </c>
       <c r="I82" s="44" t="str">
         <f t="shared" si="45"/>
@@ -60912,11 +60912,11 @@
       </c>
       <c r="O82" s="45">
         <f>IFERROR(IF(O81=0,"",(O81-O80)/ABS(O80)),"—")</f>
-        <v>0.49888213147325849</v>
+        <v>0.49888213147325855</v>
       </c>
       <c r="Q82" s="183">
         <f>IFERROR(IF(Q81=0,"",(Q81-Q80)/ABS(Q80)),"—")</f>
-        <v>4.6765093962965923E-2</v>
+        <v>4.8036516089663278E-2</v>
       </c>
     </row>
     <row r="83" spans="2:17" ht="4.5" customHeight="1">
@@ -60937,24 +60937,24 @@
       <c r="Q83" s="176"/>
     </row>
     <row r="84" spans="2:17" ht="16.5" customHeight="1">
-      <c r="B84" s="384" t="s">
+      <c r="B84" s="385" t="s">
         <v>92</v>
       </c>
-      <c r="C84" s="384"/>
-      <c r="D84" s="384"/>
-      <c r="E84" s="384"/>
-      <c r="F84" s="384"/>
-      <c r="G84" s="384"/>
-      <c r="H84" s="384"/>
-      <c r="I84" s="384"/>
-      <c r="J84" s="384"/>
-      <c r="K84" s="384"/>
-      <c r="L84" s="384"/>
-      <c r="M84" s="384"/>
-      <c r="N84" s="384"/>
-      <c r="O84" s="384"/>
-      <c r="P84" s="384"/>
-      <c r="Q84" s="384"/>
+      <c r="C84" s="385"/>
+      <c r="D84" s="385"/>
+      <c r="E84" s="385"/>
+      <c r="F84" s="385"/>
+      <c r="G84" s="385"/>
+      <c r="H84" s="385"/>
+      <c r="I84" s="385"/>
+      <c r="J84" s="385"/>
+      <c r="K84" s="385"/>
+      <c r="L84" s="385"/>
+      <c r="M84" s="385"/>
+      <c r="N84" s="385"/>
+      <c r="O84" s="385"/>
+      <c r="P84" s="385"/>
+      <c r="Q84" s="385"/>
     </row>
     <row r="85" spans="2:17" ht="13.5" customHeight="1">
       <c r="B85" s="149"/>
@@ -61081,7 +61081,7 @@
       </c>
       <c r="F87" s="154">
         <f>IF(OR(Consolidated!H28=0,Consolidated!H28=""),"",Consolidated!H28)</f>
-        <v>-64575.130000000005</v>
+        <v>-64575.130000000012</v>
       </c>
       <c r="G87" s="154">
         <f>IF(OR(Consolidated!I28=0,Consolidated!I28=""),"",Consolidated!I28)</f>
@@ -61142,7 +61142,7 @@
       </c>
       <c r="F88" s="44">
         <f t="shared" si="47"/>
-        <v>1.5022366042089489E-2</v>
+        <v>1.5022366042089378E-2</v>
       </c>
       <c r="G88" s="44">
         <f t="shared" si="47"/>
@@ -61203,24 +61203,24 @@
       <c r="Q89" s="176"/>
     </row>
     <row r="90" spans="2:17" ht="16.5" customHeight="1">
-      <c r="B90" s="383" t="s">
+      <c r="B90" s="386" t="s">
         <v>93</v>
       </c>
-      <c r="C90" s="383"/>
-      <c r="D90" s="383"/>
-      <c r="E90" s="383"/>
-      <c r="F90" s="383"/>
-      <c r="G90" s="383"/>
-      <c r="H90" s="383"/>
-      <c r="I90" s="383"/>
-      <c r="J90" s="383"/>
-      <c r="K90" s="383"/>
-      <c r="L90" s="383"/>
-      <c r="M90" s="383"/>
-      <c r="N90" s="383"/>
-      <c r="O90" s="383"/>
-      <c r="P90" s="383"/>
-      <c r="Q90" s="383"/>
+      <c r="C90" s="386"/>
+      <c r="D90" s="386"/>
+      <c r="E90" s="386"/>
+      <c r="F90" s="386"/>
+      <c r="G90" s="386"/>
+      <c r="H90" s="386"/>
+      <c r="I90" s="386"/>
+      <c r="J90" s="386"/>
+      <c r="K90" s="386"/>
+      <c r="L90" s="386"/>
+      <c r="M90" s="386"/>
+      <c r="N90" s="386"/>
+      <c r="O90" s="386"/>
+      <c r="P90" s="386"/>
+      <c r="Q90" s="386"/>
     </row>
     <row r="91" spans="2:17" ht="13.5" customHeight="1">
       <c r="B91" s="149"/>
@@ -61335,7 +61335,7 @@
       </c>
       <c r="C93" s="154">
         <f>IF(OR(Consolidated!E34=0,Consolidated!E34=""),"",Consolidated!E34)</f>
-        <v>19129.020000000051</v>
+        <v>19129.02</v>
       </c>
       <c r="D93" s="154">
         <f>IF(OR(Consolidated!F34=0,Consolidated!F34=""),"",Consolidated!F34)</f>
@@ -61347,15 +61347,15 @@
       </c>
       <c r="F93" s="154">
         <f>IF(OR(Consolidated!H34=0,Consolidated!H34=""),"",Consolidated!H34)</f>
-        <v>5731.0600000000632</v>
+        <v>5731.0600000000559</v>
       </c>
       <c r="G93" s="154">
         <f>IF(OR(Consolidated!I34=0,Consolidated!I34=""),"",Consolidated!I34)</f>
-        <v>156561.15000000002</v>
+        <v>67675.579999999987</v>
       </c>
       <c r="H93" s="154">
         <f>IF(OR(Consolidated!J34=0,Consolidated!J34=""),"",Consolidated!J34)</f>
-        <v>14464.840000000011</v>
+        <v>103350.41000000003</v>
       </c>
       <c r="I93" s="154" t="str">
         <f>IF(OR(Consolidated!K34=0,Consolidated!K34=""),"",Consolidated!K34)</f>
@@ -61383,11 +61383,11 @@
       </c>
       <c r="O93" s="155">
         <f>SUMIF(C93:N93,"&lt;&gt;")</f>
-        <v>359496.2800000002</v>
+        <v>359496.28000000014</v>
       </c>
       <c r="Q93" s="182">
         <f>SUM(C93:G93)</f>
-        <v>345031.44000000018</v>
+        <v>256145.87000000008</v>
       </c>
     </row>
     <row r="94" spans="2:17" ht="15" customHeight="1">
@@ -61396,7 +61396,7 @@
       </c>
       <c r="C94" s="44">
         <f t="shared" ref="C94:N94" si="49">IFERROR(IF(C93="","",(C93-C92)/ABS(C92)),"—")</f>
-        <v>0.22776789774244352</v>
+        <v>0.22776789774244025</v>
       </c>
       <c r="D94" s="44">
         <f t="shared" si="49"/>
@@ -61408,15 +61408,15 @@
       </c>
       <c r="F94" s="44">
         <f t="shared" si="49"/>
-        <v>0.80731621256806985</v>
+        <v>0.80731621256806751</v>
       </c>
       <c r="G94" s="44">
         <f t="shared" si="49"/>
-        <v>0.82108076808520969</v>
+        <v>-0.21281430797479445</v>
       </c>
       <c r="H94" s="44">
         <f t="shared" si="49"/>
-        <v>-0.81238167833423147</v>
+        <v>0.3405216004925769</v>
       </c>
       <c r="I94" s="44" t="str">
         <f t="shared" si="49"/>
@@ -61444,11 +61444,11 @@
       </c>
       <c r="O94" s="45">
         <f>IFERROR(IF(O93=0,"",(O93-O92)/ABS(O92)),"—")</f>
-        <v>-0.45779350392107598</v>
+        <v>-0.45779350392107609</v>
       </c>
       <c r="Q94" s="183">
         <f>IFERROR(IF(Q93=0,"",(Q93-Q92)/ABS(Q92)),"—")</f>
-        <v>0.27433784084124369</v>
+        <v>-5.3951793737400167E-2</v>
       </c>
     </row>
     <row r="95" spans="2:17" ht="4.5" customHeight="1">
@@ -61469,24 +61469,24 @@
       <c r="Q95" s="176"/>
     </row>
     <row r="96" spans="2:17" ht="16.5" customHeight="1">
-      <c r="B96" s="384" t="s">
+      <c r="B96" s="385" t="s">
         <v>94</v>
       </c>
-      <c r="C96" s="384"/>
-      <c r="D96" s="384"/>
-      <c r="E96" s="384"/>
-      <c r="F96" s="384"/>
-      <c r="G96" s="384"/>
-      <c r="H96" s="384"/>
-      <c r="I96" s="384"/>
-      <c r="J96" s="384"/>
-      <c r="K96" s="384"/>
-      <c r="L96" s="384"/>
-      <c r="M96" s="384"/>
-      <c r="N96" s="384"/>
-      <c r="O96" s="384"/>
-      <c r="P96" s="384"/>
-      <c r="Q96" s="384"/>
+      <c r="C96" s="385"/>
+      <c r="D96" s="385"/>
+      <c r="E96" s="385"/>
+      <c r="F96" s="385"/>
+      <c r="G96" s="385"/>
+      <c r="H96" s="385"/>
+      <c r="I96" s="385"/>
+      <c r="J96" s="385"/>
+      <c r="K96" s="385"/>
+      <c r="L96" s="385"/>
+      <c r="M96" s="385"/>
+      <c r="N96" s="385"/>
+      <c r="O96" s="385"/>
+      <c r="P96" s="385"/>
+      <c r="Q96" s="385"/>
     </row>
     <row r="97" spans="2:17" ht="13.5" customHeight="1">
       <c r="B97" s="149"/>
@@ -61617,7 +61617,7 @@
       </c>
       <c r="G99" s="154">
         <f>IF(OR(Consolidated!I35=0,Consolidated!I35=""),"",Consolidated!I35)</f>
-        <v>-19711.419999999995</v>
+        <v>-20692.519999999997</v>
       </c>
       <c r="H99" s="154">
         <f>IF(OR(Consolidated!J35=0,Consolidated!J35=""),"",Consolidated!J35)</f>
@@ -61649,11 +61649,11 @@
       </c>
       <c r="O99" s="155">
         <f>SUMIF(C99:N99,"&lt;&gt;")</f>
-        <v>-132864.49999999997</v>
+        <v>-133845.59999999998</v>
       </c>
       <c r="Q99" s="182">
         <f>SUM(C99:G99)</f>
-        <v>-113133.33999999998</v>
+        <v>-114114.43999999997</v>
       </c>
     </row>
     <row r="100" spans="2:17" ht="15" customHeight="1">
@@ -61678,7 +61678,7 @@
       </c>
       <c r="G100" s="44">
         <f t="shared" si="51"/>
-        <v>0.17095463698371999</v>
+        <v>0.12969041524549541</v>
       </c>
       <c r="H100" s="44">
         <f t="shared" si="51"/>
@@ -61710,11 +61710,11 @@
       </c>
       <c r="O100" s="45">
         <f>IFERROR(IF(O99=0,"",(O99-O98)/ABS(O98)),"—")</f>
-        <v>0.53748052373500876</v>
+        <v>0.53406518059847807</v>
       </c>
       <c r="Q100" s="183">
         <f>IFERROR(IF(Q99=0,"",(Q99-Q98)/ABS(Q98)),"—")</f>
-        <v>3.9830841786356964E-2</v>
+        <v>3.1504189703748978E-2</v>
       </c>
     </row>
     <row r="101" spans="2:17" ht="4.5" customHeight="1">
@@ -61735,24 +61735,24 @@
       <c r="Q101" s="176"/>
     </row>
     <row r="102" spans="2:17" ht="16.5" customHeight="1">
-      <c r="B102" s="383" t="s">
+      <c r="B102" s="386" t="s">
         <v>95</v>
       </c>
-      <c r="C102" s="383"/>
-      <c r="D102" s="383"/>
-      <c r="E102" s="383"/>
-      <c r="F102" s="383"/>
-      <c r="G102" s="383"/>
-      <c r="H102" s="383"/>
-      <c r="I102" s="383"/>
-      <c r="J102" s="383"/>
-      <c r="K102" s="383"/>
-      <c r="L102" s="383"/>
-      <c r="M102" s="383"/>
-      <c r="N102" s="383"/>
-      <c r="O102" s="383"/>
-      <c r="P102" s="383"/>
-      <c r="Q102" s="383"/>
+      <c r="C102" s="386"/>
+      <c r="D102" s="386"/>
+      <c r="E102" s="386"/>
+      <c r="F102" s="386"/>
+      <c r="G102" s="386"/>
+      <c r="H102" s="386"/>
+      <c r="I102" s="386"/>
+      <c r="J102" s="386"/>
+      <c r="K102" s="386"/>
+      <c r="L102" s="386"/>
+      <c r="M102" s="386"/>
+      <c r="N102" s="386"/>
+      <c r="O102" s="386"/>
+      <c r="P102" s="386"/>
+      <c r="Q102" s="386"/>
     </row>
     <row r="103" spans="2:17" ht="13.5" customHeight="1">
       <c r="B103" s="149"/>
@@ -61867,7 +61867,7 @@
       </c>
       <c r="C105" s="154">
         <f>IF(OR(Consolidated!E46=0,Consolidated!E46=""),"",Consolidated!E46)</f>
-        <v>-4352.479999999945</v>
+        <v>-4352.4799999999959</v>
       </c>
       <c r="D105" s="154">
         <f>IF(OR(Consolidated!F46=0,Consolidated!F46=""),"",Consolidated!F46)</f>
@@ -61879,15 +61879,15 @@
       </c>
       <c r="F105" s="154">
         <f>IF(OR(Consolidated!H46=0,Consolidated!H46=""),"",Consolidated!H46)</f>
-        <v>-15400.709999999932</v>
+        <v>-15400.709999999939</v>
       </c>
       <c r="G105" s="154">
         <f>IF(OR(Consolidated!I46=0,Consolidated!I46=""),"",Consolidated!I46)</f>
-        <v>136849.73000000004</v>
+        <v>46983.06</v>
       </c>
       <c r="H105" s="154">
         <f>IF(OR(Consolidated!J46=0,Consolidated!J46=""),"",Consolidated!J46)</f>
-        <v>-5266.3199999999888</v>
+        <v>83619.250000000044</v>
       </c>
       <c r="I105" s="154" t="str">
         <f>IF(OR(Consolidated!K46=0,Consolidated!K46=""),"",Consolidated!K46)</f>
@@ -61915,11 +61915,11 @@
       </c>
       <c r="O105" s="155">
         <f>SUMIF(C105:N105,"&lt;&gt;")</f>
-        <v>226631.78000000023</v>
+        <v>225650.68000000017</v>
       </c>
       <c r="Q105" s="182">
         <f>SUM(C105:G105)</f>
-        <v>231898.10000000021</v>
+        <v>142031.43000000011</v>
       </c>
     </row>
     <row r="106" spans="2:17" ht="15" customHeight="1">
@@ -61928,7 +61928,7 @@
       </c>
       <c r="C106" s="44">
         <f t="shared" ref="C106:N106" si="53">IFERROR(IF(C105="","",(C105-C104)/ABS(C104)),"—")</f>
-        <v>0.44020682664131672</v>
+        <v>0.44020682664131017</v>
       </c>
       <c r="D106" s="44">
         <f t="shared" si="53"/>
@@ -61940,15 +61940,15 @@
       </c>
       <c r="F106" s="44">
         <f t="shared" si="53"/>
-        <v>0.24871528217312278</v>
+        <v>0.24871528217312242</v>
       </c>
       <c r="G106" s="44">
         <f t="shared" si="53"/>
-        <v>1.200315180857755</v>
+        <v>-0.24459083579375193</v>
       </c>
       <c r="H106" s="44">
         <f t="shared" si="53"/>
-        <v>-1.0989634522676761</v>
+        <v>0.5713533655444214</v>
       </c>
       <c r="I106" s="44" t="str">
         <f t="shared" si="53"/>
@@ -61976,11 +61976,11 @@
       </c>
       <c r="O106" s="45">
         <f>IFERROR(IF(O105=0,"",(O105-O104)/ABS(O104)),"—")</f>
-        <v>-0.39687440564647097</v>
+        <v>-0.39948536568314497</v>
       </c>
       <c r="Q106" s="183">
         <f>IFERROR(IF(Q105=0,"",(Q105-Q104)/ABS(Q104)),"—")</f>
-        <v>0.51639696939509883</v>
+        <v>-7.1247112370251858E-2</v>
       </c>
     </row>
     <row r="107" spans="2:17" ht="4.5" customHeight="1">
@@ -62001,24 +62001,24 @@
       <c r="Q107" s="176"/>
     </row>
     <row r="108" spans="2:17" ht="16.5" customHeight="1">
-      <c r="B108" s="383" t="s">
+      <c r="B108" s="386" t="s">
         <v>96</v>
       </c>
-      <c r="C108" s="383"/>
-      <c r="D108" s="383"/>
-      <c r="E108" s="383"/>
-      <c r="F108" s="383"/>
-      <c r="G108" s="383"/>
-      <c r="H108" s="383"/>
-      <c r="I108" s="383"/>
-      <c r="J108" s="383"/>
-      <c r="K108" s="383"/>
-      <c r="L108" s="383"/>
-      <c r="M108" s="383"/>
-      <c r="N108" s="383"/>
-      <c r="O108" s="383"/>
-      <c r="P108" s="383"/>
-      <c r="Q108" s="383"/>
+      <c r="C108" s="386"/>
+      <c r="D108" s="386"/>
+      <c r="E108" s="386"/>
+      <c r="F108" s="386"/>
+      <c r="G108" s="386"/>
+      <c r="H108" s="386"/>
+      <c r="I108" s="386"/>
+      <c r="J108" s="386"/>
+      <c r="K108" s="386"/>
+      <c r="L108" s="386"/>
+      <c r="M108" s="386"/>
+      <c r="N108" s="386"/>
+      <c r="O108" s="386"/>
+      <c r="P108" s="386"/>
+      <c r="Q108" s="386"/>
     </row>
     <row r="109" spans="2:17" ht="13.5" customHeight="1">
       <c r="B109" s="149"/>
@@ -62133,7 +62133,7 @@
       </c>
       <c r="C111" s="154">
         <f>IF(OR(Consolidated!E49=0,Consolidated!E49=""),"",Consolidated!E49)</f>
-        <v>-5606.7099999999427</v>
+        <v>-5606.7099999999937</v>
       </c>
       <c r="D111" s="154">
         <f>IF(OR(Consolidated!F49=0,Consolidated!F49=""),"",Consolidated!F49)</f>
@@ -62145,15 +62145,15 @@
       </c>
       <c r="F111" s="154">
         <f>IF(OR(Consolidated!H49=0,Consolidated!H49=""),"",Consolidated!H49)</f>
-        <v>-16149.21999999993</v>
+        <v>-16149.219999999937</v>
       </c>
       <c r="G111" s="154">
         <f>IF(OR(Consolidated!I49=0,Consolidated!I49=""),"",Consolidated!I49)</f>
-        <v>133862.00000000003</v>
+        <v>47259.33</v>
       </c>
       <c r="H111" s="154">
         <f>IF(OR(Consolidated!J49=0,Consolidated!J49=""),"",Consolidated!J49)</f>
-        <v>-6871.1399999999867</v>
+        <v>80108.73000000004</v>
       </c>
       <c r="I111" s="154" t="str">
         <f>IF(OR(Consolidated!K49=0,Consolidated!K49=""),"",Consolidated!K49)</f>
@@ -62181,11 +62181,11 @@
       </c>
       <c r="O111" s="155">
         <f>SUMIF(C111:N111,"&lt;&gt;")</f>
-        <v>218728.03000000023</v>
+        <v>219105.23000000016</v>
       </c>
       <c r="Q111" s="182">
         <f>SUM(C111:G111)</f>
-        <v>225599.17000000022</v>
+        <v>138996.50000000012</v>
       </c>
     </row>
     <row r="112" spans="2:17" ht="15" customHeight="1">
@@ -62194,7 +62194,7 @@
       </c>
       <c r="C112" s="44">
         <f t="shared" ref="C112:N112" si="55">IFERROR(IF(C111="","",(C111-C110)/ABS(C110)),"—")</f>
-        <v>0.36947952941114259</v>
+        <v>0.36947952941113688</v>
       </c>
       <c r="D112" s="44">
         <f t="shared" si="55"/>
@@ -62206,15 +62206,15 @@
       </c>
       <c r="F112" s="44">
         <f t="shared" si="55"/>
-        <v>0.25047668300602127</v>
+        <v>0.25047668300602094</v>
       </c>
       <c r="G112" s="44">
         <f t="shared" si="55"/>
-        <v>1.1946938158194826</v>
+        <v>-0.22517399044708633</v>
       </c>
       <c r="H112" s="44">
         <f t="shared" si="55"/>
-        <v>-1.1319024919597216</v>
+        <v>0.53781484800608459</v>
       </c>
       <c r="I112" s="44" t="str">
         <f t="shared" si="55"/>
@@ -62242,11 +62242,11 @@
       </c>
       <c r="O112" s="45">
         <f>IFERROR(IF(O111=0,"",(O111-O110)/ABS(O110)),"—")</f>
-        <v>-0.39678817236272501</v>
+        <v>-0.39574792387978147</v>
       </c>
       <c r="Q112" s="183">
         <f>IFERROR(IF(Q111=0,"",(Q111-Q110)/ABS(Q110)),"—")</f>
-        <v>0.53233599997924441</v>
+        <v>-5.5894838526599981E-2</v>
       </c>
     </row>
     <row r="113" spans="2:17" ht="4.5" customHeight="1">
@@ -62267,24 +62267,24 @@
       <c r="Q113" s="176"/>
     </row>
     <row r="114" spans="2:17" ht="16.5" customHeight="1">
-      <c r="B114" s="384" t="s">
+      <c r="B114" s="385" t="s">
         <v>97</v>
       </c>
-      <c r="C114" s="384"/>
-      <c r="D114" s="384"/>
-      <c r="E114" s="384"/>
-      <c r="F114" s="384"/>
-      <c r="G114" s="384"/>
-      <c r="H114" s="384"/>
-      <c r="I114" s="384"/>
-      <c r="J114" s="384"/>
-      <c r="K114" s="384"/>
-      <c r="L114" s="384"/>
-      <c r="M114" s="384"/>
-      <c r="N114" s="384"/>
-      <c r="O114" s="384"/>
-      <c r="P114" s="384"/>
-      <c r="Q114" s="384"/>
+      <c r="C114" s="385"/>
+      <c r="D114" s="385"/>
+      <c r="E114" s="385"/>
+      <c r="F114" s="385"/>
+      <c r="G114" s="385"/>
+      <c r="H114" s="385"/>
+      <c r="I114" s="385"/>
+      <c r="J114" s="385"/>
+      <c r="K114" s="385"/>
+      <c r="L114" s="385"/>
+      <c r="M114" s="385"/>
+      <c r="N114" s="385"/>
+      <c r="O114" s="385"/>
+      <c r="P114" s="385"/>
+      <c r="Q114" s="385"/>
     </row>
     <row r="115" spans="2:17" ht="13.5" customHeight="1">
       <c r="B115" s="149"/>
@@ -62533,24 +62533,24 @@
       <c r="Q119" s="176"/>
     </row>
     <row r="120" spans="2:17" ht="16.5" customHeight="1">
-      <c r="B120" s="383" t="s">
+      <c r="B120" s="386" t="s">
         <v>98</v>
       </c>
-      <c r="C120" s="383"/>
-      <c r="D120" s="383"/>
-      <c r="E120" s="383"/>
-      <c r="F120" s="383"/>
-      <c r="G120" s="383"/>
-      <c r="H120" s="383"/>
-      <c r="I120" s="383"/>
-      <c r="J120" s="383"/>
-      <c r="K120" s="383"/>
-      <c r="L120" s="383"/>
-      <c r="M120" s="383"/>
-      <c r="N120" s="383"/>
-      <c r="O120" s="383"/>
-      <c r="P120" s="383"/>
-      <c r="Q120" s="383"/>
+      <c r="C120" s="386"/>
+      <c r="D120" s="386"/>
+      <c r="E120" s="386"/>
+      <c r="F120" s="386"/>
+      <c r="G120" s="386"/>
+      <c r="H120" s="386"/>
+      <c r="I120" s="386"/>
+      <c r="J120" s="386"/>
+      <c r="K120" s="386"/>
+      <c r="L120" s="386"/>
+      <c r="M120" s="386"/>
+      <c r="N120" s="386"/>
+      <c r="O120" s="386"/>
+      <c r="P120" s="386"/>
+      <c r="Q120" s="386"/>
     </row>
     <row r="121" spans="2:17" ht="13.5" customHeight="1">
       <c r="B121" s="149"/>
@@ -62665,7 +62665,7 @@
       </c>
       <c r="C123" s="154">
         <f>IF(OR(Consolidated!E53=0,Consolidated!E53=""),"",Consolidated!E53)</f>
-        <v>-15843.279999999942</v>
+        <v>-15843.279999999993</v>
       </c>
       <c r="D123" s="154">
         <f>IF(OR(Consolidated!F53=0,Consolidated!F53=""),"",Consolidated!F53)</f>
@@ -62677,15 +62677,15 @@
       </c>
       <c r="F123" s="154">
         <f>IF(OR(Consolidated!H53=0,Consolidated!H53=""),"",Consolidated!H53)</f>
-        <v>-26786.079999999929</v>
+        <v>-26786.079999999936</v>
       </c>
       <c r="G123" s="154">
         <f>IF(OR(Consolidated!I53=0,Consolidated!I53=""),"",Consolidated!I53)</f>
-        <v>124591.97000000003</v>
+        <v>37989.300000000003</v>
       </c>
       <c r="H123" s="154">
         <f>IF(OR(Consolidated!J53=0,Consolidated!J53=""),"",Consolidated!J53)</f>
-        <v>-15997.259999999986</v>
+        <v>70982.610000000044</v>
       </c>
       <c r="I123" s="154" t="str">
         <f>IF(OR(Consolidated!K53=0,Consolidated!K53=""),"",Consolidated!K53)</f>
@@ -62713,11 +62713,11 @@
       </c>
       <c r="O123" s="155">
         <f>SUMIF(C123:N123,"&lt;&gt;")</f>
-        <v>160599.62000000023</v>
+        <v>160976.82000000015</v>
       </c>
       <c r="Q123" s="182">
         <f>SUM(C123:G123)</f>
-        <v>176596.88000000021</v>
+        <v>89994.210000000108</v>
       </c>
     </row>
     <row r="124" spans="2:17" ht="15" customHeight="1">
@@ -62726,7 +62726,7 @@
       </c>
       <c r="C124" s="44">
         <f t="shared" ref="C124:N124" si="59">IFERROR(IF(C123="","",(C123-C122)/ABS(C122)),"—")</f>
-        <v>0.20228120967391522</v>
+        <v>0.20228120967391264</v>
       </c>
       <c r="D124" s="44">
         <f t="shared" si="59"/>
@@ -62738,15 +62738,15 @@
       </c>
       <c r="F124" s="44">
         <f t="shared" si="59"/>
-        <v>0.15833394649648597</v>
+        <v>0.15833394649648574</v>
       </c>
       <c r="G124" s="44">
         <f t="shared" si="59"/>
-        <v>1.5328580797887033</v>
+        <v>-0.22770700671546518</v>
       </c>
       <c r="H124" s="44">
         <f t="shared" si="59"/>
-        <v>-1.3894828592343365</v>
+        <v>0.72820282340324827</v>
       </c>
       <c r="I124" s="44" t="str">
         <f t="shared" si="59"/>
@@ -62774,35 +62774,35 @@
       </c>
       <c r="O124" s="45">
         <f>IFERROR(IF(O123=0,"",(O123-O122)/ABS(O122)),"—")</f>
-        <v>-0.31196494164947125</v>
+        <v>-0.31034895511096161</v>
       </c>
       <c r="Q124" s="183">
         <f>IFERROR(IF(Q123=0,"",(Q123-Q122)/ABS(Q122)),"—")</f>
-        <v>0.93548011040424273</v>
+        <v>-1.367451391812468E-2</v>
       </c>
     </row>
     <row r="125" spans="2:17" ht="4.5" customHeight="1">
       <c r="Q125" s="176"/>
     </row>
     <row r="127" spans="2:17">
-      <c r="B127" s="383" t="s">
+      <c r="B127" s="386" t="s">
         <v>28</v>
       </c>
-      <c r="C127" s="383"/>
-      <c r="D127" s="383"/>
-      <c r="E127" s="383"/>
-      <c r="F127" s="383"/>
-      <c r="G127" s="383"/>
-      <c r="H127" s="383"/>
-      <c r="I127" s="383"/>
-      <c r="J127" s="383"/>
-      <c r="K127" s="383"/>
-      <c r="L127" s="383"/>
-      <c r="M127" s="383"/>
-      <c r="N127" s="383"/>
-      <c r="O127" s="383"/>
-      <c r="P127" s="383"/>
-      <c r="Q127" s="383"/>
+      <c r="C127" s="386"/>
+      <c r="D127" s="386"/>
+      <c r="E127" s="386"/>
+      <c r="F127" s="386"/>
+      <c r="G127" s="386"/>
+      <c r="H127" s="386"/>
+      <c r="I127" s="386"/>
+      <c r="J127" s="386"/>
+      <c r="K127" s="386"/>
+      <c r="L127" s="386"/>
+      <c r="M127" s="386"/>
+      <c r="N127" s="386"/>
+      <c r="O127" s="386"/>
+      <c r="P127" s="386"/>
+      <c r="Q127" s="386"/>
     </row>
     <row r="128" spans="2:17">
       <c r="B128" s="149"/>
@@ -63132,7 +63132,7 @@
       </c>
       <c r="C137" s="3">
         <f>IF(OR(Consolidated!E7=0,Consolidated!E7=""),NA(),Consolidated!E7)</f>
-        <v>282443.93000000005</v>
+        <v>282443.93</v>
       </c>
       <c r="D137" s="3">
         <f>IF(OR(Consolidated!F7=0,Consolidated!F7=""),NA(),Consolidated!F7)</f>
@@ -63148,11 +63148,11 @@
       </c>
       <c r="G137">
         <f>IF(OR(Consolidated!I7=0,Consolidated!I7=""),NA(),Consolidated!I7)</f>
-        <v>367273.20000000007</v>
+        <v>277334.58</v>
       </c>
       <c r="H137">
         <f>IF(OR(Consolidated!J7=0,Consolidated!J7=""),NA(),Consolidated!J7)</f>
-        <v>211611.88000000003</v>
+        <v>301550.50000000006</v>
       </c>
       <c r="I137" t="e">
         <f>IF(OR(Consolidated!K7=0,Consolidated!K7=""),NA(),Consolidated!K7)</f>
@@ -63243,7 +63243,7 @@
       </c>
       <c r="E139" s="3">
         <f>IF(OR(Consolidated!G20=0,Consolidated!G20=""),NA(),Consolidated!G20)</f>
-        <v>-138181.44</v>
+        <v>-138181.44000000003</v>
       </c>
       <c r="F139" s="3">
         <f>IF(OR(Consolidated!H20=0,Consolidated!H20=""),NA(),Consolidated!H20)</f>
@@ -63251,11 +63251,11 @@
       </c>
       <c r="G139">
         <f>IF(OR(Consolidated!I20=0,Consolidated!I20=""),NA(),Consolidated!I20)</f>
-        <v>-129779.16000000002</v>
+        <v>-128726.11</v>
       </c>
       <c r="H139">
         <f>IF(OR(Consolidated!J20=0,Consolidated!J20=""),NA(),Consolidated!J20)</f>
-        <v>-127763.55000000002</v>
+        <v>-128816.60000000002</v>
       </c>
       <c r="I139" t="e">
         <f>IF(OR(Consolidated!K20=0,Consolidated!K20=""),NA(),Consolidated!K20)</f>
@@ -63350,7 +63350,7 @@
       </c>
       <c r="F141" s="3">
         <f>IF(OR(Consolidated!H28=0,Consolidated!H28=""),NA(),Consolidated!H28)</f>
-        <v>-64575.130000000005</v>
+        <v>-64575.130000000012</v>
       </c>
       <c r="G141">
         <f>IF(OR(Consolidated!I28=0,Consolidated!I28=""),NA(),Consolidated!I28)</f>
@@ -63441,7 +63441,7 @@
       </c>
       <c r="C143" s="3">
         <f>IF(OR(Consolidated!E34=0,Consolidated!E34=""),NA(),Consolidated!E34)</f>
-        <v>19129.020000000051</v>
+        <v>19129.02</v>
       </c>
       <c r="D143" s="3">
         <f>IF(OR(Consolidated!F34=0,Consolidated!F34=""),NA(),Consolidated!F34)</f>
@@ -63453,15 +63453,15 @@
       </c>
       <c r="F143" s="3">
         <f>IF(OR(Consolidated!H34=0,Consolidated!H34=""),NA(),Consolidated!H34)</f>
-        <v>5731.0600000000632</v>
+        <v>5731.0600000000559</v>
       </c>
       <c r="G143">
         <f>IF(OR(Consolidated!I34=0,Consolidated!I34=""),NA(),Consolidated!I34)</f>
-        <v>156561.15000000002</v>
+        <v>67675.579999999987</v>
       </c>
       <c r="H143">
         <f>IF(OR(Consolidated!J34=0,Consolidated!J34=""),NA(),Consolidated!J34)</f>
-        <v>14464.840000000011</v>
+        <v>103350.41000000003</v>
       </c>
       <c r="I143" t="e">
         <f>IF(OR(Consolidated!K34=0,Consolidated!K34=""),NA(),Consolidated!K34)</f>
@@ -63560,7 +63560,7 @@
       </c>
       <c r="G145">
         <f>IF(OR(Consolidated!I35=0,Consolidated!I35=""),NA(),Consolidated!I35)</f>
-        <v>-19711.419999999995</v>
+        <v>-20692.519999999997</v>
       </c>
       <c r="H145">
         <f>IF(OR(Consolidated!J35=0,Consolidated!J35=""),NA(),Consolidated!J35)</f>
@@ -63647,7 +63647,7 @@
       </c>
       <c r="C147" s="3">
         <f>IF(OR(Consolidated!E46=0,Consolidated!E46=""),NA(),Consolidated!E46)</f>
-        <v>-4352.479999999945</v>
+        <v>-4352.4799999999959</v>
       </c>
       <c r="D147" s="3">
         <f>IF(OR(Consolidated!F46=0,Consolidated!F46=""),NA(),Consolidated!F46)</f>
@@ -63659,15 +63659,15 @@
       </c>
       <c r="F147" s="3">
         <f>IF(OR(Consolidated!H46=0,Consolidated!H46=""),NA(),Consolidated!H46)</f>
-        <v>-15400.709999999932</v>
+        <v>-15400.709999999939</v>
       </c>
       <c r="G147">
         <f>IF(OR(Consolidated!I46=0,Consolidated!I46=""),NA(),Consolidated!I46)</f>
-        <v>136849.73000000004</v>
+        <v>46983.06</v>
       </c>
       <c r="H147">
         <f>IF(OR(Consolidated!J46=0,Consolidated!J46=""),NA(),Consolidated!J46)</f>
-        <v>-5266.3199999999888</v>
+        <v>83619.250000000044</v>
       </c>
       <c r="I147" t="e">
         <f>IF(OR(Consolidated!K46=0,Consolidated!K46=""),NA(),Consolidated!K46)</f>
@@ -63750,7 +63750,7 @@
       </c>
       <c r="C149" s="3">
         <f>IF(OR(Consolidated!E49=0,Consolidated!E49=""),NA(),Consolidated!E49)</f>
-        <v>-5606.7099999999427</v>
+        <v>-5606.7099999999937</v>
       </c>
       <c r="D149" s="3">
         <f>IF(OR(Consolidated!F49=0,Consolidated!F49=""),NA(),Consolidated!F49)</f>
@@ -63762,15 +63762,15 @@
       </c>
       <c r="F149" s="3">
         <f>IF(OR(Consolidated!H49=0,Consolidated!H49=""),NA(),Consolidated!H49)</f>
-        <v>-16149.21999999993</v>
+        <v>-16149.219999999937</v>
       </c>
       <c r="G149">
         <f>IF(OR(Consolidated!I49=0,Consolidated!I49=""),NA(),Consolidated!I49)</f>
-        <v>133862.00000000003</v>
+        <v>47259.33</v>
       </c>
       <c r="H149">
         <f>IF(OR(Consolidated!J49=0,Consolidated!J49=""),NA(),Consolidated!J49)</f>
-        <v>-6871.1399999999867</v>
+        <v>80108.73000000004</v>
       </c>
       <c r="I149" t="e">
         <f>IF(OR(Consolidated!K49=0,Consolidated!K49=""),NA(),Consolidated!K49)</f>
@@ -63956,7 +63956,7 @@
       </c>
       <c r="C153" s="3">
         <f>IF(OR(Consolidated!E53=0,Consolidated!E53=""),NA(),Consolidated!E53)</f>
-        <v>-15843.279999999942</v>
+        <v>-15843.279999999993</v>
       </c>
       <c r="D153" s="3">
         <f>IF(OR(Consolidated!F53=0,Consolidated!F53=""),NA(),Consolidated!F53)</f>
@@ -63968,15 +63968,15 @@
       </c>
       <c r="F153" s="3">
         <f>IF(OR(Consolidated!H53=0,Consolidated!H53=""),NA(),Consolidated!H53)</f>
-        <v>-26786.079999999929</v>
+        <v>-26786.079999999936</v>
       </c>
       <c r="G153">
         <f>IF(OR(Consolidated!I53=0,Consolidated!I53=""),NA(),Consolidated!I53)</f>
-        <v>124591.97000000003</v>
+        <v>37989.300000000003</v>
       </c>
       <c r="H153">
         <f>IF(OR(Consolidated!J53=0,Consolidated!J53=""),NA(),Consolidated!J53)</f>
-        <v>-15997.259999999986</v>
+        <v>70982.610000000044</v>
       </c>
       <c r="I153" t="e">
         <f>IF(OR(Consolidated!K53=0,Consolidated!K53=""),NA(),Consolidated!K53)</f>
@@ -64005,15 +64005,15 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="D16:G16"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="B55:O55"/>
-    <mergeCell ref="D12:G12"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="D14:G14"/>
-    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="B64:O64"/>
+    <mergeCell ref="B66:Q66"/>
+    <mergeCell ref="B84:Q84"/>
+    <mergeCell ref="B72:Q72"/>
+    <mergeCell ref="B127:Q127"/>
+    <mergeCell ref="B90:Q90"/>
+    <mergeCell ref="B96:Q96"/>
+    <mergeCell ref="B102:Q102"/>
+    <mergeCell ref="B108:Q108"/>
     <mergeCell ref="B63:O63"/>
     <mergeCell ref="B78:Q78"/>
     <mergeCell ref="B114:Q114"/>
@@ -64030,15 +64030,15 @@
     <mergeCell ref="D8:G8"/>
     <mergeCell ref="D10:G10"/>
     <mergeCell ref="D11:G11"/>
-    <mergeCell ref="B64:O64"/>
-    <mergeCell ref="B66:Q66"/>
-    <mergeCell ref="B84:Q84"/>
-    <mergeCell ref="B72:Q72"/>
-    <mergeCell ref="B127:Q127"/>
-    <mergeCell ref="B90:Q90"/>
-    <mergeCell ref="B96:Q96"/>
-    <mergeCell ref="B102:Q102"/>
-    <mergeCell ref="B108:Q108"/>
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="B55:O55"/>
+    <mergeCell ref="D12:G12"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="D14:G14"/>
+    <mergeCell ref="D15:G15"/>
   </mergeCells>
   <conditionalFormatting sqref="C70:N70">
     <cfRule type="expression" dxfId="22" priority="3">
@@ -64331,7 +64331,7 @@
       </c>
       <c r="E8" s="232">
         <f>IF(E7&gt;0,(E10/E7)*12,"")</f>
-        <v>1.1667027687707446E-2</v>
+        <v>1.1667027687707445E-2</v>
       </c>
       <c r="F8" s="233">
         <f t="shared" ref="F8:P8" si="0">IF(F7&gt;0,(F10/F7)*12,"")</f>
@@ -64347,11 +64347,11 @@
       </c>
       <c r="I8" s="233">
         <f t="shared" si="0"/>
-        <v>1.4122742257190964E-2</v>
+        <v>1.0664335955758022E-2</v>
       </c>
       <c r="J8" s="234">
         <f t="shared" si="0"/>
-        <v>8.5848934979539868E-3</v>
+        <v>1.2233618106671392E-2</v>
       </c>
       <c r="K8" s="232">
         <f t="shared" si="0"/>
@@ -64379,7 +64379,7 @@
       </c>
       <c r="Q8" s="240">
         <f>AVERAGE(E8:P8)</f>
-        <v>1.1306897256925694E-2</v>
+        <v>1.1322757115866068E-2</v>
       </c>
       <c r="U8" s="261">
         <v>4</v>
@@ -64438,7 +64438,7 @@
       </c>
       <c r="E10" s="212">
         <f>CNS!B8+CRR!B8</f>
-        <v>282443.93000000005</v>
+        <v>282443.93</v>
       </c>
       <c r="F10" s="208">
         <f>CNS!C8+CRR!C8</f>
@@ -64454,11 +64454,11 @@
       </c>
       <c r="I10" s="208">
         <f>IF(I5=$D$2,Consolidated!I7,SUM(I11:I21))</f>
-        <v>367273.20000000007</v>
+        <v>277334.58</v>
       </c>
       <c r="J10" s="208">
         <f>IF(J5=$D$2,Consolidated!J7,SUM(J11:J21))</f>
-        <v>211611.88000000003</v>
+        <v>301550.50000000006</v>
       </c>
       <c r="K10" s="212">
         <f>IF(K5=$D$2,Consolidated!K7,SUM(K11:K21))</f>
@@ -64502,23 +64502,23 @@
       </c>
       <c r="E11" s="123">
         <f>CNS!B9</f>
-        <v>175809.20000000007</v>
+        <v>175809.19999999998</v>
       </c>
       <c r="F11" s="6">
         <f>CNS!C9</f>
-        <v>178265.27999999994</v>
+        <v>178265.27999999997</v>
       </c>
       <c r="G11" s="6">
         <f>CNS!D9</f>
-        <v>183175.54000000007</v>
+        <v>183175.54000000004</v>
       </c>
       <c r="H11" s="123">
         <f>CNS!E9</f>
-        <v>191954.81999999998</v>
+        <v>191954.82</v>
       </c>
       <c r="I11" s="281">
         <f>IF(I5=$D$2,CNS!F9,'Orçamento 2026'!G32)</f>
-        <v>192414.30000000005</v>
+        <v>192414.3</v>
       </c>
       <c r="J11" s="281">
         <f>IF(J5=$D$2,CNS!G9,'Orçamento 2026'!H32)</f>
@@ -64550,18 +64550,18 @@
       </c>
       <c r="Q11" s="9">
         <f>SUM(E11:P11)</f>
-        <v>2076220.6271522276</v>
+        <v>2076220.6271522278</v>
       </c>
       <c r="R11" s="229">
         <f>Q11/$Q$10</f>
-        <v>0.63511181635518132</v>
+        <v>0.63511181635518144</v>
       </c>
       <c r="T11" s="219" t="s">
         <v>225</v>
       </c>
       <c r="U11" s="9">
         <f t="shared" ref="U11:U56" si="1">Q11/$U$8</f>
-        <v>519055.15678805689</v>
+        <v>519055.15678805695</v>
       </c>
     </row>
     <row r="12" spans="4:28">
@@ -64658,11 +64658,11 @@
       </c>
       <c r="I13" s="281">
         <f>IF(I5=$D$2,CNS!F11,'Orçamento 2026'!G34)</f>
-        <v>117700</v>
+        <v>34000</v>
       </c>
       <c r="J13" s="281">
         <f>IF(J5=$D$2,CNS!G11,'Orçamento 2026'!H34)</f>
-        <v>0</v>
+        <v>83700</v>
       </c>
       <c r="K13" s="282">
         <f>IF(K5=$D$2,CNS!H11,'Orçamento 2026'!I34)</f>
@@ -64724,13 +64724,13 @@
         <f>CNS!E12</f>
         <v>30425.54</v>
       </c>
-      <c r="I14" s="281">
+      <c r="I14" s="281" t="str">
         <f>IF(I5=$D$2,CNS!F12,'Orçamento 2026'!G35)</f>
-        <v>6238.62</v>
+        <v>0,00</v>
       </c>
       <c r="J14" s="281">
         <f>IF(J5=$D$2,CNS!G12,'Orçamento 2026'!H35)</f>
-        <v>0</v>
+        <v>6238.62</v>
       </c>
       <c r="K14" s="282">
         <f>IF(K5=$D$2,CNS!H12,'Orçamento 2026'!I35)</f>
@@ -65294,7 +65294,7 @@
       </c>
       <c r="G23" s="10">
         <f>CNS!D16+CRR!D15</f>
-        <v>-138181.44</v>
+        <v>-138181.44000000003</v>
       </c>
       <c r="H23" s="122">
         <f>CNS!E16+CRR!E15</f>
@@ -65302,11 +65302,11 @@
       </c>
       <c r="I23" s="10">
         <f>IF(I5=$D$2,Consolidated!I20,SUM(Projeção!I24:I29))</f>
-        <v>-129779.16000000002</v>
+        <v>-128726.11</v>
       </c>
       <c r="J23" s="10">
         <f>IF(J5=$D$2,Consolidated!J20,SUM(Projeção!J24:J29))</f>
-        <v>-127763.55000000002</v>
+        <v>-128816.60000000002</v>
       </c>
       <c r="K23" s="122">
         <f>IF(K5=$D$2,Consolidated!K20,SUM(Projeção!K24:K29))</f>
@@ -65370,11 +65370,11 @@
       </c>
       <c r="I24" s="281">
         <f>IF(I5=$D$2,Consolidated!I21,'Orçamento 2026'!G39+'Orçamento 2026'!G40)</f>
-        <v>-24317.29</v>
+        <v>-23264.240000000002</v>
       </c>
       <c r="J24" s="281">
         <f>IF(J5=$D$2,Consolidated!J21,'Orçamento 2026'!H39+'Orçamento 2026'!H40)</f>
-        <v>-24405.439999999999</v>
+        <v>-25458.489999999998</v>
       </c>
       <c r="K24" s="282">
         <f>IF(K5=$D$2,Consolidated!K21,'Orçamento 2026'!I39+'Orçamento 2026'!I40)</f>
@@ -65766,7 +65766,7 @@
       </c>
       <c r="E30" s="212">
         <f>CNS!B23+CRR!B22</f>
-        <v>83627.280000000057</v>
+        <v>83627.28</v>
       </c>
       <c r="F30" s="208">
         <f>CNS!C23+CRR!C22</f>
@@ -65782,11 +65782,11 @@
       </c>
       <c r="I30" s="208">
         <f>I10+I23</f>
-        <v>237494.04000000004</v>
+        <v>148608.47000000003</v>
       </c>
       <c r="J30" s="208">
         <f t="shared" ref="J30:P30" si="5">J10+J23</f>
-        <v>83848.330000000016</v>
+        <v>172733.90000000002</v>
       </c>
       <c r="K30" s="212">
         <f t="shared" si="5"/>
@@ -65846,7 +65846,7 @@
       </c>
       <c r="H31" s="122">
         <f>CNS!E24+CRR!E23</f>
-        <v>-64575.130000000005</v>
+        <v>-64575.130000000012</v>
       </c>
       <c r="I31" s="10">
         <f>IF(I5=$D$2,Consolidated!I28,'Orçamento 2026'!G45)</f>
@@ -65906,7 +65906,7 @@
       </c>
       <c r="F32" s="6">
         <f>CNS!C25+CRR!C24</f>
-        <v>-32678.579999999994</v>
+        <v>-32678.579999999998</v>
       </c>
       <c r="G32" s="6">
         <f>CNS!D25+CRR!D24</f>
@@ -65978,11 +65978,11 @@
       </c>
       <c r="G33" s="6">
         <f>CNS!D26+CRR!D25</f>
-        <v>-13097.35</v>
+        <v>-13097.349999999999</v>
       </c>
       <c r="H33" s="123">
         <f>CNS!E26+CRR!E25</f>
-        <v>-10678.38</v>
+        <v>-10678.379999999997</v>
       </c>
       <c r="I33" s="6">
         <f>IF(I5=$D$2,Consolidated!I30,0)</f>
@@ -65990,7 +65990,7 @@
       </c>
       <c r="J33" s="6">
         <f>IF(J5=$D$2,Consolidated!J30,0)</f>
-        <v>-9939.9599999999991</v>
+        <v>-9939.9600000000009</v>
       </c>
       <c r="K33" s="123">
         <f>IF(K5=$D$2,Consolidated!K30,0)</f>
@@ -66106,7 +66106,7 @@
       </c>
       <c r="E35" s="123">
         <f>CNS!B28+CRR!B27</f>
-        <v>-1119.1799999999998</v>
+        <v>-1119.18</v>
       </c>
       <c r="F35" s="6">
         <f>CNS!C28+CRR!C27</f>
@@ -66154,18 +66154,18 @@
       </c>
       <c r="Q35" s="9">
         <f t="shared" si="2"/>
-        <v>-1119.1799999999998</v>
+        <v>-1119.18</v>
       </c>
       <c r="R35" s="230">
         <f t="shared" si="6"/>
-        <v>-3.4235496619804844E-4</v>
+        <v>-3.423549661980485E-4</v>
       </c>
       <c r="T35" s="219" t="s">
         <v>509</v>
       </c>
       <c r="U35" s="9">
         <f t="shared" si="1"/>
-        <v>-279.79499999999996</v>
+        <v>-279.79500000000002</v>
       </c>
     </row>
     <row r="36" spans="4:21">
@@ -66242,7 +66242,7 @@
       </c>
       <c r="E37" s="212">
         <f>CNS!B30+CRR!B29</f>
-        <v>19129.020000000051</v>
+        <v>19129.02</v>
       </c>
       <c r="F37" s="208">
         <f>CNS!C30+CRR!C29</f>
@@ -66254,15 +66254,15 @@
       </c>
       <c r="H37" s="212">
         <f>CNS!E30+CRR!E29</f>
-        <v>5731.0600000000632</v>
+        <v>5731.0600000000559</v>
       </c>
       <c r="I37" s="208">
         <f>I30+I31</f>
-        <v>156561.15000000002</v>
+        <v>67675.580000000016</v>
       </c>
       <c r="J37" s="208">
         <f t="shared" ref="J37:P37" si="7">J30+J31</f>
-        <v>14464.839999999997</v>
+        <v>103350.41</v>
       </c>
       <c r="K37" s="212">
         <f t="shared" si="7"/>
@@ -66326,7 +66326,7 @@
       </c>
       <c r="I38" s="10">
         <f>IF(I5=$D$2,Consolidated!I35,'Orçamento 2026'!G47)</f>
-        <v>-19711.419999999995</v>
+        <v>-20692.519999999997</v>
       </c>
       <c r="J38" s="10">
         <f>IF(J5=$D$2,Consolidated!J35,'Orçamento 2026'!H47)</f>
@@ -66358,18 +66358,18 @@
       </c>
       <c r="Q38" s="11">
         <f t="shared" si="2"/>
-        <v>-278418.16586152703</v>
+        <v>-279399.265861527</v>
       </c>
       <c r="R38" s="230">
         <f t="shared" ref="R38:R55" si="8">Q38/$Q$10</f>
-        <v>-8.5167570687865887E-2</v>
+        <v>-8.5467687252973282E-2</v>
       </c>
       <c r="T38" s="221" t="s">
         <v>17</v>
       </c>
       <c r="U38" s="11">
         <f t="shared" si="1"/>
-        <v>-69604.541465381757</v>
+        <v>-69849.816465381751</v>
       </c>
     </row>
     <row r="39" spans="4:21">
@@ -66394,7 +66394,7 @@
       </c>
       <c r="I39" s="6">
         <f>IF(I5=$D$2,Consolidated!I36,0)</f>
-        <v>-8184.48</v>
+        <v>-9165.58</v>
       </c>
       <c r="J39" s="6">
         <f>IF(J5=$D$2,Consolidated!J36,0)</f>
@@ -66426,18 +66426,18 @@
       </c>
       <c r="Q39" s="9">
         <f t="shared" si="2"/>
-        <v>-51305.659999999996</v>
+        <v>-52286.76</v>
       </c>
       <c r="R39" s="230">
         <f t="shared" si="8"/>
-        <v>-1.5694300733634061E-2</v>
+        <v>-1.5994417298741466E-2</v>
       </c>
       <c r="T39" s="219" t="s">
         <v>507</v>
       </c>
       <c r="U39" s="9">
         <f t="shared" si="1"/>
-        <v>-12826.414999999999</v>
+        <v>-13071.69</v>
       </c>
     </row>
     <row r="40" spans="4:21">
@@ -66790,11 +66790,11 @@
       </c>
       <c r="F45" s="6">
         <f>CNS!C38+CRR!C37</f>
-        <v>-906.86</v>
+        <v>-906.8599999999999</v>
       </c>
       <c r="G45" s="6">
         <f>CNS!D38+CRR!D37</f>
-        <v>-906.86</v>
+        <v>-906.8599999999999</v>
       </c>
       <c r="H45" s="123">
         <f>CNS!E38+CRR!E37</f>
@@ -67058,7 +67058,7 @@
       </c>
       <c r="E49" s="212">
         <f>CNS!B42+CRR!B41</f>
-        <v>-4352.479999999945</v>
+        <v>-4352.4799999999959</v>
       </c>
       <c r="F49" s="208">
         <f>CNS!C42+CRR!C41</f>
@@ -67070,15 +67070,15 @@
       </c>
       <c r="H49" s="212">
         <f>CNS!E42+CRR!E41</f>
-        <v>-15400.709999999932</v>
+        <v>-15400.709999999939</v>
       </c>
       <c r="I49" s="208">
         <f>I37+I38</f>
-        <v>136849.73000000004</v>
+        <v>46983.060000000019</v>
       </c>
       <c r="J49" s="208">
         <f t="shared" ref="J49:P49" si="9">J37+J38</f>
-        <v>-5266.3200000000033</v>
+        <v>83619.25</v>
       </c>
       <c r="K49" s="212">
         <f>K37+K38</f>
@@ -67106,22 +67106,22 @@
       </c>
       <c r="Q49" s="215">
         <f t="shared" si="2"/>
-        <v>396252.10971749068</v>
+        <v>395271.00971749058</v>
       </c>
       <c r="R49" s="12">
         <f>Q49/$Q$10</f>
-        <v>0.12121274292628256</v>
+        <v>0.12091262636117513</v>
       </c>
       <c r="S49" s="12">
         <f>Q49/$Q$30</f>
-        <v>0.26649836074393402</v>
+        <v>0.26583852440410405</v>
       </c>
       <c r="T49" s="330" t="s">
         <v>18</v>
       </c>
       <c r="U49" s="215">
         <f t="shared" si="1"/>
-        <v>99063.027429372669</v>
+        <v>98817.752429372646</v>
       </c>
     </row>
     <row r="50" spans="4:21">
@@ -67130,11 +67130,11 @@
       </c>
       <c r="E50" s="122">
         <f>CNS!B43+CRR!B42</f>
-        <v>-1262.8599999999976</v>
+        <v>-1262.8599999999981</v>
       </c>
       <c r="F50" s="10">
         <f>CNS!C43+CRR!C42</f>
-        <v>-973.19999999999925</v>
+        <v>-973.19999999999879</v>
       </c>
       <c r="G50" s="10">
         <f>CNS!D43+CRR!D42</f>
@@ -67142,15 +67142,15 @@
       </c>
       <c r="H50" s="122">
         <f>CNS!E43+CRR!E42</f>
-        <v>-751.95999999999833</v>
+        <v>-751.95999999999879</v>
       </c>
       <c r="I50" s="10">
         <f>IF(I5=$D$2,Consolidated!I47,'Orçamento 2026'!G49)</f>
-        <v>-2992.9199999999992</v>
+        <v>271.08000000000072</v>
       </c>
       <c r="J50" s="10">
         <f>IF(J5=$D$2,Consolidated!J47,'Orçamento 2026'!H49)</f>
-        <v>-1604.8199999999993</v>
+        <v>-3510.5199999999986</v>
       </c>
       <c r="K50" s="122">
         <f>IF(K5=$D$2,Consolidated!K47,'Orçamento 2026'!I49)</f>
@@ -67178,18 +67178,18 @@
       </c>
       <c r="Q50" s="11">
         <f t="shared" si="2"/>
-        <v>-14256.393630723231</v>
+        <v>-12898.093630723231</v>
       </c>
       <c r="R50" s="230">
         <f t="shared" si="8"/>
-        <v>-4.3610028409659975E-3</v>
+        <v>-3.9455015359151488E-3</v>
       </c>
       <c r="T50" s="221" t="s">
         <v>19</v>
       </c>
       <c r="U50" s="11">
         <f t="shared" si="1"/>
-        <v>-3564.0984076808077</v>
+        <v>-3224.5234076808078</v>
       </c>
     </row>
     <row r="51" spans="4:21">
@@ -67266,7 +67266,7 @@
       </c>
       <c r="E52" s="212">
         <f>CNS!B45+CRR!B44</f>
-        <v>-5606.7099999999427</v>
+        <v>-5606.7099999999937</v>
       </c>
       <c r="F52" s="208">
         <f>CNS!C45+CRR!C44</f>
@@ -67278,15 +67278,15 @@
       </c>
       <c r="H52" s="212">
         <f>CNS!E45+CRR!E44</f>
-        <v>-16149.21999999993</v>
+        <v>-16149.219999999937</v>
       </c>
       <c r="I52" s="208">
         <f>I49+I50+I51</f>
-        <v>133862.00000000003</v>
+        <v>47259.330000000024</v>
       </c>
       <c r="J52" s="208">
         <f t="shared" ref="J52:P52" si="10">J49+J50+J51</f>
-        <v>-6871.1400000000031</v>
+        <v>80108.73</v>
       </c>
       <c r="K52" s="212">
         <f t="shared" si="10"/>
@@ -67314,22 +67314,22 @@
       </c>
       <c r="Q52" s="215">
         <f t="shared" si="2"/>
-        <v>382015.47608676733</v>
+        <v>382392.67608676729</v>
       </c>
       <c r="R52" s="12">
         <f>Q52/$Q$10</f>
-        <v>0.11685778463054793</v>
+        <v>0.11697316937049136</v>
       </c>
       <c r="S52" s="12">
         <f>Q52/$Q$30</f>
-        <v>0.25692354856740152</v>
+        <v>0.2571772334796264</v>
       </c>
       <c r="T52" s="330" t="s">
         <v>21</v>
       </c>
       <c r="U52" s="215">
         <f t="shared" si="1"/>
-        <v>95503.869021691833</v>
+        <v>95598.169021691821</v>
       </c>
     </row>
     <row r="53" spans="4:21">
@@ -67542,7 +67542,7 @@
       </c>
       <c r="E56" s="213">
         <f>CNS!B49+CRR!B48</f>
-        <v>-15843.279999999942</v>
+        <v>-15843.279999999993</v>
       </c>
       <c r="F56" s="211">
         <f>CNS!C49+CRR!C48</f>
@@ -67554,15 +67554,15 @@
       </c>
       <c r="H56" s="213">
         <f>CNS!E49+CRR!E48</f>
-        <v>-26786.079999999929</v>
+        <v>-26786.079999999936</v>
       </c>
       <c r="I56" s="211">
         <f>I52+I53</f>
-        <v>124591.97000000003</v>
+        <v>37989.300000000025</v>
       </c>
       <c r="J56" s="211">
         <f t="shared" ref="J56:P56" si="11">J52+J53</f>
-        <v>-15997.260000000002</v>
+        <v>70982.61</v>
       </c>
       <c r="K56" s="213">
         <f t="shared" si="11"/>
@@ -67590,22 +67590,22 @@
       </c>
       <c r="Q56" s="216">
         <f>SUM(E56:P56)</f>
-        <v>261702.42900499137</v>
+        <v>262079.62900499132</v>
       </c>
       <c r="R56" s="12">
         <f>Q56/$Q$10</f>
-        <v>8.005425957929109E-2</v>
+        <v>8.0169644319234526E-2</v>
       </c>
       <c r="S56" s="12">
         <f>Q56/$Q$30</f>
-        <v>0.17600731105825451</v>
+        <v>0.17626099597047937</v>
       </c>
       <c r="T56" s="332" t="s">
         <v>23</v>
       </c>
       <c r="U56" s="216">
         <f t="shared" si="1"/>
-        <v>65425.607251247842</v>
+        <v>65519.907251247831</v>
       </c>
     </row>
     <row r="61" spans="4:21">
@@ -67614,7 +67614,7 @@
       </c>
       <c r="E61" s="14">
         <f>E49+(-E24)</f>
-        <v>97162.120000000054</v>
+        <v>97162.12000000001</v>
       </c>
       <c r="F61" s="14">
         <f t="shared" ref="F61:P61" si="12">F49+(-F24)</f>
@@ -67630,11 +67630,11 @@
       </c>
       <c r="I61" s="14">
         <f t="shared" si="12"/>
-        <v>161167.02000000005</v>
+        <v>70247.300000000017</v>
       </c>
       <c r="J61" s="14">
         <f t="shared" si="12"/>
-        <v>19139.119999999995</v>
+        <v>109077.73999999999</v>
       </c>
       <c r="K61" s="14">
         <f t="shared" si="12"/>
@@ -67662,11 +67662,11 @@
       </c>
       <c r="Q61" s="14">
         <f>Q49+(-Q24)</f>
-        <v>1007499.862058525</v>
+        <v>1006518.7620585249</v>
       </c>
       <c r="R61" s="367">
         <f>Q49/Q61</f>
-        <v>0.39330239600020178</v>
+        <v>0.39271102002021818</v>
       </c>
     </row>
     <row r="62" spans="4:21" outlineLevel="1">
@@ -67837,7 +67837,7 @@
       </c>
       <c r="E66" s="18">
         <f>IF(E61&lt;&gt;0,E61/E10,"")</f>
-        <v>0.3440049853434628</v>
+        <v>0.34400498534346274</v>
       </c>
       <c r="F66" s="18">
         <f t="shared" ref="F66:P66" si="14">IF(F61&lt;&gt;0,F61/F10,"")</f>
@@ -67853,11 +67853,11 @@
       </c>
       <c r="I66" s="18">
         <f t="shared" si="14"/>
-        <v>0.43882052924090298</v>
+        <v>0.25329441427751281</v>
       </c>
       <c r="J66" s="18">
         <f t="shared" si="14"/>
-        <v>9.0444449527124812E-2</v>
+        <v>0.36172296182563107</v>
       </c>
       <c r="K66" s="18">
         <f t="shared" si="14"/>
@@ -67885,7 +67885,7 @@
       </c>
       <c r="Q66" s="18">
         <f>IF(Q61&lt;&gt;0,Q61/Q10,"")</f>
-        <v>0.30819223111526728</v>
+        <v>0.30789211455015986</v>
       </c>
     </row>
     <row r="67" spans="4:28">
@@ -67894,7 +67894,7 @@
       </c>
       <c r="E67" s="18">
         <f>IF(E37&lt;&gt;0,E37/E10,"")</f>
-        <v>6.7726787401662505E-2</v>
+        <v>6.7726787401662339E-2</v>
       </c>
       <c r="F67" s="18">
         <f t="shared" ref="F67:Q67" si="15">IF(F37&lt;&gt;0,F37/F10,"")</f>
@@ -67906,15 +67906,15 @@
       </c>
       <c r="H67" s="18">
         <f t="shared" si="15"/>
-        <v>2.1487126811300879E-2</v>
+        <v>2.1487126811300852E-2</v>
       </c>
       <c r="I67" s="18">
         <f t="shared" si="15"/>
-        <v>0.4262798102339076</v>
+        <v>0.24402142711521951</v>
       </c>
       <c r="J67" s="18">
         <f t="shared" si="15"/>
-        <v>6.8355519548335353E-2</v>
+        <v>0.3427300236610451</v>
       </c>
       <c r="K67" s="18">
         <f t="shared" si="15"/>
@@ -67951,7 +67951,7 @@
       </c>
       <c r="E68" s="18">
         <f>IF(E52&lt;&gt;0,E52/E10,"")</f>
-        <v>-1.98507009869178E-2</v>
+        <v>-1.9850700986917984E-2</v>
       </c>
       <c r="F68" s="18">
         <f t="shared" ref="F68:Q68" si="16">IF(F52&lt;&gt;0,F52/F10,"")</f>
@@ -67963,15 +67963,15 @@
       </c>
       <c r="H68" s="18">
         <f t="shared" si="16"/>
-        <v>-6.0547322492451844E-2</v>
+        <v>-6.0547322492451872E-2</v>
       </c>
       <c r="I68" s="18">
         <f t="shared" si="16"/>
-        <v>0.36447527344766784</v>
+        <v>0.17040547197540248</v>
       </c>
       <c r="J68" s="18">
         <f t="shared" si="16"/>
-        <v>-3.247048322617805E-2</v>
+        <v>0.26565610071944823</v>
       </c>
       <c r="K68" s="18">
         <f t="shared" si="16"/>
@@ -67999,7 +67999,7 @@
       </c>
       <c r="Q68" s="18">
         <f t="shared" si="16"/>
-        <v>0.11685778463054793</v>
+        <v>0.11697316937049136</v>
       </c>
       <c r="S68" s="206"/>
       <c r="T68" s="206"/>
@@ -68018,7 +68018,7 @@
       </c>
       <c r="E69" s="18">
         <f>IF(E56&lt;&gt;0,E56/E10,"")</f>
-        <v>-5.6093540406408945E-2</v>
+        <v>-5.609354040640914E-2</v>
       </c>
       <c r="F69" s="18">
         <f t="shared" ref="F69:Q69" si="17">IF(F56&lt;&gt;0,F56/F10,"")</f>
@@ -68030,15 +68030,15 @@
       </c>
       <c r="H69" s="18">
         <f t="shared" si="17"/>
-        <v>-0.1004274772446358</v>
+        <v>-0.10042747724463583</v>
       </c>
       <c r="I69" s="18">
         <f t="shared" si="17"/>
-        <v>0.33923512524191801</v>
+        <v>0.13698003328686967</v>
       </c>
       <c r="J69" s="18">
         <f t="shared" si="17"/>
-        <v>-7.5597173466820475E-2</v>
+        <v>0.23539211508520128</v>
       </c>
       <c r="K69" s="18">
         <f t="shared" si="17"/>
@@ -68066,7 +68066,7 @@
       </c>
       <c r="Q69" s="18">
         <f t="shared" si="17"/>
-        <v>8.005425957929109E-2</v>
+        <v>8.0169644319234526E-2</v>
       </c>
       <c r="S69" s="206"/>
       <c r="T69" s="206"/>
@@ -68307,18 +68307,18 @@
         <f t="shared" ref="N5:N8" si="2">IF(H5&lt;0,H5,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="P5" s="398" t="s">
+      <c r="P5" s="392" t="s">
         <v>605</v>
       </c>
-      <c r="Q5" s="392">
+      <c r="Q5" s="395">
         <f>SUM(H4:H6)</f>
         <v>51025.550000000025</v>
       </c>
-      <c r="R5" s="395">
+      <c r="R5" s="398">
         <f>IF(Q5&gt;=0,Q5,NA())</f>
         <v>51025.550000000025</v>
       </c>
-      <c r="S5" s="395" t="e">
+      <c r="S5" s="398" t="e">
         <f>IF(Q5&lt;0,Q5,NA())</f>
         <v>#N/A</v>
       </c>
@@ -68368,10 +68368,10 @@
         <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
-      <c r="P6" s="399"/>
-      <c r="Q6" s="393"/>
-      <c r="R6" s="396"/>
-      <c r="S6" s="396"/>
+      <c r="P6" s="393"/>
+      <c r="Q6" s="396"/>
+      <c r="R6" s="399"/>
+      <c r="S6" s="399"/>
       <c r="V6" s="323"/>
       <c r="W6" s="323"/>
       <c r="X6" s="323"/>
@@ -68418,10 +68418,10 @@
         <f t="shared" si="2"/>
         <v>-120711.43</v>
       </c>
-      <c r="P7" s="400"/>
-      <c r="Q7" s="394"/>
-      <c r="R7" s="397"/>
-      <c r="S7" s="397"/>
+      <c r="P7" s="394"/>
+      <c r="Q7" s="397"/>
+      <c r="R7" s="400"/>
+      <c r="S7" s="400"/>
     </row>
     <row r="8" spans="4:33" ht="15" customHeight="1">
       <c r="D8" s="107">
@@ -68456,18 +68456,18 @@
         <f t="shared" si="2"/>
         <v>-10290.099999999984</v>
       </c>
-      <c r="P8" s="398" t="s">
+      <c r="P8" s="392" t="s">
         <v>606</v>
       </c>
-      <c r="Q8" s="392">
+      <c r="Q8" s="395">
         <f>SUM(H7:H9)</f>
         <v>-128684.78999999996</v>
       </c>
-      <c r="R8" s="395" t="e">
+      <c r="R8" s="398" t="e">
         <f>IF(Q8&gt;=0,Q8,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="S8" s="395">
+      <c r="S8" s="398">
         <f>IF(Q8&lt;0,Q8,NA())</f>
         <v>-128684.78999999996</v>
       </c>
@@ -68505,10 +68505,10 @@
         <f t="shared" ref="N9:N63" si="5">IF(H9&lt;0,H9,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="P9" s="399"/>
-      <c r="Q9" s="393"/>
-      <c r="R9" s="396"/>
-      <c r="S9" s="396"/>
+      <c r="P9" s="393"/>
+      <c r="Q9" s="396"/>
+      <c r="R9" s="399"/>
+      <c r="S9" s="399"/>
     </row>
     <row r="10" spans="4:33" ht="15" customHeight="1">
       <c r="D10" s="107">
@@ -68543,10 +68543,10 @@
         <f t="shared" si="5"/>
         <v>-6944.5299999999934</v>
       </c>
-      <c r="P10" s="400"/>
-      <c r="Q10" s="394"/>
-      <c r="R10" s="397"/>
-      <c r="S10" s="397"/>
+      <c r="P10" s="394"/>
+      <c r="Q10" s="397"/>
+      <c r="R10" s="400"/>
+      <c r="S10" s="400"/>
     </row>
     <row r="11" spans="4:33" ht="15" customHeight="1">
       <c r="D11" s="107">
@@ -68581,18 +68581,18 @@
         <f t="shared" si="5"/>
         <v>-1944.2300000000014</v>
       </c>
-      <c r="P11" s="398" t="s">
+      <c r="P11" s="392" t="s">
         <v>607</v>
       </c>
-      <c r="Q11" s="392">
+      <c r="Q11" s="395">
         <f t="shared" ref="Q11" si="6">SUM(H10:H12)</f>
         <v>63263.910000000018</v>
       </c>
-      <c r="R11" s="395">
+      <c r="R11" s="398">
         <f t="shared" ref="R11" si="7">IF(Q11&gt;=0,Q11,NA())</f>
         <v>63263.910000000018</v>
       </c>
-      <c r="S11" s="395" t="e">
+      <c r="S11" s="398" t="e">
         <f t="shared" ref="S11" si="8">IF(Q11&lt;0,Q11,NA())</f>
         <v>#N/A</v>
       </c>
@@ -68630,10 +68630,10 @@
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="P12" s="399"/>
-      <c r="Q12" s="393"/>
-      <c r="R12" s="396"/>
-      <c r="S12" s="396"/>
+      <c r="P12" s="393"/>
+      <c r="Q12" s="396"/>
+      <c r="R12" s="399"/>
+      <c r="S12" s="399"/>
     </row>
     <row r="13" spans="4:33" ht="15" customHeight="1">
       <c r="D13" s="107">
@@ -68668,10 +68668,10 @@
         <f t="shared" si="5"/>
         <v>-29851.530000000013</v>
       </c>
-      <c r="P13" s="400"/>
-      <c r="Q13" s="394"/>
-      <c r="R13" s="397"/>
-      <c r="S13" s="397"/>
+      <c r="P13" s="394"/>
+      <c r="Q13" s="397"/>
+      <c r="R13" s="400"/>
+      <c r="S13" s="400"/>
     </row>
     <row r="14" spans="4:33" ht="15" customHeight="1">
       <c r="D14" s="107">
@@ -68706,18 +68706,18 @@
         <f t="shared" si="5"/>
         <v>-7189.3699999999917</v>
       </c>
-      <c r="P14" s="398" t="s">
+      <c r="P14" s="392" t="s">
         <v>608</v>
       </c>
-      <c r="Q14" s="392">
+      <c r="Q14" s="395">
         <f t="shared" ref="Q14" si="9">SUM(H13:H15)</f>
         <v>2032.5599999999977</v>
       </c>
-      <c r="R14" s="395">
+      <c r="R14" s="398">
         <f t="shared" ref="R14" si="10">IF(Q14&gt;=0,Q14,NA())</f>
         <v>2032.5599999999977</v>
       </c>
-      <c r="S14" s="395" t="e">
+      <c r="S14" s="398" t="e">
         <f t="shared" ref="S14" si="11">IF(Q14&lt;0,Q14,NA())</f>
         <v>#N/A</v>
       </c>
@@ -68755,10 +68755,10 @@
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="P15" s="399"/>
-      <c r="Q15" s="393"/>
-      <c r="R15" s="396"/>
-      <c r="S15" s="396"/>
+      <c r="P15" s="393"/>
+      <c r="Q15" s="396"/>
+      <c r="R15" s="399"/>
+      <c r="S15" s="399"/>
     </row>
     <row r="16" spans="4:33" ht="15" customHeight="1">
       <c r="D16" s="107">
@@ -68793,10 +68793,10 @@
         <f t="shared" si="5"/>
         <v>-50335.23</v>
       </c>
-      <c r="P16" s="400"/>
-      <c r="Q16" s="394"/>
-      <c r="R16" s="397"/>
-      <c r="S16" s="397"/>
+      <c r="P16" s="394"/>
+      <c r="Q16" s="397"/>
+      <c r="R16" s="400"/>
+      <c r="S16" s="400"/>
     </row>
     <row r="17" spans="4:19" ht="15" customHeight="1">
       <c r="D17" s="107">
@@ -68834,15 +68834,15 @@
       <c r="P17" s="325" t="s">
         <v>609</v>
       </c>
-      <c r="Q17" s="392">
+      <c r="Q17" s="395">
         <f t="shared" ref="Q17" si="12">SUM(H16:H18)</f>
         <v>-13021.260000000017</v>
       </c>
-      <c r="R17" s="395" t="e">
+      <c r="R17" s="398" t="e">
         <f t="shared" ref="R17" si="13">IF(Q17&gt;=0,Q17,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="S17" s="395">
+      <c r="S17" s="398">
         <f t="shared" ref="S17" si="14">IF(Q17&lt;0,Q17,NA())</f>
         <v>-13021.260000000017</v>
       </c>
@@ -68881,9 +68881,9 @@
         <v>#N/A</v>
       </c>
       <c r="P18" s="325"/>
-      <c r="Q18" s="393"/>
-      <c r="R18" s="396"/>
-      <c r="S18" s="396"/>
+      <c r="Q18" s="396"/>
+      <c r="R18" s="399"/>
+      <c r="S18" s="399"/>
     </row>
     <row r="19" spans="4:19" ht="15" customHeight="1">
       <c r="D19" s="107">
@@ -68919,9 +68919,9 @@
         <v>#N/A</v>
       </c>
       <c r="P19" s="326"/>
-      <c r="Q19" s="394"/>
-      <c r="R19" s="397"/>
-      <c r="S19" s="397"/>
+      <c r="Q19" s="397"/>
+      <c r="R19" s="400"/>
+      <c r="S19" s="400"/>
     </row>
     <row r="20" spans="4:19" ht="15" customHeight="1">
       <c r="D20" s="107">
@@ -68959,15 +68959,15 @@
       <c r="P20" s="325" t="s">
         <v>610</v>
       </c>
-      <c r="Q20" s="392">
+      <c r="Q20" s="395">
         <f t="shared" ref="Q20" si="15">SUM(H19:H21)</f>
         <v>1864.0900000000547</v>
       </c>
-      <c r="R20" s="395">
+      <c r="R20" s="398">
         <f t="shared" ref="R20" si="16">IF(Q20&gt;=0,Q20,NA())</f>
         <v>1864.0900000000547</v>
       </c>
-      <c r="S20" s="395" t="e">
+      <c r="S20" s="398" t="e">
         <f t="shared" ref="S20" si="17">IF(Q20&lt;0,Q20,NA())</f>
         <v>#N/A</v>
       </c>
@@ -69006,9 +69006,9 @@
         <v>-36345.219999999972</v>
       </c>
       <c r="P21" s="325"/>
-      <c r="Q21" s="393"/>
-      <c r="R21" s="396"/>
-      <c r="S21" s="396"/>
+      <c r="Q21" s="396"/>
+      <c r="R21" s="399"/>
+      <c r="S21" s="399"/>
     </row>
     <row r="22" spans="4:19" ht="15" customHeight="1">
       <c r="D22" s="107">
@@ -69044,9 +69044,9 @@
         <v>-6132.7899999999781</v>
       </c>
       <c r="P22" s="326"/>
-      <c r="Q22" s="394"/>
-      <c r="R22" s="397"/>
-      <c r="S22" s="397"/>
+      <c r="Q22" s="397"/>
+      <c r="R22" s="400"/>
+      <c r="S22" s="400"/>
     </row>
     <row r="23" spans="4:19" ht="15" customHeight="1">
       <c r="D23" s="107">
@@ -69084,15 +69084,15 @@
       <c r="P23" s="325" t="s">
         <v>611</v>
       </c>
-      <c r="Q23" s="392">
+      <c r="Q23" s="395">
         <f t="shared" ref="Q23" si="18">SUM(H22:H24)</f>
         <v>10423.430000000033</v>
       </c>
-      <c r="R23" s="395">
+      <c r="R23" s="398">
         <f t="shared" ref="R23" si="19">IF(Q23&gt;=0,Q23,NA())</f>
         <v>10423.430000000033</v>
       </c>
-      <c r="S23" s="395" t="e">
+      <c r="S23" s="398" t="e">
         <f t="shared" ref="S23" si="20">IF(Q23&lt;0,Q23,NA())</f>
         <v>#N/A</v>
       </c>
@@ -69131,9 +69131,9 @@
         <v>-3318.8700000000126</v>
       </c>
       <c r="P24" s="325"/>
-      <c r="Q24" s="393"/>
-      <c r="R24" s="396"/>
-      <c r="S24" s="396"/>
+      <c r="Q24" s="396"/>
+      <c r="R24" s="399"/>
+      <c r="S24" s="399"/>
     </row>
     <row r="25" spans="4:19" ht="15" customHeight="1">
       <c r="D25" s="107">
@@ -69169,9 +69169,9 @@
         <v>-44373.710000000021</v>
       </c>
       <c r="P25" s="326"/>
-      <c r="Q25" s="394"/>
-      <c r="R25" s="397"/>
-      <c r="S25" s="397"/>
+      <c r="Q25" s="397"/>
+      <c r="R25" s="400"/>
+      <c r="S25" s="400"/>
     </row>
     <row r="26" spans="4:19" ht="15" customHeight="1">
       <c r="D26" s="107">
@@ -69209,15 +69209,15 @@
       <c r="P26" s="325" t="s">
         <v>612</v>
       </c>
-      <c r="Q26" s="392">
+      <c r="Q26" s="395">
         <f t="shared" ref="Q26" si="21">SUM(H25:H27)</f>
         <v>-31621.239999999965</v>
       </c>
-      <c r="R26" s="395" t="e">
+      <c r="R26" s="398" t="e">
         <f t="shared" ref="R26" si="22">IF(Q26&gt;=0,Q26,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="S26" s="395">
+      <c r="S26" s="398">
         <f t="shared" ref="S26" si="23">IF(Q26&lt;0,Q26,NA())</f>
         <v>-31621.239999999965</v>
       </c>
@@ -69256,9 +69256,9 @@
         <v>#N/A</v>
       </c>
       <c r="P27" s="325"/>
-      <c r="Q27" s="393"/>
-      <c r="R27" s="396"/>
-      <c r="S27" s="396"/>
+      <c r="Q27" s="396"/>
+      <c r="R27" s="399"/>
+      <c r="S27" s="399"/>
     </row>
     <row r="28" spans="4:19" ht="15" customHeight="1">
       <c r="D28" s="107">
@@ -69294,9 +69294,9 @@
         <v>-44170.299999999988</v>
       </c>
       <c r="P28" s="326"/>
-      <c r="Q28" s="394"/>
-      <c r="R28" s="397"/>
-      <c r="S28" s="397"/>
+      <c r="Q28" s="397"/>
+      <c r="R28" s="400"/>
+      <c r="S28" s="400"/>
     </row>
     <row r="29" spans="4:19" ht="15" customHeight="1">
       <c r="D29" s="107">
@@ -69334,15 +69334,15 @@
       <c r="P29" s="325" t="s">
         <v>613</v>
       </c>
-      <c r="Q29" s="392">
+      <c r="Q29" s="395">
         <f t="shared" ref="Q29" si="24">SUM(H28:H30)</f>
         <v>-2864.9200000000164</v>
       </c>
-      <c r="R29" s="395" t="e">
+      <c r="R29" s="398" t="e">
         <f t="shared" ref="R29" si="25">IF(Q29&gt;=0,Q29,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="S29" s="395">
+      <c r="S29" s="398">
         <f t="shared" ref="S29" si="26">IF(Q29&lt;0,Q29,NA())</f>
         <v>-2864.9200000000164</v>
       </c>
@@ -69381,9 +69381,9 @@
         <v>#N/A</v>
       </c>
       <c r="P30" s="325"/>
-      <c r="Q30" s="393"/>
-      <c r="R30" s="396"/>
-      <c r="S30" s="396"/>
+      <c r="Q30" s="396"/>
+      <c r="R30" s="399"/>
+      <c r="S30" s="399"/>
     </row>
     <row r="31" spans="4:19" ht="15" customHeight="1">
       <c r="D31" s="107">
@@ -69419,9 +69419,9 @@
         <v>-43839.760000000009</v>
       </c>
       <c r="P31" s="326"/>
-      <c r="Q31" s="394"/>
-      <c r="R31" s="397"/>
-      <c r="S31" s="397"/>
+      <c r="Q31" s="397"/>
+      <c r="R31" s="400"/>
+      <c r="S31" s="400"/>
     </row>
     <row r="32" spans="4:19" ht="15" customHeight="1">
       <c r="D32" s="107">
@@ -69459,15 +69459,15 @@
       <c r="P32" s="325" t="s">
         <v>614</v>
       </c>
-      <c r="Q32" s="392">
+      <c r="Q32" s="395">
         <f t="shared" ref="Q32" si="27">SUM(H31:H33)</f>
         <v>16410.719999999972</v>
       </c>
-      <c r="R32" s="395">
+      <c r="R32" s="398">
         <f t="shared" ref="R32" si="28">IF(Q32&gt;=0,Q32,NA())</f>
         <v>16410.719999999972</v>
       </c>
-      <c r="S32" s="395" t="e">
+      <c r="S32" s="398" t="e">
         <f t="shared" ref="S32" si="29">IF(Q32&lt;0,Q32,NA())</f>
         <v>#N/A</v>
       </c>
@@ -69506,9 +69506,9 @@
         <v>#N/A</v>
       </c>
       <c r="P33" s="325"/>
-      <c r="Q33" s="393"/>
-      <c r="R33" s="396"/>
-      <c r="S33" s="396"/>
+      <c r="Q33" s="396"/>
+      <c r="R33" s="399"/>
+      <c r="S33" s="399"/>
     </row>
     <row r="34" spans="3:19" ht="15" customHeight="1">
       <c r="D34" s="107">
@@ -69544,9 +69544,9 @@
         <v>#N/A</v>
       </c>
       <c r="P34" s="326"/>
-      <c r="Q34" s="394"/>
-      <c r="R34" s="397"/>
-      <c r="S34" s="397"/>
+      <c r="Q34" s="397"/>
+      <c r="R34" s="400"/>
+      <c r="S34" s="400"/>
     </row>
     <row r="35" spans="3:19" ht="15" customHeight="1">
       <c r="D35" s="107">
@@ -69584,15 +69584,15 @@
       <c r="P35" s="325" t="s">
         <v>615</v>
       </c>
-      <c r="Q35" s="392">
+      <c r="Q35" s="395">
         <f t="shared" ref="Q35" si="30">SUM(H34:H36)</f>
         <v>48719.930000000044</v>
       </c>
-      <c r="R35" s="395">
+      <c r="R35" s="398">
         <f t="shared" ref="R35" si="31">IF(Q35&gt;=0,Q35,NA())</f>
         <v>48719.930000000044</v>
       </c>
-      <c r="S35" s="395" t="e">
+      <c r="S35" s="398" t="e">
         <f t="shared" ref="S35" si="32">IF(Q35&lt;0,Q35,NA())</f>
         <v>#N/A</v>
       </c>
@@ -69631,9 +69631,9 @@
         <v>#N/A</v>
       </c>
       <c r="P36" s="325"/>
-      <c r="Q36" s="393"/>
-      <c r="R36" s="396"/>
-      <c r="S36" s="396"/>
+      <c r="Q36" s="396"/>
+      <c r="R36" s="399"/>
+      <c r="S36" s="399"/>
     </row>
     <row r="37" spans="3:19" ht="15" customHeight="1">
       <c r="D37" s="107">
@@ -69669,9 +69669,9 @@
         <v>-34959.109999999971</v>
       </c>
       <c r="P37" s="326"/>
-      <c r="Q37" s="394"/>
-      <c r="R37" s="397"/>
-      <c r="S37" s="397"/>
+      <c r="Q37" s="397"/>
+      <c r="R37" s="400"/>
+      <c r="S37" s="400"/>
     </row>
     <row r="38" spans="3:19" ht="15" customHeight="1">
       <c r="D38" s="107">
@@ -69709,15 +69709,15 @@
       <c r="P38" s="325" t="s">
         <v>616</v>
       </c>
-      <c r="Q38" s="392">
+      <c r="Q38" s="395">
         <f t="shared" ref="Q38" si="33">SUM(H37:H39)</f>
         <v>57951.049999999974</v>
       </c>
-      <c r="R38" s="395">
+      <c r="R38" s="398">
         <f t="shared" ref="R38" si="34">IF(Q38&gt;=0,Q38,NA())</f>
         <v>57951.049999999974</v>
       </c>
-      <c r="S38" s="395" t="e">
+      <c r="S38" s="398" t="e">
         <f t="shared" ref="S38" si="35">IF(Q38&lt;0,Q38,NA())</f>
         <v>#N/A</v>
       </c>
@@ -69756,9 +69756,9 @@
         <v>#N/A</v>
       </c>
       <c r="P39" s="325"/>
-      <c r="Q39" s="393"/>
-      <c r="R39" s="396"/>
-      <c r="S39" s="396"/>
+      <c r="Q39" s="396"/>
+      <c r="R39" s="399"/>
+      <c r="S39" s="399"/>
     </row>
     <row r="40" spans="3:19" ht="15" customHeight="1">
       <c r="D40" s="107">
@@ -69796,9 +69796,9 @@
         <v>-45310.300000000017</v>
       </c>
       <c r="P40" s="326"/>
-      <c r="Q40" s="394"/>
-      <c r="R40" s="397"/>
-      <c r="S40" s="397"/>
+      <c r="Q40" s="397"/>
+      <c r="R40" s="400"/>
+      <c r="S40" s="400"/>
     </row>
     <row r="41" spans="3:19" ht="15" customHeight="1">
       <c r="D41" s="107">
@@ -69838,15 +69838,15 @@
       <c r="P41" s="325" t="s">
         <v>617</v>
       </c>
-      <c r="Q41" s="392">
+      <c r="Q41" s="395">
         <f t="shared" ref="Q41" si="37">SUM(H40:H42)</f>
         <v>-4982.5900000000365</v>
       </c>
-      <c r="R41" s="395" t="e">
+      <c r="R41" s="398" t="e">
         <f t="shared" ref="R41" si="38">IF(Q41&gt;=0,Q41,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="S41" s="395">
+      <c r="S41" s="398">
         <f t="shared" ref="S41" si="39">IF(Q41&lt;0,Q41,NA())</f>
         <v>-4982.5900000000365</v>
       </c>
@@ -69887,9 +69887,9 @@
         <v>#N/A</v>
       </c>
       <c r="P42" s="325"/>
-      <c r="Q42" s="393"/>
-      <c r="R42" s="396"/>
-      <c r="S42" s="396"/>
+      <c r="Q42" s="396"/>
+      <c r="R42" s="399"/>
+      <c r="S42" s="399"/>
     </row>
     <row r="43" spans="3:19" ht="15" customHeight="1">
       <c r="D43" s="107">
@@ -69927,9 +69927,9 @@
         <v>-27414.700000000044</v>
       </c>
       <c r="P43" s="326"/>
-      <c r="Q43" s="394"/>
-      <c r="R43" s="397"/>
-      <c r="S43" s="397"/>
+      <c r="Q43" s="397"/>
+      <c r="R43" s="400"/>
+      <c r="S43" s="400"/>
     </row>
     <row r="44" spans="3:19" ht="15" customHeight="1">
       <c r="D44" s="107">
@@ -69969,15 +69969,15 @@
       <c r="P44" s="325" t="s">
         <v>618</v>
       </c>
-      <c r="Q44" s="392">
+      <c r="Q44" s="395">
         <f t="shared" ref="Q44" si="40">SUM(H43:H45)</f>
         <v>42552.479999999967</v>
       </c>
-      <c r="R44" s="395">
+      <c r="R44" s="398">
         <f t="shared" ref="R44" si="41">IF(Q44&gt;=0,Q44,NA())</f>
         <v>42552.479999999967</v>
       </c>
-      <c r="S44" s="395" t="e">
+      <c r="S44" s="398" t="e">
         <f t="shared" ref="S44" si="42">IF(Q44&lt;0,Q44,NA())</f>
         <v>#N/A</v>
       </c>
@@ -70022,9 +70022,9 @@
         <v>#N/A</v>
       </c>
       <c r="P45" s="325"/>
-      <c r="Q45" s="393"/>
-      <c r="R45" s="396"/>
-      <c r="S45" s="396"/>
+      <c r="Q45" s="396"/>
+      <c r="R45" s="399"/>
+      <c r="S45" s="399"/>
     </row>
     <row r="46" spans="3:19" ht="15" customHeight="1">
       <c r="C46" s="111"/>
@@ -70063,9 +70063,9 @@
         <v>-32580.719999999943</v>
       </c>
       <c r="P46" s="326"/>
-      <c r="Q46" s="394"/>
-      <c r="R46" s="397"/>
-      <c r="S46" s="397"/>
+      <c r="Q46" s="397"/>
+      <c r="R46" s="400"/>
+      <c r="S46" s="400"/>
     </row>
     <row r="47" spans="3:19" ht="15" customHeight="1">
       <c r="D47" s="107">
@@ -70105,15 +70105,15 @@
       <c r="P47" s="325" t="s">
         <v>619</v>
       </c>
-      <c r="Q47" s="392">
+      <c r="Q47" s="395">
         <f t="shared" ref="Q47" si="43">SUM(H46:H48)</f>
         <v>84772.810000000172</v>
       </c>
-      <c r="R47" s="395">
+      <c r="R47" s="398">
         <f t="shared" ref="R47" si="44">IF(Q47&gt;=0,Q47,NA())</f>
         <v>84772.810000000172</v>
       </c>
-      <c r="S47" s="395" t="e">
+      <c r="S47" s="398" t="e">
         <f t="shared" ref="S47" si="45">IF(Q47&lt;0,Q47,NA())</f>
         <v>#N/A</v>
       </c>
@@ -70158,9 +70158,9 @@
         <v>#N/A</v>
       </c>
       <c r="P48" s="325"/>
-      <c r="Q48" s="393"/>
-      <c r="R48" s="396"/>
-      <c r="S48" s="396"/>
+      <c r="Q48" s="396"/>
+      <c r="R48" s="399"/>
+      <c r="S48" s="399"/>
     </row>
     <row r="49" spans="3:19" ht="15" customHeight="1">
       <c r="C49" s="111"/>
@@ -70199,9 +70199,9 @@
         <v>#N/A</v>
       </c>
       <c r="P49" s="326"/>
-      <c r="Q49" s="394"/>
-      <c r="R49" s="397"/>
-      <c r="S49" s="397"/>
+      <c r="Q49" s="397"/>
+      <c r="R49" s="400"/>
+      <c r="S49" s="400"/>
     </row>
     <row r="50" spans="3:19" ht="15" customHeight="1">
       <c r="D50" s="107">
@@ -70241,15 +70241,15 @@
       <c r="P50" s="325" t="s">
         <v>620</v>
       </c>
-      <c r="Q50" s="392">
+      <c r="Q50" s="395">
         <f t="shared" ref="Q50" si="46">SUM(H49:H51)</f>
         <v>154229.81000000003</v>
       </c>
-      <c r="R50" s="395">
+      <c r="R50" s="398">
         <f t="shared" ref="R50" si="47">IF(Q50&gt;=0,Q50,NA())</f>
         <v>154229.81000000003</v>
       </c>
-      <c r="S50" s="395" t="e">
+      <c r="S50" s="398" t="e">
         <f t="shared" ref="S50" si="48">IF(Q50&lt;0,Q50,NA())</f>
         <v>#N/A</v>
       </c>
@@ -70294,9 +70294,9 @@
         <v>#N/A</v>
       </c>
       <c r="P51" s="325"/>
-      <c r="Q51" s="393"/>
-      <c r="R51" s="396"/>
-      <c r="S51" s="396"/>
+      <c r="Q51" s="396"/>
+      <c r="R51" s="399"/>
+      <c r="S51" s="399"/>
     </row>
     <row r="52" spans="3:19" ht="15" customHeight="1">
       <c r="C52" s="111"/>
@@ -70305,19 +70305,19 @@
       </c>
       <c r="E52" s="5">
         <f>Consolidated!E7</f>
-        <v>282443.93000000005</v>
+        <v>282443.93</v>
       </c>
       <c r="F52" s="5">
         <f>Consolidated!E46</f>
-        <v>-4352.479999999945</v>
+        <v>-4352.4799999999959</v>
       </c>
       <c r="G52" s="5">
         <f>Consolidated!E49</f>
-        <v>-5606.7099999999427</v>
+        <v>-5606.7099999999937</v>
       </c>
       <c r="H52" s="5">
         <f>Consolidated!E53</f>
-        <v>-15843.279999999942</v>
+        <v>-15843.279999999993</v>
       </c>
       <c r="I52" s="3">
         <f t="shared" si="36"/>
@@ -70337,12 +70337,12 @@
       </c>
       <c r="N52" s="5">
         <f t="shared" si="5"/>
-        <v>-15843.279999999942</v>
+        <v>-15843.279999999993</v>
       </c>
       <c r="P52" s="326"/>
-      <c r="Q52" s="394"/>
-      <c r="R52" s="397"/>
-      <c r="S52" s="397"/>
+      <c r="Q52" s="397"/>
+      <c r="R52" s="400"/>
+      <c r="S52" s="400"/>
     </row>
     <row r="53" spans="3:19" ht="15" customHeight="1">
       <c r="D53" s="107">
@@ -70387,15 +70387,15 @@
       <c r="P53" s="325" t="s">
         <v>621</v>
       </c>
-      <c r="Q53" s="392">
+      <c r="Q53" s="395">
         <f t="shared" ref="Q53" si="49">SUM(H52:H54)</f>
-        <v>78790.990000000107</v>
-      </c>
-      <c r="R53" s="395">
+        <v>78790.990000000049</v>
+      </c>
+      <c r="R53" s="398">
         <f t="shared" ref="R53" si="50">IF(Q53&gt;=0,Q53,NA())</f>
-        <v>78790.990000000107</v>
-      </c>
-      <c r="S53" s="395" t="e">
+        <v>78790.990000000049</v>
+      </c>
+      <c r="S53" s="398" t="e">
         <f t="shared" ref="S53" si="51">IF(Q53&lt;0,Q53,NA())</f>
         <v>#N/A</v>
       </c>
@@ -70445,9 +70445,9 @@
         <v>#N/A</v>
       </c>
       <c r="P54" s="325"/>
-      <c r="Q54" s="393"/>
-      <c r="R54" s="396"/>
-      <c r="S54" s="396"/>
+      <c r="Q54" s="396"/>
+      <c r="R54" s="399"/>
+      <c r="S54" s="399"/>
     </row>
     <row r="55" spans="3:19" ht="15" customHeight="1">
       <c r="D55" s="107">
@@ -70459,15 +70459,15 @@
       </c>
       <c r="F55" s="5">
         <f>Consolidated!H46</f>
-        <v>-15400.709999999932</v>
+        <v>-15400.709999999939</v>
       </c>
       <c r="G55" s="5">
         <f>Consolidated!H49</f>
-        <v>-16149.21999999993</v>
+        <v>-16149.219999999937</v>
       </c>
       <c r="H55" s="5">
         <f>Consolidated!H53</f>
-        <v>-26786.079999999929</v>
+        <v>-26786.079999999936</v>
       </c>
       <c r="I55" s="3">
         <f t="shared" si="36"/>
@@ -70487,12 +70487,12 @@
       </c>
       <c r="N55" s="5">
         <f t="shared" si="5"/>
-        <v>-26786.079999999929</v>
+        <v>-26786.079999999936</v>
       </c>
       <c r="P55" s="326"/>
-      <c r="Q55" s="394"/>
-      <c r="R55" s="397"/>
-      <c r="S55" s="397"/>
+      <c r="Q55" s="397"/>
+      <c r="R55" s="400"/>
+      <c r="S55" s="400"/>
     </row>
     <row r="56" spans="3:19" ht="15" customHeight="1">
       <c r="D56" s="107">
@@ -70500,23 +70500,23 @@
       </c>
       <c r="E56" s="5">
         <f>Consolidated!I7</f>
-        <v>367273.20000000007</v>
+        <v>277334.58</v>
       </c>
       <c r="F56" s="5">
         <f>Consolidated!I46</f>
-        <v>136849.73000000004</v>
+        <v>46983.06</v>
       </c>
       <c r="G56" s="5">
         <f>Consolidated!I49</f>
-        <v>133862.00000000003</v>
+        <v>47259.33</v>
       </c>
       <c r="H56" s="5">
         <f>Consolidated!I53</f>
-        <v>124591.97000000003</v>
+        <v>37989.300000000003</v>
       </c>
       <c r="I56" s="3">
         <f t="shared" si="36"/>
-        <v>528668.42000000039</v>
+        <v>442065.75000000041</v>
       </c>
       <c r="J56" s="3">
         <f>Caixa!J6</f>
@@ -70528,7 +70528,7 @@
       </c>
       <c r="M56" s="5">
         <f t="shared" si="4"/>
-        <v>124591.97000000003</v>
+        <v>37989.300000000003</v>
       </c>
       <c r="N56" s="5" t="e">
         <f t="shared" si="5"/>
@@ -70537,15 +70537,15 @@
       <c r="P56" s="325" t="s">
         <v>622</v>
       </c>
-      <c r="Q56" s="392">
+      <c r="Q56" s="395">
         <f t="shared" ref="Q56" si="52">SUM(H55:H57)</f>
-        <v>81808.630000000121</v>
-      </c>
-      <c r="R56" s="395">
+        <v>82185.830000000104</v>
+      </c>
+      <c r="R56" s="398">
         <f t="shared" ref="R56" si="53">IF(Q56&gt;=0,Q56,NA())</f>
-        <v>81808.630000000121</v>
-      </c>
-      <c r="S56" s="395" t="e">
+        <v>82185.830000000104</v>
+      </c>
+      <c r="S56" s="398" t="e">
         <f t="shared" ref="S56" si="54">IF(Q56&lt;0,Q56,NA())</f>
         <v>#N/A</v>
       </c>
@@ -70553,30 +70553,30 @@
     <row r="57" spans="3:19" ht="15" customHeight="1">
       <c r="C57" s="111">
         <f>E57/E54-1</f>
-        <v>-0.22428624869797575</v>
+        <v>0.10540518595648352</v>
       </c>
       <c r="D57" s="108">
         <v>46174</v>
       </c>
       <c r="E57" s="109">
         <f>Consolidated!J7</f>
-        <v>211611.88000000003</v>
+        <v>301550.50000000006</v>
       </c>
       <c r="F57" s="109">
         <f>Consolidated!J46</f>
-        <v>-5266.3199999999888</v>
+        <v>83619.250000000044</v>
       </c>
       <c r="G57" s="109">
         <f>Consolidated!J49</f>
-        <v>-6871.1399999999867</v>
+        <v>80108.73000000004</v>
       </c>
       <c r="H57" s="109">
         <f>Consolidated!J53</f>
-        <v>-15997.259999999986</v>
+        <v>70982.610000000044</v>
       </c>
       <c r="I57" s="110">
         <f t="shared" si="36"/>
-        <v>512671.16000000038</v>
+        <v>513048.36000000045</v>
       </c>
       <c r="J57" s="110">
         <f>Caixa!K6</f>
@@ -70586,18 +70586,18 @@
         <f t="shared" si="0"/>
         <v>46174</v>
       </c>
-      <c r="M57" s="109" t="e">
+      <c r="M57" s="109">
         <f t="shared" si="4"/>
+        <v>70982.610000000044</v>
+      </c>
+      <c r="N57" s="109" t="e">
+        <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
-      <c r="N57" s="109">
-        <f t="shared" si="5"/>
-        <v>-15997.259999999986</v>
-      </c>
       <c r="P57" s="325"/>
-      <c r="Q57" s="393"/>
-      <c r="R57" s="396"/>
-      <c r="S57" s="396"/>
+      <c r="Q57" s="396"/>
+      <c r="R57" s="399"/>
+      <c r="S57" s="399"/>
     </row>
     <row r="58" spans="3:19" ht="15" customHeight="1">
       <c r="D58" s="107">
@@ -70621,7 +70621,7 @@
       </c>
       <c r="I58" s="3">
         <f t="shared" si="36"/>
-        <v>512671.16000000038</v>
+        <v>513048.36000000045</v>
       </c>
       <c r="J58" s="3"/>
       <c r="L58" s="107">
@@ -70637,9 +70637,9 @@
         <v>#N/A</v>
       </c>
       <c r="P58" s="326"/>
-      <c r="Q58" s="394"/>
-      <c r="R58" s="397"/>
-      <c r="S58" s="397"/>
+      <c r="Q58" s="397"/>
+      <c r="R58" s="400"/>
+      <c r="S58" s="400"/>
     </row>
     <row r="59" spans="3:19" ht="15" customHeight="1">
       <c r="D59" s="107">
@@ -70663,7 +70663,7 @@
       </c>
       <c r="I59" s="3">
         <f t="shared" si="36"/>
-        <v>512671.16000000038</v>
+        <v>513048.36000000045</v>
       </c>
       <c r="J59" s="3"/>
       <c r="L59" s="107">
@@ -70681,15 +70681,15 @@
       <c r="P59" s="325" t="s">
         <v>623</v>
       </c>
-      <c r="Q59" s="392">
+      <c r="Q59" s="395">
         <f t="shared" ref="Q59" si="55">SUM(H58:H60)</f>
         <v>0</v>
       </c>
-      <c r="R59" s="395">
+      <c r="R59" s="398">
         <f t="shared" ref="R59" si="56">IF(Q59&gt;=0,Q59,NA())</f>
         <v>0</v>
       </c>
-      <c r="S59" s="395" t="e">
+      <c r="S59" s="398" t="e">
         <f t="shared" ref="S59" si="57">IF(Q59&lt;0,Q59,NA())</f>
         <v>#N/A</v>
       </c>
@@ -70720,7 +70720,7 @@
       </c>
       <c r="I60" s="110">
         <f t="shared" si="36"/>
-        <v>512671.16000000038</v>
+        <v>513048.36000000045</v>
       </c>
       <c r="J60" s="110"/>
       <c r="L60" s="108">
@@ -70736,9 +70736,9 @@
         <v>#N/A</v>
       </c>
       <c r="P60" s="325"/>
-      <c r="Q60" s="393"/>
-      <c r="R60" s="396"/>
-      <c r="S60" s="396"/>
+      <c r="Q60" s="396"/>
+      <c r="R60" s="399"/>
+      <c r="S60" s="399"/>
     </row>
     <row r="61" spans="3:19" ht="15" customHeight="1">
       <c r="D61" s="107">
@@ -70762,7 +70762,7 @@
       </c>
       <c r="I61" s="3">
         <f t="shared" si="36"/>
-        <v>512671.16000000038</v>
+        <v>513048.36000000045</v>
       </c>
       <c r="J61" s="3"/>
       <c r="L61" s="107">
@@ -70778,9 +70778,9 @@
         <v>#N/A</v>
       </c>
       <c r="P61" s="326"/>
-      <c r="Q61" s="394"/>
-      <c r="R61" s="397"/>
-      <c r="S61" s="397"/>
+      <c r="Q61" s="397"/>
+      <c r="R61" s="400"/>
+      <c r="S61" s="400"/>
     </row>
     <row r="62" spans="3:19" ht="15" customHeight="1">
       <c r="D62" s="107">
@@ -70804,7 +70804,7 @@
       </c>
       <c r="I62" s="3">
         <f t="shared" si="36"/>
-        <v>512671.16000000038</v>
+        <v>513048.36000000045</v>
       </c>
       <c r="J62" s="3"/>
       <c r="L62" s="107">
@@ -70822,15 +70822,15 @@
       <c r="P62" s="325" t="s">
         <v>624</v>
       </c>
-      <c r="Q62" s="392">
+      <c r="Q62" s="395">
         <f t="shared" ref="Q62" si="58">SUM(H61:H63)</f>
         <v>0</v>
       </c>
-      <c r="R62" s="395">
+      <c r="R62" s="398">
         <f t="shared" ref="R62" si="59">IF(Q62&gt;=0,Q62,NA())</f>
         <v>0</v>
       </c>
-      <c r="S62" s="395" t="e">
+      <c r="S62" s="398" t="e">
         <f t="shared" ref="S62" si="60">IF(Q62&lt;0,Q62,NA())</f>
         <v>#N/A</v>
       </c>
@@ -70861,7 +70861,7 @@
       </c>
       <c r="I63" s="110">
         <f t="shared" si="36"/>
-        <v>512671.16000000038</v>
+        <v>513048.36000000045</v>
       </c>
       <c r="J63" s="110"/>
       <c r="L63" s="108">
@@ -70877,23 +70877,66 @@
         <v>#N/A</v>
       </c>
       <c r="P63" s="325"/>
-      <c r="Q63" s="393"/>
-      <c r="R63" s="396"/>
-      <c r="S63" s="396"/>
+      <c r="Q63" s="396"/>
+      <c r="R63" s="399"/>
+      <c r="S63" s="399"/>
     </row>
     <row r="64" spans="3:19">
       <c r="P64" s="326"/>
-      <c r="Q64" s="394"/>
-      <c r="R64" s="397"/>
-      <c r="S64" s="397"/>
+      <c r="Q64" s="397"/>
+      <c r="R64" s="400"/>
+      <c r="S64" s="400"/>
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="P5:P7"/>
-    <mergeCell ref="Q5:Q7"/>
-    <mergeCell ref="R5:R7"/>
-    <mergeCell ref="S5:S7"/>
-    <mergeCell ref="P8:P10"/>
+    <mergeCell ref="Q59:Q61"/>
+    <mergeCell ref="R59:R61"/>
+    <mergeCell ref="S59:S61"/>
+    <mergeCell ref="Q62:Q64"/>
+    <mergeCell ref="R62:R64"/>
+    <mergeCell ref="S62:S64"/>
+    <mergeCell ref="Q53:Q55"/>
+    <mergeCell ref="R53:R55"/>
+    <mergeCell ref="S53:S55"/>
+    <mergeCell ref="Q56:Q58"/>
+    <mergeCell ref="R56:R58"/>
+    <mergeCell ref="S56:S58"/>
+    <mergeCell ref="Q47:Q49"/>
+    <mergeCell ref="R47:R49"/>
+    <mergeCell ref="S47:S49"/>
+    <mergeCell ref="Q50:Q52"/>
+    <mergeCell ref="R50:R52"/>
+    <mergeCell ref="S50:S52"/>
+    <mergeCell ref="Q41:Q43"/>
+    <mergeCell ref="R41:R43"/>
+    <mergeCell ref="S41:S43"/>
+    <mergeCell ref="Q44:Q46"/>
+    <mergeCell ref="R44:R46"/>
+    <mergeCell ref="S44:S46"/>
+    <mergeCell ref="Q35:Q37"/>
+    <mergeCell ref="R35:R37"/>
+    <mergeCell ref="S35:S37"/>
+    <mergeCell ref="Q38:Q40"/>
+    <mergeCell ref="R38:R40"/>
+    <mergeCell ref="S38:S40"/>
+    <mergeCell ref="Q29:Q31"/>
+    <mergeCell ref="R29:R31"/>
+    <mergeCell ref="S29:S31"/>
+    <mergeCell ref="Q32:Q34"/>
+    <mergeCell ref="R32:R34"/>
+    <mergeCell ref="S32:S34"/>
+    <mergeCell ref="Q23:Q25"/>
+    <mergeCell ref="R23:R25"/>
+    <mergeCell ref="S23:S25"/>
+    <mergeCell ref="Q26:Q28"/>
+    <mergeCell ref="R26:R28"/>
+    <mergeCell ref="S26:S28"/>
+    <mergeCell ref="Q17:Q19"/>
+    <mergeCell ref="R17:R19"/>
+    <mergeCell ref="S17:S19"/>
+    <mergeCell ref="Q20:Q22"/>
+    <mergeCell ref="R20:R22"/>
+    <mergeCell ref="S20:S22"/>
     <mergeCell ref="P14:P16"/>
     <mergeCell ref="Q8:Q10"/>
     <mergeCell ref="R8:R10"/>
@@ -70905,54 +70948,11 @@
     <mergeCell ref="R14:R16"/>
     <mergeCell ref="S14:S16"/>
     <mergeCell ref="P11:P13"/>
-    <mergeCell ref="Q17:Q19"/>
-    <mergeCell ref="R17:R19"/>
-    <mergeCell ref="S17:S19"/>
-    <mergeCell ref="Q20:Q22"/>
-    <mergeCell ref="R20:R22"/>
-    <mergeCell ref="S20:S22"/>
-    <mergeCell ref="Q23:Q25"/>
-    <mergeCell ref="R23:R25"/>
-    <mergeCell ref="S23:S25"/>
-    <mergeCell ref="Q26:Q28"/>
-    <mergeCell ref="R26:R28"/>
-    <mergeCell ref="S26:S28"/>
-    <mergeCell ref="Q29:Q31"/>
-    <mergeCell ref="R29:R31"/>
-    <mergeCell ref="S29:S31"/>
-    <mergeCell ref="Q32:Q34"/>
-    <mergeCell ref="R32:R34"/>
-    <mergeCell ref="S32:S34"/>
-    <mergeCell ref="Q35:Q37"/>
-    <mergeCell ref="R35:R37"/>
-    <mergeCell ref="S35:S37"/>
-    <mergeCell ref="Q38:Q40"/>
-    <mergeCell ref="R38:R40"/>
-    <mergeCell ref="S38:S40"/>
-    <mergeCell ref="Q41:Q43"/>
-    <mergeCell ref="R41:R43"/>
-    <mergeCell ref="S41:S43"/>
-    <mergeCell ref="Q44:Q46"/>
-    <mergeCell ref="R44:R46"/>
-    <mergeCell ref="S44:S46"/>
-    <mergeCell ref="Q47:Q49"/>
-    <mergeCell ref="R47:R49"/>
-    <mergeCell ref="S47:S49"/>
-    <mergeCell ref="Q50:Q52"/>
-    <mergeCell ref="R50:R52"/>
-    <mergeCell ref="S50:S52"/>
-    <mergeCell ref="Q53:Q55"/>
-    <mergeCell ref="R53:R55"/>
-    <mergeCell ref="S53:S55"/>
-    <mergeCell ref="Q56:Q58"/>
-    <mergeCell ref="R56:R58"/>
-    <mergeCell ref="S56:S58"/>
-    <mergeCell ref="Q59:Q61"/>
-    <mergeCell ref="R59:R61"/>
-    <mergeCell ref="S59:S61"/>
-    <mergeCell ref="Q62:Q64"/>
-    <mergeCell ref="R62:R64"/>
-    <mergeCell ref="S62:S64"/>
+    <mergeCell ref="P5:P7"/>
+    <mergeCell ref="Q5:Q7"/>
+    <mergeCell ref="R5:R7"/>
+    <mergeCell ref="S5:S7"/>
+    <mergeCell ref="P8:P10"/>
   </mergeCells>
   <pageMargins left="0.51180555555555596" right="0.51180555555555596" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
